--- a/Horario desenvolvido/Proposta_2_Calendario_Provas_2026_2SEM.xlsx
+++ b/Horario desenvolvido/Proposta_2_Calendario_Provas_2026_2SEM.xlsx
@@ -5369,17 +5369,17 @@
       </c>
       <c r="E9" s="183" t="inlineStr">
         <is>
-          <t>Bio - Ale
-6º e 7º tempos</t>
-        </is>
-      </c>
-      <c r="F9" s="183" t="n"/>
-      <c r="G9" s="183" t="inlineStr">
-        <is>
-          <t>Soc - Kle
-6º tempo</t>
-        </is>
-      </c>
+          <t>Qui - CAl/Fab
+1º e 2º tempos</t>
+        </is>
+      </c>
+      <c r="F9" s="183" t="inlineStr">
+        <is>
+          <t>GL - CBu-EFr-Eth
+5º e 6º tempos</t>
+        </is>
+      </c>
+      <c r="G9" s="183" t="n"/>
       <c r="H9" s="183" t="n"/>
       <c r="I9" s="183" t="inlineStr">
         <is>
@@ -5467,23 +5467,18 @@
       <c r="E12" s="11" t="inlineStr">
         <is>
           <t>Ing - Isb
-5º e 6º tempos</t>
-        </is>
-      </c>
-      <c r="F12" s="11" t="inlineStr">
-        <is>
-          <t>Hist - Wag
-11º e 12º tempos</t>
-        </is>
-      </c>
-      <c r="G12" s="11" t="inlineStr">
+4º e 5º tempos</t>
+        </is>
+      </c>
+      <c r="F12" s="11" t="n"/>
+      <c r="G12" s="11" t="n"/>
+      <c r="H12" s="11" t="n"/>
+      <c r="I12" s="11" t="inlineStr">
         <is>
           <t>Geo - Mar
-11º e 12º tempos</t>
-        </is>
-      </c>
-      <c r="H12" s="11" t="n"/>
-      <c r="I12" s="11" t="n"/>
+2º e 3º tempos</t>
+        </is>
+      </c>
       <c r="J12" s="183" t="n"/>
       <c r="L12" s="15" t="n"/>
       <c r="M12" s="15" t="n"/>
@@ -5542,22 +5537,17 @@
       </c>
       <c r="E15" s="11" t="inlineStr">
         <is>
-          <t>Mat - Bre/JJ
+          <t>DaF - CBu-EFr-Eth
 3º e 4º tempos</t>
         </is>
       </c>
       <c r="F15" s="11" t="inlineStr">
         <is>
-          <t>GL - CBu-EFr-Eth
-6º e 7º tempos</t>
-        </is>
-      </c>
-      <c r="G15" s="11" t="inlineStr">
-        <is>
-          <t>Qui - CAl/Fab
-1º e 2º tempos</t>
-        </is>
-      </c>
+          <t>Bio - Ale
+2º e 3º tempos</t>
+        </is>
+      </c>
+      <c r="G15" s="11" t="n"/>
       <c r="H15" s="11" t="n"/>
       <c r="I15" s="11" t="n"/>
       <c r="J15" s="183" t="n"/>
@@ -5627,11 +5617,16 @@
       </c>
       <c r="G18" s="11" t="inlineStr">
         <is>
-          <t>DaF - CBu-EFr-Eth
-5º e 6º tempos</t>
-        </is>
-      </c>
-      <c r="H18" s="11" t="n"/>
+          <t>Hist - Wag
+1º e 2º tempos</t>
+        </is>
+      </c>
+      <c r="H18" s="11" t="inlineStr">
+        <is>
+          <t>Mat - Bre/JJ
+3º e 4º tempos</t>
+        </is>
+      </c>
       <c r="I18" s="350" t="n"/>
       <c r="J18" s="262" t="inlineStr">
         <is>
@@ -5698,12 +5693,7 @@
         <f>B21+4</f>
         <v/>
       </c>
-      <c r="E21" s="11" t="inlineStr">
-        <is>
-          <t>DaF - CBu-EFr-Eth
-4º e 5º tempos</t>
-        </is>
-      </c>
+      <c r="E21" s="11" t="n"/>
       <c r="F21" s="62" t="n"/>
       <c r="G21" s="11" t="inlineStr">
         <is>
@@ -5780,14 +5770,19 @@
         <f>B24+4</f>
         <v/>
       </c>
-      <c r="E24" s="283" t="n"/>
-      <c r="F24" s="283" t="inlineStr">
-        <is>
-          <t>Fis - Cadu
+      <c r="E24" s="283" t="inlineStr">
+        <is>
+          <t>Qui - CAl/Fab
 1º e 2º tempos</t>
         </is>
       </c>
-      <c r="G24" s="79" t="n"/>
+      <c r="F24" s="283" t="n"/>
+      <c r="G24" s="362" t="inlineStr">
+        <is>
+          <t>Fil - LAn
+4º tempo</t>
+        </is>
+      </c>
       <c r="H24" s="283" t="n"/>
       <c r="I24" s="78" t="n"/>
       <c r="J24" s="265" t="n"/>
@@ -5857,17 +5852,17 @@
       </c>
       <c r="E27" s="78" t="inlineStr">
         <is>
-          <t>Qui - CAl/Fab
+          <t>Geo - Mar
+1º e 2º tempos</t>
+        </is>
+      </c>
+      <c r="F27" s="283" t="inlineStr">
+        <is>
+          <t>Bio - Ale
 2º e 3º tempos</t>
         </is>
       </c>
-      <c r="F27" s="283" t="n"/>
-      <c r="G27" s="283" t="inlineStr">
-        <is>
-          <t>Fil - LAn
-4º tempo</t>
-        </is>
-      </c>
+      <c r="G27" s="283" t="n"/>
       <c r="H27" s="283" t="n"/>
       <c r="I27" s="283" t="n"/>
       <c r="J27" s="265" t="n"/>
@@ -5935,21 +5930,16 @@
         <f>B30+4</f>
         <v/>
       </c>
-      <c r="E30" s="283" t="n"/>
-      <c r="F30" s="283" t="inlineStr">
-        <is>
-          <t>Hist - Wag
-11º e 12º tempos</t>
-        </is>
-      </c>
+      <c r="E30" s="283" t="inlineStr">
+        <is>
+          <t>Ing - Isb
+4º e 5º tempos</t>
+        </is>
+      </c>
+      <c r="F30" s="283" t="n"/>
       <c r="G30" s="283" t="n"/>
       <c r="H30" s="283" t="n"/>
-      <c r="I30" s="283" t="inlineStr">
-        <is>
-          <t>LP/LIT/RED - AMu/Deb
-2º ao 4º tempos</t>
-        </is>
-      </c>
+      <c r="I30" s="283" t="n"/>
       <c r="J30" s="183" t="inlineStr">
         <is>
           <t>unterrichtsfrei sem aula</t>
@@ -6115,14 +6105,14 @@
         <f>B36+4</f>
         <v/>
       </c>
-      <c r="E36" s="283" t="inlineStr">
-        <is>
-          <t>Geo - Mar
+      <c r="E36" s="283" t="n"/>
+      <c r="F36" s="283" t="n"/>
+      <c r="G36" s="283" t="inlineStr">
+        <is>
+          <t>Hist - Wag
 1º e 2º tempos</t>
         </is>
       </c>
-      <c r="F36" s="283" t="n"/>
-      <c r="G36" s="283" t="n"/>
       <c r="H36" s="283" t="n"/>
       <c r="I36" s="283" t="n"/>
       <c r="J36" s="265" t="n"/>
@@ -6192,16 +6182,16 @@
       <c r="E39" s="283" t="inlineStr">
         <is>
           <t>Mat - Bre/JJ
-3º e 4º tempos</t>
-        </is>
-      </c>
-      <c r="F39" s="283" t="inlineStr">
-        <is>
-          <t>GL - CBu-EFr-Eth
-6º e 7º tempos</t>
-        </is>
-      </c>
-      <c r="G39" s="283" t="n"/>
+2º e 3º tempos</t>
+        </is>
+      </c>
+      <c r="F39" s="283" t="n"/>
+      <c r="G39" s="283" t="inlineStr">
+        <is>
+          <t>Soc - Kle
+6º tempo</t>
+        </is>
+      </c>
       <c r="H39" s="283" t="n"/>
       <c r="I39" s="283" t="n"/>
       <c r="J39" s="265" t="n"/>
@@ -6249,15 +6239,20 @@
         <v/>
       </c>
       <c r="E42" s="283" t="n"/>
-      <c r="F42" s="283" t="n"/>
+      <c r="F42" s="283" t="inlineStr">
+        <is>
+          <t>GL - CBu-EFr-Eth
+5º e 6º tempos</t>
+        </is>
+      </c>
       <c r="G42" s="283" t="n"/>
-      <c r="H42" s="283" t="inlineStr">
-        <is>
-          <t>Ing - Isb
-11º e 12º tempos</t>
-        </is>
-      </c>
-      <c r="I42" s="283" t="n"/>
+      <c r="H42" s="283" t="n"/>
+      <c r="I42" s="283" t="inlineStr">
+        <is>
+          <t>LP/LIT/RED - AMu/Deb
+2º ao 4º tempos</t>
+        </is>
+      </c>
       <c r="J42" s="265" t="n"/>
       <c r="L42" s="259" t="inlineStr">
         <is>
@@ -6312,11 +6307,16 @@
       </c>
       <c r="E45" s="283" t="inlineStr">
         <is>
-          <t>Bio - Ale
-6º e 7º tempos</t>
-        </is>
-      </c>
-      <c r="F45" s="283" t="n"/>
+          <t>DaF - CBu-EFr-Eth
+3º e 4º tempos</t>
+        </is>
+      </c>
+      <c r="F45" s="283" t="inlineStr">
+        <is>
+          <t>Fis - Cadu
+1º e 2º tempos</t>
+        </is>
+      </c>
       <c r="G45" s="283" t="n"/>
       <c r="H45" s="283" t="n"/>
       <c r="I45" s="357" t="inlineStr">
@@ -8590,13 +8590,13 @@
       <c r="E9" s="183" t="inlineStr">
         <is>
           <t>GL - Caro-EFr-Eth
-6º e 7º tempos</t>
+5º e 6º tempos</t>
         </is>
       </c>
       <c r="F9" s="183" t="inlineStr">
         <is>
-          <t>Port - Jana
-1º e 2º tempos</t>
+          <t>Mat - BrSa
+2º e 3º tempos</t>
         </is>
       </c>
       <c r="G9" s="183" t="n"/>
@@ -8682,16 +8682,21 @@
       <c r="E12" s="11" t="inlineStr">
         <is>
           <t>Geo - Mar
-2º e 3º tempos</t>
+1º e 2º tempos</t>
         </is>
       </c>
       <c r="F12" s="11" t="inlineStr">
         <is>
+          <t>Hist - JuLa
+3º e 4º tempos</t>
+        </is>
+      </c>
+      <c r="G12" s="11" t="inlineStr">
+        <is>
           <t>DaF - Caro-SGa-EFr
-2º e 3º tempos</t>
-        </is>
-      </c>
-      <c r="G12" s="11" t="n"/>
+1º e 2º tempos</t>
+        </is>
+      </c>
       <c r="H12" s="11" t="n"/>
       <c r="I12" s="11" t="n"/>
       <c r="J12" s="183" t="n"/>
@@ -8752,23 +8757,18 @@
       </c>
       <c r="E15" s="11" t="inlineStr">
         <is>
+          <t>Ing - APa-PaH-Velo
+2º e 3º tempos</t>
+        </is>
+      </c>
+      <c r="F15" s="11" t="n"/>
+      <c r="G15" s="11" t="n"/>
+      <c r="H15" s="11" t="inlineStr">
+        <is>
           <t>Redação - Raf
-6º e 7º tempos</t>
-        </is>
-      </c>
-      <c r="F15" s="11" t="inlineStr">
-        <is>
-          <t>Hist - JuLa
-4º e 5º tempos</t>
-        </is>
-      </c>
-      <c r="G15" s="11" t="inlineStr">
-        <is>
-          <t>Mat - BrSa
-4º e 5º tempos</t>
-        </is>
-      </c>
-      <c r="H15" s="11" t="n"/>
+5º e 6º tempos</t>
+        </is>
+      </c>
       <c r="I15" s="11" t="n"/>
       <c r="J15" s="183" t="n"/>
       <c r="L15" s="17" t="n"/>
@@ -8831,8 +8831,8 @@
       </c>
       <c r="F18" s="11" t="inlineStr">
         <is>
-          <t>Ing - APa-PaH-Velo
-5º e 6º tempos</t>
+          <t>Port - Jana
+1º e 2º tempos</t>
         </is>
       </c>
       <c r="G18" s="11" t="n"/>
@@ -8903,20 +8903,20 @@
         <f>B21+4</f>
         <v/>
       </c>
-      <c r="E21" s="11" t="inlineStr">
-        <is>
-          <t>GL - Caro-EFr-Eth
-6º e 7º tempos</t>
-        </is>
-      </c>
+      <c r="E21" s="11" t="n"/>
       <c r="F21" s="62" t="inlineStr">
         <is>
-          <t>Hist - JuLa
-4º e 5º tempos</t>
+          <t>Mat - BrSa
+2º e 3º tempos</t>
         </is>
       </c>
       <c r="G21" s="11" t="n"/>
-      <c r="H21" s="11" t="n"/>
+      <c r="H21" s="11" t="inlineStr">
+        <is>
+          <t>Fis - VSi
+7º tempo</t>
+        </is>
+      </c>
       <c r="I21" s="11" t="n"/>
       <c r="J21" s="183" t="n"/>
       <c r="L21" s="80" t="inlineStr">
@@ -8982,8 +8982,8 @@
       </c>
       <c r="E24" s="283" t="inlineStr">
         <is>
-          <t>Redação - Raf
-6º e 7º tempos</t>
+          <t>GL - Caro-EFr-Eth
+5º e 6º tempos</t>
         </is>
       </c>
       <c r="F24" s="283" t="n"/>
@@ -9055,7 +9055,12 @@
         <f>B27+4</f>
         <v/>
       </c>
-      <c r="E27" s="78" t="n"/>
+      <c r="E27" s="78" t="inlineStr">
+        <is>
+          <t>Ing - APa-PaH-Velo
+2º e 3º tempos</t>
+        </is>
+      </c>
       <c r="F27" s="283" t="n"/>
       <c r="G27" s="283" t="n"/>
       <c r="H27" s="283" t="n"/>
@@ -9307,8 +9312,8 @@
       </c>
       <c r="E36" s="283" t="inlineStr">
         <is>
-          <t>Bio - Ale
-1º tempo</t>
+          <t>Geo - Mar
+1º e 2º tempos</t>
         </is>
       </c>
       <c r="F36" s="283" t="n"/>
@@ -9379,13 +9384,13 @@
         <f>B39+4</f>
         <v/>
       </c>
-      <c r="E39" s="283" t="inlineStr">
-        <is>
-          <t>Ing - APa-PaH-Velo
-3º e 4º tempos</t>
-        </is>
-      </c>
-      <c r="F39" s="283" t="n"/>
+      <c r="E39" s="283" t="n"/>
+      <c r="F39" s="283" t="inlineStr">
+        <is>
+          <t>Port - Jana
+1º e 2º tempos</t>
+        </is>
+      </c>
       <c r="G39" s="283" t="n"/>
       <c r="H39" s="283" t="n"/>
       <c r="I39" s="283" t="n"/>
@@ -9434,17 +9439,12 @@
         <v/>
       </c>
       <c r="E42" s="283" t="n"/>
-      <c r="F42" s="283" t="inlineStr">
-        <is>
-          <t>DaF - Caro-SGa-EFr
-2º e 3º tempos</t>
-        </is>
-      </c>
+      <c r="F42" s="283" t="n"/>
       <c r="G42" s="283" t="n"/>
       <c r="H42" s="283" t="inlineStr">
         <is>
-          <t>Fis - VSi
-7º tempo</t>
+          <t>Redação - Raf
+5º e 6º tempos</t>
         </is>
       </c>
       <c r="I42" s="283" t="n"/>
@@ -9503,8 +9503,8 @@
       <c r="E45" s="283" t="n"/>
       <c r="F45" s="283" t="inlineStr">
         <is>
-          <t>Port - Jana
-1º e 2º tempos</t>
+          <t>Hist - JuLa
+3º e 4º tempos</t>
         </is>
       </c>
       <c r="G45" s="283" t="n"/>
@@ -9559,14 +9559,14 @@
       </c>
       <c r="E48" s="283" t="inlineStr">
         <is>
-          <t>Geo - Mar
-2º e 3º tempos</t>
+          <t>Bio - Ale
+1º tempo</t>
         </is>
       </c>
       <c r="F48" s="360" t="inlineStr">
         <is>
-          <t>Mat - BrSa
-3º e 4º tempos</t>
+          <t>DaF - Caro-SGa-EFr
+1º e 2º tempos</t>
         </is>
       </c>
       <c r="G48" s="283" t="n"/>
@@ -10262,8 +10262,8 @@
       <c r="F9" s="183" t="n"/>
       <c r="G9" s="183" t="inlineStr">
         <is>
-          <t>Geo - Mar
-6º e 7º tempos</t>
+          <t>GL - Caro-EFr-Eth
+5º e 6º tempos</t>
         </is>
       </c>
       <c r="H9" s="183" t="n"/>
@@ -10353,8 +10353,8 @@
       </c>
       <c r="F12" s="11" t="inlineStr">
         <is>
-          <t>Mat - BrSa
-4º e 5º tempos</t>
+          <t>DaF - Caro-SGa-EFr
+1º e 2º tempos</t>
         </is>
       </c>
       <c r="G12" s="11" t="n"/>
@@ -10416,20 +10416,20 @@
         <f>B15+4</f>
         <v/>
       </c>
-      <c r="E15" s="11" t="inlineStr">
-        <is>
-          <t>GL - Caro-EFr-Eth
-6º e 7º tempos</t>
-        </is>
-      </c>
+      <c r="E15" s="11" t="n"/>
       <c r="F15" s="11" t="n"/>
       <c r="G15" s="11" t="inlineStr">
         <is>
           <t>Port - Jana
+3º e 4º tempos</t>
+        </is>
+      </c>
+      <c r="H15" s="11" t="inlineStr">
+        <is>
+          <t>Redação - Raf
 4º e 5º tempos</t>
         </is>
       </c>
-      <c r="H15" s="11" t="n"/>
       <c r="I15" s="11" t="n"/>
       <c r="J15" s="183" t="n"/>
       <c r="L15" s="17" t="n"/>
@@ -10492,18 +10492,18 @@
       </c>
       <c r="F18" s="11" t="inlineStr">
         <is>
-          <t>DaF - Caro-SGa-EFr
-2º e 3º tempos</t>
+          <t>Mat - BrSa
+4º e 5º tempos</t>
         </is>
       </c>
       <c r="G18" s="11" t="n"/>
-      <c r="H18" s="11" t="inlineStr">
-        <is>
-          <t>Redação - Raf
+      <c r="H18" s="11" t="n"/>
+      <c r="I18" s="350" t="inlineStr">
+        <is>
+          <t>Geo - Mar
 5º e 6º tempos</t>
         </is>
       </c>
-      <c r="I18" s="350" t="n"/>
       <c r="J18" s="262" t="inlineStr">
         <is>
           <t>2CH 9,10,11,12</t>
@@ -10641,19 +10641,14 @@
         <f>B24+4</f>
         <v/>
       </c>
-      <c r="E24" s="283" t="inlineStr">
-        <is>
-          <t>GL - Caro-EFr-Eth
-6º e 7º tempos</t>
-        </is>
-      </c>
-      <c r="F24" s="283" t="n"/>
-      <c r="G24" s="362" t="inlineStr">
-        <is>
-          <t>Port - Jana
-4º e 5º tempos</t>
-        </is>
-      </c>
+      <c r="E24" s="283" t="n"/>
+      <c r="F24" s="283" t="inlineStr">
+        <is>
+          <t>Bio - Ale
+1º tempo</t>
+        </is>
+      </c>
+      <c r="G24" s="79" t="n"/>
       <c r="H24" s="283" t="n"/>
       <c r="I24" s="78" t="n"/>
       <c r="J24" s="265" t="n"/>
@@ -10798,14 +10793,14 @@
       </c>
       <c r="E30" s="283" t="inlineStr">
         <is>
-          <t>Hist - JuLa
-6º e 7º tempos</t>
+          <t>GL - Caro-EFr-Eth
+5º e 6º tempos</t>
         </is>
       </c>
       <c r="F30" s="283" t="inlineStr">
         <is>
-          <t>DaF - Caro-SGa-EFr
-2º e 3º tempos</t>
+          <t>Mat - BrSa
+4º e 5º tempos</t>
         </is>
       </c>
       <c r="G30" s="283" t="n"/>
@@ -10976,14 +10971,14 @@
         <f>B36+4</f>
         <v/>
       </c>
-      <c r="E36" s="283" t="inlineStr">
-        <is>
-          <t>Redação - Raf
-1º e 2º tempos</t>
-        </is>
-      </c>
+      <c r="E36" s="283" t="n"/>
       <c r="F36" s="283" t="n"/>
-      <c r="G36" s="283" t="n"/>
+      <c r="G36" s="283" t="inlineStr">
+        <is>
+          <t>Port - Jana
+3º e 4º tempos</t>
+        </is>
+      </c>
       <c r="H36" s="283" t="n"/>
       <c r="I36" s="283" t="n"/>
       <c r="J36" s="265" t="n"/>
@@ -11050,14 +11045,14 @@
         <f>B39+4</f>
         <v/>
       </c>
-      <c r="E39" s="283" t="n"/>
+      <c r="E39" s="283" t="inlineStr">
+        <is>
+          <t>Hist - JuLa
+6º e 7º tempos</t>
+        </is>
+      </c>
       <c r="F39" s="283" t="n"/>
-      <c r="G39" s="283" t="inlineStr">
-        <is>
-          <t>Geo - Mar
-6º e 7º tempos</t>
-        </is>
-      </c>
+      <c r="G39" s="283" t="n"/>
       <c r="H39" s="283" t="n"/>
       <c r="I39" s="283" t="n"/>
       <c r="J39" s="265" t="n"/>
@@ -11107,13 +11102,18 @@
       <c r="E42" s="283" t="n"/>
       <c r="F42" s="283" t="inlineStr">
         <is>
-          <t>Ing - APa-PaH-Velo
-5º e 6º tempos</t>
+          <t>DaF - Caro-SGa-EFr
+1º e 2º tempos</t>
         </is>
       </c>
       <c r="G42" s="283" t="n"/>
       <c r="H42" s="283" t="n"/>
-      <c r="I42" s="283" t="n"/>
+      <c r="I42" s="283" t="inlineStr">
+        <is>
+          <t>Geo - Mar
+5º e 6º tempos</t>
+        </is>
+      </c>
       <c r="J42" s="265" t="n"/>
       <c r="L42" s="259" t="inlineStr">
         <is>
@@ -11168,18 +11168,18 @@
       </c>
       <c r="E45" s="283" t="inlineStr">
         <is>
-          <t>Fis - VSi
-2º tempo</t>
-        </is>
-      </c>
-      <c r="F45" s="283" t="inlineStr">
-        <is>
-          <t>Mat - BrSa
+          <t>Ing - APa-PaH-Velo
+3º e 4º tempos</t>
+        </is>
+      </c>
+      <c r="F45" s="283" t="n"/>
+      <c r="G45" s="283" t="n"/>
+      <c r="H45" s="283" t="inlineStr">
+        <is>
+          <t>Redação - Raf
 4º e 5º tempos</t>
         </is>
       </c>
-      <c r="G45" s="283" t="n"/>
-      <c r="H45" s="283" t="n"/>
       <c r="I45" s="357" t="n"/>
       <c r="J45" s="269" t="n"/>
       <c r="L45" s="331" t="n"/>
@@ -11228,13 +11228,13 @@
         <f>B48+4</f>
         <v/>
       </c>
-      <c r="E48" s="283" t="n"/>
-      <c r="F48" s="360" t="inlineStr">
-        <is>
-          <t>Bio - Ale
-1º tempo</t>
-        </is>
-      </c>
+      <c r="E48" s="283" t="inlineStr">
+        <is>
+          <t>Fis - VSi
+2º tempo</t>
+        </is>
+      </c>
+      <c r="F48" s="360" t="n"/>
       <c r="G48" s="283" t="n"/>
       <c r="H48" s="283" t="n"/>
       <c r="I48" s="183" t="inlineStr">
@@ -11922,16 +11922,21 @@
       <c r="E9" s="183" t="inlineStr">
         <is>
           <t>Fis - VSi
-4º e 5º tempos</t>
+3º e 4º tempos</t>
         </is>
       </c>
       <c r="F9" s="183" t="inlineStr">
         <is>
-          <t>Mat - BrSa/FBri
-10º e 11º tempos</t>
-        </is>
-      </c>
-      <c r="G9" s="183" t="n"/>
+          <t>Qui - CAl
+5º e 6º tempos</t>
+        </is>
+      </c>
+      <c r="G9" s="183" t="inlineStr">
+        <is>
+          <t>Ing - APa
+3º e 4º tempos</t>
+        </is>
+      </c>
       <c r="H9" s="183" t="n"/>
       <c r="I9" s="183" t="n"/>
       <c r="J9" s="183" t="n"/>
@@ -12013,21 +12018,21 @@
       </c>
       <c r="E12" s="11" t="inlineStr">
         <is>
-          <t>Bio - Lza
-6º e 7º tempos</t>
-        </is>
-      </c>
-      <c r="F12" s="11" t="inlineStr">
-        <is>
-          <t>DaF - Eth-EFr-Swa
-1º e 2º tempos</t>
-        </is>
-      </c>
-      <c r="G12" s="11" t="n"/>
+          <t>LP/LIT/RED - BPad/MFo/SMo
+1º ao 3º tempos</t>
+        </is>
+      </c>
+      <c r="F12" s="11" t="n"/>
+      <c r="G12" s="11" t="inlineStr">
+        <is>
+          <t>GL - EFr-Car-Swa
+2º e 3º tempos</t>
+        </is>
+      </c>
       <c r="H12" s="11" t="inlineStr">
         <is>
-          <t>Geo - Mlo
-4º e 5º tempos</t>
+          <t>Hist - ALu
+5º e 6º tempos</t>
         </is>
       </c>
       <c r="I12" s="11" t="n"/>
@@ -12089,23 +12094,23 @@
       </c>
       <c r="E15" s="11" t="inlineStr">
         <is>
-          <t>Ing - APa
-5º e 6º tempos</t>
+          <t>Mat - BrSa/FBri
+1º e 2º tempos</t>
         </is>
       </c>
       <c r="F15" s="11" t="inlineStr">
         <is>
-          <t>Qui - CAl
+          <t>Bio - Lza
 6º e 7º tempos</t>
         </is>
       </c>
-      <c r="G15" s="11" t="inlineStr">
-        <is>
-          <t>GL - EFr-Car-Swa
+      <c r="G15" s="11" t="n"/>
+      <c r="H15" s="11" t="inlineStr">
+        <is>
+          <t>Geo - Mlo
 3º e 4º tempos</t>
         </is>
       </c>
-      <c r="H15" s="11" t="n"/>
       <c r="I15" s="11" t="n"/>
       <c r="J15" s="183" t="n"/>
       <c r="L15" s="17" t="n"/>
@@ -12166,19 +12171,14 @@
           <t>unterrichtsfrei sem aula</t>
         </is>
       </c>
-      <c r="F18" s="11" t="inlineStr">
-        <is>
-          <t>Hist - ALu
-10º e 11º tempos</t>
-        </is>
-      </c>
-      <c r="G18" s="11" t="n"/>
-      <c r="H18" s="11" t="inlineStr">
-        <is>
-          <t>LP/LIT/RED - BPad/MFo/SMo
-8º ao 10º tempos</t>
-        </is>
-      </c>
+      <c r="F18" s="11" t="n"/>
+      <c r="G18" s="11" t="inlineStr">
+        <is>
+          <t>DaF - Eth-EFr-Swa
+2º e 3º tempos</t>
+        </is>
+      </c>
+      <c r="H18" s="11" t="n"/>
       <c r="I18" s="350" t="inlineStr">
         <is>
           <t>AG10
@@ -12250,20 +12250,20 @@
         <f>B21+4</f>
         <v/>
       </c>
-      <c r="E21" s="11" t="inlineStr">
-        <is>
-          <t>DaF - Eth-EFr-Swa
-2º e 3º tempos</t>
-        </is>
-      </c>
-      <c r="F21" s="62" t="inlineStr">
-        <is>
-          <t>Hist - ALu
-10º e 11º tempos</t>
-        </is>
-      </c>
-      <c r="G21" s="11" t="n"/>
-      <c r="H21" s="11" t="n"/>
+      <c r="E21" s="11" t="n"/>
+      <c r="F21" s="62" t="n"/>
+      <c r="G21" s="11" t="inlineStr">
+        <is>
+          <t>Soc - Kle
+5º tempo</t>
+        </is>
+      </c>
+      <c r="H21" s="11" t="inlineStr">
+        <is>
+          <t>Geo - Mlo
+3º e 4º tempos</t>
+        </is>
+      </c>
       <c r="I21" s="11" t="n"/>
       <c r="J21" s="183" t="n"/>
       <c r="L21" s="80" t="inlineStr">
@@ -12329,16 +12329,16 @@
       </c>
       <c r="E24" s="283" t="inlineStr">
         <is>
-          <t>Ing - APa
-5º e 6º tempos</t>
+          <t>LP/LIT/RED - BPad/MFo/SMo
+1º ao 3º tempos</t>
         </is>
       </c>
       <c r="F24" s="283" t="n"/>
       <c r="G24" s="79" t="n"/>
       <c r="H24" s="283" t="inlineStr">
         <is>
-          <t>Geo - Mlo
-4º e 5º tempos</t>
+          <t>Hist - ALu
+5º e 6º tempos</t>
         </is>
       </c>
       <c r="I24" s="78" t="n"/>
@@ -12409,16 +12409,11 @@
       </c>
       <c r="E27" s="78" t="inlineStr">
         <is>
-          <t>LP/LIT/RED - BPad/MFo/SMo
-1º ao 3º tempos</t>
-        </is>
-      </c>
-      <c r="F27" s="283" t="inlineStr">
-        <is>
-          <t>Qui - CAl
-6º e 7º tempos</t>
-        </is>
-      </c>
+          <t>Fis - VSi
+3º e 4º tempos</t>
+        </is>
+      </c>
+      <c r="F27" s="283" t="n"/>
       <c r="G27" s="283" t="n"/>
       <c r="H27" s="283" t="n"/>
       <c r="I27" s="283" t="n"/>
@@ -12487,14 +12482,19 @@
         <f>B30+4</f>
         <v/>
       </c>
-      <c r="E30" s="283" t="n"/>
-      <c r="F30" s="283" t="n"/>
-      <c r="G30" s="283" t="inlineStr">
-        <is>
-          <t>Soc - Kle
-5º tempo</t>
-        </is>
-      </c>
+      <c r="E30" s="283" t="inlineStr">
+        <is>
+          <t>Ing - APa
+4º e 5º tempos</t>
+        </is>
+      </c>
+      <c r="F30" s="283" t="inlineStr">
+        <is>
+          <t>Bio - Lza
+6º e 7º tempos</t>
+        </is>
+      </c>
+      <c r="G30" s="283" t="n"/>
       <c r="H30" s="283" t="n"/>
       <c r="I30" s="283" t="n"/>
       <c r="J30" s="183" t="inlineStr">
@@ -12664,8 +12664,8 @@
       </c>
       <c r="E36" s="283" t="inlineStr">
         <is>
-          <t>Bio - Lza
-6º e 7º tempos</t>
+          <t>Mat - BrSa/FBri
+1º e 2º tempos</t>
         </is>
       </c>
       <c r="F36" s="283" t="n"/>
@@ -12736,13 +12736,13 @@
         <f>B39+4</f>
         <v/>
       </c>
-      <c r="E39" s="283" t="inlineStr">
-        <is>
-          <t>Fis - VSi
-4º e 5º tempos</t>
-        </is>
-      </c>
-      <c r="F39" s="283" t="n"/>
+      <c r="E39" s="283" t="n"/>
+      <c r="F39" s="283" t="inlineStr">
+        <is>
+          <t>Qui - CAl
+5º e 6º tempos</t>
+        </is>
+      </c>
       <c r="G39" s="283" t="n"/>
       <c r="H39" s="283" t="n"/>
       <c r="I39" s="283" t="n"/>
@@ -12794,8 +12794,8 @@
       <c r="F42" s="283" t="n"/>
       <c r="G42" s="283" t="inlineStr">
         <is>
-          <t>Fil - LAn
-1º tempo</t>
+          <t>GL - EFr-Car-Swa
+2º e 3º tempos</t>
         </is>
       </c>
       <c r="H42" s="283" t="n"/>
@@ -12854,15 +12854,15 @@
       </c>
       <c r="E45" s="283" t="inlineStr">
         <is>
-          <t>Mat - BrSa/FBri
+          <t>DaF - Eth-EFr-Swa
 1º e 2º tempos</t>
         </is>
       </c>
       <c r="F45" s="283" t="n"/>
       <c r="G45" s="283" t="inlineStr">
         <is>
-          <t>GL - EFr-Car-Swa
-3º e 4º tempos</t>
+          <t>Fil - LAn
+1º tempo</t>
         </is>
       </c>
       <c r="H45" s="283" t="n"/>
@@ -13602,23 +13602,18 @@
       </c>
       <c r="E9" s="183" t="inlineStr">
         <is>
-          <t>Bio - Lza
-6º e 7º tempos</t>
-        </is>
-      </c>
-      <c r="F9" s="183" t="inlineStr">
-        <is>
-          <t>Ing - Vir
-5º e 6º tempos</t>
-        </is>
-      </c>
-      <c r="G9" s="183" t="inlineStr">
-        <is>
-          <t>Geo - Mlo
-1º e 2º tempos</t>
-        </is>
-      </c>
-      <c r="H9" s="183" t="n"/>
+          <t>Qui - CAl
+3º e 4º tempos</t>
+        </is>
+      </c>
+      <c r="F9" s="183" t="n"/>
+      <c r="G9" s="183" t="n"/>
+      <c r="H9" s="183" t="inlineStr">
+        <is>
+          <t>LP/LIT/RED - BPad/MFo/SMo
+1º ao 3º tempos</t>
+        </is>
+      </c>
       <c r="I9" s="183" t="n"/>
       <c r="J9" s="183" t="n"/>
       <c r="L9" s="16" t="inlineStr">
@@ -13699,23 +13694,23 @@
       </c>
       <c r="E12" s="11" t="inlineStr">
         <is>
-          <t>Qui - CAl
-4º e 5º tempos</t>
-        </is>
-      </c>
-      <c r="F12" s="11" t="inlineStr">
-        <is>
-          <t>Mat - BrSa/FBri
+          <t>Fis - VSi
 6º e 7º tempos</t>
         </is>
       </c>
+      <c r="F12" s="11" t="n"/>
       <c r="G12" s="11" t="inlineStr">
         <is>
-          <t>GL - EFr-Car-Swa
-3º e 4º tempos</t>
-        </is>
-      </c>
-      <c r="H12" s="11" t="n"/>
+          <t>DaF - Eth-EFr-Swa
+1º e 2º tempos</t>
+        </is>
+      </c>
+      <c r="H12" s="11" t="inlineStr">
+        <is>
+          <t>Hist - ALu
+2º e 3º tempos</t>
+        </is>
+      </c>
       <c r="I12" s="11" t="n"/>
       <c r="J12" s="183" t="n"/>
       <c r="L12" s="15" t="n"/>
@@ -13775,18 +13770,23 @@
       </c>
       <c r="E15" s="11" t="inlineStr">
         <is>
-          <t>Fis - VSi
-6º e 7º tempos</t>
-        </is>
-      </c>
-      <c r="F15" s="11" t="n"/>
-      <c r="G15" s="11" t="n"/>
-      <c r="H15" s="11" t="inlineStr">
-        <is>
-          <t>LP/LIT/RED - BPad/MFo/SMo
-1º ao 3º tempos</t>
-        </is>
-      </c>
+          <t>Bio - Lza
+5º e 6º tempos</t>
+        </is>
+      </c>
+      <c r="F15" s="11" t="inlineStr">
+        <is>
+          <t>Ing - Vir
+4º e 5º tempos</t>
+        </is>
+      </c>
+      <c r="G15" s="11" t="inlineStr">
+        <is>
+          <t>Geo - Mlo
+1º e 2º tempos</t>
+        </is>
+      </c>
+      <c r="H15" s="11" t="n"/>
       <c r="I15" s="11" t="n"/>
       <c r="J15" s="183" t="n"/>
       <c r="L15" s="17" t="n"/>
@@ -13849,13 +13849,13 @@
       </c>
       <c r="F18" s="11" t="inlineStr">
         <is>
-          <t>Hist - ALu
-10º e 11º tempos</t>
+          <t>Mat - BrSa/FBri
+5º e 6º tempos</t>
         </is>
       </c>
       <c r="G18" s="11" t="inlineStr">
         <is>
-          <t>DaF - Eth-EFr-Swa
+          <t>GL - EFr-Car-Swa
 2º e 3º tempos</t>
         </is>
       </c>
@@ -13931,19 +13931,14 @@
         <f>B21+4</f>
         <v/>
       </c>
-      <c r="E21" s="11" t="n"/>
-      <c r="F21" s="62" t="inlineStr">
-        <is>
-          <t>Ing - Vir
-5º e 6º tempos</t>
-        </is>
-      </c>
-      <c r="G21" s="11" t="inlineStr">
-        <is>
-          <t>Geo - Mlo
-1º e 2º tempos</t>
-        </is>
-      </c>
+      <c r="E21" s="11" t="inlineStr">
+        <is>
+          <t>Qui - CAl
+3º e 4º tempos</t>
+        </is>
+      </c>
+      <c r="F21" s="62" t="n"/>
+      <c r="G21" s="11" t="n"/>
       <c r="H21" s="11" t="n"/>
       <c r="I21" s="11" t="n"/>
       <c r="J21" s="183" t="n"/>
@@ -14010,19 +14005,19 @@
       </c>
       <c r="E24" s="283" t="inlineStr">
         <is>
-          <t>LP/LIT/RED - BPad/MFo/SMo
-1º ao 3º tempos</t>
+          <t>DaF - Eth-EFr-Swa
+1º e 2º tempos</t>
         </is>
       </c>
       <c r="F24" s="283" t="n"/>
-      <c r="G24" s="362" t="inlineStr">
-        <is>
-          <t>GL - EFr-Car-Swa
-3º e 4º tempos</t>
-        </is>
-      </c>
+      <c r="G24" s="79" t="n"/>
       <c r="H24" s="283" t="n"/>
-      <c r="I24" s="78" t="n"/>
+      <c r="I24" s="78" t="inlineStr">
+        <is>
+          <t>Soc - Kle
+5º tempo</t>
+        </is>
+      </c>
       <c r="J24" s="265" t="n"/>
       <c r="L24" s="318" t="inlineStr">
         <is>
@@ -14088,14 +14083,14 @@
         <f>B27+4</f>
         <v/>
       </c>
-      <c r="E27" s="78" t="inlineStr">
-        <is>
-          <t>Qui - CAl
-4º e 5º tempos</t>
-        </is>
-      </c>
+      <c r="E27" s="78" t="n"/>
       <c r="F27" s="283" t="n"/>
-      <c r="G27" s="283" t="n"/>
+      <c r="G27" s="283" t="inlineStr">
+        <is>
+          <t>Geo - Mlo
+1º e 2º tempos</t>
+        </is>
+      </c>
       <c r="H27" s="283" t="n"/>
       <c r="I27" s="283" t="n"/>
       <c r="J27" s="265" t="n"/>
@@ -14165,8 +14160,8 @@
       </c>
       <c r="E30" s="283" t="inlineStr">
         <is>
-          <t>Fis - VSi
-6º e 7º tempos</t>
+          <t>Bio - Lza
+5º e 6º tempos</t>
         </is>
       </c>
       <c r="F30" s="283" t="n"/>
@@ -14340,19 +14335,19 @@
       </c>
       <c r="E36" s="283" t="inlineStr">
         <is>
-          <t>DaF - Eth-EFr-Swa
-2º e 3º tempos</t>
-        </is>
-      </c>
-      <c r="F36" s="283" t="n"/>
+          <t>Fis - VSi
+6º e 7º tempos</t>
+        </is>
+      </c>
+      <c r="F36" s="283" t="inlineStr">
+        <is>
+          <t>Ing - Vir
+4º e 5º tempos</t>
+        </is>
+      </c>
       <c r="G36" s="283" t="n"/>
       <c r="H36" s="283" t="n"/>
-      <c r="I36" s="283" t="inlineStr">
-        <is>
-          <t>Soc - Kle
-5º tempo</t>
-        </is>
-      </c>
+      <c r="I36" s="283" t="n"/>
       <c r="J36" s="265" t="n"/>
       <c r="L36" s="81" t="inlineStr">
         <is>
@@ -14417,7 +14412,12 @@
         <f>B39+4</f>
         <v/>
       </c>
-      <c r="E39" s="283" t="n"/>
+      <c r="E39" s="283" t="inlineStr">
+        <is>
+          <t>LP/LIT/RED - BPad/MFo/SMo
+1º ao 3º tempos</t>
+        </is>
+      </c>
       <c r="F39" s="283" t="n"/>
       <c r="G39" s="283" t="inlineStr">
         <is>
@@ -14472,14 +14472,14 @@
         <v/>
       </c>
       <c r="E42" s="283" t="n"/>
-      <c r="F42" s="283" t="inlineStr">
-        <is>
-          <t>Bio - Lza
-9º e 10º tempos</t>
-        </is>
-      </c>
+      <c r="F42" s="283" t="n"/>
       <c r="G42" s="283" t="n"/>
-      <c r="H42" s="283" t="n"/>
+      <c r="H42" s="283" t="inlineStr">
+        <is>
+          <t>Hist - ALu
+2º e 3º tempos</t>
+        </is>
+      </c>
       <c r="I42" s="283" t="n"/>
       <c r="J42" s="265" t="n"/>
       <c r="L42" s="259" t="inlineStr">
@@ -14536,16 +14536,16 @@
       <c r="E45" s="283" t="inlineStr">
         <is>
           <t>Mat - BrSa/FBri
-3º e 4º tempos</t>
-        </is>
-      </c>
-      <c r="F45" s="283" t="inlineStr">
-        <is>
-          <t>Hist - ALu
-10º e 11º tempos</t>
-        </is>
-      </c>
-      <c r="G45" s="283" t="n"/>
+2º e 3º tempos</t>
+        </is>
+      </c>
+      <c r="F45" s="283" t="n"/>
+      <c r="G45" s="283" t="inlineStr">
+        <is>
+          <t>GL - EFr-Car-Swa
+2º e 3º tempos</t>
+        </is>
+      </c>
       <c r="H45" s="283" t="n"/>
       <c r="I45" s="357" t="inlineStr">
         <is>
@@ -15302,23 +15302,18 @@
       <c r="E9" s="183" t="inlineStr">
         <is>
           <t>GL - CBu-Swa-SGa
-5º e 6º tempos</t>
+4º e 5º tempos</t>
         </is>
       </c>
       <c r="F9" s="183" t="inlineStr">
         <is>
-          <t>Hist - Ver
-2º e 3º tempos</t>
+          <t>DaF - CBu-SGa-Swa
+3º e 4º tempos</t>
         </is>
       </c>
       <c r="G9" s="183" t="n"/>
       <c r="H9" s="183" t="n"/>
-      <c r="I9" s="183" t="inlineStr">
-        <is>
-          <t>LP/LIT/RED - ACo/AMu/Raf
-5º ao 7º tempos</t>
-        </is>
-      </c>
+      <c r="I9" s="183" t="n"/>
       <c r="J9" s="183" t="n"/>
       <c r="L9" s="16" t="inlineStr">
         <is>
@@ -15398,8 +15393,8 @@
       </c>
       <c r="E12" s="11" t="inlineStr">
         <is>
-          <t>Ing - Bea
-6º e 7º tempos</t>
+          <t>Mat - ClaMe/JJ
+1º e 2º tempos</t>
         </is>
       </c>
       <c r="F12" s="11" t="inlineStr">
@@ -15414,7 +15409,12 @@
 2º ao 7º tempos</t>
         </is>
       </c>
-      <c r="H12" s="11" t="n"/>
+      <c r="H12" s="11" t="inlineStr">
+        <is>
+          <t>Fis - Cadu
+1º e 2º tempos</t>
+        </is>
+      </c>
       <c r="I12" s="11" t="n"/>
       <c r="J12" s="183" t="n"/>
       <c r="L12" s="15" t="n"/>
@@ -15478,20 +15478,20 @@
 1º e 2º tempos</t>
         </is>
       </c>
-      <c r="F15" s="11" t="inlineStr">
+      <c r="F15" s="11" t="n"/>
+      <c r="G15" s="11" t="n"/>
+      <c r="H15" s="11" t="inlineStr">
+        <is>
+          <t>LP/LIT/RED - ACo/AMu/Raf
+2º ao 4º tempos</t>
+        </is>
+      </c>
+      <c r="I15" s="11" t="inlineStr">
         <is>
           <t>Bio - Ale
-9º e 10º tempos</t>
-        </is>
-      </c>
-      <c r="G15" s="11" t="inlineStr">
-        <is>
-          <t>DaF - CBu-SGa-Swa
-6º e 7º tempos</t>
-        </is>
-      </c>
-      <c r="H15" s="11" t="n"/>
-      <c r="I15" s="11" t="n"/>
+3º e 4º tempos</t>
+        </is>
+      </c>
       <c r="J15" s="183" t="n"/>
       <c r="L15" s="17" t="n"/>
       <c r="M15" s="15" t="n"/>
@@ -15553,21 +15553,21 @@
       </c>
       <c r="F18" s="11" t="inlineStr">
         <is>
-          <t>Fis - Cadu
-11º e 12º tempos</t>
-        </is>
-      </c>
-      <c r="G18" s="11" t="inlineStr">
-        <is>
-          <t>Mat - ClaMe/JJ
-2º e 3º tempos</t>
-        </is>
-      </c>
-      <c r="H18" s="11" t="n"/>
+          <t>Hist - Ver
+1º e 2º tempos</t>
+        </is>
+      </c>
+      <c r="G18" s="11" t="n"/>
+      <c r="H18" s="11" t="inlineStr">
+        <is>
+          <t>Ing - Bea
+4º e 5º tempos</t>
+        </is>
+      </c>
       <c r="I18" s="350" t="inlineStr">
         <is>
           <t>Geo - Mar
-4º e 5º tempos</t>
+3º e 4º tempos</t>
         </is>
       </c>
       <c r="J18" s="262" t="inlineStr">
@@ -15637,19 +15637,19 @@
       </c>
       <c r="E21" s="11" t="inlineStr">
         <is>
-          <t>Geo - Mar
-3º e 4º tempos</t>
-        </is>
-      </c>
-      <c r="F21" s="62" t="inlineStr">
-        <is>
-          <t>Bio - Ale
-9º e 10º tempos</t>
-        </is>
-      </c>
+          <t>Mat - ClaMe/JJ
+1º e 2º tempos</t>
+        </is>
+      </c>
+      <c r="F21" s="62" t="n"/>
       <c r="G21" s="11" t="n"/>
       <c r="H21" s="11" t="n"/>
-      <c r="I21" s="11" t="n"/>
+      <c r="I21" s="11" t="inlineStr">
+        <is>
+          <t>Bio - Ale
+3º e 4º tempos</t>
+        </is>
+      </c>
       <c r="J21" s="183" t="n"/>
       <c r="L21" s="80" t="inlineStr">
         <is>
@@ -15714,19 +15714,19 @@
       </c>
       <c r="E24" s="283" t="inlineStr">
         <is>
-          <t>Mat - ClaMe/JJ
-2º e 3º tempos</t>
+          <t>DaF - CBu-SGa-Swa
+5º e 6º tempos</t>
         </is>
       </c>
       <c r="F24" s="283" t="n"/>
-      <c r="G24" s="362" t="inlineStr">
-        <is>
-          <t>Fil - LAn
-9º tempo</t>
-        </is>
-      </c>
+      <c r="G24" s="79" t="n"/>
       <c r="H24" s="283" t="n"/>
-      <c r="I24" s="78" t="n"/>
+      <c r="I24" s="78" t="inlineStr">
+        <is>
+          <t>Soc - Kle
+2º tempo</t>
+        </is>
+      </c>
       <c r="J24" s="265" t="n"/>
       <c r="L24" s="318" t="inlineStr">
         <is>
@@ -15792,21 +15792,16 @@
         <f>B27+4</f>
         <v/>
       </c>
-      <c r="E27" s="78" t="n"/>
-      <c r="F27" s="283" t="inlineStr">
-        <is>
-          <t>Hist - Ver
-2º e 3º tempos</t>
-        </is>
-      </c>
+      <c r="E27" s="78" t="inlineStr">
+        <is>
+          <t>Qui - CAl
+1º e 2º tempos</t>
+        </is>
+      </c>
+      <c r="F27" s="283" t="n"/>
       <c r="G27" s="283" t="n"/>
       <c r="H27" s="283" t="n"/>
-      <c r="I27" s="283" t="inlineStr">
-        <is>
-          <t>LP/LIT/RED - ACo/AMu/Raf
-5º ao 7º tempos</t>
-        </is>
-      </c>
+      <c r="I27" s="283" t="n"/>
       <c r="J27" s="265" t="n"/>
       <c r="L27" s="45" t="n"/>
       <c r="M27" s="323" t="inlineStr">
@@ -15874,11 +15869,16 @@
       </c>
       <c r="E30" s="283" t="inlineStr">
         <is>
-          <t>GL - CBu-Swa-SGa
-5º e 6º tempos</t>
-        </is>
-      </c>
-      <c r="F30" s="283" t="n"/>
+          <t>Geo - Mar
+2º e 3º tempos</t>
+        </is>
+      </c>
+      <c r="F30" s="283" t="inlineStr">
+        <is>
+          <t>Hist - Ver
+1º e 2º tempos</t>
+        </is>
+      </c>
       <c r="G30" s="283" t="n"/>
       <c r="H30" s="283" t="n"/>
       <c r="I30" s="283" t="n"/>
@@ -16047,21 +16047,16 @@
         <f>B36+4</f>
         <v/>
       </c>
-      <c r="E36" s="283" t="inlineStr">
-        <is>
-          <t>DaF - CBu-SGa-Swa
-6º e 7º tempos</t>
-        </is>
-      </c>
+      <c r="E36" s="283" t="n"/>
       <c r="F36" s="283" t="n"/>
-      <c r="G36" s="283" t="n"/>
+      <c r="G36" s="283" t="inlineStr">
+        <is>
+          <t>Fil - LAn
+9º tempo</t>
+        </is>
+      </c>
       <c r="H36" s="283" t="n"/>
-      <c r="I36" s="283" t="inlineStr">
-        <is>
-          <t>Soc - Kle
-2º tempo</t>
-        </is>
-      </c>
+      <c r="I36" s="283" t="n"/>
       <c r="J36" s="265" t="n"/>
       <c r="L36" s="81" t="inlineStr">
         <is>
@@ -16187,13 +16182,13 @@
       </c>
       <c r="E42" s="283" t="n"/>
       <c r="F42" s="283" t="n"/>
-      <c r="G42" s="283" t="n"/>
-      <c r="H42" s="283" t="inlineStr">
-        <is>
-          <t>Ing - Bea
-5º e 6º tempos</t>
-        </is>
-      </c>
+      <c r="G42" s="283" t="inlineStr">
+        <is>
+          <t>GL - CBu-Swa-SGa
+3º e 4º tempos</t>
+        </is>
+      </c>
+      <c r="H42" s="283" t="n"/>
       <c r="I42" s="283" t="n"/>
       <c r="J42" s="265" t="n"/>
       <c r="L42" s="259" t="inlineStr">
@@ -16247,15 +16242,20 @@
         <f>B45+4</f>
         <v/>
       </c>
-      <c r="E45" s="283" t="n"/>
-      <c r="F45" s="283" t="inlineStr">
+      <c r="E45" s="283" t="inlineStr">
+        <is>
+          <t>LP/LIT/RED - ACo/AMu/Raf
+2º ao 4º tempos</t>
+        </is>
+      </c>
+      <c r="F45" s="283" t="n"/>
+      <c r="G45" s="283" t="n"/>
+      <c r="H45" s="283" t="inlineStr">
         <is>
           <t>Fis - Cadu
-11º e 12º tempos</t>
-        </is>
-      </c>
-      <c r="G45" s="283" t="n"/>
-      <c r="H45" s="283" t="n"/>
+1º e 2º tempos</t>
+        </is>
+      </c>
       <c r="I45" s="357" t="n"/>
       <c r="J45" s="269" t="n"/>
       <c r="L45" s="331" t="n"/>
@@ -16304,15 +16304,15 @@
         <f>B48+4</f>
         <v/>
       </c>
-      <c r="E48" s="283" t="inlineStr">
-        <is>
-          <t>Qui - CAl
-1º e 2º tempos</t>
-        </is>
-      </c>
+      <c r="E48" s="283" t="n"/>
       <c r="F48" s="360" t="n"/>
       <c r="G48" s="283" t="n"/>
-      <c r="H48" s="283" t="n"/>
+      <c r="H48" s="283" t="inlineStr">
+        <is>
+          <t>Ing - Bea
+4º e 5º tempos</t>
+        </is>
+      </c>
       <c r="I48" s="183" t="inlineStr">
         <is>
           <t>unterrichtsfrei sem aula</t>
@@ -16997,23 +16997,23 @@
       </c>
       <c r="E9" s="183" t="inlineStr">
         <is>
-          <t>Geo - Mar
-6º e 7º tempos</t>
-        </is>
-      </c>
-      <c r="F9" s="183" t="inlineStr">
-        <is>
-          <t>Fis - Cadu
-8º e 9º tempos</t>
-        </is>
-      </c>
+          <t>GL - CBu-Swa-SGa
+4º e 5º tempos</t>
+        </is>
+      </c>
+      <c r="F9" s="183" t="n"/>
       <c r="G9" s="183" t="inlineStr">
         <is>
-          <t>DaF - CBu-SGa-Swa
-6º e 7º tempos</t>
-        </is>
-      </c>
-      <c r="H9" s="183" t="n"/>
+          <t>Hist - Ver
+1º e 2º tempos</t>
+        </is>
+      </c>
+      <c r="H9" s="183" t="inlineStr">
+        <is>
+          <t>Ing - PaH
+1º e 2º tempos</t>
+        </is>
+      </c>
       <c r="I9" s="183" t="n"/>
       <c r="J9" s="183" t="n"/>
       <c r="L9" s="16" t="inlineStr">
@@ -17094,8 +17094,8 @@
       </c>
       <c r="E12" s="11" t="inlineStr">
         <is>
-          <t>Mat - ClaMe/JJ
-3º e 4º tempos</t>
+          <t>DaF - CBu-SGa-Swa
+5º e 6º tempos</t>
         </is>
       </c>
       <c r="F12" s="11" t="inlineStr">
@@ -17171,7 +17171,7 @@
       <c r="E15" s="11" t="inlineStr">
         <is>
           <t>Bio - Ale
-2º e 3º tempos</t>
+1º e 2º tempos</t>
         </is>
       </c>
       <c r="F15" s="11" t="inlineStr">
@@ -17249,20 +17249,20 @@
       </c>
       <c r="F18" s="11" t="inlineStr">
         <is>
-          <t>Hist - Ver
-10º e 11º tempos</t>
+          <t>Mat - ClaMe/JJ
+1º e 2º tempos</t>
         </is>
       </c>
       <c r="G18" s="11" t="inlineStr">
         <is>
-          <t>GL - CBu-Swa-SGa
-4º e 5º tempos</t>
+          <t>Geo - Mar
+1º e 2º tempos</t>
         </is>
       </c>
       <c r="H18" s="11" t="inlineStr">
         <is>
-          <t>Ing - PaH
-2º e 3º tempos</t>
+          <t>Fis - Cadu
+3º e 4º tempos</t>
         </is>
       </c>
       <c r="I18" s="350" t="n"/>
@@ -17333,18 +17333,18 @@
       </c>
       <c r="E21" s="11" t="inlineStr">
         <is>
-          <t>GL - CBu-Swa-SGa
-5º e 6º tempos</t>
+          <t>Ing - PaH
+3º e 4º tempos</t>
         </is>
       </c>
       <c r="F21" s="62" t="n"/>
-      <c r="G21" s="11" t="n"/>
-      <c r="H21" s="11" t="inlineStr">
-        <is>
-          <t>LP/LIT/RED - ACo/AMu/Raf
-4º ao 6º tempos</t>
-        </is>
-      </c>
+      <c r="G21" s="11" t="inlineStr">
+        <is>
+          <t>Fil - LAn
+11º tempo</t>
+        </is>
+      </c>
+      <c r="H21" s="11" t="n"/>
       <c r="I21" s="11" t="n"/>
       <c r="J21" s="183" t="n"/>
       <c r="L21" s="80" t="inlineStr">
@@ -17411,16 +17411,16 @@
       <c r="E24" s="283" t="inlineStr">
         <is>
           <t>DaF - CBu-SGa-Swa
-6º e 7º tempos</t>
-        </is>
-      </c>
-      <c r="F24" s="283" t="n"/>
-      <c r="G24" s="362" t="inlineStr">
-        <is>
-          <t>Fil - LAn
-11º tempo</t>
-        </is>
-      </c>
+5º e 6º tempos</t>
+        </is>
+      </c>
+      <c r="F24" s="283" t="inlineStr">
+        <is>
+          <t>Qui - CAl
+1º e 2º tempos</t>
+        </is>
+      </c>
+      <c r="G24" s="79" t="n"/>
       <c r="H24" s="283" t="n"/>
       <c r="I24" s="78" t="n"/>
       <c r="J24" s="265" t="n"/>
@@ -17488,15 +17488,20 @@
         <f>B27+4</f>
         <v/>
       </c>
-      <c r="E27" s="78" t="n"/>
-      <c r="F27" s="283" t="inlineStr">
-        <is>
-          <t>Qui - CAl
+      <c r="E27" s="78" t="inlineStr">
+        <is>
+          <t>Bio - Ale
 1º e 2º tempos</t>
         </is>
       </c>
+      <c r="F27" s="283" t="n"/>
       <c r="G27" s="283" t="n"/>
-      <c r="H27" s="283" t="n"/>
+      <c r="H27" s="283" t="inlineStr">
+        <is>
+          <t>LP/LIT/RED - ACo/AMu/Raf
+4º ao 6º tempos</t>
+        </is>
+      </c>
       <c r="I27" s="283" t="n"/>
       <c r="J27" s="265" t="n"/>
       <c r="L27" s="45" t="n"/>
@@ -17563,14 +17568,14 @@
         <f>B30+4</f>
         <v/>
       </c>
-      <c r="E30" s="283" t="inlineStr">
-        <is>
-          <t>Ing - PaH
-4º e 5º tempos</t>
-        </is>
-      </c>
+      <c r="E30" s="283" t="n"/>
       <c r="F30" s="283" t="n"/>
-      <c r="G30" s="283" t="n"/>
+      <c r="G30" s="283" t="inlineStr">
+        <is>
+          <t>Hist - Ver
+1º e 2º tempos</t>
+        </is>
+      </c>
       <c r="H30" s="283" t="n"/>
       <c r="I30" s="283" t="n"/>
       <c r="J30" s="183" t="inlineStr">
@@ -17738,20 +17743,15 @@
         <f>B36+4</f>
         <v/>
       </c>
-      <c r="E36" s="283" t="inlineStr">
-        <is>
-          <t>Bio - Ale
-2º e 3º tempos</t>
-        </is>
-      </c>
-      <c r="F36" s="283" t="inlineStr">
-        <is>
-          <t>Hist - Ver
-10º e 11º tempos</t>
-        </is>
-      </c>
+      <c r="E36" s="283" t="n"/>
+      <c r="F36" s="283" t="n"/>
       <c r="G36" s="283" t="n"/>
-      <c r="H36" s="283" t="n"/>
+      <c r="H36" s="283" t="inlineStr">
+        <is>
+          <t>Fis - Cadu
+3º e 4º tempos</t>
+        </is>
+      </c>
       <c r="I36" s="283" t="n"/>
       <c r="J36" s="265" t="n"/>
       <c r="L36" s="81" t="inlineStr">
@@ -17877,15 +17877,15 @@
         <v/>
       </c>
       <c r="E42" s="283" t="n"/>
-      <c r="F42" s="283" t="inlineStr">
-        <is>
-          <t>Fis - Cadu
-8º e 9º tempos</t>
-        </is>
-      </c>
+      <c r="F42" s="283" t="n"/>
       <c r="G42" s="283" t="n"/>
       <c r="H42" s="283" t="n"/>
-      <c r="I42" s="283" t="n"/>
+      <c r="I42" s="283" t="inlineStr">
+        <is>
+          <t>Soc - Kle
+4º tempo</t>
+        </is>
+      </c>
       <c r="J42" s="265" t="n"/>
       <c r="L42" s="259" t="inlineStr">
         <is>
@@ -17940,19 +17940,14 @@
       </c>
       <c r="E45" s="283" t="inlineStr">
         <is>
-          <t>Mat - ClaMe/JJ
-3º e 4º tempos</t>
+          <t>GL - CBu-Swa-SGa
+4º e 5º tempos</t>
         </is>
       </c>
       <c r="F45" s="283" t="n"/>
       <c r="G45" s="283" t="n"/>
       <c r="H45" s="283" t="n"/>
-      <c r="I45" s="357" t="inlineStr">
-        <is>
-          <t>Soc - Kle
-4º tempo</t>
-        </is>
-      </c>
+      <c r="I45" s="357" t="n"/>
       <c r="J45" s="269" t="n"/>
       <c r="L45" s="331" t="n"/>
     </row>
@@ -18002,12 +17997,17 @@
       </c>
       <c r="E48" s="283" t="inlineStr">
         <is>
+          <t>Mat - ClaMe/JJ
+2º e 3º tempos</t>
+        </is>
+      </c>
+      <c r="F48" s="360" t="n"/>
+      <c r="G48" s="283" t="inlineStr">
+        <is>
           <t>Geo - Mar
-6º e 7º tempos</t>
-        </is>
-      </c>
-      <c r="F48" s="360" t="n"/>
-      <c r="G48" s="283" t="n"/>
+1º e 2º tempos</t>
+        </is>
+      </c>
       <c r="H48" s="283" t="n"/>
       <c r="I48" s="183" t="inlineStr">
         <is>
@@ -18693,20 +18693,20 @@
       </c>
       <c r="E9" s="183" t="inlineStr">
         <is>
-          <t>Ing - PaH
+          <t>Geo - Mar
+4º e 5º tempos</t>
+        </is>
+      </c>
+      <c r="F9" s="183" t="inlineStr">
+        <is>
+          <t>Mat - Bre/JJ
 1º e 2º tempos</t>
         </is>
       </c>
-      <c r="F9" s="183" t="inlineStr">
-        <is>
-          <t>GL - CBu-EFr-Eth
+      <c r="G9" s="183" t="inlineStr">
+        <is>
+          <t>Qui - CAl/Fab
 5º e 6º tempos</t>
-        </is>
-      </c>
-      <c r="G9" s="183" t="inlineStr">
-        <is>
-          <t>Hist - Wag
-11º e 12º tempos</t>
         </is>
       </c>
       <c r="H9" s="183" t="n"/>
@@ -18790,23 +18790,23 @@
       </c>
       <c r="E12" s="11" t="inlineStr">
         <is>
-          <t>Qui - CAl/Fab
-6º e 7º tempos</t>
-        </is>
-      </c>
-      <c r="F12" s="11" t="inlineStr">
-        <is>
-          <t>Fis - Cadu
-3º e 4º tempos</t>
-        </is>
-      </c>
+          <t>Bio - Ale
+2º e 3º tempos</t>
+        </is>
+      </c>
+      <c r="F12" s="11" t="n"/>
       <c r="G12" s="11" t="inlineStr">
         <is>
-          <t>DaF - CBu-EFr-Eth
-5º e 6º tempos</t>
-        </is>
-      </c>
-      <c r="H12" s="11" t="n"/>
+          <t>Soc - Kle
+2º tempo</t>
+        </is>
+      </c>
+      <c r="H12" s="11" t="inlineStr">
+        <is>
+          <t>LP/LIT/RED - AMu/Deb
+3º ao 5º tempos</t>
+        </is>
+      </c>
       <c r="I12" s="11" t="n"/>
       <c r="J12" s="183" t="n"/>
       <c r="L12" s="15" t="n"/>
@@ -18864,19 +18864,19 @@
         <f>B15+4</f>
         <v/>
       </c>
-      <c r="E15" s="11" t="n"/>
+      <c r="E15" s="11" t="inlineStr">
+        <is>
+          <t>Ing - PaH
+1º e 2º tempos</t>
+        </is>
+      </c>
       <c r="F15" s="11" t="inlineStr">
         <is>
-          <t>Mat - Bre/JJ
-1º e 2º tempos</t>
-        </is>
-      </c>
-      <c r="G15" s="11" t="inlineStr">
-        <is>
-          <t>Soc - Kle
-2º tempo</t>
-        </is>
-      </c>
+          <t>GL - CBu-EFr-Eth
+5º e 6º tempos</t>
+        </is>
+      </c>
+      <c r="G15" s="11" t="n"/>
       <c r="H15" s="11" t="n"/>
       <c r="I15" s="11" t="n"/>
       <c r="J15" s="183" t="n"/>
@@ -18940,21 +18940,21 @@
       </c>
       <c r="F18" s="11" t="inlineStr">
         <is>
-          <t>Bio - Ale
+          <t>Fis - Cadu
 2º e 3º tempos</t>
         </is>
       </c>
-      <c r="G18" s="11" t="n"/>
-      <c r="H18" s="11" t="inlineStr">
-        <is>
-          <t>LP/LIT/RED - AMu/Deb
-3º ao 5º tempos</t>
-        </is>
-      </c>
+      <c r="G18" s="11" t="inlineStr">
+        <is>
+          <t>DaF - CBu-EFr-Eth
+4º e 5º tempos</t>
+        </is>
+      </c>
+      <c r="H18" s="11" t="n"/>
       <c r="I18" s="350" t="inlineStr">
         <is>
-          <t>Geo - Mar
-2º e 3º tempos</t>
+          <t>Hist - Wag
+3º e 4º tempos</t>
         </is>
       </c>
       <c r="J18" s="262" t="inlineStr">
@@ -19022,13 +19022,13 @@
         <f>B21+4</f>
         <v/>
       </c>
-      <c r="E21" s="11" t="n"/>
-      <c r="F21" s="62" t="inlineStr">
-        <is>
-          <t>Hist - Wag
-8º e 9º tempos</t>
-        </is>
-      </c>
+      <c r="E21" s="11" t="inlineStr">
+        <is>
+          <t>DaF - CBu-EFr-Eth
+3º e 4º tempos</t>
+        </is>
+      </c>
+      <c r="F21" s="62" t="n"/>
       <c r="G21" s="11" t="inlineStr">
         <is>
           <t>S4-12
@@ -19106,17 +19106,12 @@
       </c>
       <c r="E24" s="283" t="inlineStr">
         <is>
-          <t>DaF - CBu-EFr-Eth
-4º e 5º tempos</t>
+          <t>Bio - Ale
+2º e 3º tempos</t>
         </is>
       </c>
       <c r="F24" s="283" t="n"/>
-      <c r="G24" s="362" t="inlineStr">
-        <is>
-          <t>Fil - LAn
-10º tempo</t>
-        </is>
-      </c>
+      <c r="G24" s="79" t="n"/>
       <c r="H24" s="283" t="n"/>
       <c r="I24" s="78" t="n"/>
       <c r="J24" s="265" t="n"/>
@@ -19184,13 +19179,13 @@
         <f>B27+4</f>
         <v/>
       </c>
-      <c r="E27" s="78" t="inlineStr">
-        <is>
-          <t>Qui - CAl/Fab
-6º e 7º tempos</t>
-        </is>
-      </c>
-      <c r="F27" s="283" t="n"/>
+      <c r="E27" s="78" t="n"/>
+      <c r="F27" s="283" t="inlineStr">
+        <is>
+          <t>GL - CBu-EFr-Eth
+5º e 6º tempos</t>
+        </is>
+      </c>
       <c r="G27" s="283" t="n"/>
       <c r="H27" s="283" t="n"/>
       <c r="I27" s="283" t="n"/>
@@ -19259,14 +19254,19 @@
         <f>B30+4</f>
         <v/>
       </c>
-      <c r="E30" s="283" t="n"/>
-      <c r="F30" s="283" t="inlineStr">
-        <is>
-          <t>Mat - Bre/JJ
+      <c r="E30" s="283" t="inlineStr">
+        <is>
+          <t>Ing - PaH
 1º e 2º tempos</t>
         </is>
       </c>
-      <c r="G30" s="283" t="n"/>
+      <c r="F30" s="283" t="n"/>
+      <c r="G30" s="283" t="inlineStr">
+        <is>
+          <t>Fil - LAn
+10º tempo</t>
+        </is>
+      </c>
       <c r="H30" s="283" t="n"/>
       <c r="I30" s="283" t="n"/>
       <c r="J30" s="183" t="inlineStr">
@@ -19434,16 +19434,21 @@
         <f>B36+4</f>
         <v/>
       </c>
-      <c r="E36" s="283" t="n"/>
-      <c r="F36" s="283" t="inlineStr">
-        <is>
-          <t>Fis - Cadu
-3º e 4º tempos</t>
-        </is>
-      </c>
+      <c r="E36" s="283" t="inlineStr">
+        <is>
+          <t>Geo - Mar
+4º e 5º tempos</t>
+        </is>
+      </c>
+      <c r="F36" s="283" t="n"/>
       <c r="G36" s="283" t="n"/>
       <c r="H36" s="283" t="n"/>
-      <c r="I36" s="283" t="n"/>
+      <c r="I36" s="283" t="inlineStr">
+        <is>
+          <t>Hist - Wag
+3º e 4º tempos</t>
+        </is>
+      </c>
       <c r="J36" s="265" t="n"/>
       <c r="L36" s="81" t="inlineStr">
         <is>
@@ -19508,19 +19513,14 @@
         <f>B39+4</f>
         <v/>
       </c>
-      <c r="E39" s="283" t="inlineStr">
-        <is>
-          <t>Geo - Mar
+      <c r="E39" s="283" t="n"/>
+      <c r="F39" s="283" t="n"/>
+      <c r="G39" s="283" t="inlineStr">
+        <is>
+          <t>Qui - CAl/Fab
 5º e 6º tempos</t>
         </is>
       </c>
-      <c r="F39" s="283" t="inlineStr">
-        <is>
-          <t>GL - CBu-EFr-Eth
-5º e 6º tempos</t>
-        </is>
-      </c>
-      <c r="G39" s="283" t="n"/>
       <c r="H39" s="283" t="n"/>
       <c r="I39" s="283" t="n"/>
       <c r="J39" s="265" t="n"/>
@@ -19570,17 +19570,12 @@
       <c r="E42" s="283" t="n"/>
       <c r="F42" s="283" t="inlineStr">
         <is>
-          <t>Bio - Ale
-2º e 3º tempos</t>
+          <t>Mat - Bre/JJ
+1º e 2º tempos</t>
         </is>
       </c>
       <c r="G42" s="283" t="n"/>
-      <c r="H42" s="283" t="inlineStr">
-        <is>
-          <t>LP/LIT/RED - AMu/Deb
-3º ao 5º tempos</t>
-        </is>
-      </c>
+      <c r="H42" s="283" t="n"/>
       <c r="I42" s="283" t="n"/>
       <c r="J42" s="265" t="n"/>
       <c r="L42" s="259" t="inlineStr">
@@ -19634,15 +19629,20 @@
         <f>B45+4</f>
         <v/>
       </c>
-      <c r="E45" s="283" t="inlineStr">
-        <is>
-          <t>Ing - PaH
-1º e 2º tempos</t>
-        </is>
-      </c>
-      <c r="F45" s="283" t="n"/>
+      <c r="E45" s="283" t="n"/>
+      <c r="F45" s="283" t="inlineStr">
+        <is>
+          <t>Fis - Cadu
+2º e 3º tempos</t>
+        </is>
+      </c>
       <c r="G45" s="283" t="n"/>
-      <c r="H45" s="283" t="n"/>
+      <c r="H45" s="283" t="inlineStr">
+        <is>
+          <t>LP/LIT/RED - AMu/Deb
+3º ao 5º tempos</t>
+        </is>
+      </c>
       <c r="I45" s="357" t="inlineStr">
         <is>
           <t>2CH

--- a/Horario desenvolvido/Proposta_2_Calendario_Provas_2026_2SEM.xlsx
+++ b/Horario desenvolvido/Proposta_2_Calendario_Provas_2026_2SEM.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" tabRatio="600" firstSheet="2" activeTab="5" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Planungshilfe 1.Sem" sheetId="1" state="hidden" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Planungshilfe 2.Sem" sheetId="2" state="hidden" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="9C1" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="9C2" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10C1" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10C2" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11C1" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11C2" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12C1" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12C2" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tabelle1" sheetId="11" state="hidden" r:id="rId11"/>
+    <sheet name="Planungshilfe 1.Sem" sheetId="1" state="hidden" r:id="rId1"/>
+    <sheet name="Planungshilfe 2.Sem" sheetId="2" state="hidden" r:id="rId2"/>
+    <sheet name="9C1" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="9C2" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="10C1" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="10C2" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="11C1" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="11C2" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="12C1" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="12C2" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Tabelle1" sheetId="11" state="hidden" r:id="rId11"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Planungshilfe 1.Sem'!$A$1:$K$65</definedName>
@@ -2929,6 +2929,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="54" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="71" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="51" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
@@ -2951,9 +2954,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -5367,24 +5367,24 @@
         <f>B9+4</f>
         <v/>
       </c>
-      <c r="E9" s="183" t="inlineStr">
-        <is>
-          <t>Qui - CAl/Fab
+      <c r="E9" s="183" t="n"/>
+      <c r="F9" s="183" t="inlineStr">
+        <is>
+          <t>Fis - Cadu
 1º e 2º tempos</t>
         </is>
       </c>
-      <c r="F9" s="183" t="inlineStr">
-        <is>
-          <t>GL - CBu-EFr-Eth
-5º e 6º tempos</t>
-        </is>
-      </c>
       <c r="G9" s="183" t="n"/>
-      <c r="H9" s="183" t="n"/>
+      <c r="H9" s="183" t="inlineStr">
+        <is>
+          <t>Mat - Bre/JJ
+4º e 5º tempos</t>
+        </is>
+      </c>
       <c r="I9" s="183" t="inlineStr">
         <is>
-          <t>LP/LIT/RED - AMu/Deb
-2º ao 4º tempos</t>
+          <t>Geo - Mar
+2º e 3º tempos</t>
         </is>
       </c>
       <c r="J9" s="183" t="n"/>
@@ -5466,7 +5466,7 @@
       </c>
       <c r="E12" s="11" t="inlineStr">
         <is>
-          <t>Ing - Isb
+          <t>DaF - CBu-EFr-Eth
 4º e 5º tempos</t>
         </is>
       </c>
@@ -5475,8 +5475,8 @@
       <c r="H12" s="11" t="n"/>
       <c r="I12" s="11" t="inlineStr">
         <is>
-          <t>Geo - Mar
-2º e 3º tempos</t>
+          <t>Hist - Wag
+1º e 2º tempos</t>
         </is>
       </c>
       <c r="J12" s="183" t="n"/>
@@ -5537,8 +5537,8 @@
       </c>
       <c r="E15" s="11" t="inlineStr">
         <is>
-          <t>DaF - CBu-EFr-Eth
-3º e 4º tempos</t>
+          <t>Ing - Isb
+4º e 5º tempos</t>
         </is>
       </c>
       <c r="F15" s="11" t="inlineStr">
@@ -5549,7 +5549,12 @@
       </c>
       <c r="G15" s="11" t="n"/>
       <c r="H15" s="11" t="n"/>
-      <c r="I15" s="11" t="n"/>
+      <c r="I15" s="11" t="inlineStr">
+        <is>
+          <t>LP/LIT/RED - AMu/Deb
+1º ao 3º tempos</t>
+        </is>
+      </c>
       <c r="J15" s="183" t="n"/>
       <c r="L15" s="17" t="n"/>
       <c r="M15" s="15" t="n"/>
@@ -5609,25 +5614,20 @@
           <t>unterrichtsfrei sem aula</t>
         </is>
       </c>
-      <c r="F18" s="11" t="inlineStr">
-        <is>
-          <t>Fis - Cadu
-1º e 2º tempos</t>
-        </is>
-      </c>
-      <c r="G18" s="11" t="inlineStr">
-        <is>
-          <t>Hist - Wag
-1º e 2º tempos</t>
-        </is>
-      </c>
+      <c r="F18" s="11" t="n"/>
+      <c r="G18" s="11" t="n"/>
       <c r="H18" s="11" t="inlineStr">
         <is>
-          <t>Mat - Bre/JJ
-3º e 4º tempos</t>
-        </is>
-      </c>
-      <c r="I18" s="350" t="n"/>
+          <t>GL - CBu-EFr-Eth
+9º e 10º tempos</t>
+        </is>
+      </c>
+      <c r="I18" s="350" t="inlineStr">
+        <is>
+          <t>Qui - CAl/Fab
+4º e 5º tempos</t>
+        </is>
+      </c>
       <c r="J18" s="262" t="inlineStr">
         <is>
           <t>2CH 9,10,11,12</t>
@@ -5770,21 +5770,21 @@
         <f>B24+4</f>
         <v/>
       </c>
-      <c r="E24" s="283" t="inlineStr">
-        <is>
-          <t>Qui - CAl/Fab
-1º e 2º tempos</t>
-        </is>
-      </c>
+      <c r="E24" s="283" t="n"/>
       <c r="F24" s="283" t="n"/>
-      <c r="G24" s="362" t="inlineStr">
-        <is>
-          <t>Fil - LAn
-4º tempo</t>
-        </is>
-      </c>
-      <c r="H24" s="283" t="n"/>
-      <c r="I24" s="78" t="n"/>
+      <c r="G24" s="79" t="n"/>
+      <c r="H24" s="283" t="inlineStr">
+        <is>
+          <t>Mat - Bre/JJ
+4º e 5º tempos</t>
+        </is>
+      </c>
+      <c r="I24" s="78" t="inlineStr">
+        <is>
+          <t>Geo - Mar
+2º e 3º tempos</t>
+        </is>
+      </c>
       <c r="J24" s="265" t="n"/>
       <c r="L24" s="318" t="inlineStr">
         <is>
@@ -5798,13 +5798,13 @@
       <c r="A25" s="316" t="n"/>
       <c r="B25" s="313" t="n"/>
       <c r="C25" s="313" t="n"/>
-      <c r="D25" s="353" t="n"/>
+      <c r="D25" s="354" t="n"/>
       <c r="E25" s="283" t="n"/>
       <c r="F25" s="283" t="n"/>
       <c r="G25" s="79" t="n"/>
       <c r="H25" s="283" t="n"/>
       <c r="I25" s="78" t="n"/>
-      <c r="J25" s="354" t="n"/>
+      <c r="J25" s="355" t="n"/>
       <c r="L25" s="44" t="n"/>
       <c r="M25" s="321" t="inlineStr">
         <is>
@@ -5817,13 +5817,13 @@
       <c r="A26" s="316" t="n"/>
       <c r="B26" s="313" t="n"/>
       <c r="C26" s="313" t="n"/>
-      <c r="D26" s="353" t="n"/>
+      <c r="D26" s="354" t="n"/>
       <c r="E26" s="283" t="n"/>
       <c r="F26" s="283" t="n"/>
       <c r="G26" s="79" t="n"/>
       <c r="H26" s="283" t="n"/>
       <c r="I26" s="78" t="n"/>
-      <c r="J26" s="354" t="n"/>
+      <c r="J26" s="355" t="n"/>
       <c r="L26" s="43" t="n"/>
       <c r="M26" s="323" t="inlineStr">
         <is>
@@ -5850,20 +5850,15 @@
         <f>B27+4</f>
         <v/>
       </c>
-      <c r="E27" s="78" t="inlineStr">
-        <is>
-          <t>Geo - Mar
-1º e 2º tempos</t>
-        </is>
-      </c>
-      <c r="F27" s="283" t="inlineStr">
-        <is>
-          <t>Bio - Ale
-2º e 3º tempos</t>
-        </is>
-      </c>
+      <c r="E27" s="78" t="n"/>
+      <c r="F27" s="283" t="n"/>
       <c r="G27" s="283" t="n"/>
-      <c r="H27" s="283" t="n"/>
+      <c r="H27" s="283" t="inlineStr">
+        <is>
+          <t>GL - CBu-EFr-Eth
+9º e 10º tempos</t>
+        </is>
+      </c>
       <c r="I27" s="283" t="n"/>
       <c r="J27" s="265" t="n"/>
       <c r="L27" s="45" t="n"/>
@@ -5878,13 +5873,13 @@
       <c r="A28" s="316" t="n"/>
       <c r="B28" s="313" t="n"/>
       <c r="C28" s="313" t="n"/>
-      <c r="D28" s="353" t="n"/>
+      <c r="D28" s="354" t="n"/>
       <c r="E28" s="78" t="n"/>
       <c r="F28" s="283" t="n"/>
       <c r="G28" s="283" t="n"/>
       <c r="H28" s="283" t="n"/>
       <c r="I28" s="283" t="n"/>
-      <c r="J28" s="354" t="n"/>
+      <c r="J28" s="355" t="n"/>
       <c r="L28" s="23" t="n"/>
       <c r="M28" s="325" t="inlineStr">
         <is>
@@ -5897,13 +5892,13 @@
       <c r="A29" s="316" t="n"/>
       <c r="B29" s="313" t="n"/>
       <c r="C29" s="313" t="n"/>
-      <c r="D29" s="353" t="n"/>
+      <c r="D29" s="354" t="n"/>
       <c r="E29" s="78" t="n"/>
       <c r="F29" s="283" t="n"/>
       <c r="G29" s="283" t="n"/>
       <c r="H29" s="283" t="n"/>
       <c r="I29" s="283" t="n"/>
-      <c r="J29" s="354" t="n"/>
+      <c r="J29" s="355" t="n"/>
       <c r="L29" s="46" t="n"/>
       <c r="M29" s="157" t="inlineStr">
         <is>
@@ -5939,7 +5934,12 @@
       <c r="F30" s="283" t="n"/>
       <c r="G30" s="283" t="n"/>
       <c r="H30" s="283" t="n"/>
-      <c r="I30" s="283" t="n"/>
+      <c r="I30" s="283" t="inlineStr">
+        <is>
+          <t>LP/LIT/RED - AMu/Deb
+1º ao 3º tempos</t>
+        </is>
+      </c>
       <c r="J30" s="183" t="inlineStr">
         <is>
           <t>unterrichtsfrei sem aula</t>
@@ -5957,7 +5957,7 @@
       <c r="A31" s="316" t="n"/>
       <c r="B31" s="313" t="n"/>
       <c r="C31" s="313" t="n"/>
-      <c r="D31" s="353" t="n"/>
+      <c r="D31" s="354" t="n"/>
       <c r="E31" s="283" t="n"/>
       <c r="F31" s="283" t="n"/>
       <c r="G31" s="283" t="n"/>
@@ -5976,7 +5976,7 @@
       <c r="A32" s="316" t="n"/>
       <c r="B32" s="313" t="n"/>
       <c r="C32" s="313" t="n"/>
-      <c r="D32" s="353" t="n"/>
+      <c r="D32" s="354" t="n"/>
       <c r="E32" s="283" t="n"/>
       <c r="F32" s="283" t="n"/>
       <c r="G32" s="283" t="n"/>
@@ -6046,7 +6046,7 @@
     <row r="34" ht="26.25" customFormat="1" customHeight="1" s="4">
       <c r="A34" s="330" t="n"/>
       <c r="B34" s="331" t="n"/>
-      <c r="D34" s="355" t="n"/>
+      <c r="D34" s="356" t="n"/>
       <c r="E34" s="315" t="n"/>
       <c r="F34" s="315" t="n"/>
       <c r="G34" s="315" t="n"/>
@@ -6068,7 +6068,7 @@
     <row r="35" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A35" s="330" t="n"/>
       <c r="B35" s="332" t="n"/>
-      <c r="D35" s="356" t="n"/>
+      <c r="D35" s="357" t="n"/>
       <c r="E35" s="315" t="n"/>
       <c r="F35" s="315" t="n"/>
       <c r="G35" s="315" t="n"/>
@@ -6106,15 +6106,20 @@
         <v/>
       </c>
       <c r="E36" s="283" t="n"/>
-      <c r="F36" s="283" t="n"/>
-      <c r="G36" s="283" t="inlineStr">
+      <c r="F36" s="283" t="inlineStr">
+        <is>
+          <t>Fis - Cadu
+1º e 2º tempos</t>
+        </is>
+      </c>
+      <c r="G36" s="283" t="n"/>
+      <c r="H36" s="283" t="n"/>
+      <c r="I36" s="283" t="inlineStr">
         <is>
           <t>Hist - Wag
 1º e 2º tempos</t>
         </is>
       </c>
-      <c r="H36" s="283" t="n"/>
-      <c r="I36" s="283" t="n"/>
       <c r="J36" s="265" t="n"/>
       <c r="L36" s="81" t="inlineStr">
         <is>
@@ -6131,13 +6136,13 @@
       <c r="A37" s="316" t="n"/>
       <c r="B37" s="313" t="n"/>
       <c r="C37" s="313" t="n"/>
-      <c r="D37" s="353" t="n"/>
+      <c r="D37" s="354" t="n"/>
       <c r="E37" s="283" t="n"/>
       <c r="F37" s="283" t="n"/>
       <c r="G37" s="283" t="n"/>
       <c r="H37" s="283" t="n"/>
       <c r="I37" s="283" t="n"/>
-      <c r="J37" s="354" t="n"/>
+      <c r="J37" s="355" t="n"/>
       <c r="L37" s="4" t="inlineStr">
         <is>
           <t>18.08,19.08</t>
@@ -6153,13 +6158,13 @@
       <c r="A38" s="316" t="n"/>
       <c r="B38" s="313" t="n"/>
       <c r="C38" s="313" t="n"/>
-      <c r="D38" s="353" t="n"/>
+      <c r="D38" s="354" t="n"/>
       <c r="E38" s="283" t="n"/>
       <c r="F38" s="283" t="n"/>
       <c r="G38" s="283" t="n"/>
       <c r="H38" s="283" t="n"/>
       <c r="I38" s="283" t="n"/>
-      <c r="J38" s="354" t="n"/>
+      <c r="J38" s="355" t="n"/>
     </row>
     <row r="39" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A39" s="119">
@@ -6181,17 +6186,17 @@
       </c>
       <c r="E39" s="283" t="inlineStr">
         <is>
-          <t>Mat - Bre/JJ
+          <t>DaF - CBu-EFr-Eth
+4º e 5º tempos</t>
+        </is>
+      </c>
+      <c r="F39" s="283" t="inlineStr">
+        <is>
+          <t>Bio - Ale
 2º e 3º tempos</t>
         </is>
       </c>
-      <c r="F39" s="283" t="n"/>
-      <c r="G39" s="283" t="inlineStr">
-        <is>
-          <t>Soc - Kle
-6º tempo</t>
-        </is>
-      </c>
+      <c r="G39" s="283" t="n"/>
       <c r="H39" s="283" t="n"/>
       <c r="I39" s="283" t="n"/>
       <c r="J39" s="265" t="n"/>
@@ -6200,25 +6205,25 @@
       <c r="A40" s="316" t="n"/>
       <c r="B40" s="313" t="n"/>
       <c r="C40" s="313" t="n"/>
-      <c r="D40" s="353" t="n"/>
+      <c r="D40" s="354" t="n"/>
       <c r="E40" s="283" t="n"/>
       <c r="F40" s="283" t="n"/>
       <c r="G40" s="283" t="n"/>
       <c r="H40" s="283" t="n"/>
       <c r="I40" s="283" t="n"/>
-      <c r="J40" s="354" t="n"/>
+      <c r="J40" s="355" t="n"/>
     </row>
     <row r="41" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A41" s="316" t="n"/>
       <c r="B41" s="313" t="n"/>
       <c r="C41" s="313" t="n"/>
-      <c r="D41" s="353" t="n"/>
+      <c r="D41" s="354" t="n"/>
       <c r="E41" s="283" t="n"/>
       <c r="F41" s="283" t="n"/>
       <c r="G41" s="283" t="n"/>
       <c r="H41" s="283" t="n"/>
       <c r="I41" s="283" t="n"/>
-      <c r="J41" s="354" t="n"/>
+      <c r="J41" s="355" t="n"/>
     </row>
     <row r="42" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A42" s="119">
@@ -6239,20 +6244,15 @@
         <v/>
       </c>
       <c r="E42" s="283" t="n"/>
-      <c r="F42" s="283" t="inlineStr">
-        <is>
-          <t>GL - CBu-EFr-Eth
-5º e 6º tempos</t>
-        </is>
-      </c>
-      <c r="G42" s="283" t="n"/>
+      <c r="F42" s="283" t="n"/>
+      <c r="G42" s="283" t="inlineStr">
+        <is>
+          <t>Fil - LAn
+4º tempo</t>
+        </is>
+      </c>
       <c r="H42" s="283" t="n"/>
-      <c r="I42" s="283" t="inlineStr">
-        <is>
-          <t>LP/LIT/RED - AMu/Deb
-2º ao 4º tempos</t>
-        </is>
-      </c>
+      <c r="I42" s="283" t="n"/>
       <c r="J42" s="265" t="n"/>
       <c r="L42" s="259" t="inlineStr">
         <is>
@@ -6265,26 +6265,26 @@
       <c r="A43" s="316" t="n"/>
       <c r="B43" s="313" t="n"/>
       <c r="C43" s="313" t="n"/>
-      <c r="D43" s="353" t="n"/>
+      <c r="D43" s="354" t="n"/>
       <c r="E43" s="283" t="n"/>
       <c r="F43" s="283" t="n"/>
       <c r="G43" s="283" t="n"/>
       <c r="H43" s="283" t="n"/>
       <c r="I43" s="283" t="n"/>
-      <c r="J43" s="354" t="n"/>
+      <c r="J43" s="355" t="n"/>
       <c r="L43" s="331" t="n"/>
     </row>
     <row r="44" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A44" s="316" t="n"/>
       <c r="B44" s="313" t="n"/>
       <c r="C44" s="313" t="n"/>
-      <c r="D44" s="353" t="n"/>
+      <c r="D44" s="354" t="n"/>
       <c r="E44" s="283" t="n"/>
       <c r="F44" s="283" t="n"/>
       <c r="G44" s="283" t="n"/>
       <c r="H44" s="283" t="n"/>
       <c r="I44" s="283" t="n"/>
-      <c r="J44" s="354" t="n"/>
+      <c r="J44" s="355" t="n"/>
       <c r="L44" s="331" t="n"/>
     </row>
     <row r="45" ht="18" customFormat="1" customHeight="1" s="4">
@@ -6307,19 +6307,19 @@
       </c>
       <c r="E45" s="283" t="inlineStr">
         <is>
-          <t>DaF - CBu-EFr-Eth
-3º e 4º tempos</t>
-        </is>
-      </c>
-      <c r="F45" s="283" t="inlineStr">
-        <is>
-          <t>Fis - Cadu
+          <t>Qui - CAl/Fab
 1º e 2º tempos</t>
         </is>
       </c>
-      <c r="G45" s="283" t="n"/>
+      <c r="F45" s="283" t="n"/>
+      <c r="G45" s="283" t="inlineStr">
+        <is>
+          <t>Soc - Kle
+2º tempo</t>
+        </is>
+      </c>
       <c r="H45" s="283" t="n"/>
-      <c r="I45" s="357" t="inlineStr">
+      <c r="I45" s="358" t="inlineStr">
         <is>
           <t>2CH
 10,12</t>
@@ -6332,26 +6332,26 @@
       <c r="A46" s="316" t="n"/>
       <c r="B46" s="313" t="n"/>
       <c r="C46" s="313" t="n"/>
-      <c r="D46" s="353" t="n"/>
+      <c r="D46" s="354" t="n"/>
       <c r="E46" s="283" t="n"/>
       <c r="F46" s="283" t="n"/>
       <c r="G46" s="283" t="n"/>
       <c r="H46" s="283" t="n"/>
-      <c r="I46" s="358" t="n"/>
-      <c r="J46" s="354" t="n"/>
+      <c r="I46" s="359" t="n"/>
+      <c r="J46" s="355" t="n"/>
       <c r="L46" s="331" t="n"/>
     </row>
     <row r="47" ht="51" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A47" s="316" t="n"/>
       <c r="B47" s="313" t="n"/>
       <c r="C47" s="313" t="n"/>
-      <c r="D47" s="353" t="n"/>
+      <c r="D47" s="354" t="n"/>
       <c r="E47" s="283" t="n"/>
       <c r="F47" s="283" t="n"/>
       <c r="G47" s="283" t="n"/>
       <c r="H47" s="283" t="n"/>
-      <c r="I47" s="359" t="n"/>
-      <c r="J47" s="354" t="n"/>
+      <c r="I47" s="360" t="n"/>
+      <c r="J47" s="355" t="n"/>
       <c r="L47" s="332" t="n"/>
     </row>
     <row r="48" ht="23.25" customFormat="1" customHeight="1" s="4">
@@ -6373,7 +6373,7 @@
         <v/>
       </c>
       <c r="E48" s="283" t="n"/>
-      <c r="F48" s="360" t="inlineStr">
+      <c r="F48" s="361" t="inlineStr">
         <is>
           <t>CC
 10,12</t>
@@ -6392,25 +6392,25 @@
       <c r="A49" s="316" t="n"/>
       <c r="B49" s="313" t="n"/>
       <c r="C49" s="313" t="n"/>
-      <c r="D49" s="353" t="n"/>
+      <c r="D49" s="354" t="n"/>
       <c r="E49" s="283" t="n"/>
-      <c r="F49" s="358" t="n"/>
+      <c r="F49" s="359" t="n"/>
       <c r="G49" s="283" t="n"/>
       <c r="H49" s="283" t="n"/>
       <c r="I49" s="315" t="n"/>
-      <c r="J49" s="354" t="n"/>
+      <c r="J49" s="355" t="n"/>
     </row>
     <row r="50" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A50" s="316" t="n"/>
       <c r="B50" s="313" t="n"/>
       <c r="C50" s="313" t="n"/>
-      <c r="D50" s="353" t="n"/>
+      <c r="D50" s="354" t="n"/>
       <c r="E50" s="78" t="n"/>
-      <c r="F50" s="359" t="n"/>
+      <c r="F50" s="360" t="n"/>
       <c r="G50" s="283" t="n"/>
       <c r="H50" s="283" t="n"/>
       <c r="I50" s="315" t="n"/>
-      <c r="J50" s="354" t="n"/>
+      <c r="J50" s="355" t="n"/>
     </row>
     <row r="51" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A51" s="119">
@@ -6434,32 +6434,32 @@
       <c r="F51" s="183" t="n"/>
       <c r="G51" s="183" t="n"/>
       <c r="H51" s="183" t="n"/>
-      <c r="I51" s="357" t="n"/>
+      <c r="I51" s="358" t="n"/>
       <c r="J51" s="274" t="n"/>
     </row>
     <row r="52" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A52" s="316" t="n"/>
       <c r="B52" s="313" t="n"/>
       <c r="C52" s="313" t="n"/>
-      <c r="D52" s="353" t="n"/>
+      <c r="D52" s="354" t="n"/>
       <c r="E52" s="283" t="n"/>
       <c r="F52" s="315" t="n"/>
       <c r="G52" s="315" t="n"/>
       <c r="H52" s="315" t="n"/>
-      <c r="I52" s="358" t="n"/>
-      <c r="J52" s="354" t="n"/>
+      <c r="I52" s="359" t="n"/>
+      <c r="J52" s="355" t="n"/>
     </row>
     <row r="53" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A53" s="316" t="n"/>
       <c r="B53" s="313" t="n"/>
       <c r="C53" s="313" t="n"/>
-      <c r="D53" s="353" t="n"/>
+      <c r="D53" s="354" t="n"/>
       <c r="E53" s="283" t="n"/>
       <c r="F53" s="315" t="n"/>
       <c r="G53" s="315" t="n"/>
       <c r="H53" s="315" t="n"/>
-      <c r="I53" s="359" t="n"/>
-      <c r="J53" s="354" t="n"/>
+      <c r="I53" s="360" t="n"/>
+      <c r="J53" s="355" t="n"/>
     </row>
     <row r="54" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A54" s="119">
@@ -6490,25 +6490,25 @@
       <c r="A55" s="316" t="n"/>
       <c r="B55" s="313" t="n"/>
       <c r="C55" s="313" t="n"/>
-      <c r="D55" s="353" t="n"/>
+      <c r="D55" s="354" t="n"/>
       <c r="E55" s="315" t="n"/>
       <c r="F55" s="315" t="n"/>
       <c r="G55" s="315" t="n"/>
       <c r="H55" s="315" t="n"/>
       <c r="I55" s="315" t="n"/>
-      <c r="J55" s="354" t="n"/>
+      <c r="J55" s="355" t="n"/>
     </row>
     <row r="56" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A56" s="316" t="n"/>
       <c r="B56" s="313" t="n"/>
       <c r="C56" s="313" t="n"/>
-      <c r="D56" s="353" t="n"/>
+      <c r="D56" s="354" t="n"/>
       <c r="E56" s="315" t="n"/>
       <c r="F56" s="315" t="n"/>
       <c r="G56" s="315" t="n"/>
       <c r="H56" s="315" t="n"/>
       <c r="I56" s="315" t="n"/>
-      <c r="J56" s="354" t="n"/>
+      <c r="J56" s="355" t="n"/>
     </row>
     <row r="57" ht="25.5" customFormat="1" customHeight="1" s="4">
       <c r="A57" s="119">
@@ -6529,7 +6529,7 @@
         <v/>
       </c>
       <c r="E57" s="183" t="n"/>
-      <c r="F57" s="360" t="n"/>
+      <c r="F57" s="361" t="n"/>
       <c r="G57" s="183" t="n"/>
       <c r="H57" s="183" t="n"/>
       <c r="I57" s="183" t="n"/>
@@ -6539,25 +6539,25 @@
       <c r="A58" s="316" t="n"/>
       <c r="B58" s="313" t="n"/>
       <c r="C58" s="313" t="n"/>
-      <c r="D58" s="353" t="n"/>
+      <c r="D58" s="354" t="n"/>
       <c r="E58" s="315" t="n"/>
-      <c r="F58" s="358" t="n"/>
+      <c r="F58" s="359" t="n"/>
       <c r="G58" s="315" t="n"/>
       <c r="H58" s="315" t="n"/>
       <c r="I58" s="315" t="n"/>
-      <c r="J58" s="354" t="n"/>
+      <c r="J58" s="355" t="n"/>
     </row>
     <row r="59" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A59" s="316" t="n"/>
       <c r="B59" s="313" t="n"/>
       <c r="C59" s="313" t="n"/>
-      <c r="D59" s="353" t="n"/>
+      <c r="D59" s="354" t="n"/>
       <c r="E59" s="315" t="n"/>
-      <c r="F59" s="359" t="n"/>
+      <c r="F59" s="360" t="n"/>
       <c r="G59" s="315" t="n"/>
       <c r="H59" s="315" t="n"/>
       <c r="I59" s="315" t="n"/>
-      <c r="J59" s="354" t="n"/>
+      <c r="J59" s="355" t="n"/>
     </row>
     <row r="60" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A60" s="281">
@@ -6589,24 +6589,24 @@
       <c r="B61" s="331" t="n"/>
       <c r="C61" s="331" t="n"/>
       <c r="D61" s="331" t="n"/>
-      <c r="E61" s="358" t="n"/>
-      <c r="F61" s="358" t="n"/>
-      <c r="G61" s="358" t="n"/>
-      <c r="H61" s="358" t="n"/>
-      <c r="I61" s="358" t="n"/>
-      <c r="J61" s="358" t="n"/>
+      <c r="E61" s="359" t="n"/>
+      <c r="F61" s="359" t="n"/>
+      <c r="G61" s="359" t="n"/>
+      <c r="H61" s="359" t="n"/>
+      <c r="I61" s="359" t="n"/>
+      <c r="J61" s="359" t="n"/>
     </row>
     <row r="62" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A62" s="332" t="n"/>
       <c r="B62" s="332" t="n"/>
       <c r="C62" s="332" t="n"/>
       <c r="D62" s="332" t="n"/>
-      <c r="E62" s="361" t="n"/>
-      <c r="F62" s="361" t="n"/>
-      <c r="G62" s="361" t="n"/>
-      <c r="H62" s="361" t="n"/>
-      <c r="I62" s="361" t="n"/>
-      <c r="J62" s="361" t="n"/>
+      <c r="E62" s="362" t="n"/>
+      <c r="F62" s="362" t="n"/>
+      <c r="G62" s="362" t="n"/>
+      <c r="H62" s="362" t="n"/>
+      <c r="I62" s="362" t="n"/>
+      <c r="J62" s="362" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="146">
@@ -8587,20 +8587,20 @@
         <f>B9+4</f>
         <v/>
       </c>
-      <c r="E9" s="183" t="inlineStr">
-        <is>
-          <t>GL - Caro-EFr-Eth
-5º e 6º tempos</t>
-        </is>
-      </c>
-      <c r="F9" s="183" t="inlineStr">
-        <is>
-          <t>Mat - BrSa
-2º e 3º tempos</t>
-        </is>
-      </c>
-      <c r="G9" s="183" t="n"/>
-      <c r="H9" s="183" t="n"/>
+      <c r="E9" s="183" t="n"/>
+      <c r="F9" s="183" t="n"/>
+      <c r="G9" s="183" t="inlineStr">
+        <is>
+          <t>Geo - Mar
+6º e 7º tempos</t>
+        </is>
+      </c>
+      <c r="H9" s="183" t="inlineStr">
+        <is>
+          <t>DaF - Caro-SGa-EFr
+1º e 2º tempos</t>
+        </is>
+      </c>
       <c r="I9" s="183" t="n"/>
       <c r="J9" s="183" t="n"/>
       <c r="L9" s="16" t="inlineStr">
@@ -8679,26 +8679,21 @@
         <f>B12+4</f>
         <v/>
       </c>
-      <c r="E12" s="11" t="inlineStr">
-        <is>
-          <t>Geo - Mar
-1º e 2º tempos</t>
-        </is>
-      </c>
-      <c r="F12" s="11" t="inlineStr">
-        <is>
-          <t>Hist - JuLa
-3º e 4º tempos</t>
-        </is>
-      </c>
+      <c r="E12" s="11" t="n"/>
+      <c r="F12" s="11" t="n"/>
       <c r="G12" s="11" t="inlineStr">
         <is>
-          <t>DaF - Caro-SGa-EFr
-1º e 2º tempos</t>
+          <t>Port - Jana
+4º e 5º tempos</t>
         </is>
       </c>
       <c r="H12" s="11" t="n"/>
-      <c r="I12" s="11" t="n"/>
+      <c r="I12" s="11" t="inlineStr">
+        <is>
+          <t>GL - Caro-EFr-Eth
+4º e 5º tempos</t>
+        </is>
+      </c>
       <c r="J12" s="183" t="n"/>
       <c r="L12" s="15" t="n"/>
       <c r="M12" s="15" t="n"/>
@@ -8755,21 +8750,21 @@
         <f>B15+4</f>
         <v/>
       </c>
-      <c r="E15" s="11" t="inlineStr">
+      <c r="E15" s="11" t="n"/>
+      <c r="F15" s="11" t="inlineStr">
+        <is>
+          <t>Hist - JuLa
+4º e 5º tempos</t>
+        </is>
+      </c>
+      <c r="G15" s="11" t="n"/>
+      <c r="H15" s="11" t="n"/>
+      <c r="I15" s="11" t="inlineStr">
         <is>
           <t>Ing - APa-PaH-Velo
 2º e 3º tempos</t>
         </is>
       </c>
-      <c r="F15" s="11" t="n"/>
-      <c r="G15" s="11" t="n"/>
-      <c r="H15" s="11" t="inlineStr">
-        <is>
-          <t>Redação - Raf
-5º e 6º tempos</t>
-        </is>
-      </c>
-      <c r="I15" s="11" t="n"/>
       <c r="J15" s="183" t="n"/>
       <c r="L15" s="17" t="n"/>
       <c r="M15" s="15" t="n"/>
@@ -8829,14 +8824,19 @@
           <t>unterrichtsfrei sem aula</t>
         </is>
       </c>
-      <c r="F18" s="11" t="inlineStr">
-        <is>
-          <t>Port - Jana
-1º e 2º tempos</t>
-        </is>
-      </c>
-      <c r="G18" s="11" t="n"/>
-      <c r="H18" s="11" t="n"/>
+      <c r="F18" s="11" t="n"/>
+      <c r="G18" s="11" t="inlineStr">
+        <is>
+          <t>Mat - BrSa
+4º e 5º tempos</t>
+        </is>
+      </c>
+      <c r="H18" s="11" t="inlineStr">
+        <is>
+          <t>Redação - Raf
+4º e 5º tempos</t>
+        </is>
+      </c>
       <c r="I18" s="350" t="n"/>
       <c r="J18" s="262" t="inlineStr">
         <is>
@@ -8904,19 +8904,14 @@
         <v/>
       </c>
       <c r="E21" s="11" t="n"/>
-      <c r="F21" s="62" t="inlineStr">
-        <is>
-          <t>Mat - BrSa
-2º e 3º tempos</t>
-        </is>
-      </c>
-      <c r="G21" s="11" t="n"/>
-      <c r="H21" s="11" t="inlineStr">
-        <is>
-          <t>Fis - VSi
-7º tempo</t>
-        </is>
-      </c>
+      <c r="F21" s="62" t="n"/>
+      <c r="G21" s="11" t="inlineStr">
+        <is>
+          <t>Geo - Mar
+6º e 7º tempos</t>
+        </is>
+      </c>
+      <c r="H21" s="11" t="n"/>
       <c r="I21" s="11" t="n"/>
       <c r="J21" s="183" t="n"/>
       <c r="L21" s="80" t="inlineStr">
@@ -8980,14 +8975,14 @@
         <f>B24+4</f>
         <v/>
       </c>
-      <c r="E24" s="283" t="inlineStr">
-        <is>
-          <t>GL - Caro-EFr-Eth
-5º e 6º tempos</t>
-        </is>
-      </c>
+      <c r="E24" s="283" t="n"/>
       <c r="F24" s="283" t="n"/>
-      <c r="G24" s="79" t="n"/>
+      <c r="G24" s="353" t="inlineStr">
+        <is>
+          <t>Port - Jana
+4º e 5º tempos</t>
+        </is>
+      </c>
       <c r="H24" s="283" t="n"/>
       <c r="I24" s="78" t="n"/>
       <c r="J24" s="265" t="n"/>
@@ -9003,13 +8998,13 @@
       <c r="A25" s="316" t="n"/>
       <c r="B25" s="313" t="n"/>
       <c r="C25" s="313" t="n"/>
-      <c r="D25" s="353" t="n"/>
+      <c r="D25" s="354" t="n"/>
       <c r="E25" s="283" t="n"/>
       <c r="F25" s="283" t="n"/>
       <c r="G25" s="79" t="n"/>
       <c r="H25" s="283" t="n"/>
       <c r="I25" s="78" t="n"/>
-      <c r="J25" s="354" t="n"/>
+      <c r="J25" s="355" t="n"/>
       <c r="L25" s="44" t="n"/>
       <c r="M25" s="321" t="inlineStr">
         <is>
@@ -9022,13 +9017,13 @@
       <c r="A26" s="316" t="n"/>
       <c r="B26" s="313" t="n"/>
       <c r="C26" s="313" t="n"/>
-      <c r="D26" s="353" t="n"/>
+      <c r="D26" s="354" t="n"/>
       <c r="E26" s="283" t="n"/>
       <c r="F26" s="283" t="n"/>
       <c r="G26" s="79" t="n"/>
       <c r="H26" s="283" t="n"/>
       <c r="I26" s="78" t="n"/>
-      <c r="J26" s="354" t="n"/>
+      <c r="J26" s="355" t="n"/>
       <c r="L26" s="43" t="n"/>
       <c r="M26" s="323" t="inlineStr">
         <is>
@@ -9055,15 +9050,15 @@
         <f>B27+4</f>
         <v/>
       </c>
-      <c r="E27" s="78" t="inlineStr">
-        <is>
-          <t>Ing - APa-PaH-Velo
-2º e 3º tempos</t>
-        </is>
-      </c>
+      <c r="E27" s="78" t="n"/>
       <c r="F27" s="283" t="n"/>
       <c r="G27" s="283" t="n"/>
-      <c r="H27" s="283" t="n"/>
+      <c r="H27" s="283" t="inlineStr">
+        <is>
+          <t>DaF - Caro-SGa-EFr
+1º e 2º tempos</t>
+        </is>
+      </c>
       <c r="I27" s="283" t="inlineStr">
         <is>
           <t>AG9
@@ -9083,13 +9078,13 @@
       <c r="A28" s="316" t="n"/>
       <c r="B28" s="313" t="n"/>
       <c r="C28" s="313" t="n"/>
-      <c r="D28" s="353" t="n"/>
+      <c r="D28" s="354" t="n"/>
       <c r="E28" s="78" t="n"/>
       <c r="F28" s="283" t="n"/>
       <c r="G28" s="283" t="n"/>
       <c r="H28" s="283" t="n"/>
       <c r="I28" s="283" t="n"/>
-      <c r="J28" s="354" t="n"/>
+      <c r="J28" s="355" t="n"/>
       <c r="L28" s="23" t="n"/>
       <c r="M28" s="325" t="inlineStr">
         <is>
@@ -9102,13 +9097,13 @@
       <c r="A29" s="316" t="n"/>
       <c r="B29" s="313" t="n"/>
       <c r="C29" s="313" t="n"/>
-      <c r="D29" s="353" t="n"/>
+      <c r="D29" s="354" t="n"/>
       <c r="E29" s="78" t="n"/>
       <c r="F29" s="283" t="n"/>
       <c r="G29" s="283" t="n"/>
       <c r="H29" s="283" t="n"/>
       <c r="I29" s="283" t="n"/>
-      <c r="J29" s="354" t="n"/>
+      <c r="J29" s="355" t="n"/>
       <c r="L29" s="46" t="n"/>
       <c r="M29" s="157" t="inlineStr">
         <is>
@@ -9135,16 +9130,16 @@
         <f>B30+4</f>
         <v/>
       </c>
-      <c r="E30" s="283" t="n"/>
+      <c r="E30" s="283" t="inlineStr">
+        <is>
+          <t>Fis - VSi
+2º tempo</t>
+        </is>
+      </c>
       <c r="F30" s="283" t="n"/>
       <c r="G30" s="283" t="n"/>
       <c r="H30" s="283" t="n"/>
-      <c r="I30" s="283" t="inlineStr">
-        <is>
-          <t>Qui - Fab
-7º tempo</t>
-        </is>
-      </c>
+      <c r="I30" s="283" t="n"/>
       <c r="J30" s="183" t="inlineStr">
         <is>
           <t>unterrichtsfrei sem aula</t>
@@ -9162,7 +9157,7 @@
       <c r="A31" s="316" t="n"/>
       <c r="B31" s="313" t="n"/>
       <c r="C31" s="313" t="n"/>
-      <c r="D31" s="353" t="n"/>
+      <c r="D31" s="354" t="n"/>
       <c r="E31" s="283" t="n"/>
       <c r="F31" s="283" t="n"/>
       <c r="G31" s="283" t="n"/>
@@ -9181,7 +9176,7 @@
       <c r="A32" s="316" t="n"/>
       <c r="B32" s="313" t="n"/>
       <c r="C32" s="313" t="n"/>
-      <c r="D32" s="353" t="n"/>
+      <c r="D32" s="354" t="n"/>
       <c r="E32" s="283" t="n"/>
       <c r="F32" s="283" t="n"/>
       <c r="G32" s="283" t="n"/>
@@ -9251,7 +9246,7 @@
     <row r="34" ht="26.25" customFormat="1" customHeight="1" s="4">
       <c r="A34" s="330" t="n"/>
       <c r="B34" s="331" t="n"/>
-      <c r="D34" s="355" t="n"/>
+      <c r="D34" s="356" t="n"/>
       <c r="E34" s="315" t="n"/>
       <c r="F34" s="315" t="n"/>
       <c r="G34" s="315" t="n"/>
@@ -9273,7 +9268,7 @@
     <row r="35" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A35" s="330" t="n"/>
       <c r="B35" s="332" t="n"/>
-      <c r="D35" s="356" t="n"/>
+      <c r="D35" s="357" t="n"/>
       <c r="E35" s="315" t="n"/>
       <c r="F35" s="315" t="n"/>
       <c r="G35" s="315" t="n"/>
@@ -9310,16 +9305,21 @@
         <f>B36+4</f>
         <v/>
       </c>
-      <c r="E36" s="283" t="inlineStr">
-        <is>
-          <t>Geo - Mar
-1º e 2º tempos</t>
-        </is>
-      </c>
+      <c r="E36" s="283" t="n"/>
       <c r="F36" s="283" t="n"/>
-      <c r="G36" s="283" t="n"/>
+      <c r="G36" s="283" t="inlineStr">
+        <is>
+          <t>Mat - BrSa
+4º e 5º tempos</t>
+        </is>
+      </c>
       <c r="H36" s="283" t="n"/>
-      <c r="I36" s="283" t="n"/>
+      <c r="I36" s="283" t="inlineStr">
+        <is>
+          <t>GL - Caro-EFr-Eth
+4º e 5º tempos</t>
+        </is>
+      </c>
       <c r="J36" s="265" t="n"/>
       <c r="L36" s="81" t="inlineStr">
         <is>
@@ -9336,13 +9336,13 @@
       <c r="A37" s="316" t="n"/>
       <c r="B37" s="313" t="n"/>
       <c r="C37" s="313" t="n"/>
-      <c r="D37" s="353" t="n"/>
+      <c r="D37" s="354" t="n"/>
       <c r="E37" s="283" t="n"/>
       <c r="F37" s="283" t="n"/>
       <c r="G37" s="283" t="n"/>
       <c r="H37" s="283" t="n"/>
       <c r="I37" s="283" t="n"/>
-      <c r="J37" s="354" t="n"/>
+      <c r="J37" s="355" t="n"/>
       <c r="L37" s="4" t="inlineStr">
         <is>
           <t>18.08,19.08</t>
@@ -9358,13 +9358,13 @@
       <c r="A38" s="316" t="n"/>
       <c r="B38" s="313" t="n"/>
       <c r="C38" s="313" t="n"/>
-      <c r="D38" s="353" t="n"/>
+      <c r="D38" s="354" t="n"/>
       <c r="E38" s="283" t="n"/>
       <c r="F38" s="283" t="n"/>
       <c r="G38" s="283" t="n"/>
       <c r="H38" s="283" t="n"/>
       <c r="I38" s="283" t="n"/>
-      <c r="J38" s="354" t="n"/>
+      <c r="J38" s="355" t="n"/>
     </row>
     <row r="39" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A39" s="119">
@@ -9387,8 +9387,8 @@
       <c r="E39" s="283" t="n"/>
       <c r="F39" s="283" t="inlineStr">
         <is>
-          <t>Port - Jana
-1º e 2º tempos</t>
+          <t>Hist - JuLa
+4º e 5º tempos</t>
         </is>
       </c>
       <c r="G39" s="283" t="n"/>
@@ -9400,25 +9400,25 @@
       <c r="A40" s="316" t="n"/>
       <c r="B40" s="313" t="n"/>
       <c r="C40" s="313" t="n"/>
-      <c r="D40" s="353" t="n"/>
+      <c r="D40" s="354" t="n"/>
       <c r="E40" s="283" t="n"/>
       <c r="F40" s="283" t="n"/>
       <c r="G40" s="283" t="n"/>
       <c r="H40" s="283" t="n"/>
       <c r="I40" s="283" t="n"/>
-      <c r="J40" s="354" t="n"/>
+      <c r="J40" s="355" t="n"/>
     </row>
     <row r="41" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A41" s="316" t="n"/>
       <c r="B41" s="313" t="n"/>
       <c r="C41" s="313" t="n"/>
-      <c r="D41" s="353" t="n"/>
+      <c r="D41" s="354" t="n"/>
       <c r="E41" s="283" t="n"/>
       <c r="F41" s="283" t="n"/>
       <c r="G41" s="283" t="n"/>
       <c r="H41" s="283" t="n"/>
       <c r="I41" s="283" t="n"/>
-      <c r="J41" s="354" t="n"/>
+      <c r="J41" s="355" t="n"/>
     </row>
     <row r="42" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A42" s="119">
@@ -9441,13 +9441,13 @@
       <c r="E42" s="283" t="n"/>
       <c r="F42" s="283" t="n"/>
       <c r="G42" s="283" t="n"/>
-      <c r="H42" s="283" t="inlineStr">
-        <is>
-          <t>Redação - Raf
-5º e 6º tempos</t>
-        </is>
-      </c>
-      <c r="I42" s="283" t="n"/>
+      <c r="H42" s="283" t="n"/>
+      <c r="I42" s="283" t="inlineStr">
+        <is>
+          <t>Ing - APa-PaH-Velo
+2º e 3º tempos</t>
+        </is>
+      </c>
       <c r="J42" s="265" t="n"/>
       <c r="L42" s="259" t="inlineStr">
         <is>
@@ -9460,26 +9460,26 @@
       <c r="A43" s="316" t="n"/>
       <c r="B43" s="313" t="n"/>
       <c r="C43" s="313" t="n"/>
-      <c r="D43" s="353" t="n"/>
+      <c r="D43" s="354" t="n"/>
       <c r="E43" s="283" t="n"/>
       <c r="F43" s="283" t="n"/>
       <c r="G43" s="283" t="n"/>
       <c r="H43" s="283" t="n"/>
       <c r="I43" s="283" t="n"/>
-      <c r="J43" s="354" t="n"/>
+      <c r="J43" s="355" t="n"/>
       <c r="L43" s="331" t="n"/>
     </row>
     <row r="44" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A44" s="316" t="n"/>
       <c r="B44" s="313" t="n"/>
       <c r="C44" s="313" t="n"/>
-      <c r="D44" s="353" t="n"/>
+      <c r="D44" s="354" t="n"/>
       <c r="E44" s="283" t="n"/>
       <c r="F44" s="283" t="n"/>
       <c r="G44" s="283" t="n"/>
       <c r="H44" s="283" t="n"/>
       <c r="I44" s="283" t="n"/>
-      <c r="J44" s="354" t="n"/>
+      <c r="J44" s="355" t="n"/>
       <c r="L44" s="331" t="n"/>
     </row>
     <row r="45" ht="18" customFormat="1" customHeight="1" s="4">
@@ -9500,16 +9500,21 @@
         <f>B45+4</f>
         <v/>
       </c>
-      <c r="E45" s="283" t="n"/>
-      <c r="F45" s="283" t="inlineStr">
-        <is>
-          <t>Hist - JuLa
-3º e 4º tempos</t>
-        </is>
-      </c>
+      <c r="E45" s="283" t="inlineStr">
+        <is>
+          <t>Bio - Ale
+1º tempo</t>
+        </is>
+      </c>
+      <c r="F45" s="283" t="n"/>
       <c r="G45" s="283" t="n"/>
-      <c r="H45" s="283" t="n"/>
-      <c r="I45" s="357" t="n"/>
+      <c r="H45" s="283" t="inlineStr">
+        <is>
+          <t>Redação - Raf
+4º e 5º tempos</t>
+        </is>
+      </c>
+      <c r="I45" s="358" t="n"/>
       <c r="J45" s="269" t="n"/>
       <c r="L45" s="331" t="n"/>
     </row>
@@ -9517,26 +9522,26 @@
       <c r="A46" s="316" t="n"/>
       <c r="B46" s="313" t="n"/>
       <c r="C46" s="313" t="n"/>
-      <c r="D46" s="353" t="n"/>
+      <c r="D46" s="354" t="n"/>
       <c r="E46" s="283" t="n"/>
       <c r="F46" s="283" t="n"/>
       <c r="G46" s="283" t="n"/>
       <c r="H46" s="283" t="n"/>
-      <c r="I46" s="358" t="n"/>
-      <c r="J46" s="354" t="n"/>
+      <c r="I46" s="359" t="n"/>
+      <c r="J46" s="355" t="n"/>
       <c r="L46" s="331" t="n"/>
     </row>
     <row r="47" ht="51" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A47" s="316" t="n"/>
       <c r="B47" s="313" t="n"/>
       <c r="C47" s="313" t="n"/>
-      <c r="D47" s="353" t="n"/>
+      <c r="D47" s="354" t="n"/>
       <c r="E47" s="283" t="n"/>
       <c r="F47" s="283" t="n"/>
       <c r="G47" s="283" t="n"/>
       <c r="H47" s="283" t="n"/>
-      <c r="I47" s="359" t="n"/>
-      <c r="J47" s="354" t="n"/>
+      <c r="I47" s="360" t="n"/>
+      <c r="J47" s="355" t="n"/>
       <c r="L47" s="332" t="n"/>
     </row>
     <row r="48" ht="23.25" customFormat="1" customHeight="1" s="4">
@@ -9557,19 +9562,14 @@
         <f>B48+4</f>
         <v/>
       </c>
-      <c r="E48" s="283" t="inlineStr">
-        <is>
-          <t>Bio - Ale
-1º tempo</t>
-        </is>
-      </c>
-      <c r="F48" s="360" t="inlineStr">
-        <is>
-          <t>DaF - Caro-SGa-EFr
-1º e 2º tempos</t>
-        </is>
-      </c>
-      <c r="G48" s="283" t="n"/>
+      <c r="E48" s="283" t="n"/>
+      <c r="F48" s="361" t="n"/>
+      <c r="G48" s="283" t="inlineStr">
+        <is>
+          <t>Qui - Fab
+2º tempo</t>
+        </is>
+      </c>
       <c r="H48" s="283" t="n"/>
       <c r="I48" s="183" t="inlineStr">
         <is>
@@ -9582,25 +9582,25 @@
       <c r="A49" s="316" t="n"/>
       <c r="B49" s="313" t="n"/>
       <c r="C49" s="313" t="n"/>
-      <c r="D49" s="353" t="n"/>
+      <c r="D49" s="354" t="n"/>
       <c r="E49" s="283" t="n"/>
-      <c r="F49" s="358" t="n"/>
+      <c r="F49" s="359" t="n"/>
       <c r="G49" s="283" t="n"/>
       <c r="H49" s="283" t="n"/>
       <c r="I49" s="315" t="n"/>
-      <c r="J49" s="354" t="n"/>
+      <c r="J49" s="355" t="n"/>
     </row>
     <row r="50" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A50" s="316" t="n"/>
       <c r="B50" s="313" t="n"/>
       <c r="C50" s="313" t="n"/>
-      <c r="D50" s="353" t="n"/>
+      <c r="D50" s="354" t="n"/>
       <c r="E50" s="78" t="n"/>
-      <c r="F50" s="359" t="n"/>
+      <c r="F50" s="360" t="n"/>
       <c r="G50" s="283" t="n"/>
       <c r="H50" s="283" t="n"/>
       <c r="I50" s="315" t="n"/>
-      <c r="J50" s="354" t="n"/>
+      <c r="J50" s="355" t="n"/>
     </row>
     <row r="51" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A51" s="119">
@@ -9624,7 +9624,7 @@
       <c r="F51" s="183" t="n"/>
       <c r="G51" s="183" t="n"/>
       <c r="H51" s="183" t="n"/>
-      <c r="I51" s="357" t="inlineStr">
+      <c r="I51" s="358" t="inlineStr">
         <is>
           <t>2CH
 9,11</t>
@@ -9636,25 +9636,25 @@
       <c r="A52" s="316" t="n"/>
       <c r="B52" s="313" t="n"/>
       <c r="C52" s="313" t="n"/>
-      <c r="D52" s="353" t="n"/>
+      <c r="D52" s="354" t="n"/>
       <c r="E52" s="283" t="n"/>
       <c r="F52" s="315" t="n"/>
       <c r="G52" s="315" t="n"/>
       <c r="H52" s="315" t="n"/>
-      <c r="I52" s="358" t="n"/>
-      <c r="J52" s="354" t="n"/>
+      <c r="I52" s="359" t="n"/>
+      <c r="J52" s="355" t="n"/>
     </row>
     <row r="53" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A53" s="316" t="n"/>
       <c r="B53" s="313" t="n"/>
       <c r="C53" s="313" t="n"/>
-      <c r="D53" s="353" t="n"/>
+      <c r="D53" s="354" t="n"/>
       <c r="E53" s="283" t="n"/>
       <c r="F53" s="315" t="n"/>
       <c r="G53" s="315" t="n"/>
       <c r="H53" s="315" t="n"/>
-      <c r="I53" s="359" t="n"/>
-      <c r="J53" s="354" t="n"/>
+      <c r="I53" s="360" t="n"/>
+      <c r="J53" s="355" t="n"/>
     </row>
     <row r="54" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A54" s="119">
@@ -9685,25 +9685,25 @@
       <c r="A55" s="316" t="n"/>
       <c r="B55" s="313" t="n"/>
       <c r="C55" s="313" t="n"/>
-      <c r="D55" s="353" t="n"/>
+      <c r="D55" s="354" t="n"/>
       <c r="E55" s="315" t="n"/>
       <c r="F55" s="315" t="n"/>
       <c r="G55" s="315" t="n"/>
       <c r="H55" s="315" t="n"/>
       <c r="I55" s="315" t="n"/>
-      <c r="J55" s="354" t="n"/>
+      <c r="J55" s="355" t="n"/>
     </row>
     <row r="56" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A56" s="316" t="n"/>
       <c r="B56" s="313" t="n"/>
       <c r="C56" s="313" t="n"/>
-      <c r="D56" s="353" t="n"/>
+      <c r="D56" s="354" t="n"/>
       <c r="E56" s="315" t="n"/>
       <c r="F56" s="315" t="n"/>
       <c r="G56" s="315" t="n"/>
       <c r="H56" s="315" t="n"/>
       <c r="I56" s="315" t="n"/>
-      <c r="J56" s="354" t="n"/>
+      <c r="J56" s="355" t="n"/>
     </row>
     <row r="57" ht="25.5" customFormat="1" customHeight="1" s="4">
       <c r="A57" s="119">
@@ -9724,7 +9724,7 @@
         <v/>
       </c>
       <c r="E57" s="183" t="n"/>
-      <c r="F57" s="360" t="inlineStr">
+      <c r="F57" s="361" t="inlineStr">
         <is>
           <t>CC
 9,11</t>
@@ -9739,25 +9739,25 @@
       <c r="A58" s="316" t="n"/>
       <c r="B58" s="313" t="n"/>
       <c r="C58" s="313" t="n"/>
-      <c r="D58" s="353" t="n"/>
+      <c r="D58" s="354" t="n"/>
       <c r="E58" s="315" t="n"/>
-      <c r="F58" s="358" t="n"/>
+      <c r="F58" s="359" t="n"/>
       <c r="G58" s="315" t="n"/>
       <c r="H58" s="315" t="n"/>
       <c r="I58" s="315" t="n"/>
-      <c r="J58" s="354" t="n"/>
+      <c r="J58" s="355" t="n"/>
     </row>
     <row r="59" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A59" s="316" t="n"/>
       <c r="B59" s="313" t="n"/>
       <c r="C59" s="313" t="n"/>
-      <c r="D59" s="353" t="n"/>
+      <c r="D59" s="354" t="n"/>
       <c r="E59" s="315" t="n"/>
-      <c r="F59" s="359" t="n"/>
+      <c r="F59" s="360" t="n"/>
       <c r="G59" s="315" t="n"/>
       <c r="H59" s="315" t="n"/>
       <c r="I59" s="315" t="n"/>
-      <c r="J59" s="354" t="n"/>
+      <c r="J59" s="355" t="n"/>
     </row>
     <row r="60" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A60" s="281">
@@ -9789,24 +9789,24 @@
       <c r="B61" s="331" t="n"/>
       <c r="C61" s="331" t="n"/>
       <c r="D61" s="331" t="n"/>
-      <c r="E61" s="358" t="n"/>
-      <c r="F61" s="358" t="n"/>
-      <c r="G61" s="358" t="n"/>
-      <c r="H61" s="358" t="n"/>
-      <c r="I61" s="358" t="n"/>
-      <c r="J61" s="358" t="n"/>
+      <c r="E61" s="359" t="n"/>
+      <c r="F61" s="359" t="n"/>
+      <c r="G61" s="359" t="n"/>
+      <c r="H61" s="359" t="n"/>
+      <c r="I61" s="359" t="n"/>
+      <c r="J61" s="359" t="n"/>
     </row>
     <row r="62" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A62" s="332" t="n"/>
       <c r="B62" s="332" t="n"/>
       <c r="C62" s="332" t="n"/>
       <c r="D62" s="332" t="n"/>
-      <c r="E62" s="361" t="n"/>
-      <c r="F62" s="361" t="n"/>
-      <c r="G62" s="361" t="n"/>
-      <c r="H62" s="361" t="n"/>
-      <c r="I62" s="361" t="n"/>
-      <c r="J62" s="361" t="n"/>
+      <c r="E62" s="362" t="n"/>
+      <c r="F62" s="362" t="n"/>
+      <c r="G62" s="362" t="n"/>
+      <c r="H62" s="362" t="n"/>
+      <c r="I62" s="362" t="n"/>
+      <c r="J62" s="362" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="146">
@@ -10253,20 +10253,20 @@
         <f>B9+4</f>
         <v/>
       </c>
-      <c r="E9" s="183" t="inlineStr">
-        <is>
-          <t>Ing - APa-PaH-Velo
-3º e 4º tempos</t>
-        </is>
-      </c>
+      <c r="E9" s="183" t="n"/>
       <c r="F9" s="183" t="n"/>
       <c r="G9" s="183" t="inlineStr">
         <is>
-          <t>GL - Caro-EFr-Eth
-5º e 6º tempos</t>
-        </is>
-      </c>
-      <c r="H9" s="183" t="n"/>
+          <t>Geo - Mar
+6º e 7º tempos</t>
+        </is>
+      </c>
+      <c r="H9" s="183" t="inlineStr">
+        <is>
+          <t>DaF - Caro-SGa-EFr
+1º e 2º tempos</t>
+        </is>
+      </c>
       <c r="I9" s="183" t="n"/>
       <c r="J9" s="183" t="n"/>
       <c r="L9" s="16" t="inlineStr">
@@ -10345,21 +10345,21 @@
         <f>B12+4</f>
         <v/>
       </c>
-      <c r="E12" s="11" t="inlineStr">
-        <is>
-          <t>Hist - JuLa
-6º e 7º tempos</t>
-        </is>
-      </c>
-      <c r="F12" s="11" t="inlineStr">
-        <is>
-          <t>DaF - Caro-SGa-EFr
-1º e 2º tempos</t>
-        </is>
-      </c>
-      <c r="G12" s="11" t="n"/>
+      <c r="E12" s="11" t="n"/>
+      <c r="F12" s="11" t="n"/>
+      <c r="G12" s="11" t="inlineStr">
+        <is>
+          <t>Port - Jana
+4º e 5º tempos</t>
+        </is>
+      </c>
       <c r="H12" s="11" t="n"/>
-      <c r="I12" s="11" t="n"/>
+      <c r="I12" s="11" t="inlineStr">
+        <is>
+          <t>GL - Caro-EFr-Eth
+4º e 5º tempos</t>
+        </is>
+      </c>
       <c r="J12" s="183" t="n"/>
       <c r="L12" s="15" t="n"/>
       <c r="M12" s="15" t="n"/>
@@ -10417,20 +10417,20 @@
         <v/>
       </c>
       <c r="E15" s="11" t="n"/>
-      <c r="F15" s="11" t="n"/>
-      <c r="G15" s="11" t="inlineStr">
-        <is>
-          <t>Port - Jana
-3º e 4º tempos</t>
-        </is>
-      </c>
-      <c r="H15" s="11" t="inlineStr">
-        <is>
-          <t>Redação - Raf
+      <c r="F15" s="11" t="inlineStr">
+        <is>
+          <t>Hist - JuLa
 4º e 5º tempos</t>
         </is>
       </c>
-      <c r="I15" s="11" t="n"/>
+      <c r="G15" s="11" t="n"/>
+      <c r="H15" s="11" t="n"/>
+      <c r="I15" s="11" t="inlineStr">
+        <is>
+          <t>Ing - APa-PaH-Velo
+2º e 3º tempos</t>
+        </is>
+      </c>
       <c r="J15" s="183" t="n"/>
       <c r="L15" s="17" t="n"/>
       <c r="M15" s="15" t="n"/>
@@ -10490,20 +10490,20 @@
           <t>unterrichtsfrei sem aula</t>
         </is>
       </c>
-      <c r="F18" s="11" t="inlineStr">
+      <c r="F18" s="11" t="n"/>
+      <c r="G18" s="11" t="inlineStr">
         <is>
           <t>Mat - BrSa
 4º e 5º tempos</t>
         </is>
       </c>
-      <c r="G18" s="11" t="n"/>
-      <c r="H18" s="11" t="n"/>
-      <c r="I18" s="350" t="inlineStr">
-        <is>
-          <t>Geo - Mar
-5º e 6º tempos</t>
-        </is>
-      </c>
+      <c r="H18" s="11" t="inlineStr">
+        <is>
+          <t>Redação - Raf
+4º e 5º tempos</t>
+        </is>
+      </c>
+      <c r="I18" s="350" t="n"/>
       <c r="J18" s="262" t="inlineStr">
         <is>
           <t>2CH 9,10,11,12</t>
@@ -10573,8 +10573,8 @@
       <c r="F21" s="62" t="n"/>
       <c r="G21" s="11" t="inlineStr">
         <is>
-          <t>Qui - Fab
-2º tempo</t>
+          <t>Geo - Mar
+6º e 7º tempos</t>
         </is>
       </c>
       <c r="H21" s="11" t="n"/>
@@ -10642,13 +10642,13 @@
         <v/>
       </c>
       <c r="E24" s="283" t="n"/>
-      <c r="F24" s="283" t="inlineStr">
-        <is>
-          <t>Bio - Ale
-1º tempo</t>
-        </is>
-      </c>
-      <c r="G24" s="79" t="n"/>
+      <c r="F24" s="283" t="n"/>
+      <c r="G24" s="353" t="inlineStr">
+        <is>
+          <t>Port - Jana
+4º e 5º tempos</t>
+        </is>
+      </c>
       <c r="H24" s="283" t="n"/>
       <c r="I24" s="78" t="n"/>
       <c r="J24" s="265" t="n"/>
@@ -10664,13 +10664,13 @@
       <c r="A25" s="316" t="n"/>
       <c r="B25" s="313" t="n"/>
       <c r="C25" s="313" t="n"/>
-      <c r="D25" s="353" t="n"/>
+      <c r="D25" s="354" t="n"/>
       <c r="E25" s="283" t="n"/>
       <c r="F25" s="283" t="n"/>
       <c r="G25" s="79" t="n"/>
       <c r="H25" s="283" t="n"/>
       <c r="I25" s="78" t="n"/>
-      <c r="J25" s="354" t="n"/>
+      <c r="J25" s="355" t="n"/>
       <c r="L25" s="44" t="n"/>
       <c r="M25" s="321" t="inlineStr">
         <is>
@@ -10683,13 +10683,13 @@
       <c r="A26" s="316" t="n"/>
       <c r="B26" s="313" t="n"/>
       <c r="C26" s="313" t="n"/>
-      <c r="D26" s="353" t="n"/>
+      <c r="D26" s="354" t="n"/>
       <c r="E26" s="283" t="n"/>
       <c r="F26" s="283" t="n"/>
       <c r="G26" s="79" t="n"/>
       <c r="H26" s="283" t="n"/>
       <c r="I26" s="78" t="n"/>
-      <c r="J26" s="354" t="n"/>
+      <c r="J26" s="355" t="n"/>
       <c r="L26" s="43" t="n"/>
       <c r="M26" s="323" t="inlineStr">
         <is>
@@ -10719,7 +10719,12 @@
       <c r="E27" s="78" t="n"/>
       <c r="F27" s="283" t="n"/>
       <c r="G27" s="283" t="n"/>
-      <c r="H27" s="283" t="n"/>
+      <c r="H27" s="283" t="inlineStr">
+        <is>
+          <t>DaF - Caro-SGa-EFr
+1º e 2º tempos</t>
+        </is>
+      </c>
       <c r="I27" s="283" t="inlineStr">
         <is>
           <t>AG9
@@ -10739,13 +10744,13 @@
       <c r="A28" s="316" t="n"/>
       <c r="B28" s="313" t="n"/>
       <c r="C28" s="313" t="n"/>
-      <c r="D28" s="353" t="n"/>
+      <c r="D28" s="354" t="n"/>
       <c r="E28" s="78" t="n"/>
       <c r="F28" s="283" t="n"/>
       <c r="G28" s="283" t="n"/>
       <c r="H28" s="283" t="n"/>
       <c r="I28" s="283" t="n"/>
-      <c r="J28" s="354" t="n"/>
+      <c r="J28" s="355" t="n"/>
       <c r="L28" s="23" t="n"/>
       <c r="M28" s="325" t="inlineStr">
         <is>
@@ -10758,13 +10763,13 @@
       <c r="A29" s="316" t="n"/>
       <c r="B29" s="313" t="n"/>
       <c r="C29" s="313" t="n"/>
-      <c r="D29" s="353" t="n"/>
+      <c r="D29" s="354" t="n"/>
       <c r="E29" s="78" t="n"/>
       <c r="F29" s="283" t="n"/>
       <c r="G29" s="283" t="n"/>
       <c r="H29" s="283" t="n"/>
       <c r="I29" s="283" t="n"/>
-      <c r="J29" s="354" t="n"/>
+      <c r="J29" s="355" t="n"/>
       <c r="L29" s="46" t="n"/>
       <c r="M29" s="157" t="inlineStr">
         <is>
@@ -10793,16 +10798,11 @@
       </c>
       <c r="E30" s="283" t="inlineStr">
         <is>
-          <t>GL - Caro-EFr-Eth
-5º e 6º tempos</t>
-        </is>
-      </c>
-      <c r="F30" s="283" t="inlineStr">
-        <is>
-          <t>Mat - BrSa
-4º e 5º tempos</t>
-        </is>
-      </c>
+          <t>Fis - VSi
+2º tempo</t>
+        </is>
+      </c>
+      <c r="F30" s="283" t="n"/>
       <c r="G30" s="283" t="n"/>
       <c r="H30" s="283" t="n"/>
       <c r="I30" s="283" t="n"/>
@@ -10823,7 +10823,7 @@
       <c r="A31" s="316" t="n"/>
       <c r="B31" s="313" t="n"/>
       <c r="C31" s="313" t="n"/>
-      <c r="D31" s="353" t="n"/>
+      <c r="D31" s="354" t="n"/>
       <c r="E31" s="283" t="n"/>
       <c r="F31" s="283" t="n"/>
       <c r="G31" s="283" t="n"/>
@@ -10842,7 +10842,7 @@
       <c r="A32" s="316" t="n"/>
       <c r="B32" s="313" t="n"/>
       <c r="C32" s="313" t="n"/>
-      <c r="D32" s="353" t="n"/>
+      <c r="D32" s="354" t="n"/>
       <c r="E32" s="283" t="n"/>
       <c r="F32" s="283" t="n"/>
       <c r="G32" s="283" t="n"/>
@@ -10912,7 +10912,7 @@
     <row r="34" ht="26.25" customFormat="1" customHeight="1" s="4">
       <c r="A34" s="330" t="n"/>
       <c r="B34" s="331" t="n"/>
-      <c r="D34" s="355" t="n"/>
+      <c r="D34" s="356" t="n"/>
       <c r="E34" s="315" t="n"/>
       <c r="F34" s="315" t="n"/>
       <c r="G34" s="315" t="n"/>
@@ -10934,7 +10934,7 @@
     <row r="35" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A35" s="330" t="n"/>
       <c r="B35" s="332" t="n"/>
-      <c r="D35" s="356" t="n"/>
+      <c r="D35" s="357" t="n"/>
       <c r="E35" s="315" t="n"/>
       <c r="F35" s="315" t="n"/>
       <c r="G35" s="315" t="n"/>
@@ -10975,12 +10975,17 @@
       <c r="F36" s="283" t="n"/>
       <c r="G36" s="283" t="inlineStr">
         <is>
-          <t>Port - Jana
-3º e 4º tempos</t>
+          <t>Mat - BrSa
+4º e 5º tempos</t>
         </is>
       </c>
       <c r="H36" s="283" t="n"/>
-      <c r="I36" s="283" t="n"/>
+      <c r="I36" s="283" t="inlineStr">
+        <is>
+          <t>GL - Caro-EFr-Eth
+4º e 5º tempos</t>
+        </is>
+      </c>
       <c r="J36" s="265" t="n"/>
       <c r="L36" s="81" t="inlineStr">
         <is>
@@ -10997,13 +11002,13 @@
       <c r="A37" s="316" t="n"/>
       <c r="B37" s="313" t="n"/>
       <c r="C37" s="313" t="n"/>
-      <c r="D37" s="353" t="n"/>
+      <c r="D37" s="354" t="n"/>
       <c r="E37" s="283" t="n"/>
       <c r="F37" s="283" t="n"/>
       <c r="G37" s="283" t="n"/>
       <c r="H37" s="283" t="n"/>
       <c r="I37" s="283" t="n"/>
-      <c r="J37" s="354" t="n"/>
+      <c r="J37" s="355" t="n"/>
       <c r="L37" s="4" t="inlineStr">
         <is>
           <t>18.08,19.08</t>
@@ -11019,13 +11024,13 @@
       <c r="A38" s="316" t="n"/>
       <c r="B38" s="313" t="n"/>
       <c r="C38" s="313" t="n"/>
-      <c r="D38" s="353" t="n"/>
+      <c r="D38" s="354" t="n"/>
       <c r="E38" s="283" t="n"/>
       <c r="F38" s="283" t="n"/>
       <c r="G38" s="283" t="n"/>
       <c r="H38" s="283" t="n"/>
       <c r="I38" s="283" t="n"/>
-      <c r="J38" s="354" t="n"/>
+      <c r="J38" s="355" t="n"/>
     </row>
     <row r="39" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A39" s="119">
@@ -11045,13 +11050,13 @@
         <f>B39+4</f>
         <v/>
       </c>
-      <c r="E39" s="283" t="inlineStr">
+      <c r="E39" s="283" t="n"/>
+      <c r="F39" s="283" t="inlineStr">
         <is>
           <t>Hist - JuLa
-6º e 7º tempos</t>
-        </is>
-      </c>
-      <c r="F39" s="283" t="n"/>
+4º e 5º tempos</t>
+        </is>
+      </c>
       <c r="G39" s="283" t="n"/>
       <c r="H39" s="283" t="n"/>
       <c r="I39" s="283" t="n"/>
@@ -11061,25 +11066,25 @@
       <c r="A40" s="316" t="n"/>
       <c r="B40" s="313" t="n"/>
       <c r="C40" s="313" t="n"/>
-      <c r="D40" s="353" t="n"/>
+      <c r="D40" s="354" t="n"/>
       <c r="E40" s="283" t="n"/>
       <c r="F40" s="283" t="n"/>
       <c r="G40" s="283" t="n"/>
       <c r="H40" s="283" t="n"/>
       <c r="I40" s="283" t="n"/>
-      <c r="J40" s="354" t="n"/>
+      <c r="J40" s="355" t="n"/>
     </row>
     <row r="41" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A41" s="316" t="n"/>
       <c r="B41" s="313" t="n"/>
       <c r="C41" s="313" t="n"/>
-      <c r="D41" s="353" t="n"/>
+      <c r="D41" s="354" t="n"/>
       <c r="E41" s="283" t="n"/>
       <c r="F41" s="283" t="n"/>
       <c r="G41" s="283" t="n"/>
       <c r="H41" s="283" t="n"/>
       <c r="I41" s="283" t="n"/>
-      <c r="J41" s="354" t="n"/>
+      <c r="J41" s="355" t="n"/>
     </row>
     <row r="42" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A42" s="119">
@@ -11100,18 +11105,13 @@
         <v/>
       </c>
       <c r="E42" s="283" t="n"/>
-      <c r="F42" s="283" t="inlineStr">
-        <is>
-          <t>DaF - Caro-SGa-EFr
-1º e 2º tempos</t>
-        </is>
-      </c>
+      <c r="F42" s="283" t="n"/>
       <c r="G42" s="283" t="n"/>
       <c r="H42" s="283" t="n"/>
       <c r="I42" s="283" t="inlineStr">
         <is>
-          <t>Geo - Mar
-5º e 6º tempos</t>
+          <t>Ing - APa-PaH-Velo
+2º e 3º tempos</t>
         </is>
       </c>
       <c r="J42" s="265" t="n"/>
@@ -11126,26 +11126,26 @@
       <c r="A43" s="316" t="n"/>
       <c r="B43" s="313" t="n"/>
       <c r="C43" s="313" t="n"/>
-      <c r="D43" s="353" t="n"/>
+      <c r="D43" s="354" t="n"/>
       <c r="E43" s="283" t="n"/>
       <c r="F43" s="283" t="n"/>
       <c r="G43" s="283" t="n"/>
       <c r="H43" s="283" t="n"/>
       <c r="I43" s="283" t="n"/>
-      <c r="J43" s="354" t="n"/>
+      <c r="J43" s="355" t="n"/>
       <c r="L43" s="331" t="n"/>
     </row>
     <row r="44" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A44" s="316" t="n"/>
       <c r="B44" s="313" t="n"/>
       <c r="C44" s="313" t="n"/>
-      <c r="D44" s="353" t="n"/>
+      <c r="D44" s="354" t="n"/>
       <c r="E44" s="283" t="n"/>
       <c r="F44" s="283" t="n"/>
       <c r="G44" s="283" t="n"/>
       <c r="H44" s="283" t="n"/>
       <c r="I44" s="283" t="n"/>
-      <c r="J44" s="354" t="n"/>
+      <c r="J44" s="355" t="n"/>
       <c r="L44" s="331" t="n"/>
     </row>
     <row r="45" ht="18" customFormat="1" customHeight="1" s="4">
@@ -11168,8 +11168,8 @@
       </c>
       <c r="E45" s="283" t="inlineStr">
         <is>
-          <t>Ing - APa-PaH-Velo
-3º e 4º tempos</t>
+          <t>Bio - Ale
+1º tempo</t>
         </is>
       </c>
       <c r="F45" s="283" t="n"/>
@@ -11180,7 +11180,7 @@
 4º e 5º tempos</t>
         </is>
       </c>
-      <c r="I45" s="357" t="n"/>
+      <c r="I45" s="358" t="n"/>
       <c r="J45" s="269" t="n"/>
       <c r="L45" s="331" t="n"/>
     </row>
@@ -11188,26 +11188,26 @@
       <c r="A46" s="316" t="n"/>
       <c r="B46" s="313" t="n"/>
       <c r="C46" s="313" t="n"/>
-      <c r="D46" s="353" t="n"/>
+      <c r="D46" s="354" t="n"/>
       <c r="E46" s="283" t="n"/>
       <c r="F46" s="283" t="n"/>
       <c r="G46" s="283" t="n"/>
       <c r="H46" s="283" t="n"/>
-      <c r="I46" s="358" t="n"/>
-      <c r="J46" s="354" t="n"/>
+      <c r="I46" s="359" t="n"/>
+      <c r="J46" s="355" t="n"/>
       <c r="L46" s="331" t="n"/>
     </row>
     <row r="47" ht="51" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A47" s="316" t="n"/>
       <c r="B47" s="313" t="n"/>
       <c r="C47" s="313" t="n"/>
-      <c r="D47" s="353" t="n"/>
+      <c r="D47" s="354" t="n"/>
       <c r="E47" s="283" t="n"/>
       <c r="F47" s="283" t="n"/>
       <c r="G47" s="283" t="n"/>
       <c r="H47" s="283" t="n"/>
-      <c r="I47" s="359" t="n"/>
-      <c r="J47" s="354" t="n"/>
+      <c r="I47" s="360" t="n"/>
+      <c r="J47" s="355" t="n"/>
       <c r="L47" s="332" t="n"/>
     </row>
     <row r="48" ht="23.25" customFormat="1" customHeight="1" s="4">
@@ -11228,14 +11228,14 @@
         <f>B48+4</f>
         <v/>
       </c>
-      <c r="E48" s="283" t="inlineStr">
-        <is>
-          <t>Fis - VSi
+      <c r="E48" s="283" t="n"/>
+      <c r="F48" s="361" t="n"/>
+      <c r="G48" s="283" t="inlineStr">
+        <is>
+          <t>Qui - Fab
 2º tempo</t>
         </is>
       </c>
-      <c r="F48" s="360" t="n"/>
-      <c r="G48" s="283" t="n"/>
       <c r="H48" s="283" t="n"/>
       <c r="I48" s="183" t="inlineStr">
         <is>
@@ -11248,25 +11248,25 @@
       <c r="A49" s="316" t="n"/>
       <c r="B49" s="313" t="n"/>
       <c r="C49" s="313" t="n"/>
-      <c r="D49" s="353" t="n"/>
+      <c r="D49" s="354" t="n"/>
       <c r="E49" s="283" t="n"/>
-      <c r="F49" s="358" t="n"/>
+      <c r="F49" s="359" t="n"/>
       <c r="G49" s="283" t="n"/>
       <c r="H49" s="283" t="n"/>
       <c r="I49" s="315" t="n"/>
-      <c r="J49" s="354" t="n"/>
+      <c r="J49" s="355" t="n"/>
     </row>
     <row r="50" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A50" s="316" t="n"/>
       <c r="B50" s="313" t="n"/>
       <c r="C50" s="313" t="n"/>
-      <c r="D50" s="353" t="n"/>
+      <c r="D50" s="354" t="n"/>
       <c r="E50" s="78" t="n"/>
-      <c r="F50" s="359" t="n"/>
+      <c r="F50" s="360" t="n"/>
       <c r="G50" s="283" t="n"/>
       <c r="H50" s="283" t="n"/>
       <c r="I50" s="315" t="n"/>
-      <c r="J50" s="354" t="n"/>
+      <c r="J50" s="355" t="n"/>
     </row>
     <row r="51" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A51" s="119">
@@ -11290,7 +11290,7 @@
       <c r="F51" s="183" t="n"/>
       <c r="G51" s="183" t="n"/>
       <c r="H51" s="183" t="n"/>
-      <c r="I51" s="357" t="inlineStr">
+      <c r="I51" s="358" t="inlineStr">
         <is>
           <t>2CH
 9,11</t>
@@ -11302,25 +11302,25 @@
       <c r="A52" s="316" t="n"/>
       <c r="B52" s="313" t="n"/>
       <c r="C52" s="313" t="n"/>
-      <c r="D52" s="353" t="n"/>
+      <c r="D52" s="354" t="n"/>
       <c r="E52" s="283" t="n"/>
       <c r="F52" s="315" t="n"/>
       <c r="G52" s="315" t="n"/>
       <c r="H52" s="315" t="n"/>
-      <c r="I52" s="358" t="n"/>
-      <c r="J52" s="354" t="n"/>
+      <c r="I52" s="359" t="n"/>
+      <c r="J52" s="355" t="n"/>
     </row>
     <row r="53" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A53" s="316" t="n"/>
       <c r="B53" s="313" t="n"/>
       <c r="C53" s="313" t="n"/>
-      <c r="D53" s="353" t="n"/>
+      <c r="D53" s="354" t="n"/>
       <c r="E53" s="283" t="n"/>
       <c r="F53" s="315" t="n"/>
       <c r="G53" s="315" t="n"/>
       <c r="H53" s="315" t="n"/>
-      <c r="I53" s="359" t="n"/>
-      <c r="J53" s="354" t="n"/>
+      <c r="I53" s="360" t="n"/>
+      <c r="J53" s="355" t="n"/>
     </row>
     <row r="54" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A54" s="119">
@@ -11351,25 +11351,25 @@
       <c r="A55" s="316" t="n"/>
       <c r="B55" s="313" t="n"/>
       <c r="C55" s="313" t="n"/>
-      <c r="D55" s="353" t="n"/>
+      <c r="D55" s="354" t="n"/>
       <c r="E55" s="315" t="n"/>
       <c r="F55" s="315" t="n"/>
       <c r="G55" s="315" t="n"/>
       <c r="H55" s="315" t="n"/>
       <c r="I55" s="315" t="n"/>
-      <c r="J55" s="354" t="n"/>
+      <c r="J55" s="355" t="n"/>
     </row>
     <row r="56" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A56" s="316" t="n"/>
       <c r="B56" s="313" t="n"/>
       <c r="C56" s="313" t="n"/>
-      <c r="D56" s="353" t="n"/>
+      <c r="D56" s="354" t="n"/>
       <c r="E56" s="315" t="n"/>
       <c r="F56" s="315" t="n"/>
       <c r="G56" s="315" t="n"/>
       <c r="H56" s="315" t="n"/>
       <c r="I56" s="315" t="n"/>
-      <c r="J56" s="354" t="n"/>
+      <c r="J56" s="355" t="n"/>
     </row>
     <row r="57" ht="25.5" customFormat="1" customHeight="1" s="4">
       <c r="A57" s="119">
@@ -11390,7 +11390,7 @@
         <v/>
       </c>
       <c r="E57" s="183" t="n"/>
-      <c r="F57" s="360" t="inlineStr">
+      <c r="F57" s="361" t="inlineStr">
         <is>
           <t>CC
 9,11</t>
@@ -11405,25 +11405,25 @@
       <c r="A58" s="316" t="n"/>
       <c r="B58" s="313" t="n"/>
       <c r="C58" s="313" t="n"/>
-      <c r="D58" s="353" t="n"/>
+      <c r="D58" s="354" t="n"/>
       <c r="E58" s="315" t="n"/>
-      <c r="F58" s="358" t="n"/>
+      <c r="F58" s="359" t="n"/>
       <c r="G58" s="315" t="n"/>
       <c r="H58" s="315" t="n"/>
       <c r="I58" s="315" t="n"/>
-      <c r="J58" s="354" t="n"/>
+      <c r="J58" s="355" t="n"/>
     </row>
     <row r="59" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A59" s="316" t="n"/>
       <c r="B59" s="313" t="n"/>
       <c r="C59" s="313" t="n"/>
-      <c r="D59" s="353" t="n"/>
+      <c r="D59" s="354" t="n"/>
       <c r="E59" s="315" t="n"/>
-      <c r="F59" s="359" t="n"/>
+      <c r="F59" s="360" t="n"/>
       <c r="G59" s="315" t="n"/>
       <c r="H59" s="315" t="n"/>
       <c r="I59" s="315" t="n"/>
-      <c r="J59" s="354" t="n"/>
+      <c r="J59" s="355" t="n"/>
     </row>
     <row r="60" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A60" s="281">
@@ -11455,24 +11455,24 @@
       <c r="B61" s="331" t="n"/>
       <c r="C61" s="331" t="n"/>
       <c r="D61" s="331" t="n"/>
-      <c r="E61" s="358" t="n"/>
-      <c r="F61" s="358" t="n"/>
-      <c r="G61" s="358" t="n"/>
-      <c r="H61" s="358" t="n"/>
-      <c r="I61" s="358" t="n"/>
-      <c r="J61" s="358" t="n"/>
+      <c r="E61" s="359" t="n"/>
+      <c r="F61" s="359" t="n"/>
+      <c r="G61" s="359" t="n"/>
+      <c r="H61" s="359" t="n"/>
+      <c r="I61" s="359" t="n"/>
+      <c r="J61" s="359" t="n"/>
     </row>
     <row r="62" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A62" s="332" t="n"/>
       <c r="B62" s="332" t="n"/>
       <c r="C62" s="332" t="n"/>
       <c r="D62" s="332" t="n"/>
-      <c r="E62" s="361" t="n"/>
-      <c r="F62" s="361" t="n"/>
-      <c r="G62" s="361" t="n"/>
-      <c r="H62" s="361" t="n"/>
-      <c r="I62" s="361" t="n"/>
-      <c r="J62" s="361" t="n"/>
+      <c r="E62" s="362" t="n"/>
+      <c r="F62" s="362" t="n"/>
+      <c r="G62" s="362" t="n"/>
+      <c r="H62" s="362" t="n"/>
+      <c r="I62" s="362" t="n"/>
+      <c r="J62" s="362" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="146">
@@ -11921,23 +11921,18 @@
       </c>
       <c r="E9" s="183" t="inlineStr">
         <is>
-          <t>Fis - VSi
-3º e 4º tempos</t>
-        </is>
-      </c>
-      <c r="F9" s="183" t="inlineStr">
-        <is>
           <t>Qui - CAl
-5º e 6º tempos</t>
-        </is>
-      </c>
-      <c r="G9" s="183" t="inlineStr">
-        <is>
-          <t>Ing - APa
-3º e 4º tempos</t>
-        </is>
-      </c>
-      <c r="H9" s="183" t="n"/>
+4º e 5º tempos</t>
+        </is>
+      </c>
+      <c r="F9" s="183" t="n"/>
+      <c r="G9" s="183" t="n"/>
+      <c r="H9" s="183" t="inlineStr">
+        <is>
+          <t>Mat - BrSa/FBri
+4º e 5º tempos</t>
+        </is>
+      </c>
       <c r="I9" s="183" t="n"/>
       <c r="J9" s="183" t="n"/>
       <c r="L9" s="16" t="inlineStr">
@@ -12018,21 +12013,21 @@
       </c>
       <c r="E12" s="11" t="inlineStr">
         <is>
-          <t>LP/LIT/RED - BPad/MFo/SMo
-1º ao 3º tempos</t>
-        </is>
-      </c>
-      <c r="F12" s="11" t="n"/>
-      <c r="G12" s="11" t="inlineStr">
-        <is>
-          <t>GL - EFr-Car-Swa
-2º e 3º tempos</t>
-        </is>
-      </c>
+          <t>DaF - Eth-EFr-Swa
+1º e 2º tempos</t>
+        </is>
+      </c>
+      <c r="F12" s="11" t="inlineStr">
+        <is>
+          <t>Bio - Lza
+6º e 7º tempos</t>
+        </is>
+      </c>
+      <c r="G12" s="11" t="n"/>
       <c r="H12" s="11" t="inlineStr">
         <is>
-          <t>Hist - ALu
-5º e 6º tempos</t>
+          <t>Fis - VSi
+1º e 2º tempos</t>
         </is>
       </c>
       <c r="I12" s="11" t="n"/>
@@ -12094,24 +12089,24 @@
       </c>
       <c r="E15" s="11" t="inlineStr">
         <is>
-          <t>Mat - BrSa/FBri
-1º e 2º tempos</t>
-        </is>
-      </c>
-      <c r="F15" s="11" t="inlineStr">
-        <is>
-          <t>Bio - Lza
-6º e 7º tempos</t>
-        </is>
-      </c>
+          <t>Ing - APa
+4º e 5º tempos</t>
+        </is>
+      </c>
+      <c r="F15" s="11" t="n"/>
       <c r="G15" s="11" t="n"/>
       <c r="H15" s="11" t="inlineStr">
         <is>
+          <t>Hist - ALu
+2º e 3º tempos</t>
+        </is>
+      </c>
+      <c r="I15" s="11" t="inlineStr">
+        <is>
           <t>Geo - Mlo
-3º e 4º tempos</t>
-        </is>
-      </c>
-      <c r="I15" s="11" t="n"/>
+2º e 3º tempos</t>
+        </is>
+      </c>
       <c r="J15" s="183" t="n"/>
       <c r="L15" s="17" t="n"/>
       <c r="M15" s="15" t="n"/>
@@ -12174,11 +12169,16 @@
       <c r="F18" s="11" t="n"/>
       <c r="G18" s="11" t="inlineStr">
         <is>
-          <t>DaF - Eth-EFr-Swa
+          <t>GL - EFr-Car-Swa
 2º e 3º tempos</t>
         </is>
       </c>
-      <c r="H18" s="11" t="n"/>
+      <c r="H18" s="11" t="inlineStr">
+        <is>
+          <t>LP/LIT/RED - BPad/MFo/SMo
+1º ao 3º tempos</t>
+        </is>
+      </c>
       <c r="I18" s="350" t="inlineStr">
         <is>
           <t>AG10
@@ -12251,17 +12251,17 @@
         <v/>
       </c>
       <c r="E21" s="11" t="n"/>
-      <c r="F21" s="62" t="n"/>
-      <c r="G21" s="11" t="inlineStr">
-        <is>
-          <t>Soc - Kle
-5º tempo</t>
-        </is>
-      </c>
+      <c r="F21" s="62" t="inlineStr">
+        <is>
+          <t>Bio - Lza
+6º e 7º tempos</t>
+        </is>
+      </c>
+      <c r="G21" s="11" t="n"/>
       <c r="H21" s="11" t="inlineStr">
         <is>
           <t>Geo - Mlo
-3º e 4º tempos</t>
+4º e 5º tempos</t>
         </is>
       </c>
       <c r="I21" s="11" t="n"/>
@@ -12329,18 +12329,18 @@
       </c>
       <c r="E24" s="283" t="inlineStr">
         <is>
-          <t>LP/LIT/RED - BPad/MFo/SMo
-1º ao 3º tempos</t>
+          <t>DaF - Eth-EFr-Swa
+1º e 2º tempos</t>
         </is>
       </c>
       <c r="F24" s="283" t="n"/>
-      <c r="G24" s="79" t="n"/>
-      <c r="H24" s="283" t="inlineStr">
-        <is>
-          <t>Hist - ALu
-5º e 6º tempos</t>
-        </is>
-      </c>
+      <c r="G24" s="353" t="inlineStr">
+        <is>
+          <t>Soc - Kle
+5º tempo</t>
+        </is>
+      </c>
+      <c r="H24" s="283" t="n"/>
       <c r="I24" s="78" t="n"/>
       <c r="J24" s="265" t="n"/>
       <c r="L24" s="318" t="inlineStr">
@@ -12355,13 +12355,13 @@
       <c r="A25" s="316" t="n"/>
       <c r="B25" s="313" t="n"/>
       <c r="C25" s="313" t="n"/>
-      <c r="D25" s="353" t="n"/>
+      <c r="D25" s="354" t="n"/>
       <c r="E25" s="283" t="n"/>
       <c r="F25" s="283" t="n"/>
       <c r="G25" s="79" t="n"/>
       <c r="H25" s="283" t="n"/>
       <c r="I25" s="78" t="n"/>
-      <c r="J25" s="354" t="n"/>
+      <c r="J25" s="355" t="n"/>
       <c r="L25" s="44" t="n"/>
       <c r="M25" s="321" t="inlineStr">
         <is>
@@ -12374,13 +12374,13 @@
       <c r="A26" s="316" t="n"/>
       <c r="B26" s="313" t="n"/>
       <c r="C26" s="313" t="n"/>
-      <c r="D26" s="353" t="n"/>
+      <c r="D26" s="354" t="n"/>
       <c r="E26" s="283" t="n"/>
       <c r="F26" s="283" t="n"/>
       <c r="G26" s="79" t="n"/>
       <c r="H26" s="283" t="n"/>
       <c r="I26" s="78" t="n"/>
-      <c r="J26" s="354" t="n"/>
+      <c r="J26" s="355" t="n"/>
       <c r="L26" s="43" t="n"/>
       <c r="M26" s="323" t="inlineStr">
         <is>
@@ -12409,12 +12409,17 @@
       </c>
       <c r="E27" s="78" t="inlineStr">
         <is>
-          <t>Fis - VSi
-3º e 4º tempos</t>
+          <t>Mat - BrSa/FBri
+1º e 2º tempos</t>
         </is>
       </c>
       <c r="F27" s="283" t="n"/>
-      <c r="G27" s="283" t="n"/>
+      <c r="G27" s="283" t="inlineStr">
+        <is>
+          <t>GL - EFr-Car-Swa
+2º e 3º tempos</t>
+        </is>
+      </c>
       <c r="H27" s="283" t="n"/>
       <c r="I27" s="283" t="n"/>
       <c r="J27" s="265" t="n"/>
@@ -12430,13 +12435,13 @@
       <c r="A28" s="316" t="n"/>
       <c r="B28" s="313" t="n"/>
       <c r="C28" s="313" t="n"/>
-      <c r="D28" s="353" t="n"/>
+      <c r="D28" s="354" t="n"/>
       <c r="E28" s="78" t="n"/>
       <c r="F28" s="283" t="n"/>
       <c r="G28" s="283" t="n"/>
       <c r="H28" s="283" t="n"/>
       <c r="I28" s="283" t="n"/>
-      <c r="J28" s="354" t="n"/>
+      <c r="J28" s="355" t="n"/>
       <c r="L28" s="23" t="n"/>
       <c r="M28" s="325" t="inlineStr">
         <is>
@@ -12449,13 +12454,13 @@
       <c r="A29" s="316" t="n"/>
       <c r="B29" s="313" t="n"/>
       <c r="C29" s="313" t="n"/>
-      <c r="D29" s="353" t="n"/>
+      <c r="D29" s="354" t="n"/>
       <c r="E29" s="78" t="n"/>
       <c r="F29" s="283" t="n"/>
       <c r="G29" s="283" t="n"/>
       <c r="H29" s="283" t="n"/>
       <c r="I29" s="283" t="n"/>
-      <c r="J29" s="354" t="n"/>
+      <c r="J29" s="355" t="n"/>
       <c r="L29" s="46" t="n"/>
       <c r="M29" s="157" t="inlineStr">
         <is>
@@ -12484,16 +12489,11 @@
       </c>
       <c r="E30" s="283" t="inlineStr">
         <is>
-          <t>Ing - APa
-4º e 5º tempos</t>
-        </is>
-      </c>
-      <c r="F30" s="283" t="inlineStr">
-        <is>
-          <t>Bio - Lza
-6º e 7º tempos</t>
-        </is>
-      </c>
+          <t>LP/LIT/RED - BPad/MFo/SMo
+1º ao 3º tempos</t>
+        </is>
+      </c>
+      <c r="F30" s="283" t="n"/>
       <c r="G30" s="283" t="n"/>
       <c r="H30" s="283" t="n"/>
       <c r="I30" s="283" t="n"/>
@@ -12514,7 +12514,7 @@
       <c r="A31" s="316" t="n"/>
       <c r="B31" s="313" t="n"/>
       <c r="C31" s="313" t="n"/>
-      <c r="D31" s="353" t="n"/>
+      <c r="D31" s="354" t="n"/>
       <c r="E31" s="283" t="n"/>
       <c r="F31" s="283" t="n"/>
       <c r="G31" s="283" t="n"/>
@@ -12533,7 +12533,7 @@
       <c r="A32" s="316" t="n"/>
       <c r="B32" s="313" t="n"/>
       <c r="C32" s="313" t="n"/>
-      <c r="D32" s="353" t="n"/>
+      <c r="D32" s="354" t="n"/>
       <c r="E32" s="283" t="n"/>
       <c r="F32" s="283" t="n"/>
       <c r="G32" s="283" t="n"/>
@@ -12603,7 +12603,7 @@
     <row r="34" ht="26.25" customFormat="1" customHeight="1" s="4">
       <c r="A34" s="330" t="n"/>
       <c r="B34" s="331" t="n"/>
-      <c r="D34" s="355" t="n"/>
+      <c r="D34" s="356" t="n"/>
       <c r="E34" s="315" t="n"/>
       <c r="F34" s="315" t="n"/>
       <c r="G34" s="315" t="n"/>
@@ -12625,7 +12625,7 @@
     <row r="35" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A35" s="330" t="n"/>
       <c r="B35" s="332" t="n"/>
-      <c r="D35" s="356" t="n"/>
+      <c r="D35" s="357" t="n"/>
       <c r="E35" s="315" t="n"/>
       <c r="F35" s="315" t="n"/>
       <c r="G35" s="315" t="n"/>
@@ -12664,13 +12664,18 @@
       </c>
       <c r="E36" s="283" t="inlineStr">
         <is>
-          <t>Mat - BrSa/FBri
-1º e 2º tempos</t>
+          <t>Qui - CAl
+4º e 5º tempos</t>
         </is>
       </c>
       <c r="F36" s="283" t="n"/>
       <c r="G36" s="283" t="n"/>
-      <c r="H36" s="283" t="n"/>
+      <c r="H36" s="283" t="inlineStr">
+        <is>
+          <t>Ing - APa
+2º e 3º tempos</t>
+        </is>
+      </c>
       <c r="I36" s="283" t="n"/>
       <c r="J36" s="265" t="n"/>
       <c r="L36" s="81" t="inlineStr">
@@ -12688,13 +12693,13 @@
       <c r="A37" s="316" t="n"/>
       <c r="B37" s="313" t="n"/>
       <c r="C37" s="313" t="n"/>
-      <c r="D37" s="353" t="n"/>
+      <c r="D37" s="354" t="n"/>
       <c r="E37" s="283" t="n"/>
       <c r="F37" s="283" t="n"/>
       <c r="G37" s="283" t="n"/>
       <c r="H37" s="283" t="n"/>
       <c r="I37" s="283" t="n"/>
-      <c r="J37" s="354" t="n"/>
+      <c r="J37" s="355" t="n"/>
       <c r="L37" s="4" t="inlineStr">
         <is>
           <t>18.08,19.08</t>
@@ -12710,13 +12715,13 @@
       <c r="A38" s="316" t="n"/>
       <c r="B38" s="313" t="n"/>
       <c r="C38" s="313" t="n"/>
-      <c r="D38" s="353" t="n"/>
+      <c r="D38" s="354" t="n"/>
       <c r="E38" s="283" t="n"/>
       <c r="F38" s="283" t="n"/>
       <c r="G38" s="283" t="n"/>
       <c r="H38" s="283" t="n"/>
       <c r="I38" s="283" t="n"/>
-      <c r="J38" s="354" t="n"/>
+      <c r="J38" s="355" t="n"/>
     </row>
     <row r="39" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A39" s="119">
@@ -12737,13 +12742,13 @@
         <v/>
       </c>
       <c r="E39" s="283" t="n"/>
-      <c r="F39" s="283" t="inlineStr">
-        <is>
-          <t>Qui - CAl
-5º e 6º tempos</t>
-        </is>
-      </c>
-      <c r="G39" s="283" t="n"/>
+      <c r="F39" s="283" t="n"/>
+      <c r="G39" s="283" t="inlineStr">
+        <is>
+          <t>Fil - LAn
+1º tempo</t>
+        </is>
+      </c>
       <c r="H39" s="283" t="n"/>
       <c r="I39" s="283" t="n"/>
       <c r="J39" s="265" t="n"/>
@@ -12752,25 +12757,25 @@
       <c r="A40" s="316" t="n"/>
       <c r="B40" s="313" t="n"/>
       <c r="C40" s="313" t="n"/>
-      <c r="D40" s="353" t="n"/>
+      <c r="D40" s="354" t="n"/>
       <c r="E40" s="283" t="n"/>
       <c r="F40" s="283" t="n"/>
       <c r="G40" s="283" t="n"/>
       <c r="H40" s="283" t="n"/>
       <c r="I40" s="283" t="n"/>
-      <c r="J40" s="354" t="n"/>
+      <c r="J40" s="355" t="n"/>
     </row>
     <row r="41" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A41" s="316" t="n"/>
       <c r="B41" s="313" t="n"/>
       <c r="C41" s="313" t="n"/>
-      <c r="D41" s="353" t="n"/>
+      <c r="D41" s="354" t="n"/>
       <c r="E41" s="283" t="n"/>
       <c r="F41" s="283" t="n"/>
       <c r="G41" s="283" t="n"/>
       <c r="H41" s="283" t="n"/>
       <c r="I41" s="283" t="n"/>
-      <c r="J41" s="354" t="n"/>
+      <c r="J41" s="355" t="n"/>
     </row>
     <row r="42" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A42" s="119">
@@ -12792,13 +12797,13 @@
       </c>
       <c r="E42" s="283" t="n"/>
       <c r="F42" s="283" t="n"/>
-      <c r="G42" s="283" t="inlineStr">
-        <is>
-          <t>GL - EFr-Car-Swa
-2º e 3º tempos</t>
-        </is>
-      </c>
-      <c r="H42" s="283" t="n"/>
+      <c r="G42" s="283" t="n"/>
+      <c r="H42" s="283" t="inlineStr">
+        <is>
+          <t>Fis - VSi
+1º e 2º tempos</t>
+        </is>
+      </c>
       <c r="I42" s="283" t="n"/>
       <c r="J42" s="265" t="n"/>
       <c r="L42" s="259" t="inlineStr">
@@ -12812,26 +12817,26 @@
       <c r="A43" s="316" t="n"/>
       <c r="B43" s="313" t="n"/>
       <c r="C43" s="313" t="n"/>
-      <c r="D43" s="353" t="n"/>
+      <c r="D43" s="354" t="n"/>
       <c r="E43" s="283" t="n"/>
       <c r="F43" s="283" t="n"/>
       <c r="G43" s="283" t="n"/>
       <c r="H43" s="283" t="n"/>
       <c r="I43" s="283" t="n"/>
-      <c r="J43" s="354" t="n"/>
+      <c r="J43" s="355" t="n"/>
       <c r="L43" s="331" t="n"/>
     </row>
     <row r="44" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A44" s="316" t="n"/>
       <c r="B44" s="313" t="n"/>
       <c r="C44" s="313" t="n"/>
-      <c r="D44" s="353" t="n"/>
+      <c r="D44" s="354" t="n"/>
       <c r="E44" s="283" t="n"/>
       <c r="F44" s="283" t="n"/>
       <c r="G44" s="283" t="n"/>
       <c r="H44" s="283" t="n"/>
       <c r="I44" s="283" t="n"/>
-      <c r="J44" s="354" t="n"/>
+      <c r="J44" s="355" t="n"/>
       <c r="L44" s="331" t="n"/>
     </row>
     <row r="45" ht="18" customFormat="1" customHeight="1" s="4">
@@ -12852,21 +12857,16 @@
         <f>B45+4</f>
         <v/>
       </c>
-      <c r="E45" s="283" t="inlineStr">
-        <is>
-          <t>DaF - Eth-EFr-Swa
-1º e 2º tempos</t>
-        </is>
-      </c>
+      <c r="E45" s="283" t="n"/>
       <c r="F45" s="283" t="n"/>
-      <c r="G45" s="283" t="inlineStr">
-        <is>
-          <t>Fil - LAn
-1º tempo</t>
-        </is>
-      </c>
-      <c r="H45" s="283" t="n"/>
-      <c r="I45" s="357" t="inlineStr">
+      <c r="G45" s="283" t="n"/>
+      <c r="H45" s="283" t="inlineStr">
+        <is>
+          <t>Hist - ALu
+2º e 3º tempos</t>
+        </is>
+      </c>
+      <c r="I45" s="358" t="inlineStr">
         <is>
           <t>2CH
 10,12</t>
@@ -12879,26 +12879,26 @@
       <c r="A46" s="316" t="n"/>
       <c r="B46" s="313" t="n"/>
       <c r="C46" s="313" t="n"/>
-      <c r="D46" s="353" t="n"/>
+      <c r="D46" s="354" t="n"/>
       <c r="E46" s="283" t="n"/>
       <c r="F46" s="283" t="n"/>
       <c r="G46" s="283" t="n"/>
       <c r="H46" s="283" t="n"/>
-      <c r="I46" s="358" t="n"/>
-      <c r="J46" s="354" t="n"/>
+      <c r="I46" s="359" t="n"/>
+      <c r="J46" s="355" t="n"/>
       <c r="L46" s="331" t="n"/>
     </row>
     <row r="47" ht="51" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A47" s="316" t="n"/>
       <c r="B47" s="313" t="n"/>
       <c r="C47" s="313" t="n"/>
-      <c r="D47" s="353" t="n"/>
+      <c r="D47" s="354" t="n"/>
       <c r="E47" s="283" t="n"/>
       <c r="F47" s="283" t="n"/>
       <c r="G47" s="283" t="n"/>
       <c r="H47" s="283" t="n"/>
-      <c r="I47" s="359" t="n"/>
-      <c r="J47" s="354" t="n"/>
+      <c r="I47" s="360" t="n"/>
+      <c r="J47" s="355" t="n"/>
       <c r="L47" s="332" t="n"/>
     </row>
     <row r="48" ht="23.25" customFormat="1" customHeight="1" s="4">
@@ -12920,7 +12920,7 @@
         <v/>
       </c>
       <c r="E48" s="283" t="n"/>
-      <c r="F48" s="360" t="inlineStr">
+      <c r="F48" s="361" t="inlineStr">
         <is>
           <t>CC
 10,12</t>
@@ -12939,25 +12939,25 @@
       <c r="A49" s="316" t="n"/>
       <c r="B49" s="313" t="n"/>
       <c r="C49" s="313" t="n"/>
-      <c r="D49" s="353" t="n"/>
+      <c r="D49" s="354" t="n"/>
       <c r="E49" s="283" t="n"/>
-      <c r="F49" s="358" t="n"/>
+      <c r="F49" s="359" t="n"/>
       <c r="G49" s="283" t="n"/>
       <c r="H49" s="283" t="n"/>
       <c r="I49" s="315" t="n"/>
-      <c r="J49" s="354" t="n"/>
+      <c r="J49" s="355" t="n"/>
     </row>
     <row r="50" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A50" s="316" t="n"/>
       <c r="B50" s="313" t="n"/>
       <c r="C50" s="313" t="n"/>
-      <c r="D50" s="353" t="n"/>
+      <c r="D50" s="354" t="n"/>
       <c r="E50" s="78" t="n"/>
-      <c r="F50" s="359" t="n"/>
+      <c r="F50" s="360" t="n"/>
       <c r="G50" s="283" t="n"/>
       <c r="H50" s="283" t="n"/>
       <c r="I50" s="315" t="n"/>
-      <c r="J50" s="354" t="n"/>
+      <c r="J50" s="355" t="n"/>
     </row>
     <row r="51" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A51" s="119">
@@ -12981,32 +12981,32 @@
       <c r="F51" s="183" t="n"/>
       <c r="G51" s="183" t="n"/>
       <c r="H51" s="183" t="n"/>
-      <c r="I51" s="357" t="n"/>
+      <c r="I51" s="358" t="n"/>
       <c r="J51" s="274" t="n"/>
     </row>
     <row r="52" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A52" s="316" t="n"/>
       <c r="B52" s="313" t="n"/>
       <c r="C52" s="313" t="n"/>
-      <c r="D52" s="353" t="n"/>
+      <c r="D52" s="354" t="n"/>
       <c r="E52" s="283" t="n"/>
       <c r="F52" s="315" t="n"/>
       <c r="G52" s="315" t="n"/>
       <c r="H52" s="315" t="n"/>
-      <c r="I52" s="358" t="n"/>
-      <c r="J52" s="354" t="n"/>
+      <c r="I52" s="359" t="n"/>
+      <c r="J52" s="355" t="n"/>
     </row>
     <row r="53" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A53" s="316" t="n"/>
       <c r="B53" s="313" t="n"/>
       <c r="C53" s="313" t="n"/>
-      <c r="D53" s="353" t="n"/>
+      <c r="D53" s="354" t="n"/>
       <c r="E53" s="283" t="n"/>
       <c r="F53" s="315" t="n"/>
       <c r="G53" s="315" t="n"/>
       <c r="H53" s="315" t="n"/>
-      <c r="I53" s="359" t="n"/>
-      <c r="J53" s="354" t="n"/>
+      <c r="I53" s="360" t="n"/>
+      <c r="J53" s="355" t="n"/>
     </row>
     <row r="54" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A54" s="119">
@@ -13037,25 +13037,25 @@
       <c r="A55" s="316" t="n"/>
       <c r="B55" s="313" t="n"/>
       <c r="C55" s="313" t="n"/>
-      <c r="D55" s="353" t="n"/>
+      <c r="D55" s="354" t="n"/>
       <c r="E55" s="315" t="n"/>
       <c r="F55" s="315" t="n"/>
       <c r="G55" s="315" t="n"/>
       <c r="H55" s="315" t="n"/>
       <c r="I55" s="315" t="n"/>
-      <c r="J55" s="354" t="n"/>
+      <c r="J55" s="355" t="n"/>
     </row>
     <row r="56" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A56" s="316" t="n"/>
       <c r="B56" s="313" t="n"/>
       <c r="C56" s="313" t="n"/>
-      <c r="D56" s="353" t="n"/>
+      <c r="D56" s="354" t="n"/>
       <c r="E56" s="315" t="n"/>
       <c r="F56" s="315" t="n"/>
       <c r="G56" s="315" t="n"/>
       <c r="H56" s="315" t="n"/>
       <c r="I56" s="315" t="n"/>
-      <c r="J56" s="354" t="n"/>
+      <c r="J56" s="355" t="n"/>
     </row>
     <row r="57" ht="25.5" customFormat="1" customHeight="1" s="4">
       <c r="A57" s="119">
@@ -13076,7 +13076,7 @@
         <v/>
       </c>
       <c r="E57" s="183" t="n"/>
-      <c r="F57" s="360" t="n"/>
+      <c r="F57" s="361" t="n"/>
       <c r="G57" s="183" t="n"/>
       <c r="H57" s="183" t="n"/>
       <c r="I57" s="183" t="n"/>
@@ -13086,25 +13086,25 @@
       <c r="A58" s="316" t="n"/>
       <c r="B58" s="313" t="n"/>
       <c r="C58" s="313" t="n"/>
-      <c r="D58" s="353" t="n"/>
+      <c r="D58" s="354" t="n"/>
       <c r="E58" s="315" t="n"/>
-      <c r="F58" s="358" t="n"/>
+      <c r="F58" s="359" t="n"/>
       <c r="G58" s="315" t="n"/>
       <c r="H58" s="315" t="n"/>
       <c r="I58" s="315" t="n"/>
-      <c r="J58" s="354" t="n"/>
+      <c r="J58" s="355" t="n"/>
     </row>
     <row r="59" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A59" s="316" t="n"/>
       <c r="B59" s="313" t="n"/>
       <c r="C59" s="313" t="n"/>
-      <c r="D59" s="353" t="n"/>
+      <c r="D59" s="354" t="n"/>
       <c r="E59" s="315" t="n"/>
-      <c r="F59" s="359" t="n"/>
+      <c r="F59" s="360" t="n"/>
       <c r="G59" s="315" t="n"/>
       <c r="H59" s="315" t="n"/>
       <c r="I59" s="315" t="n"/>
-      <c r="J59" s="354" t="n"/>
+      <c r="J59" s="355" t="n"/>
     </row>
     <row r="60" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A60" s="281">
@@ -13136,24 +13136,24 @@
       <c r="B61" s="331" t="n"/>
       <c r="C61" s="331" t="n"/>
       <c r="D61" s="331" t="n"/>
-      <c r="E61" s="358" t="n"/>
-      <c r="F61" s="358" t="n"/>
-      <c r="G61" s="358" t="n"/>
-      <c r="H61" s="358" t="n"/>
-      <c r="I61" s="358" t="n"/>
-      <c r="J61" s="358" t="n"/>
+      <c r="E61" s="359" t="n"/>
+      <c r="F61" s="359" t="n"/>
+      <c r="G61" s="359" t="n"/>
+      <c r="H61" s="359" t="n"/>
+      <c r="I61" s="359" t="n"/>
+      <c r="J61" s="359" t="n"/>
     </row>
     <row r="62" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A62" s="332" t="n"/>
       <c r="B62" s="332" t="n"/>
       <c r="C62" s="332" t="n"/>
       <c r="D62" s="332" t="n"/>
-      <c r="E62" s="361" t="n"/>
-      <c r="F62" s="361" t="n"/>
-      <c r="G62" s="361" t="n"/>
-      <c r="H62" s="361" t="n"/>
-      <c r="I62" s="361" t="n"/>
-      <c r="J62" s="361" t="n"/>
+      <c r="E62" s="362" t="n"/>
+      <c r="F62" s="362" t="n"/>
+      <c r="G62" s="362" t="n"/>
+      <c r="H62" s="362" t="n"/>
+      <c r="I62" s="362" t="n"/>
+      <c r="J62" s="362" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="146">
@@ -13603,15 +13603,15 @@
       <c r="E9" s="183" t="inlineStr">
         <is>
           <t>Qui - CAl
-3º e 4º tempos</t>
+4º e 5º tempos</t>
         </is>
       </c>
       <c r="F9" s="183" t="n"/>
       <c r="G9" s="183" t="n"/>
       <c r="H9" s="183" t="inlineStr">
         <is>
-          <t>LP/LIT/RED - BPad/MFo/SMo
-1º ao 3º tempos</t>
+          <t>Mat - BrSa/FBri
+4º e 5º tempos</t>
         </is>
       </c>
       <c r="I9" s="183" t="n"/>
@@ -13694,21 +13694,21 @@
       </c>
       <c r="E12" s="11" t="inlineStr">
         <is>
-          <t>Fis - VSi
-6º e 7º tempos</t>
-        </is>
-      </c>
-      <c r="F12" s="11" t="n"/>
-      <c r="G12" s="11" t="inlineStr">
-        <is>
           <t>DaF - Eth-EFr-Swa
 1º e 2º tempos</t>
         </is>
       </c>
+      <c r="F12" s="11" t="inlineStr">
+        <is>
+          <t>Bio - Lza
+6º e 7º tempos</t>
+        </is>
+      </c>
+      <c r="G12" s="11" t="n"/>
       <c r="H12" s="11" t="inlineStr">
         <is>
-          <t>Hist - ALu
-2º e 3º tempos</t>
+          <t>Fis - VSi
+1º e 2º tempos</t>
         </is>
       </c>
       <c r="I12" s="11" t="n"/>
@@ -13768,26 +13768,26 @@
         <f>B15+4</f>
         <v/>
       </c>
-      <c r="E15" s="11" t="inlineStr">
-        <is>
-          <t>Bio - Lza
-5º e 6º tempos</t>
-        </is>
-      </c>
+      <c r="E15" s="11" t="n"/>
       <c r="F15" s="11" t="inlineStr">
         <is>
           <t>Ing - Vir
 4º e 5º tempos</t>
         </is>
       </c>
-      <c r="G15" s="11" t="inlineStr">
+      <c r="G15" s="11" t="n"/>
+      <c r="H15" s="11" t="inlineStr">
+        <is>
+          <t>Hist - ALu
+2º e 3º tempos</t>
+        </is>
+      </c>
+      <c r="I15" s="11" t="inlineStr">
         <is>
           <t>Geo - Mlo
-1º e 2º tempos</t>
-        </is>
-      </c>
-      <c r="H15" s="11" t="n"/>
-      <c r="I15" s="11" t="n"/>
+2º e 3º tempos</t>
+        </is>
+      </c>
       <c r="J15" s="183" t="n"/>
       <c r="L15" s="17" t="n"/>
       <c r="M15" s="15" t="n"/>
@@ -13847,19 +13847,19 @@
           <t>unterrichtsfrei sem aula</t>
         </is>
       </c>
-      <c r="F18" s="11" t="inlineStr">
-        <is>
-          <t>Mat - BrSa/FBri
-5º e 6º tempos</t>
-        </is>
-      </c>
+      <c r="F18" s="11" t="n"/>
       <c r="G18" s="11" t="inlineStr">
         <is>
           <t>GL - EFr-Car-Swa
 2º e 3º tempos</t>
         </is>
       </c>
-      <c r="H18" s="11" t="n"/>
+      <c r="H18" s="11" t="inlineStr">
+        <is>
+          <t>LP/LIT/RED - BPad/MFo/SMo
+1º ao 3º tempos</t>
+        </is>
+      </c>
       <c r="I18" s="350" t="inlineStr">
         <is>
           <t>AG10
@@ -13931,15 +13931,20 @@
         <f>B21+4</f>
         <v/>
       </c>
-      <c r="E21" s="11" t="inlineStr">
-        <is>
-          <t>Qui - CAl
-3º e 4º tempos</t>
-        </is>
-      </c>
-      <c r="F21" s="62" t="n"/>
+      <c r="E21" s="11" t="n"/>
+      <c r="F21" s="62" t="inlineStr">
+        <is>
+          <t>Bio - Lza
+6º e 7º tempos</t>
+        </is>
+      </c>
       <c r="G21" s="11" t="n"/>
-      <c r="H21" s="11" t="n"/>
+      <c r="H21" s="11" t="inlineStr">
+        <is>
+          <t>Geo - Mlo
+4º e 5º tempos</t>
+        </is>
+      </c>
       <c r="I21" s="11" t="n"/>
       <c r="J21" s="183" t="n"/>
       <c r="L21" s="80" t="inlineStr">
@@ -14010,14 +14015,14 @@
         </is>
       </c>
       <c r="F24" s="283" t="n"/>
-      <c r="G24" s="79" t="n"/>
-      <c r="H24" s="283" t="n"/>
-      <c r="I24" s="78" t="inlineStr">
+      <c r="G24" s="353" t="inlineStr">
         <is>
           <t>Soc - Kle
 5º tempo</t>
         </is>
       </c>
+      <c r="H24" s="283" t="n"/>
+      <c r="I24" s="78" t="n"/>
       <c r="J24" s="265" t="n"/>
       <c r="L24" s="318" t="inlineStr">
         <is>
@@ -14031,13 +14036,13 @@
       <c r="A25" s="316" t="n"/>
       <c r="B25" s="313" t="n"/>
       <c r="C25" s="313" t="n"/>
-      <c r="D25" s="353" t="n"/>
+      <c r="D25" s="354" t="n"/>
       <c r="E25" s="283" t="n"/>
       <c r="F25" s="283" t="n"/>
       <c r="G25" s="79" t="n"/>
       <c r="H25" s="283" t="n"/>
       <c r="I25" s="78" t="n"/>
-      <c r="J25" s="354" t="n"/>
+      <c r="J25" s="355" t="n"/>
       <c r="L25" s="44" t="n"/>
       <c r="M25" s="321" t="inlineStr">
         <is>
@@ -14050,13 +14055,13 @@
       <c r="A26" s="316" t="n"/>
       <c r="B26" s="313" t="n"/>
       <c r="C26" s="313" t="n"/>
-      <c r="D26" s="353" t="n"/>
+      <c r="D26" s="354" t="n"/>
       <c r="E26" s="283" t="n"/>
       <c r="F26" s="283" t="n"/>
       <c r="G26" s="79" t="n"/>
       <c r="H26" s="283" t="n"/>
       <c r="I26" s="78" t="n"/>
-      <c r="J26" s="354" t="n"/>
+      <c r="J26" s="355" t="n"/>
       <c r="L26" s="43" t="n"/>
       <c r="M26" s="323" t="inlineStr">
         <is>
@@ -14083,12 +14088,17 @@
         <f>B27+4</f>
         <v/>
       </c>
-      <c r="E27" s="78" t="n"/>
+      <c r="E27" s="78" t="inlineStr">
+        <is>
+          <t>Mat - BrSa/FBri
+1º e 2º tempos</t>
+        </is>
+      </c>
       <c r="F27" s="283" t="n"/>
       <c r="G27" s="283" t="inlineStr">
         <is>
-          <t>Geo - Mlo
-1º e 2º tempos</t>
+          <t>GL - EFr-Car-Swa
+2º e 3º tempos</t>
         </is>
       </c>
       <c r="H27" s="283" t="n"/>
@@ -14106,13 +14116,13 @@
       <c r="A28" s="316" t="n"/>
       <c r="B28" s="313" t="n"/>
       <c r="C28" s="313" t="n"/>
-      <c r="D28" s="353" t="n"/>
+      <c r="D28" s="354" t="n"/>
       <c r="E28" s="78" t="n"/>
       <c r="F28" s="283" t="n"/>
       <c r="G28" s="283" t="n"/>
       <c r="H28" s="283" t="n"/>
       <c r="I28" s="283" t="n"/>
-      <c r="J28" s="354" t="n"/>
+      <c r="J28" s="355" t="n"/>
       <c r="L28" s="23" t="n"/>
       <c r="M28" s="325" t="inlineStr">
         <is>
@@ -14125,13 +14135,13 @@
       <c r="A29" s="316" t="n"/>
       <c r="B29" s="313" t="n"/>
       <c r="C29" s="313" t="n"/>
-      <c r="D29" s="353" t="n"/>
+      <c r="D29" s="354" t="n"/>
       <c r="E29" s="78" t="n"/>
       <c r="F29" s="283" t="n"/>
       <c r="G29" s="283" t="n"/>
       <c r="H29" s="283" t="n"/>
       <c r="I29" s="283" t="n"/>
-      <c r="J29" s="354" t="n"/>
+      <c r="J29" s="355" t="n"/>
       <c r="L29" s="46" t="n"/>
       <c r="M29" s="157" t="inlineStr">
         <is>
@@ -14160,12 +14170,17 @@
       </c>
       <c r="E30" s="283" t="inlineStr">
         <is>
-          <t>Bio - Lza
-5º e 6º tempos</t>
+          <t>LP/LIT/RED - BPad/MFo/SMo
+1º ao 3º tempos</t>
         </is>
       </c>
       <c r="F30" s="283" t="n"/>
-      <c r="G30" s="283" t="n"/>
+      <c r="G30" s="283" t="inlineStr">
+        <is>
+          <t>Ing - Vir
+4º e 5º tempos</t>
+        </is>
+      </c>
       <c r="H30" s="283" t="n"/>
       <c r="I30" s="283" t="n"/>
       <c r="J30" s="183" t="inlineStr">
@@ -14185,7 +14200,7 @@
       <c r="A31" s="316" t="n"/>
       <c r="B31" s="313" t="n"/>
       <c r="C31" s="313" t="n"/>
-      <c r="D31" s="353" t="n"/>
+      <c r="D31" s="354" t="n"/>
       <c r="E31" s="283" t="n"/>
       <c r="F31" s="283" t="n"/>
       <c r="G31" s="283" t="n"/>
@@ -14204,7 +14219,7 @@
       <c r="A32" s="316" t="n"/>
       <c r="B32" s="313" t="n"/>
       <c r="C32" s="313" t="n"/>
-      <c r="D32" s="353" t="n"/>
+      <c r="D32" s="354" t="n"/>
       <c r="E32" s="283" t="n"/>
       <c r="F32" s="283" t="n"/>
       <c r="G32" s="283" t="n"/>
@@ -14274,7 +14289,7 @@
     <row r="34" ht="26.25" customFormat="1" customHeight="1" s="4">
       <c r="A34" s="330" t="n"/>
       <c r="B34" s="331" t="n"/>
-      <c r="D34" s="355" t="n"/>
+      <c r="D34" s="356" t="n"/>
       <c r="E34" s="315" t="n"/>
       <c r="F34" s="315" t="n"/>
       <c r="G34" s="315" t="n"/>
@@ -14296,7 +14311,7 @@
     <row r="35" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A35" s="330" t="n"/>
       <c r="B35" s="332" t="n"/>
-      <c r="D35" s="356" t="n"/>
+      <c r="D35" s="357" t="n"/>
       <c r="E35" s="315" t="n"/>
       <c r="F35" s="315" t="n"/>
       <c r="G35" s="315" t="n"/>
@@ -14335,16 +14350,11 @@
       </c>
       <c r="E36" s="283" t="inlineStr">
         <is>
-          <t>Fis - VSi
-6º e 7º tempos</t>
-        </is>
-      </c>
-      <c r="F36" s="283" t="inlineStr">
-        <is>
-          <t>Ing - Vir
+          <t>Qui - CAl
 4º e 5º tempos</t>
         </is>
       </c>
+      <c r="F36" s="283" t="n"/>
       <c r="G36" s="283" t="n"/>
       <c r="H36" s="283" t="n"/>
       <c r="I36" s="283" t="n"/>
@@ -14364,13 +14374,13 @@
       <c r="A37" s="316" t="n"/>
       <c r="B37" s="313" t="n"/>
       <c r="C37" s="313" t="n"/>
-      <c r="D37" s="353" t="n"/>
+      <c r="D37" s="354" t="n"/>
       <c r="E37" s="283" t="n"/>
       <c r="F37" s="283" t="n"/>
       <c r="G37" s="283" t="n"/>
       <c r="H37" s="283" t="n"/>
       <c r="I37" s="283" t="n"/>
-      <c r="J37" s="354" t="n"/>
+      <c r="J37" s="355" t="n"/>
       <c r="L37" s="4" t="inlineStr">
         <is>
           <t>18.08,19.08</t>
@@ -14386,13 +14396,13 @@
       <c r="A38" s="316" t="n"/>
       <c r="B38" s="313" t="n"/>
       <c r="C38" s="313" t="n"/>
-      <c r="D38" s="353" t="n"/>
+      <c r="D38" s="354" t="n"/>
       <c r="E38" s="283" t="n"/>
       <c r="F38" s="283" t="n"/>
       <c r="G38" s="283" t="n"/>
       <c r="H38" s="283" t="n"/>
       <c r="I38" s="283" t="n"/>
-      <c r="J38" s="354" t="n"/>
+      <c r="J38" s="355" t="n"/>
     </row>
     <row r="39" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A39" s="119">
@@ -14412,17 +14422,12 @@
         <f>B39+4</f>
         <v/>
       </c>
-      <c r="E39" s="283" t="inlineStr">
-        <is>
-          <t>LP/LIT/RED - BPad/MFo/SMo
-1º ao 3º tempos</t>
-        </is>
-      </c>
+      <c r="E39" s="283" t="n"/>
       <c r="F39" s="283" t="n"/>
       <c r="G39" s="283" t="inlineStr">
         <is>
           <t>Fil - LAn
-7º tempo</t>
+1º tempo</t>
         </is>
       </c>
       <c r="H39" s="283" t="n"/>
@@ -14433,25 +14438,25 @@
       <c r="A40" s="316" t="n"/>
       <c r="B40" s="313" t="n"/>
       <c r="C40" s="313" t="n"/>
-      <c r="D40" s="353" t="n"/>
+      <c r="D40" s="354" t="n"/>
       <c r="E40" s="283" t="n"/>
       <c r="F40" s="283" t="n"/>
       <c r="G40" s="283" t="n"/>
       <c r="H40" s="283" t="n"/>
       <c r="I40" s="283" t="n"/>
-      <c r="J40" s="354" t="n"/>
+      <c r="J40" s="355" t="n"/>
     </row>
     <row r="41" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A41" s="316" t="n"/>
       <c r="B41" s="313" t="n"/>
       <c r="C41" s="313" t="n"/>
-      <c r="D41" s="353" t="n"/>
+      <c r="D41" s="354" t="n"/>
       <c r="E41" s="283" t="n"/>
       <c r="F41" s="283" t="n"/>
       <c r="G41" s="283" t="n"/>
       <c r="H41" s="283" t="n"/>
       <c r="I41" s="283" t="n"/>
-      <c r="J41" s="354" t="n"/>
+      <c r="J41" s="355" t="n"/>
     </row>
     <row r="42" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A42" s="119">
@@ -14476,8 +14481,8 @@
       <c r="G42" s="283" t="n"/>
       <c r="H42" s="283" t="inlineStr">
         <is>
-          <t>Hist - ALu
-2º e 3º tempos</t>
+          <t>Fis - VSi
+1º e 2º tempos</t>
         </is>
       </c>
       <c r="I42" s="283" t="n"/>
@@ -14493,26 +14498,26 @@
       <c r="A43" s="316" t="n"/>
       <c r="B43" s="313" t="n"/>
       <c r="C43" s="313" t="n"/>
-      <c r="D43" s="353" t="n"/>
+      <c r="D43" s="354" t="n"/>
       <c r="E43" s="283" t="n"/>
       <c r="F43" s="283" t="n"/>
       <c r="G43" s="283" t="n"/>
       <c r="H43" s="283" t="n"/>
       <c r="I43" s="283" t="n"/>
-      <c r="J43" s="354" t="n"/>
+      <c r="J43" s="355" t="n"/>
       <c r="L43" s="331" t="n"/>
     </row>
     <row r="44" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A44" s="316" t="n"/>
       <c r="B44" s="313" t="n"/>
       <c r="C44" s="313" t="n"/>
-      <c r="D44" s="353" t="n"/>
+      <c r="D44" s="354" t="n"/>
       <c r="E44" s="283" t="n"/>
       <c r="F44" s="283" t="n"/>
       <c r="G44" s="283" t="n"/>
       <c r="H44" s="283" t="n"/>
       <c r="I44" s="283" t="n"/>
-      <c r="J44" s="354" t="n"/>
+      <c r="J44" s="355" t="n"/>
       <c r="L44" s="331" t="n"/>
     </row>
     <row r="45" ht="18" customFormat="1" customHeight="1" s="4">
@@ -14533,21 +14538,16 @@
         <f>B45+4</f>
         <v/>
       </c>
-      <c r="E45" s="283" t="inlineStr">
-        <is>
-          <t>Mat - BrSa/FBri
+      <c r="E45" s="283" t="n"/>
+      <c r="F45" s="283" t="n"/>
+      <c r="G45" s="283" t="n"/>
+      <c r="H45" s="283" t="inlineStr">
+        <is>
+          <t>Hist - ALu
 2º e 3º tempos</t>
         </is>
       </c>
-      <c r="F45" s="283" t="n"/>
-      <c r="G45" s="283" t="inlineStr">
-        <is>
-          <t>GL - EFr-Car-Swa
-2º e 3º tempos</t>
-        </is>
-      </c>
-      <c r="H45" s="283" t="n"/>
-      <c r="I45" s="357" t="inlineStr">
+      <c r="I45" s="358" t="inlineStr">
         <is>
           <t>2CH
 10,12</t>
@@ -14560,26 +14560,26 @@
       <c r="A46" s="316" t="n"/>
       <c r="B46" s="313" t="n"/>
       <c r="C46" s="313" t="n"/>
-      <c r="D46" s="353" t="n"/>
+      <c r="D46" s="354" t="n"/>
       <c r="E46" s="283" t="n"/>
       <c r="F46" s="283" t="n"/>
       <c r="G46" s="283" t="n"/>
       <c r="H46" s="283" t="n"/>
-      <c r="I46" s="358" t="n"/>
-      <c r="J46" s="354" t="n"/>
+      <c r="I46" s="359" t="n"/>
+      <c r="J46" s="355" t="n"/>
       <c r="L46" s="331" t="n"/>
     </row>
     <row r="47" ht="51" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A47" s="316" t="n"/>
       <c r="B47" s="313" t="n"/>
       <c r="C47" s="313" t="n"/>
-      <c r="D47" s="353" t="n"/>
+      <c r="D47" s="354" t="n"/>
       <c r="E47" s="283" t="n"/>
       <c r="F47" s="283" t="n"/>
       <c r="G47" s="283" t="n"/>
       <c r="H47" s="283" t="n"/>
-      <c r="I47" s="359" t="n"/>
-      <c r="J47" s="354" t="n"/>
+      <c r="I47" s="360" t="n"/>
+      <c r="J47" s="355" t="n"/>
       <c r="L47" s="332" t="n"/>
     </row>
     <row r="48" ht="23.25" customFormat="1" customHeight="1" s="4">
@@ -14601,7 +14601,7 @@
         <v/>
       </c>
       <c r="E48" s="283" t="n"/>
-      <c r="F48" s="360" t="inlineStr">
+      <c r="F48" s="361" t="inlineStr">
         <is>
           <t>CC
 10,12</t>
@@ -14620,25 +14620,25 @@
       <c r="A49" s="316" t="n"/>
       <c r="B49" s="313" t="n"/>
       <c r="C49" s="313" t="n"/>
-      <c r="D49" s="353" t="n"/>
+      <c r="D49" s="354" t="n"/>
       <c r="E49" s="283" t="n"/>
-      <c r="F49" s="358" t="n"/>
+      <c r="F49" s="359" t="n"/>
       <c r="G49" s="283" t="n"/>
       <c r="H49" s="283" t="n"/>
       <c r="I49" s="315" t="n"/>
-      <c r="J49" s="354" t="n"/>
+      <c r="J49" s="355" t="n"/>
     </row>
     <row r="50" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A50" s="316" t="n"/>
       <c r="B50" s="313" t="n"/>
       <c r="C50" s="313" t="n"/>
-      <c r="D50" s="353" t="n"/>
+      <c r="D50" s="354" t="n"/>
       <c r="E50" s="78" t="n"/>
-      <c r="F50" s="359" t="n"/>
+      <c r="F50" s="360" t="n"/>
       <c r="G50" s="283" t="n"/>
       <c r="H50" s="283" t="n"/>
       <c r="I50" s="315" t="n"/>
-      <c r="J50" s="354" t="n"/>
+      <c r="J50" s="355" t="n"/>
     </row>
     <row r="51" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A51" s="119">
@@ -14662,7 +14662,7 @@
       <c r="F51" s="183" t="n"/>
       <c r="G51" s="183" t="n"/>
       <c r="H51" s="183" t="n"/>
-      <c r="I51" s="357" t="inlineStr">
+      <c r="I51" s="358" t="inlineStr">
         <is>
           <t>2CH
 9,11</t>
@@ -14674,25 +14674,25 @@
       <c r="A52" s="316" t="n"/>
       <c r="B52" s="313" t="n"/>
       <c r="C52" s="313" t="n"/>
-      <c r="D52" s="353" t="n"/>
+      <c r="D52" s="354" t="n"/>
       <c r="E52" s="283" t="n"/>
       <c r="F52" s="315" t="n"/>
       <c r="G52" s="315" t="n"/>
       <c r="H52" s="315" t="n"/>
-      <c r="I52" s="358" t="n"/>
-      <c r="J52" s="354" t="n"/>
+      <c r="I52" s="359" t="n"/>
+      <c r="J52" s="355" t="n"/>
     </row>
     <row r="53" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A53" s="316" t="n"/>
       <c r="B53" s="313" t="n"/>
       <c r="C53" s="313" t="n"/>
-      <c r="D53" s="353" t="n"/>
+      <c r="D53" s="354" t="n"/>
       <c r="E53" s="283" t="n"/>
       <c r="F53" s="315" t="n"/>
       <c r="G53" s="315" t="n"/>
       <c r="H53" s="315" t="n"/>
-      <c r="I53" s="359" t="n"/>
-      <c r="J53" s="354" t="n"/>
+      <c r="I53" s="360" t="n"/>
+      <c r="J53" s="355" t="n"/>
     </row>
     <row r="54" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A54" s="119">
@@ -14723,25 +14723,25 @@
       <c r="A55" s="316" t="n"/>
       <c r="B55" s="313" t="n"/>
       <c r="C55" s="313" t="n"/>
-      <c r="D55" s="353" t="n"/>
+      <c r="D55" s="354" t="n"/>
       <c r="E55" s="315" t="n"/>
       <c r="F55" s="315" t="n"/>
       <c r="G55" s="315" t="n"/>
       <c r="H55" s="315" t="n"/>
       <c r="I55" s="315" t="n"/>
-      <c r="J55" s="354" t="n"/>
+      <c r="J55" s="355" t="n"/>
     </row>
     <row r="56" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A56" s="316" t="n"/>
       <c r="B56" s="313" t="n"/>
       <c r="C56" s="313" t="n"/>
-      <c r="D56" s="353" t="n"/>
+      <c r="D56" s="354" t="n"/>
       <c r="E56" s="315" t="n"/>
       <c r="F56" s="315" t="n"/>
       <c r="G56" s="315" t="n"/>
       <c r="H56" s="315" t="n"/>
       <c r="I56" s="315" t="n"/>
-      <c r="J56" s="354" t="n"/>
+      <c r="J56" s="355" t="n"/>
     </row>
     <row r="57" ht="25.5" customFormat="1" customHeight="1" s="4">
       <c r="A57" s="119">
@@ -14762,7 +14762,7 @@
         <v/>
       </c>
       <c r="E57" s="183" t="n"/>
-      <c r="F57" s="360" t="inlineStr">
+      <c r="F57" s="361" t="inlineStr">
         <is>
           <t>CC
 9,11</t>
@@ -14777,25 +14777,25 @@
       <c r="A58" s="316" t="n"/>
       <c r="B58" s="313" t="n"/>
       <c r="C58" s="313" t="n"/>
-      <c r="D58" s="353" t="n"/>
+      <c r="D58" s="354" t="n"/>
       <c r="E58" s="315" t="n"/>
-      <c r="F58" s="358" t="n"/>
+      <c r="F58" s="359" t="n"/>
       <c r="G58" s="315" t="n"/>
       <c r="H58" s="315" t="n"/>
       <c r="I58" s="315" t="n"/>
-      <c r="J58" s="354" t="n"/>
+      <c r="J58" s="355" t="n"/>
     </row>
     <row r="59" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A59" s="316" t="n"/>
       <c r="B59" s="313" t="n"/>
       <c r="C59" s="313" t="n"/>
-      <c r="D59" s="353" t="n"/>
+      <c r="D59" s="354" t="n"/>
       <c r="E59" s="315" t="n"/>
-      <c r="F59" s="359" t="n"/>
+      <c r="F59" s="360" t="n"/>
       <c r="G59" s="315" t="n"/>
       <c r="H59" s="315" t="n"/>
       <c r="I59" s="315" t="n"/>
-      <c r="J59" s="354" t="n"/>
+      <c r="J59" s="355" t="n"/>
     </row>
     <row r="60" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A60" s="281">
@@ -14827,24 +14827,24 @@
       <c r="B61" s="331" t="n"/>
       <c r="C61" s="331" t="n"/>
       <c r="D61" s="331" t="n"/>
-      <c r="E61" s="358" t="n"/>
-      <c r="F61" s="358" t="n"/>
-      <c r="G61" s="358" t="n"/>
-      <c r="H61" s="358" t="n"/>
-      <c r="I61" s="358" t="n"/>
-      <c r="J61" s="358" t="n"/>
+      <c r="E61" s="359" t="n"/>
+      <c r="F61" s="359" t="n"/>
+      <c r="G61" s="359" t="n"/>
+      <c r="H61" s="359" t="n"/>
+      <c r="I61" s="359" t="n"/>
+      <c r="J61" s="359" t="n"/>
     </row>
     <row r="62" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A62" s="332" t="n"/>
       <c r="B62" s="332" t="n"/>
       <c r="C62" s="332" t="n"/>
       <c r="D62" s="332" t="n"/>
-      <c r="E62" s="361" t="n"/>
-      <c r="F62" s="361" t="n"/>
-      <c r="G62" s="361" t="n"/>
-      <c r="H62" s="361" t="n"/>
-      <c r="I62" s="361" t="n"/>
-      <c r="J62" s="361" t="n"/>
+      <c r="E62" s="362" t="n"/>
+      <c r="F62" s="362" t="n"/>
+      <c r="G62" s="362" t="n"/>
+      <c r="H62" s="362" t="n"/>
+      <c r="I62" s="362" t="n"/>
+      <c r="J62" s="362" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="146">
@@ -15301,18 +15301,23 @@
       </c>
       <c r="E9" s="183" t="inlineStr">
         <is>
-          <t>GL - CBu-Swa-SGa
-4º e 5º tempos</t>
-        </is>
-      </c>
-      <c r="F9" s="183" t="inlineStr">
-        <is>
-          <t>DaF - CBu-SGa-Swa
-3º e 4º tempos</t>
-        </is>
-      </c>
-      <c r="G9" s="183" t="n"/>
-      <c r="H9" s="183" t="n"/>
+          <t>LP/LIT/RED - ACo/AMu/Raf
+1º ao 3º tempos</t>
+        </is>
+      </c>
+      <c r="F9" s="183" t="n"/>
+      <c r="G9" s="183" t="inlineStr">
+        <is>
+          <t>Geo - Mar
+1º e 2º tempos</t>
+        </is>
+      </c>
+      <c r="H9" s="183" t="inlineStr">
+        <is>
+          <t>Bio - Ale
+2º e 3º tempos</t>
+        </is>
+      </c>
       <c r="I9" s="183" t="n"/>
       <c r="J9" s="183" t="n"/>
       <c r="L9" s="16" t="inlineStr">
@@ -15393,7 +15398,7 @@
       </c>
       <c r="E12" s="11" t="inlineStr">
         <is>
-          <t>Mat - ClaMe/JJ
+          <t>Qui - CAl
 1º e 2º tempos</t>
         </is>
       </c>
@@ -15411,8 +15416,8 @@
       </c>
       <c r="H12" s="11" t="inlineStr">
         <is>
-          <t>Fis - Cadu
-1º e 2º tempos</t>
+          <t>Ing - Bea
+4º e 5º tempos</t>
         </is>
       </c>
       <c r="I12" s="11" t="n"/>
@@ -15474,24 +15479,19 @@
       </c>
       <c r="E15" s="11" t="inlineStr">
         <is>
-          <t>Qui - CAl
+          <t>GL - CBu-Swa-SGa
+4º e 5º tempos</t>
+        </is>
+      </c>
+      <c r="F15" s="11" t="inlineStr">
+        <is>
+          <t>Mat - ClaMe/JJ
 1º e 2º tempos</t>
         </is>
       </c>
-      <c r="F15" s="11" t="n"/>
       <c r="G15" s="11" t="n"/>
-      <c r="H15" s="11" t="inlineStr">
-        <is>
-          <t>LP/LIT/RED - ACo/AMu/Raf
-2º ao 4º tempos</t>
-        </is>
-      </c>
-      <c r="I15" s="11" t="inlineStr">
-        <is>
-          <t>Bio - Ale
-3º e 4º tempos</t>
-        </is>
-      </c>
+      <c r="H15" s="11" t="n"/>
+      <c r="I15" s="11" t="n"/>
       <c r="J15" s="183" t="n"/>
       <c r="L15" s="17" t="n"/>
       <c r="M15" s="15" t="n"/>
@@ -15553,23 +15553,23 @@
       </c>
       <c r="F18" s="11" t="inlineStr">
         <is>
+          <t>DaF - CBu-SGa-Swa
+4º e 5º tempos</t>
+        </is>
+      </c>
+      <c r="G18" s="11" t="inlineStr">
+        <is>
           <t>Hist - Ver
 1º e 2º tempos</t>
         </is>
       </c>
-      <c r="G18" s="11" t="n"/>
       <c r="H18" s="11" t="inlineStr">
         <is>
-          <t>Ing - Bea
-4º e 5º tempos</t>
-        </is>
-      </c>
-      <c r="I18" s="350" t="inlineStr">
-        <is>
-          <t>Geo - Mar
-3º e 4º tempos</t>
-        </is>
-      </c>
+          <t>Fis - Cadu
+1º e 2º tempos</t>
+        </is>
+      </c>
+      <c r="I18" s="350" t="n"/>
       <c r="J18" s="262" t="inlineStr">
         <is>
           <t>2CH 9,10,11,12</t>
@@ -15635,19 +15635,19 @@
         <f>B21+4</f>
         <v/>
       </c>
-      <c r="E21" s="11" t="inlineStr">
-        <is>
-          <t>Mat - ClaMe/JJ
-1º e 2º tempos</t>
-        </is>
-      </c>
+      <c r="E21" s="11" t="n"/>
       <c r="F21" s="62" t="n"/>
       <c r="G21" s="11" t="n"/>
-      <c r="H21" s="11" t="n"/>
+      <c r="H21" s="11" t="inlineStr">
+        <is>
+          <t>Fis - Cadu
+1º e 2º tempos</t>
+        </is>
+      </c>
       <c r="I21" s="11" t="inlineStr">
         <is>
-          <t>Bio - Ale
-3º e 4º tempos</t>
+          <t>Soc - Kle
+4º tempo</t>
         </is>
       </c>
       <c r="J21" s="183" t="n"/>
@@ -15712,21 +15712,16 @@
         <f>B24+4</f>
         <v/>
       </c>
-      <c r="E24" s="283" t="inlineStr">
+      <c r="E24" s="283" t="n"/>
+      <c r="F24" s="283" t="inlineStr">
         <is>
           <t>DaF - CBu-SGa-Swa
-5º e 6º tempos</t>
-        </is>
-      </c>
-      <c r="F24" s="283" t="n"/>
+4º e 5º tempos</t>
+        </is>
+      </c>
       <c r="G24" s="79" t="n"/>
       <c r="H24" s="283" t="n"/>
-      <c r="I24" s="78" t="inlineStr">
-        <is>
-          <t>Soc - Kle
-2º tempo</t>
-        </is>
-      </c>
+      <c r="I24" s="78" t="n"/>
       <c r="J24" s="265" t="n"/>
       <c r="L24" s="318" t="inlineStr">
         <is>
@@ -15740,13 +15735,13 @@
       <c r="A25" s="316" t="n"/>
       <c r="B25" s="313" t="n"/>
       <c r="C25" s="313" t="n"/>
-      <c r="D25" s="353" t="n"/>
+      <c r="D25" s="354" t="n"/>
       <c r="E25" s="283" t="n"/>
       <c r="F25" s="283" t="n"/>
       <c r="G25" s="79" t="n"/>
       <c r="H25" s="283" t="n"/>
       <c r="I25" s="78" t="n"/>
-      <c r="J25" s="354" t="n"/>
+      <c r="J25" s="355" t="n"/>
       <c r="L25" s="44" t="n"/>
       <c r="M25" s="321" t="inlineStr">
         <is>
@@ -15759,13 +15754,13 @@
       <c r="A26" s="316" t="n"/>
       <c r="B26" s="313" t="n"/>
       <c r="C26" s="313" t="n"/>
-      <c r="D26" s="353" t="n"/>
+      <c r="D26" s="354" t="n"/>
       <c r="E26" s="283" t="n"/>
       <c r="F26" s="283" t="n"/>
       <c r="G26" s="79" t="n"/>
       <c r="H26" s="283" t="n"/>
       <c r="I26" s="78" t="n"/>
-      <c r="J26" s="354" t="n"/>
+      <c r="J26" s="355" t="n"/>
       <c r="L26" s="43" t="n"/>
       <c r="M26" s="323" t="inlineStr">
         <is>
@@ -15792,15 +15787,20 @@
         <f>B27+4</f>
         <v/>
       </c>
-      <c r="E27" s="78" t="inlineStr">
-        <is>
-          <t>Qui - CAl
-1º e 2º tempos</t>
-        </is>
-      </c>
+      <c r="E27" s="78" t="n"/>
       <c r="F27" s="283" t="n"/>
-      <c r="G27" s="283" t="n"/>
-      <c r="H27" s="283" t="n"/>
+      <c r="G27" s="283" t="inlineStr">
+        <is>
+          <t>GL - CBu-Swa-SGa
+4º e 5º tempos</t>
+        </is>
+      </c>
+      <c r="H27" s="283" t="inlineStr">
+        <is>
+          <t>Ing - Bea
+4º e 5º tempos</t>
+        </is>
+      </c>
       <c r="I27" s="283" t="n"/>
       <c r="J27" s="265" t="n"/>
       <c r="L27" s="45" t="n"/>
@@ -15815,13 +15815,13 @@
       <c r="A28" s="316" t="n"/>
       <c r="B28" s="313" t="n"/>
       <c r="C28" s="313" t="n"/>
-      <c r="D28" s="353" t="n"/>
+      <c r="D28" s="354" t="n"/>
       <c r="E28" s="78" t="n"/>
       <c r="F28" s="283" t="n"/>
       <c r="G28" s="283" t="n"/>
       <c r="H28" s="283" t="n"/>
       <c r="I28" s="283" t="n"/>
-      <c r="J28" s="354" t="n"/>
+      <c r="J28" s="355" t="n"/>
       <c r="L28" s="23" t="n"/>
       <c r="M28" s="325" t="inlineStr">
         <is>
@@ -15834,13 +15834,13 @@
       <c r="A29" s="316" t="n"/>
       <c r="B29" s="313" t="n"/>
       <c r="C29" s="313" t="n"/>
-      <c r="D29" s="353" t="n"/>
+      <c r="D29" s="354" t="n"/>
       <c r="E29" s="78" t="n"/>
       <c r="F29" s="283" t="n"/>
       <c r="G29" s="283" t="n"/>
       <c r="H29" s="283" t="n"/>
       <c r="I29" s="283" t="n"/>
-      <c r="J29" s="354" t="n"/>
+      <c r="J29" s="355" t="n"/>
       <c r="L29" s="46" t="n"/>
       <c r="M29" s="157" t="inlineStr">
         <is>
@@ -15869,17 +15869,17 @@
       </c>
       <c r="E30" s="283" t="inlineStr">
         <is>
-          <t>Geo - Mar
-2º e 3º tempos</t>
-        </is>
-      </c>
-      <c r="F30" s="283" t="inlineStr">
+          <t>LP/LIT/RED - ACo/AMu/Raf
+1º ao 3º tempos</t>
+        </is>
+      </c>
+      <c r="F30" s="283" t="n"/>
+      <c r="G30" s="283" t="inlineStr">
         <is>
           <t>Hist - Ver
 1º e 2º tempos</t>
         </is>
       </c>
-      <c r="G30" s="283" t="n"/>
       <c r="H30" s="283" t="n"/>
       <c r="I30" s="283" t="n"/>
       <c r="J30" s="183" t="inlineStr">
@@ -15899,7 +15899,7 @@
       <c r="A31" s="316" t="n"/>
       <c r="B31" s="313" t="n"/>
       <c r="C31" s="313" t="n"/>
-      <c r="D31" s="353" t="n"/>
+      <c r="D31" s="354" t="n"/>
       <c r="E31" s="283" t="n"/>
       <c r="F31" s="283" t="n"/>
       <c r="G31" s="283" t="n"/>
@@ -15918,7 +15918,7 @@
       <c r="A32" s="316" t="n"/>
       <c r="B32" s="313" t="n"/>
       <c r="C32" s="313" t="n"/>
-      <c r="D32" s="353" t="n"/>
+      <c r="D32" s="354" t="n"/>
       <c r="E32" s="283" t="n"/>
       <c r="F32" s="283" t="n"/>
       <c r="G32" s="283" t="n"/>
@@ -15988,7 +15988,7 @@
     <row r="34" ht="26.25" customFormat="1" customHeight="1" s="4">
       <c r="A34" s="330" t="n"/>
       <c r="B34" s="331" t="n"/>
-      <c r="D34" s="355" t="n"/>
+      <c r="D34" s="356" t="n"/>
       <c r="E34" s="315" t="n"/>
       <c r="F34" s="315" t="n"/>
       <c r="G34" s="315" t="n"/>
@@ -16010,7 +16010,7 @@
     <row r="35" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A35" s="330" t="n"/>
       <c r="B35" s="332" t="n"/>
-      <c r="D35" s="356" t="n"/>
+      <c r="D35" s="357" t="n"/>
       <c r="E35" s="315" t="n"/>
       <c r="F35" s="315" t="n"/>
       <c r="G35" s="315" t="n"/>
@@ -16047,14 +16047,19 @@
         <f>B36+4</f>
         <v/>
       </c>
-      <c r="E36" s="283" t="n"/>
-      <c r="F36" s="283" t="n"/>
-      <c r="G36" s="283" t="inlineStr">
-        <is>
-          <t>Fil - LAn
-9º tempo</t>
-        </is>
-      </c>
+      <c r="E36" s="283" t="inlineStr">
+        <is>
+          <t>Mat - ClaMe/JJ
+2º e 3º tempos</t>
+        </is>
+      </c>
+      <c r="F36" s="283" t="inlineStr">
+        <is>
+          <t>Qui - CAl
+1º e 2º tempos</t>
+        </is>
+      </c>
+      <c r="G36" s="283" t="n"/>
       <c r="H36" s="283" t="n"/>
       <c r="I36" s="283" t="n"/>
       <c r="J36" s="265" t="n"/>
@@ -16073,13 +16078,13 @@
       <c r="A37" s="316" t="n"/>
       <c r="B37" s="313" t="n"/>
       <c r="C37" s="313" t="n"/>
-      <c r="D37" s="353" t="n"/>
+      <c r="D37" s="354" t="n"/>
       <c r="E37" s="283" t="n"/>
       <c r="F37" s="283" t="n"/>
       <c r="G37" s="283" t="n"/>
       <c r="H37" s="283" t="n"/>
       <c r="I37" s="283" t="n"/>
-      <c r="J37" s="354" t="n"/>
+      <c r="J37" s="355" t="n"/>
       <c r="L37" s="4" t="inlineStr">
         <is>
           <t>18.08,19.08</t>
@@ -16095,13 +16100,13 @@
       <c r="A38" s="316" t="n"/>
       <c r="B38" s="313" t="n"/>
       <c r="C38" s="313" t="n"/>
-      <c r="D38" s="353" t="n"/>
+      <c r="D38" s="354" t="n"/>
       <c r="E38" s="283" t="n"/>
       <c r="F38" s="283" t="n"/>
       <c r="G38" s="283" t="n"/>
       <c r="H38" s="283" t="n"/>
       <c r="I38" s="283" t="n"/>
-      <c r="J38" s="354" t="n"/>
+      <c r="J38" s="355" t="n"/>
     </row>
     <row r="39" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A39" s="119">
@@ -16142,25 +16147,25 @@
       <c r="A40" s="316" t="n"/>
       <c r="B40" s="313" t="n"/>
       <c r="C40" s="313" t="n"/>
-      <c r="D40" s="353" t="n"/>
+      <c r="D40" s="354" t="n"/>
       <c r="E40" s="283" t="n"/>
       <c r="F40" s="283" t="n"/>
       <c r="G40" s="283" t="n"/>
       <c r="H40" s="283" t="n"/>
       <c r="I40" s="283" t="n"/>
-      <c r="J40" s="354" t="n"/>
+      <c r="J40" s="355" t="n"/>
     </row>
     <row r="41" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A41" s="316" t="n"/>
       <c r="B41" s="313" t="n"/>
       <c r="C41" s="313" t="n"/>
-      <c r="D41" s="353" t="n"/>
+      <c r="D41" s="354" t="n"/>
       <c r="E41" s="283" t="n"/>
       <c r="F41" s="283" t="n"/>
       <c r="G41" s="283" t="n"/>
       <c r="H41" s="283" t="n"/>
       <c r="I41" s="283" t="n"/>
-      <c r="J41" s="354" t="n"/>
+      <c r="J41" s="355" t="n"/>
     </row>
     <row r="42" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A42" s="119">
@@ -16184,8 +16189,8 @@
       <c r="F42" s="283" t="n"/>
       <c r="G42" s="283" t="inlineStr">
         <is>
-          <t>GL - CBu-Swa-SGa
-3º e 4º tempos</t>
+          <t>Fil - LAn
+11º tempo</t>
         </is>
       </c>
       <c r="H42" s="283" t="n"/>
@@ -16202,26 +16207,26 @@
       <c r="A43" s="316" t="n"/>
       <c r="B43" s="313" t="n"/>
       <c r="C43" s="313" t="n"/>
-      <c r="D43" s="353" t="n"/>
+      <c r="D43" s="354" t="n"/>
       <c r="E43" s="283" t="n"/>
       <c r="F43" s="283" t="n"/>
       <c r="G43" s="283" t="n"/>
       <c r="H43" s="283" t="n"/>
       <c r="I43" s="283" t="n"/>
-      <c r="J43" s="354" t="n"/>
+      <c r="J43" s="355" t="n"/>
       <c r="L43" s="331" t="n"/>
     </row>
     <row r="44" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A44" s="316" t="n"/>
       <c r="B44" s="313" t="n"/>
       <c r="C44" s="313" t="n"/>
-      <c r="D44" s="353" t="n"/>
+      <c r="D44" s="354" t="n"/>
       <c r="E44" s="283" t="n"/>
       <c r="F44" s="283" t="n"/>
       <c r="G44" s="283" t="n"/>
       <c r="H44" s="283" t="n"/>
       <c r="I44" s="283" t="n"/>
-      <c r="J44" s="354" t="n"/>
+      <c r="J44" s="355" t="n"/>
       <c r="L44" s="331" t="n"/>
     </row>
     <row r="45" ht="18" customFormat="1" customHeight="1" s="4">
@@ -16242,21 +16247,16 @@
         <f>B45+4</f>
         <v/>
       </c>
-      <c r="E45" s="283" t="inlineStr">
-        <is>
-          <t>LP/LIT/RED - ACo/AMu/Raf
-2º ao 4º tempos</t>
-        </is>
-      </c>
+      <c r="E45" s="283" t="n"/>
       <c r="F45" s="283" t="n"/>
-      <c r="G45" s="283" t="n"/>
-      <c r="H45" s="283" t="inlineStr">
-        <is>
-          <t>Fis - Cadu
+      <c r="G45" s="283" t="inlineStr">
+        <is>
+          <t>Geo - Mar
 1º e 2º tempos</t>
         </is>
       </c>
-      <c r="I45" s="357" t="n"/>
+      <c r="H45" s="283" t="n"/>
+      <c r="I45" s="358" t="n"/>
       <c r="J45" s="269" t="n"/>
       <c r="L45" s="331" t="n"/>
     </row>
@@ -16264,26 +16264,26 @@
       <c r="A46" s="316" t="n"/>
       <c r="B46" s="313" t="n"/>
       <c r="C46" s="313" t="n"/>
-      <c r="D46" s="353" t="n"/>
+      <c r="D46" s="354" t="n"/>
       <c r="E46" s="283" t="n"/>
       <c r="F46" s="283" t="n"/>
       <c r="G46" s="283" t="n"/>
       <c r="H46" s="283" t="n"/>
-      <c r="I46" s="358" t="n"/>
-      <c r="J46" s="354" t="n"/>
+      <c r="I46" s="359" t="n"/>
+      <c r="J46" s="355" t="n"/>
       <c r="L46" s="331" t="n"/>
     </row>
     <row r="47" ht="51" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A47" s="316" t="n"/>
       <c r="B47" s="313" t="n"/>
       <c r="C47" s="313" t="n"/>
-      <c r="D47" s="353" t="n"/>
+      <c r="D47" s="354" t="n"/>
       <c r="E47" s="283" t="n"/>
       <c r="F47" s="283" t="n"/>
       <c r="G47" s="283" t="n"/>
       <c r="H47" s="283" t="n"/>
-      <c r="I47" s="359" t="n"/>
-      <c r="J47" s="354" t="n"/>
+      <c r="I47" s="360" t="n"/>
+      <c r="J47" s="355" t="n"/>
       <c r="L47" s="332" t="n"/>
     </row>
     <row r="48" ht="23.25" customFormat="1" customHeight="1" s="4">
@@ -16305,12 +16305,12 @@
         <v/>
       </c>
       <c r="E48" s="283" t="n"/>
-      <c r="F48" s="360" t="n"/>
+      <c r="F48" s="361" t="n"/>
       <c r="G48" s="283" t="n"/>
       <c r="H48" s="283" t="inlineStr">
         <is>
-          <t>Ing - Bea
-4º e 5º tempos</t>
+          <t>Bio - Ale
+2º e 3º tempos</t>
         </is>
       </c>
       <c r="I48" s="183" t="inlineStr">
@@ -16324,25 +16324,25 @@
       <c r="A49" s="316" t="n"/>
       <c r="B49" s="313" t="n"/>
       <c r="C49" s="313" t="n"/>
-      <c r="D49" s="353" t="n"/>
+      <c r="D49" s="354" t="n"/>
       <c r="E49" s="283" t="n"/>
-      <c r="F49" s="358" t="n"/>
+      <c r="F49" s="359" t="n"/>
       <c r="G49" s="283" t="n"/>
       <c r="H49" s="283" t="n"/>
       <c r="I49" s="315" t="n"/>
-      <c r="J49" s="354" t="n"/>
+      <c r="J49" s="355" t="n"/>
     </row>
     <row r="50" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A50" s="316" t="n"/>
       <c r="B50" s="313" t="n"/>
       <c r="C50" s="313" t="n"/>
-      <c r="D50" s="353" t="n"/>
+      <c r="D50" s="354" t="n"/>
       <c r="E50" s="78" t="n"/>
-      <c r="F50" s="359" t="n"/>
+      <c r="F50" s="360" t="n"/>
       <c r="G50" s="283" t="n"/>
       <c r="H50" s="283" t="n"/>
       <c r="I50" s="315" t="n"/>
-      <c r="J50" s="354" t="n"/>
+      <c r="J50" s="355" t="n"/>
     </row>
     <row r="51" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A51" s="119">
@@ -16366,7 +16366,7 @@
       <c r="F51" s="183" t="n"/>
       <c r="G51" s="183" t="n"/>
       <c r="H51" s="183" t="n"/>
-      <c r="I51" s="357" t="inlineStr">
+      <c r="I51" s="358" t="inlineStr">
         <is>
           <t>2CH
 9,11</t>
@@ -16378,25 +16378,25 @@
       <c r="A52" s="316" t="n"/>
       <c r="B52" s="313" t="n"/>
       <c r="C52" s="313" t="n"/>
-      <c r="D52" s="353" t="n"/>
+      <c r="D52" s="354" t="n"/>
       <c r="E52" s="283" t="n"/>
       <c r="F52" s="315" t="n"/>
       <c r="G52" s="315" t="n"/>
       <c r="H52" s="315" t="n"/>
-      <c r="I52" s="358" t="n"/>
-      <c r="J52" s="354" t="n"/>
+      <c r="I52" s="359" t="n"/>
+      <c r="J52" s="355" t="n"/>
     </row>
     <row r="53" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A53" s="316" t="n"/>
       <c r="B53" s="313" t="n"/>
       <c r="C53" s="313" t="n"/>
-      <c r="D53" s="353" t="n"/>
+      <c r="D53" s="354" t="n"/>
       <c r="E53" s="283" t="n"/>
       <c r="F53" s="315" t="n"/>
       <c r="G53" s="315" t="n"/>
       <c r="H53" s="315" t="n"/>
-      <c r="I53" s="359" t="n"/>
-      <c r="J53" s="354" t="n"/>
+      <c r="I53" s="360" t="n"/>
+      <c r="J53" s="355" t="n"/>
     </row>
     <row r="54" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A54" s="119">
@@ -16427,25 +16427,25 @@
       <c r="A55" s="316" t="n"/>
       <c r="B55" s="313" t="n"/>
       <c r="C55" s="313" t="n"/>
-      <c r="D55" s="353" t="n"/>
+      <c r="D55" s="354" t="n"/>
       <c r="E55" s="315" t="n"/>
       <c r="F55" s="315" t="n"/>
       <c r="G55" s="315" t="n"/>
       <c r="H55" s="315" t="n"/>
       <c r="I55" s="315" t="n"/>
-      <c r="J55" s="354" t="n"/>
+      <c r="J55" s="355" t="n"/>
     </row>
     <row r="56" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A56" s="316" t="n"/>
       <c r="B56" s="313" t="n"/>
       <c r="C56" s="313" t="n"/>
-      <c r="D56" s="353" t="n"/>
+      <c r="D56" s="354" t="n"/>
       <c r="E56" s="315" t="n"/>
       <c r="F56" s="315" t="n"/>
       <c r="G56" s="315" t="n"/>
       <c r="H56" s="315" t="n"/>
       <c r="I56" s="315" t="n"/>
-      <c r="J56" s="354" t="n"/>
+      <c r="J56" s="355" t="n"/>
     </row>
     <row r="57" ht="25.5" customFormat="1" customHeight="1" s="4">
       <c r="A57" s="119">
@@ -16466,7 +16466,7 @@
         <v/>
       </c>
       <c r="E57" s="183" t="n"/>
-      <c r="F57" s="360" t="inlineStr">
+      <c r="F57" s="361" t="inlineStr">
         <is>
           <t>CC
 9,11</t>
@@ -16481,25 +16481,25 @@
       <c r="A58" s="316" t="n"/>
       <c r="B58" s="313" t="n"/>
       <c r="C58" s="313" t="n"/>
-      <c r="D58" s="353" t="n"/>
+      <c r="D58" s="354" t="n"/>
       <c r="E58" s="315" t="n"/>
-      <c r="F58" s="358" t="n"/>
+      <c r="F58" s="359" t="n"/>
       <c r="G58" s="315" t="n"/>
       <c r="H58" s="315" t="n"/>
       <c r="I58" s="315" t="n"/>
-      <c r="J58" s="354" t="n"/>
+      <c r="J58" s="355" t="n"/>
     </row>
     <row r="59" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A59" s="316" t="n"/>
       <c r="B59" s="313" t="n"/>
       <c r="C59" s="313" t="n"/>
-      <c r="D59" s="353" t="n"/>
+      <c r="D59" s="354" t="n"/>
       <c r="E59" s="315" t="n"/>
-      <c r="F59" s="359" t="n"/>
+      <c r="F59" s="360" t="n"/>
       <c r="G59" s="315" t="n"/>
       <c r="H59" s="315" t="n"/>
       <c r="I59" s="315" t="n"/>
-      <c r="J59" s="354" t="n"/>
+      <c r="J59" s="355" t="n"/>
     </row>
     <row r="60" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A60" s="281">
@@ -16531,24 +16531,24 @@
       <c r="B61" s="331" t="n"/>
       <c r="C61" s="331" t="n"/>
       <c r="D61" s="331" t="n"/>
-      <c r="E61" s="358" t="n"/>
-      <c r="F61" s="358" t="n"/>
-      <c r="G61" s="358" t="n"/>
-      <c r="H61" s="358" t="n"/>
-      <c r="I61" s="358" t="n"/>
-      <c r="J61" s="358" t="n"/>
+      <c r="E61" s="359" t="n"/>
+      <c r="F61" s="359" t="n"/>
+      <c r="G61" s="359" t="n"/>
+      <c r="H61" s="359" t="n"/>
+      <c r="I61" s="359" t="n"/>
+      <c r="J61" s="359" t="n"/>
     </row>
     <row r="62" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A62" s="332" t="n"/>
       <c r="B62" s="332" t="n"/>
       <c r="C62" s="332" t="n"/>
       <c r="D62" s="332" t="n"/>
-      <c r="E62" s="361" t="n"/>
-      <c r="F62" s="361" t="n"/>
-      <c r="G62" s="361" t="n"/>
-      <c r="H62" s="361" t="n"/>
-      <c r="I62" s="361" t="n"/>
-      <c r="J62" s="361" t="n"/>
+      <c r="E62" s="362" t="n"/>
+      <c r="F62" s="362" t="n"/>
+      <c r="G62" s="362" t="n"/>
+      <c r="H62" s="362" t="n"/>
+      <c r="I62" s="362" t="n"/>
+      <c r="J62" s="362" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="146">
@@ -16997,21 +16997,21 @@
       </c>
       <c r="E9" s="183" t="inlineStr">
         <is>
-          <t>GL - CBu-Swa-SGa
-4º e 5º tempos</t>
+          <t>LP/LIT/RED - ACo/AMu/Raf
+1º ao 3º tempos</t>
         </is>
       </c>
       <c r="F9" s="183" t="n"/>
       <c r="G9" s="183" t="inlineStr">
         <is>
-          <t>Hist - Ver
+          <t>Geo - Mar
 1º e 2º tempos</t>
         </is>
       </c>
       <c r="H9" s="183" t="inlineStr">
         <is>
-          <t>Ing - PaH
-1º e 2º tempos</t>
+          <t>Bio - Ale
+2º e 3º tempos</t>
         </is>
       </c>
       <c r="I9" s="183" t="n"/>
@@ -17094,8 +17094,8 @@
       </c>
       <c r="E12" s="11" t="inlineStr">
         <is>
-          <t>DaF - CBu-SGa-Swa
-5º e 6º tempos</t>
+          <t>Qui - CAl
+1º e 2º tempos</t>
         </is>
       </c>
       <c r="F12" s="11" t="inlineStr">
@@ -17110,7 +17110,12 @@
 2º ao 7º tempos</t>
         </is>
       </c>
-      <c r="H12" s="11" t="n"/>
+      <c r="H12" s="11" t="inlineStr">
+        <is>
+          <t>Ing - PaH
+1º e 2º tempos</t>
+        </is>
+      </c>
       <c r="I12" s="11" t="n"/>
       <c r="J12" s="183" t="n"/>
       <c r="L12" s="15" t="n"/>
@@ -17170,23 +17175,18 @@
       </c>
       <c r="E15" s="11" t="inlineStr">
         <is>
-          <t>Bio - Ale
+          <t>GL - CBu-Swa-SGa
+4º e 5º tempos</t>
+        </is>
+      </c>
+      <c r="F15" s="11" t="inlineStr">
+        <is>
+          <t>Mat - ClaMe/JJ
 1º e 2º tempos</t>
         </is>
       </c>
-      <c r="F15" s="11" t="inlineStr">
-        <is>
-          <t>Qui - CAl
-1º e 2º tempos</t>
-        </is>
-      </c>
       <c r="G15" s="11" t="n"/>
-      <c r="H15" s="11" t="inlineStr">
-        <is>
-          <t>LP/LIT/RED - ACo/AMu/Raf
-4º ao 6º tempos</t>
-        </is>
-      </c>
+      <c r="H15" s="11" t="n"/>
       <c r="I15" s="11" t="n"/>
       <c r="J15" s="183" t="n"/>
       <c r="L15" s="17" t="n"/>
@@ -17249,20 +17249,20 @@
       </c>
       <c r="F18" s="11" t="inlineStr">
         <is>
-          <t>Mat - ClaMe/JJ
+          <t>DaF - CBu-SGa-Swa
+4º e 5º tempos</t>
+        </is>
+      </c>
+      <c r="G18" s="11" t="inlineStr">
+        <is>
+          <t>Hist - Ver
 1º e 2º tempos</t>
         </is>
       </c>
-      <c r="G18" s="11" t="inlineStr">
-        <is>
-          <t>Geo - Mar
+      <c r="H18" s="11" t="inlineStr">
+        <is>
+          <t>Fis - Cadu
 1º e 2º tempos</t>
-        </is>
-      </c>
-      <c r="H18" s="11" t="inlineStr">
-        <is>
-          <t>Fis - Cadu
-3º e 4º tempos</t>
         </is>
       </c>
       <c r="I18" s="350" t="n"/>
@@ -17331,21 +17331,21 @@
         <f>B21+4</f>
         <v/>
       </c>
-      <c r="E21" s="11" t="inlineStr">
-        <is>
-          <t>Ing - PaH
-3º e 4º tempos</t>
-        </is>
-      </c>
+      <c r="E21" s="11" t="n"/>
       <c r="F21" s="62" t="n"/>
-      <c r="G21" s="11" t="inlineStr">
-        <is>
-          <t>Fil - LAn
-11º tempo</t>
-        </is>
-      </c>
-      <c r="H21" s="11" t="n"/>
-      <c r="I21" s="11" t="n"/>
+      <c r="G21" s="11" t="n"/>
+      <c r="H21" s="11" t="inlineStr">
+        <is>
+          <t>Fis - Cadu
+1º e 2º tempos</t>
+        </is>
+      </c>
+      <c r="I21" s="11" t="inlineStr">
+        <is>
+          <t>Soc - Kle
+4º tempo</t>
+        </is>
+      </c>
       <c r="J21" s="183" t="n"/>
       <c r="L21" s="80" t="inlineStr">
         <is>
@@ -17408,16 +17408,11 @@
         <f>B24+4</f>
         <v/>
       </c>
-      <c r="E24" s="283" t="inlineStr">
+      <c r="E24" s="283" t="n"/>
+      <c r="F24" s="283" t="inlineStr">
         <is>
           <t>DaF - CBu-SGa-Swa
-5º e 6º tempos</t>
-        </is>
-      </c>
-      <c r="F24" s="283" t="inlineStr">
-        <is>
-          <t>Qui - CAl
-1º e 2º tempos</t>
+4º e 5º tempos</t>
         </is>
       </c>
       <c r="G24" s="79" t="n"/>
@@ -17436,13 +17431,13 @@
       <c r="A25" s="316" t="n"/>
       <c r="B25" s="313" t="n"/>
       <c r="C25" s="313" t="n"/>
-      <c r="D25" s="353" t="n"/>
+      <c r="D25" s="354" t="n"/>
       <c r="E25" s="283" t="n"/>
       <c r="F25" s="283" t="n"/>
       <c r="G25" s="79" t="n"/>
       <c r="H25" s="283" t="n"/>
       <c r="I25" s="78" t="n"/>
-      <c r="J25" s="354" t="n"/>
+      <c r="J25" s="355" t="n"/>
       <c r="L25" s="44" t="n"/>
       <c r="M25" s="321" t="inlineStr">
         <is>
@@ -17455,13 +17450,13 @@
       <c r="A26" s="316" t="n"/>
       <c r="B26" s="313" t="n"/>
       <c r="C26" s="313" t="n"/>
-      <c r="D26" s="353" t="n"/>
+      <c r="D26" s="354" t="n"/>
       <c r="E26" s="283" t="n"/>
       <c r="F26" s="283" t="n"/>
       <c r="G26" s="79" t="n"/>
       <c r="H26" s="283" t="n"/>
       <c r="I26" s="78" t="n"/>
-      <c r="J26" s="354" t="n"/>
+      <c r="J26" s="355" t="n"/>
       <c r="L26" s="43" t="n"/>
       <c r="M26" s="323" t="inlineStr">
         <is>
@@ -17490,18 +17485,18 @@
       </c>
       <c r="E27" s="78" t="inlineStr">
         <is>
-          <t>Bio - Ale
-1º e 2º tempos</t>
+          <t>Ing - PaH
+4º e 5º tempos</t>
         </is>
       </c>
       <c r="F27" s="283" t="n"/>
-      <c r="G27" s="283" t="n"/>
-      <c r="H27" s="283" t="inlineStr">
-        <is>
-          <t>LP/LIT/RED - ACo/AMu/Raf
-4º ao 6º tempos</t>
-        </is>
-      </c>
+      <c r="G27" s="283" t="inlineStr">
+        <is>
+          <t>GL - CBu-Swa-SGa
+4º e 5º tempos</t>
+        </is>
+      </c>
+      <c r="H27" s="283" t="n"/>
       <c r="I27" s="283" t="n"/>
       <c r="J27" s="265" t="n"/>
       <c r="L27" s="45" t="n"/>
@@ -17516,13 +17511,13 @@
       <c r="A28" s="316" t="n"/>
       <c r="B28" s="313" t="n"/>
       <c r="C28" s="313" t="n"/>
-      <c r="D28" s="353" t="n"/>
+      <c r="D28" s="354" t="n"/>
       <c r="E28" s="78" t="n"/>
       <c r="F28" s="283" t="n"/>
       <c r="G28" s="283" t="n"/>
       <c r="H28" s="283" t="n"/>
       <c r="I28" s="283" t="n"/>
-      <c r="J28" s="354" t="n"/>
+      <c r="J28" s="355" t="n"/>
       <c r="L28" s="23" t="n"/>
       <c r="M28" s="325" t="inlineStr">
         <is>
@@ -17535,13 +17530,13 @@
       <c r="A29" s="316" t="n"/>
       <c r="B29" s="313" t="n"/>
       <c r="C29" s="313" t="n"/>
-      <c r="D29" s="353" t="n"/>
+      <c r="D29" s="354" t="n"/>
       <c r="E29" s="78" t="n"/>
       <c r="F29" s="283" t="n"/>
       <c r="G29" s="283" t="n"/>
       <c r="H29" s="283" t="n"/>
       <c r="I29" s="283" t="n"/>
-      <c r="J29" s="354" t="n"/>
+      <c r="J29" s="355" t="n"/>
       <c r="L29" s="46" t="n"/>
       <c r="M29" s="157" t="inlineStr">
         <is>
@@ -17568,7 +17563,12 @@
         <f>B30+4</f>
         <v/>
       </c>
-      <c r="E30" s="283" t="n"/>
+      <c r="E30" s="283" t="inlineStr">
+        <is>
+          <t>LP/LIT/RED - ACo/AMu/Raf
+1º ao 3º tempos</t>
+        </is>
+      </c>
       <c r="F30" s="283" t="n"/>
       <c r="G30" s="283" t="inlineStr">
         <is>
@@ -17595,7 +17595,7 @@
       <c r="A31" s="316" t="n"/>
       <c r="B31" s="313" t="n"/>
       <c r="C31" s="313" t="n"/>
-      <c r="D31" s="353" t="n"/>
+      <c r="D31" s="354" t="n"/>
       <c r="E31" s="283" t="n"/>
       <c r="F31" s="283" t="n"/>
       <c r="G31" s="283" t="n"/>
@@ -17614,7 +17614,7 @@
       <c r="A32" s="316" t="n"/>
       <c r="B32" s="313" t="n"/>
       <c r="C32" s="313" t="n"/>
-      <c r="D32" s="353" t="n"/>
+      <c r="D32" s="354" t="n"/>
       <c r="E32" s="283" t="n"/>
       <c r="F32" s="283" t="n"/>
       <c r="G32" s="283" t="n"/>
@@ -17684,7 +17684,7 @@
     <row r="34" ht="26.25" customFormat="1" customHeight="1" s="4">
       <c r="A34" s="330" t="n"/>
       <c r="B34" s="331" t="n"/>
-      <c r="D34" s="355" t="n"/>
+      <c r="D34" s="356" t="n"/>
       <c r="E34" s="315" t="n"/>
       <c r="F34" s="315" t="n"/>
       <c r="G34" s="315" t="n"/>
@@ -17706,7 +17706,7 @@
     <row r="35" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A35" s="330" t="n"/>
       <c r="B35" s="332" t="n"/>
-      <c r="D35" s="356" t="n"/>
+      <c r="D35" s="357" t="n"/>
       <c r="E35" s="315" t="n"/>
       <c r="F35" s="315" t="n"/>
       <c r="G35" s="315" t="n"/>
@@ -17743,15 +17743,20 @@
         <f>B36+4</f>
         <v/>
       </c>
-      <c r="E36" s="283" t="n"/>
-      <c r="F36" s="283" t="n"/>
+      <c r="E36" s="283" t="inlineStr">
+        <is>
+          <t>Mat - ClaMe/JJ
+2º e 3º tempos</t>
+        </is>
+      </c>
+      <c r="F36" s="283" t="inlineStr">
+        <is>
+          <t>Qui - CAl
+1º e 2º tempos</t>
+        </is>
+      </c>
       <c r="G36" s="283" t="n"/>
-      <c r="H36" s="283" t="inlineStr">
-        <is>
-          <t>Fis - Cadu
-3º e 4º tempos</t>
-        </is>
-      </c>
+      <c r="H36" s="283" t="n"/>
       <c r="I36" s="283" t="n"/>
       <c r="J36" s="265" t="n"/>
       <c r="L36" s="81" t="inlineStr">
@@ -17769,13 +17774,13 @@
       <c r="A37" s="316" t="n"/>
       <c r="B37" s="313" t="n"/>
       <c r="C37" s="313" t="n"/>
-      <c r="D37" s="353" t="n"/>
+      <c r="D37" s="354" t="n"/>
       <c r="E37" s="283" t="n"/>
       <c r="F37" s="283" t="n"/>
       <c r="G37" s="283" t="n"/>
       <c r="H37" s="283" t="n"/>
       <c r="I37" s="283" t="n"/>
-      <c r="J37" s="354" t="n"/>
+      <c r="J37" s="355" t="n"/>
       <c r="L37" s="4" t="inlineStr">
         <is>
           <t>18.08,19.08</t>
@@ -17791,13 +17796,13 @@
       <c r="A38" s="316" t="n"/>
       <c r="B38" s="313" t="n"/>
       <c r="C38" s="313" t="n"/>
-      <c r="D38" s="353" t="n"/>
+      <c r="D38" s="354" t="n"/>
       <c r="E38" s="283" t="n"/>
       <c r="F38" s="283" t="n"/>
       <c r="G38" s="283" t="n"/>
       <c r="H38" s="283" t="n"/>
       <c r="I38" s="283" t="n"/>
-      <c r="J38" s="354" t="n"/>
+      <c r="J38" s="355" t="n"/>
     </row>
     <row r="39" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A39" s="119">
@@ -17838,25 +17843,25 @@
       <c r="A40" s="316" t="n"/>
       <c r="B40" s="313" t="n"/>
       <c r="C40" s="313" t="n"/>
-      <c r="D40" s="353" t="n"/>
+      <c r="D40" s="354" t="n"/>
       <c r="E40" s="283" t="n"/>
       <c r="F40" s="283" t="n"/>
       <c r="G40" s="283" t="n"/>
       <c r="H40" s="283" t="n"/>
       <c r="I40" s="283" t="n"/>
-      <c r="J40" s="354" t="n"/>
+      <c r="J40" s="355" t="n"/>
     </row>
     <row r="41" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A41" s="316" t="n"/>
       <c r="B41" s="313" t="n"/>
       <c r="C41" s="313" t="n"/>
-      <c r="D41" s="353" t="n"/>
+      <c r="D41" s="354" t="n"/>
       <c r="E41" s="283" t="n"/>
       <c r="F41" s="283" t="n"/>
       <c r="G41" s="283" t="n"/>
       <c r="H41" s="283" t="n"/>
       <c r="I41" s="283" t="n"/>
-      <c r="J41" s="354" t="n"/>
+      <c r="J41" s="355" t="n"/>
     </row>
     <row r="42" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A42" s="119">
@@ -17878,14 +17883,14 @@
       </c>
       <c r="E42" s="283" t="n"/>
       <c r="F42" s="283" t="n"/>
-      <c r="G42" s="283" t="n"/>
+      <c r="G42" s="283" t="inlineStr">
+        <is>
+          <t>Fil - LAn
+11º tempo</t>
+        </is>
+      </c>
       <c r="H42" s="283" t="n"/>
-      <c r="I42" s="283" t="inlineStr">
-        <is>
-          <t>Soc - Kle
-4º tempo</t>
-        </is>
-      </c>
+      <c r="I42" s="283" t="n"/>
       <c r="J42" s="265" t="n"/>
       <c r="L42" s="259" t="inlineStr">
         <is>
@@ -17898,26 +17903,26 @@
       <c r="A43" s="316" t="n"/>
       <c r="B43" s="313" t="n"/>
       <c r="C43" s="313" t="n"/>
-      <c r="D43" s="353" t="n"/>
+      <c r="D43" s="354" t="n"/>
       <c r="E43" s="283" t="n"/>
       <c r="F43" s="283" t="n"/>
       <c r="G43" s="283" t="n"/>
       <c r="H43" s="283" t="n"/>
       <c r="I43" s="283" t="n"/>
-      <c r="J43" s="354" t="n"/>
+      <c r="J43" s="355" t="n"/>
       <c r="L43" s="331" t="n"/>
     </row>
     <row r="44" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A44" s="316" t="n"/>
       <c r="B44" s="313" t="n"/>
       <c r="C44" s="313" t="n"/>
-      <c r="D44" s="353" t="n"/>
+      <c r="D44" s="354" t="n"/>
       <c r="E44" s="283" t="n"/>
       <c r="F44" s="283" t="n"/>
       <c r="G44" s="283" t="n"/>
       <c r="H44" s="283" t="n"/>
       <c r="I44" s="283" t="n"/>
-      <c r="J44" s="354" t="n"/>
+      <c r="J44" s="355" t="n"/>
       <c r="L44" s="331" t="n"/>
     </row>
     <row r="45" ht="18" customFormat="1" customHeight="1" s="4">
@@ -17938,16 +17943,16 @@
         <f>B45+4</f>
         <v/>
       </c>
-      <c r="E45" s="283" t="inlineStr">
-        <is>
-          <t>GL - CBu-Swa-SGa
-4º e 5º tempos</t>
-        </is>
-      </c>
+      <c r="E45" s="283" t="n"/>
       <c r="F45" s="283" t="n"/>
-      <c r="G45" s="283" t="n"/>
+      <c r="G45" s="283" t="inlineStr">
+        <is>
+          <t>Geo - Mar
+1º e 2º tempos</t>
+        </is>
+      </c>
       <c r="H45" s="283" t="n"/>
-      <c r="I45" s="357" t="n"/>
+      <c r="I45" s="358" t="n"/>
       <c r="J45" s="269" t="n"/>
       <c r="L45" s="331" t="n"/>
     </row>
@@ -17955,26 +17960,26 @@
       <c r="A46" s="316" t="n"/>
       <c r="B46" s="313" t="n"/>
       <c r="C46" s="313" t="n"/>
-      <c r="D46" s="353" t="n"/>
+      <c r="D46" s="354" t="n"/>
       <c r="E46" s="283" t="n"/>
       <c r="F46" s="283" t="n"/>
       <c r="G46" s="283" t="n"/>
       <c r="H46" s="283" t="n"/>
-      <c r="I46" s="358" t="n"/>
-      <c r="J46" s="354" t="n"/>
+      <c r="I46" s="359" t="n"/>
+      <c r="J46" s="355" t="n"/>
       <c r="L46" s="331" t="n"/>
     </row>
     <row r="47" ht="51" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A47" s="316" t="n"/>
       <c r="B47" s="313" t="n"/>
       <c r="C47" s="313" t="n"/>
-      <c r="D47" s="353" t="n"/>
+      <c r="D47" s="354" t="n"/>
       <c r="E47" s="283" t="n"/>
       <c r="F47" s="283" t="n"/>
       <c r="G47" s="283" t="n"/>
       <c r="H47" s="283" t="n"/>
-      <c r="I47" s="359" t="n"/>
-      <c r="J47" s="354" t="n"/>
+      <c r="I47" s="360" t="n"/>
+      <c r="J47" s="355" t="n"/>
       <c r="L47" s="332" t="n"/>
     </row>
     <row r="48" ht="23.25" customFormat="1" customHeight="1" s="4">
@@ -17995,20 +18000,15 @@
         <f>B48+4</f>
         <v/>
       </c>
-      <c r="E48" s="283" t="inlineStr">
-        <is>
-          <t>Mat - ClaMe/JJ
+      <c r="E48" s="283" t="n"/>
+      <c r="F48" s="361" t="n"/>
+      <c r="G48" s="283" t="n"/>
+      <c r="H48" s="283" t="inlineStr">
+        <is>
+          <t>Bio - Ale
 2º e 3º tempos</t>
         </is>
       </c>
-      <c r="F48" s="360" t="n"/>
-      <c r="G48" s="283" t="inlineStr">
-        <is>
-          <t>Geo - Mar
-1º e 2º tempos</t>
-        </is>
-      </c>
-      <c r="H48" s="283" t="n"/>
       <c r="I48" s="183" t="inlineStr">
         <is>
           <t>unterrichtsfrei sem aula</t>
@@ -18020,25 +18020,25 @@
       <c r="A49" s="316" t="n"/>
       <c r="B49" s="313" t="n"/>
       <c r="C49" s="313" t="n"/>
-      <c r="D49" s="353" t="n"/>
+      <c r="D49" s="354" t="n"/>
       <c r="E49" s="283" t="n"/>
-      <c r="F49" s="358" t="n"/>
+      <c r="F49" s="359" t="n"/>
       <c r="G49" s="283" t="n"/>
       <c r="H49" s="283" t="n"/>
       <c r="I49" s="315" t="n"/>
-      <c r="J49" s="354" t="n"/>
+      <c r="J49" s="355" t="n"/>
     </row>
     <row r="50" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A50" s="316" t="n"/>
       <c r="B50" s="313" t="n"/>
       <c r="C50" s="313" t="n"/>
-      <c r="D50" s="353" t="n"/>
+      <c r="D50" s="354" t="n"/>
       <c r="E50" s="78" t="n"/>
-      <c r="F50" s="359" t="n"/>
+      <c r="F50" s="360" t="n"/>
       <c r="G50" s="283" t="n"/>
       <c r="H50" s="283" t="n"/>
       <c r="I50" s="315" t="n"/>
-      <c r="J50" s="354" t="n"/>
+      <c r="J50" s="355" t="n"/>
     </row>
     <row r="51" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A51" s="119">
@@ -18062,7 +18062,7 @@
       <c r="F51" s="183" t="n"/>
       <c r="G51" s="183" t="n"/>
       <c r="H51" s="183" t="n"/>
-      <c r="I51" s="357" t="inlineStr">
+      <c r="I51" s="358" t="inlineStr">
         <is>
           <t>2CH
 9,11</t>
@@ -18074,25 +18074,25 @@
       <c r="A52" s="316" t="n"/>
       <c r="B52" s="313" t="n"/>
       <c r="C52" s="313" t="n"/>
-      <c r="D52" s="353" t="n"/>
+      <c r="D52" s="354" t="n"/>
       <c r="E52" s="283" t="n"/>
       <c r="F52" s="315" t="n"/>
       <c r="G52" s="315" t="n"/>
       <c r="H52" s="315" t="n"/>
-      <c r="I52" s="358" t="n"/>
-      <c r="J52" s="354" t="n"/>
+      <c r="I52" s="359" t="n"/>
+      <c r="J52" s="355" t="n"/>
     </row>
     <row r="53" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A53" s="316" t="n"/>
       <c r="B53" s="313" t="n"/>
       <c r="C53" s="313" t="n"/>
-      <c r="D53" s="353" t="n"/>
+      <c r="D53" s="354" t="n"/>
       <c r="E53" s="283" t="n"/>
       <c r="F53" s="315" t="n"/>
       <c r="G53" s="315" t="n"/>
       <c r="H53" s="315" t="n"/>
-      <c r="I53" s="359" t="n"/>
-      <c r="J53" s="354" t="n"/>
+      <c r="I53" s="360" t="n"/>
+      <c r="J53" s="355" t="n"/>
     </row>
     <row r="54" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A54" s="119">
@@ -18123,25 +18123,25 @@
       <c r="A55" s="316" t="n"/>
       <c r="B55" s="313" t="n"/>
       <c r="C55" s="313" t="n"/>
-      <c r="D55" s="353" t="n"/>
+      <c r="D55" s="354" t="n"/>
       <c r="E55" s="315" t="n"/>
       <c r="F55" s="315" t="n"/>
       <c r="G55" s="315" t="n"/>
       <c r="H55" s="315" t="n"/>
       <c r="I55" s="315" t="n"/>
-      <c r="J55" s="354" t="n"/>
+      <c r="J55" s="355" t="n"/>
     </row>
     <row r="56" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A56" s="316" t="n"/>
       <c r="B56" s="313" t="n"/>
       <c r="C56" s="313" t="n"/>
-      <c r="D56" s="353" t="n"/>
+      <c r="D56" s="354" t="n"/>
       <c r="E56" s="315" t="n"/>
       <c r="F56" s="315" t="n"/>
       <c r="G56" s="315" t="n"/>
       <c r="H56" s="315" t="n"/>
       <c r="I56" s="315" t="n"/>
-      <c r="J56" s="354" t="n"/>
+      <c r="J56" s="355" t="n"/>
     </row>
     <row r="57" ht="25.5" customFormat="1" customHeight="1" s="4">
       <c r="A57" s="119">
@@ -18162,7 +18162,7 @@
         <v/>
       </c>
       <c r="E57" s="183" t="n"/>
-      <c r="F57" s="360" t="inlineStr">
+      <c r="F57" s="361" t="inlineStr">
         <is>
           <t>CC
 9,11</t>
@@ -18177,25 +18177,25 @@
       <c r="A58" s="316" t="n"/>
       <c r="B58" s="313" t="n"/>
       <c r="C58" s="313" t="n"/>
-      <c r="D58" s="353" t="n"/>
+      <c r="D58" s="354" t="n"/>
       <c r="E58" s="315" t="n"/>
-      <c r="F58" s="358" t="n"/>
+      <c r="F58" s="359" t="n"/>
       <c r="G58" s="315" t="n"/>
       <c r="H58" s="315" t="n"/>
       <c r="I58" s="315" t="n"/>
-      <c r="J58" s="354" t="n"/>
+      <c r="J58" s="355" t="n"/>
     </row>
     <row r="59" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A59" s="316" t="n"/>
       <c r="B59" s="313" t="n"/>
       <c r="C59" s="313" t="n"/>
-      <c r="D59" s="353" t="n"/>
+      <c r="D59" s="354" t="n"/>
       <c r="E59" s="315" t="n"/>
-      <c r="F59" s="359" t="n"/>
+      <c r="F59" s="360" t="n"/>
       <c r="G59" s="315" t="n"/>
       <c r="H59" s="315" t="n"/>
       <c r="I59" s="315" t="n"/>
-      <c r="J59" s="354" t="n"/>
+      <c r="J59" s="355" t="n"/>
     </row>
     <row r="60" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A60" s="281">
@@ -18227,24 +18227,24 @@
       <c r="B61" s="331" t="n"/>
       <c r="C61" s="331" t="n"/>
       <c r="D61" s="331" t="n"/>
-      <c r="E61" s="358" t="n"/>
-      <c r="F61" s="358" t="n"/>
-      <c r="G61" s="358" t="n"/>
-      <c r="H61" s="358" t="n"/>
-      <c r="I61" s="358" t="n"/>
-      <c r="J61" s="358" t="n"/>
+      <c r="E61" s="359" t="n"/>
+      <c r="F61" s="359" t="n"/>
+      <c r="G61" s="359" t="n"/>
+      <c r="H61" s="359" t="n"/>
+      <c r="I61" s="359" t="n"/>
+      <c r="J61" s="359" t="n"/>
     </row>
     <row r="62" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A62" s="332" t="n"/>
       <c r="B62" s="332" t="n"/>
       <c r="C62" s="332" t="n"/>
       <c r="D62" s="332" t="n"/>
-      <c r="E62" s="361" t="n"/>
-      <c r="F62" s="361" t="n"/>
-      <c r="G62" s="361" t="n"/>
-      <c r="H62" s="361" t="n"/>
-      <c r="I62" s="361" t="n"/>
-      <c r="J62" s="361" t="n"/>
+      <c r="E62" s="362" t="n"/>
+      <c r="F62" s="362" t="n"/>
+      <c r="G62" s="362" t="n"/>
+      <c r="H62" s="362" t="n"/>
+      <c r="I62" s="362" t="n"/>
+      <c r="J62" s="362" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="146">
@@ -18691,26 +18691,26 @@
         <f>B9+4</f>
         <v/>
       </c>
-      <c r="E9" s="183" t="inlineStr">
+      <c r="E9" s="183" t="n"/>
+      <c r="F9" s="183" t="inlineStr">
+        <is>
+          <t>Fis - Cadu
+1º e 2º tempos</t>
+        </is>
+      </c>
+      <c r="G9" s="183" t="n"/>
+      <c r="H9" s="183" t="inlineStr">
+        <is>
+          <t>Mat - Bre/JJ
+4º e 5º tempos</t>
+        </is>
+      </c>
+      <c r="I9" s="183" t="inlineStr">
         <is>
           <t>Geo - Mar
-4º e 5º tempos</t>
-        </is>
-      </c>
-      <c r="F9" s="183" t="inlineStr">
-        <is>
-          <t>Mat - Bre/JJ
-1º e 2º tempos</t>
-        </is>
-      </c>
-      <c r="G9" s="183" t="inlineStr">
-        <is>
-          <t>Qui - CAl/Fab
-5º e 6º tempos</t>
-        </is>
-      </c>
-      <c r="H9" s="183" t="n"/>
-      <c r="I9" s="183" t="n"/>
+2º e 3º tempos</t>
+        </is>
+      </c>
       <c r="J9" s="183" t="n"/>
       <c r="L9" s="16" t="inlineStr">
         <is>
@@ -18790,24 +18790,19 @@
       </c>
       <c r="E12" s="11" t="inlineStr">
         <is>
-          <t>Bio - Ale
-2º e 3º tempos</t>
+          <t>DaF - CBu-EFr-Eth
+4º e 5º tempos</t>
         </is>
       </c>
       <c r="F12" s="11" t="n"/>
-      <c r="G12" s="11" t="inlineStr">
-        <is>
-          <t>Soc - Kle
-2º tempo</t>
-        </is>
-      </c>
-      <c r="H12" s="11" t="inlineStr">
-        <is>
-          <t>LP/LIT/RED - AMu/Deb
-3º ao 5º tempos</t>
-        </is>
-      </c>
-      <c r="I12" s="11" t="n"/>
+      <c r="G12" s="11" t="n"/>
+      <c r="H12" s="11" t="n"/>
+      <c r="I12" s="11" t="inlineStr">
+        <is>
+          <t>Hist - Wag
+1º e 2º tempos</t>
+        </is>
+      </c>
       <c r="J12" s="183" t="n"/>
       <c r="L12" s="15" t="n"/>
       <c r="M12" s="15" t="n"/>
@@ -18872,13 +18867,18 @@
       </c>
       <c r="F15" s="11" t="inlineStr">
         <is>
-          <t>GL - CBu-EFr-Eth
-5º e 6º tempos</t>
+          <t>Bio - Ale
+2º e 3º tempos</t>
         </is>
       </c>
       <c r="G15" s="11" t="n"/>
       <c r="H15" s="11" t="n"/>
-      <c r="I15" s="11" t="n"/>
+      <c r="I15" s="11" t="inlineStr">
+        <is>
+          <t>LP/LIT/RED - AMu/Deb
+1º ao 3º tempos</t>
+        </is>
+      </c>
       <c r="J15" s="183" t="n"/>
       <c r="L15" s="17" t="n"/>
       <c r="M15" s="15" t="n"/>
@@ -18938,23 +18938,18 @@
           <t>unterrichtsfrei sem aula</t>
         </is>
       </c>
-      <c r="F18" s="11" t="inlineStr">
-        <is>
-          <t>Fis - Cadu
-2º e 3º tempos</t>
-        </is>
-      </c>
-      <c r="G18" s="11" t="inlineStr">
-        <is>
-          <t>DaF - CBu-EFr-Eth
+      <c r="F18" s="11" t="n"/>
+      <c r="G18" s="11" t="n"/>
+      <c r="H18" s="11" t="inlineStr">
+        <is>
+          <t>GL - CBu-EFr-Eth
+9º e 10º tempos</t>
+        </is>
+      </c>
+      <c r="I18" s="350" t="inlineStr">
+        <is>
+          <t>Qui - CAl/Fab
 4º e 5º tempos</t>
-        </is>
-      </c>
-      <c r="H18" s="11" t="n"/>
-      <c r="I18" s="350" t="inlineStr">
-        <is>
-          <t>Hist - Wag
-3º e 4º tempos</t>
         </is>
       </c>
       <c r="J18" s="262" t="inlineStr">
@@ -19022,12 +19017,7 @@
         <f>B21+4</f>
         <v/>
       </c>
-      <c r="E21" s="11" t="inlineStr">
-        <is>
-          <t>DaF - CBu-EFr-Eth
-3º e 4º tempos</t>
-        </is>
-      </c>
+      <c r="E21" s="11" t="n"/>
       <c r="F21" s="62" t="n"/>
       <c r="G21" s="11" t="inlineStr">
         <is>
@@ -19104,16 +19094,21 @@
         <f>B24+4</f>
         <v/>
       </c>
-      <c r="E24" s="283" t="inlineStr">
-        <is>
-          <t>Bio - Ale
-2º e 3º tempos</t>
-        </is>
-      </c>
+      <c r="E24" s="283" t="n"/>
       <c r="F24" s="283" t="n"/>
       <c r="G24" s="79" t="n"/>
-      <c r="H24" s="283" t="n"/>
-      <c r="I24" s="78" t="n"/>
+      <c r="H24" s="283" t="inlineStr">
+        <is>
+          <t>Mat - Bre/JJ
+4º e 5º tempos</t>
+        </is>
+      </c>
+      <c r="I24" s="78" t="inlineStr">
+        <is>
+          <t>Geo - Mar
+2º e 3º tempos</t>
+        </is>
+      </c>
       <c r="J24" s="265" t="n"/>
       <c r="L24" s="318" t="inlineStr">
         <is>
@@ -19127,13 +19122,13 @@
       <c r="A25" s="316" t="n"/>
       <c r="B25" s="313" t="n"/>
       <c r="C25" s="313" t="n"/>
-      <c r="D25" s="353" t="n"/>
+      <c r="D25" s="354" t="n"/>
       <c r="E25" s="283" t="n"/>
       <c r="F25" s="283" t="n"/>
       <c r="G25" s="79" t="n"/>
       <c r="H25" s="283" t="n"/>
       <c r="I25" s="78" t="n"/>
-      <c r="J25" s="354" t="n"/>
+      <c r="J25" s="355" t="n"/>
       <c r="L25" s="44" t="n"/>
       <c r="M25" s="321" t="inlineStr">
         <is>
@@ -19146,13 +19141,13 @@
       <c r="A26" s="316" t="n"/>
       <c r="B26" s="313" t="n"/>
       <c r="C26" s="313" t="n"/>
-      <c r="D26" s="353" t="n"/>
+      <c r="D26" s="354" t="n"/>
       <c r="E26" s="283" t="n"/>
       <c r="F26" s="283" t="n"/>
       <c r="G26" s="79" t="n"/>
       <c r="H26" s="283" t="n"/>
       <c r="I26" s="78" t="n"/>
-      <c r="J26" s="354" t="n"/>
+      <c r="J26" s="355" t="n"/>
       <c r="L26" s="43" t="n"/>
       <c r="M26" s="323" t="inlineStr">
         <is>
@@ -19179,15 +19174,20 @@
         <f>B27+4</f>
         <v/>
       </c>
-      <c r="E27" s="78" t="n"/>
-      <c r="F27" s="283" t="inlineStr">
+      <c r="E27" s="78" t="inlineStr">
+        <is>
+          <t>Ing - PaH
+1º e 2º tempos</t>
+        </is>
+      </c>
+      <c r="F27" s="283" t="n"/>
+      <c r="G27" s="283" t="n"/>
+      <c r="H27" s="283" t="inlineStr">
         <is>
           <t>GL - CBu-EFr-Eth
-5º e 6º tempos</t>
-        </is>
-      </c>
-      <c r="G27" s="283" t="n"/>
-      <c r="H27" s="283" t="n"/>
+9º e 10º tempos</t>
+        </is>
+      </c>
       <c r="I27" s="283" t="n"/>
       <c r="J27" s="265" t="n"/>
       <c r="L27" s="45" t="n"/>
@@ -19202,13 +19202,13 @@
       <c r="A28" s="316" t="n"/>
       <c r="B28" s="313" t="n"/>
       <c r="C28" s="313" t="n"/>
-      <c r="D28" s="353" t="n"/>
+      <c r="D28" s="354" t="n"/>
       <c r="E28" s="78" t="n"/>
       <c r="F28" s="283" t="n"/>
       <c r="G28" s="283" t="n"/>
       <c r="H28" s="283" t="n"/>
       <c r="I28" s="283" t="n"/>
-      <c r="J28" s="354" t="n"/>
+      <c r="J28" s="355" t="n"/>
       <c r="L28" s="23" t="n"/>
       <c r="M28" s="325" t="inlineStr">
         <is>
@@ -19221,13 +19221,13 @@
       <c r="A29" s="316" t="n"/>
       <c r="B29" s="313" t="n"/>
       <c r="C29" s="313" t="n"/>
-      <c r="D29" s="353" t="n"/>
+      <c r="D29" s="354" t="n"/>
       <c r="E29" s="78" t="n"/>
       <c r="F29" s="283" t="n"/>
       <c r="G29" s="283" t="n"/>
       <c r="H29" s="283" t="n"/>
       <c r="I29" s="283" t="n"/>
-      <c r="J29" s="354" t="n"/>
+      <c r="J29" s="355" t="n"/>
       <c r="L29" s="46" t="n"/>
       <c r="M29" s="157" t="inlineStr">
         <is>
@@ -19254,21 +19254,16 @@
         <f>B30+4</f>
         <v/>
       </c>
-      <c r="E30" s="283" t="inlineStr">
-        <is>
-          <t>Ing - PaH
-1º e 2º tempos</t>
-        </is>
-      </c>
+      <c r="E30" s="283" t="n"/>
       <c r="F30" s="283" t="n"/>
-      <c r="G30" s="283" t="inlineStr">
-        <is>
-          <t>Fil - LAn
-10º tempo</t>
-        </is>
-      </c>
+      <c r="G30" s="283" t="n"/>
       <c r="H30" s="283" t="n"/>
-      <c r="I30" s="283" t="n"/>
+      <c r="I30" s="283" t="inlineStr">
+        <is>
+          <t>LP/LIT/RED - AMu/Deb
+1º ao 3º tempos</t>
+        </is>
+      </c>
       <c r="J30" s="183" t="inlineStr">
         <is>
           <t>unterrichtsfrei sem aula</t>
@@ -19286,7 +19281,7 @@
       <c r="A31" s="316" t="n"/>
       <c r="B31" s="313" t="n"/>
       <c r="C31" s="313" t="n"/>
-      <c r="D31" s="353" t="n"/>
+      <c r="D31" s="354" t="n"/>
       <c r="E31" s="283" t="n"/>
       <c r="F31" s="283" t="n"/>
       <c r="G31" s="283" t="n"/>
@@ -19305,7 +19300,7 @@
       <c r="A32" s="316" t="n"/>
       <c r="B32" s="313" t="n"/>
       <c r="C32" s="313" t="n"/>
-      <c r="D32" s="353" t="n"/>
+      <c r="D32" s="354" t="n"/>
       <c r="E32" s="283" t="n"/>
       <c r="F32" s="283" t="n"/>
       <c r="G32" s="283" t="n"/>
@@ -19375,7 +19370,7 @@
     <row r="34" ht="26.25" customFormat="1" customHeight="1" s="4">
       <c r="A34" s="330" t="n"/>
       <c r="B34" s="331" t="n"/>
-      <c r="D34" s="355" t="n"/>
+      <c r="D34" s="356" t="n"/>
       <c r="E34" s="315" t="n"/>
       <c r="F34" s="315" t="n"/>
       <c r="G34" s="315" t="n"/>
@@ -19397,7 +19392,7 @@
     <row r="35" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A35" s="330" t="n"/>
       <c r="B35" s="332" t="n"/>
-      <c r="D35" s="356" t="n"/>
+      <c r="D35" s="357" t="n"/>
       <c r="E35" s="315" t="n"/>
       <c r="F35" s="315" t="n"/>
       <c r="G35" s="315" t="n"/>
@@ -19434,19 +19429,19 @@
         <f>B36+4</f>
         <v/>
       </c>
-      <c r="E36" s="283" t="inlineStr">
-        <is>
-          <t>Geo - Mar
-4º e 5º tempos</t>
-        </is>
-      </c>
-      <c r="F36" s="283" t="n"/>
+      <c r="E36" s="283" t="n"/>
+      <c r="F36" s="283" t="inlineStr">
+        <is>
+          <t>Fis - Cadu
+1º e 2º tempos</t>
+        </is>
+      </c>
       <c r="G36" s="283" t="n"/>
       <c r="H36" s="283" t="n"/>
       <c r="I36" s="283" t="inlineStr">
         <is>
           <t>Hist - Wag
-3º e 4º tempos</t>
+1º e 2º tempos</t>
         </is>
       </c>
       <c r="J36" s="265" t="n"/>
@@ -19465,13 +19460,13 @@
       <c r="A37" s="316" t="n"/>
       <c r="B37" s="313" t="n"/>
       <c r="C37" s="313" t="n"/>
-      <c r="D37" s="353" t="n"/>
+      <c r="D37" s="354" t="n"/>
       <c r="E37" s="283" t="n"/>
       <c r="F37" s="283" t="n"/>
       <c r="G37" s="283" t="n"/>
       <c r="H37" s="283" t="n"/>
       <c r="I37" s="283" t="n"/>
-      <c r="J37" s="354" t="n"/>
+      <c r="J37" s="355" t="n"/>
       <c r="L37" s="4" t="inlineStr">
         <is>
           <t>18.08,19.08</t>
@@ -19487,13 +19482,13 @@
       <c r="A38" s="316" t="n"/>
       <c r="B38" s="313" t="n"/>
       <c r="C38" s="313" t="n"/>
-      <c r="D38" s="353" t="n"/>
+      <c r="D38" s="354" t="n"/>
       <c r="E38" s="283" t="n"/>
       <c r="F38" s="283" t="n"/>
       <c r="G38" s="283" t="n"/>
       <c r="H38" s="283" t="n"/>
       <c r="I38" s="283" t="n"/>
-      <c r="J38" s="354" t="n"/>
+      <c r="J38" s="355" t="n"/>
     </row>
     <row r="39" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A39" s="119">
@@ -19513,14 +19508,19 @@
         <f>B39+4</f>
         <v/>
       </c>
-      <c r="E39" s="283" t="n"/>
-      <c r="F39" s="283" t="n"/>
-      <c r="G39" s="283" t="inlineStr">
-        <is>
-          <t>Qui - CAl/Fab
-5º e 6º tempos</t>
-        </is>
-      </c>
+      <c r="E39" s="283" t="inlineStr">
+        <is>
+          <t>DaF - CBu-EFr-Eth
+4º e 5º tempos</t>
+        </is>
+      </c>
+      <c r="F39" s="283" t="inlineStr">
+        <is>
+          <t>Bio - Ale
+2º e 3º tempos</t>
+        </is>
+      </c>
+      <c r="G39" s="283" t="n"/>
       <c r="H39" s="283" t="n"/>
       <c r="I39" s="283" t="n"/>
       <c r="J39" s="265" t="n"/>
@@ -19529,25 +19529,25 @@
       <c r="A40" s="316" t="n"/>
       <c r="B40" s="313" t="n"/>
       <c r="C40" s="313" t="n"/>
-      <c r="D40" s="353" t="n"/>
+      <c r="D40" s="354" t="n"/>
       <c r="E40" s="283" t="n"/>
       <c r="F40" s="283" t="n"/>
       <c r="G40" s="283" t="n"/>
       <c r="H40" s="283" t="n"/>
       <c r="I40" s="283" t="n"/>
-      <c r="J40" s="354" t="n"/>
+      <c r="J40" s="355" t="n"/>
     </row>
     <row r="41" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A41" s="316" t="n"/>
       <c r="B41" s="313" t="n"/>
       <c r="C41" s="313" t="n"/>
-      <c r="D41" s="353" t="n"/>
+      <c r="D41" s="354" t="n"/>
       <c r="E41" s="283" t="n"/>
       <c r="F41" s="283" t="n"/>
       <c r="G41" s="283" t="n"/>
       <c r="H41" s="283" t="n"/>
       <c r="I41" s="283" t="n"/>
-      <c r="J41" s="354" t="n"/>
+      <c r="J41" s="355" t="n"/>
     </row>
     <row r="42" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A42" s="119">
@@ -19568,13 +19568,13 @@
         <v/>
       </c>
       <c r="E42" s="283" t="n"/>
-      <c r="F42" s="283" t="inlineStr">
-        <is>
-          <t>Mat - Bre/JJ
-1º e 2º tempos</t>
-        </is>
-      </c>
-      <c r="G42" s="283" t="n"/>
+      <c r="F42" s="283" t="n"/>
+      <c r="G42" s="283" t="inlineStr">
+        <is>
+          <t>Fil - LAn
+4º tempo</t>
+        </is>
+      </c>
       <c r="H42" s="283" t="n"/>
       <c r="I42" s="283" t="n"/>
       <c r="J42" s="265" t="n"/>
@@ -19589,26 +19589,26 @@
       <c r="A43" s="316" t="n"/>
       <c r="B43" s="313" t="n"/>
       <c r="C43" s="313" t="n"/>
-      <c r="D43" s="353" t="n"/>
+      <c r="D43" s="354" t="n"/>
       <c r="E43" s="283" t="n"/>
       <c r="F43" s="283" t="n"/>
       <c r="G43" s="283" t="n"/>
       <c r="H43" s="283" t="n"/>
       <c r="I43" s="283" t="n"/>
-      <c r="J43" s="354" t="n"/>
+      <c r="J43" s="355" t="n"/>
       <c r="L43" s="331" t="n"/>
     </row>
     <row r="44" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A44" s="316" t="n"/>
       <c r="B44" s="313" t="n"/>
       <c r="C44" s="313" t="n"/>
-      <c r="D44" s="353" t="n"/>
+      <c r="D44" s="354" t="n"/>
       <c r="E44" s="283" t="n"/>
       <c r="F44" s="283" t="n"/>
       <c r="G44" s="283" t="n"/>
       <c r="H44" s="283" t="n"/>
       <c r="I44" s="283" t="n"/>
-      <c r="J44" s="354" t="n"/>
+      <c r="J44" s="355" t="n"/>
       <c r="L44" s="331" t="n"/>
     </row>
     <row r="45" ht="18" customFormat="1" customHeight="1" s="4">
@@ -19629,21 +19629,21 @@
         <f>B45+4</f>
         <v/>
       </c>
-      <c r="E45" s="283" t="n"/>
-      <c r="F45" s="283" t="inlineStr">
-        <is>
-          <t>Fis - Cadu
-2º e 3º tempos</t>
-        </is>
-      </c>
-      <c r="G45" s="283" t="n"/>
-      <c r="H45" s="283" t="inlineStr">
-        <is>
-          <t>LP/LIT/RED - AMu/Deb
-3º ao 5º tempos</t>
-        </is>
-      </c>
-      <c r="I45" s="357" t="inlineStr">
+      <c r="E45" s="283" t="inlineStr">
+        <is>
+          <t>Qui - CAl/Fab
+1º e 2º tempos</t>
+        </is>
+      </c>
+      <c r="F45" s="283" t="n"/>
+      <c r="G45" s="283" t="inlineStr">
+        <is>
+          <t>Soc - Kle
+2º tempo</t>
+        </is>
+      </c>
+      <c r="H45" s="283" t="n"/>
+      <c r="I45" s="358" t="inlineStr">
         <is>
           <t>2CH
 10,12</t>
@@ -19656,26 +19656,26 @@
       <c r="A46" s="316" t="n"/>
       <c r="B46" s="313" t="n"/>
       <c r="C46" s="313" t="n"/>
-      <c r="D46" s="353" t="n"/>
+      <c r="D46" s="354" t="n"/>
       <c r="E46" s="283" t="n"/>
       <c r="F46" s="283" t="n"/>
       <c r="G46" s="283" t="n"/>
       <c r="H46" s="283" t="n"/>
-      <c r="I46" s="358" t="n"/>
-      <c r="J46" s="354" t="n"/>
+      <c r="I46" s="359" t="n"/>
+      <c r="J46" s="355" t="n"/>
       <c r="L46" s="331" t="n"/>
     </row>
     <row r="47" ht="51" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A47" s="316" t="n"/>
       <c r="B47" s="313" t="n"/>
       <c r="C47" s="313" t="n"/>
-      <c r="D47" s="353" t="n"/>
+      <c r="D47" s="354" t="n"/>
       <c r="E47" s="283" t="n"/>
       <c r="F47" s="283" t="n"/>
       <c r="G47" s="283" t="n"/>
       <c r="H47" s="283" t="n"/>
-      <c r="I47" s="359" t="n"/>
-      <c r="J47" s="354" t="n"/>
+      <c r="I47" s="360" t="n"/>
+      <c r="J47" s="355" t="n"/>
       <c r="L47" s="332" t="n"/>
     </row>
     <row r="48" ht="23.25" customFormat="1" customHeight="1" s="4">
@@ -19697,7 +19697,7 @@
         <v/>
       </c>
       <c r="E48" s="283" t="n"/>
-      <c r="F48" s="360" t="inlineStr">
+      <c r="F48" s="361" t="inlineStr">
         <is>
           <t>CC
 10,12</t>
@@ -19716,25 +19716,25 @@
       <c r="A49" s="316" t="n"/>
       <c r="B49" s="313" t="n"/>
       <c r="C49" s="313" t="n"/>
-      <c r="D49" s="353" t="n"/>
+      <c r="D49" s="354" t="n"/>
       <c r="E49" s="283" t="n"/>
-      <c r="F49" s="358" t="n"/>
+      <c r="F49" s="359" t="n"/>
       <c r="G49" s="283" t="n"/>
       <c r="H49" s="283" t="n"/>
       <c r="I49" s="315" t="n"/>
-      <c r="J49" s="354" t="n"/>
+      <c r="J49" s="355" t="n"/>
     </row>
     <row r="50" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A50" s="316" t="n"/>
       <c r="B50" s="313" t="n"/>
       <c r="C50" s="313" t="n"/>
-      <c r="D50" s="353" t="n"/>
+      <c r="D50" s="354" t="n"/>
       <c r="E50" s="78" t="n"/>
-      <c r="F50" s="359" t="n"/>
+      <c r="F50" s="360" t="n"/>
       <c r="G50" s="283" t="n"/>
       <c r="H50" s="283" t="n"/>
       <c r="I50" s="315" t="n"/>
-      <c r="J50" s="354" t="n"/>
+      <c r="J50" s="355" t="n"/>
     </row>
     <row r="51" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A51" s="119">
@@ -19758,32 +19758,32 @@
       <c r="F51" s="183" t="n"/>
       <c r="G51" s="183" t="n"/>
       <c r="H51" s="183" t="n"/>
-      <c r="I51" s="357" t="n"/>
+      <c r="I51" s="358" t="n"/>
       <c r="J51" s="274" t="n"/>
     </row>
     <row r="52" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A52" s="316" t="n"/>
       <c r="B52" s="313" t="n"/>
       <c r="C52" s="313" t="n"/>
-      <c r="D52" s="353" t="n"/>
+      <c r="D52" s="354" t="n"/>
       <c r="E52" s="283" t="n"/>
       <c r="F52" s="315" t="n"/>
       <c r="G52" s="315" t="n"/>
       <c r="H52" s="315" t="n"/>
-      <c r="I52" s="358" t="n"/>
-      <c r="J52" s="354" t="n"/>
+      <c r="I52" s="359" t="n"/>
+      <c r="J52" s="355" t="n"/>
     </row>
     <row r="53" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A53" s="316" t="n"/>
       <c r="B53" s="313" t="n"/>
       <c r="C53" s="313" t="n"/>
-      <c r="D53" s="353" t="n"/>
+      <c r="D53" s="354" t="n"/>
       <c r="E53" s="283" t="n"/>
       <c r="F53" s="315" t="n"/>
       <c r="G53" s="315" t="n"/>
       <c r="H53" s="315" t="n"/>
-      <c r="I53" s="359" t="n"/>
-      <c r="J53" s="354" t="n"/>
+      <c r="I53" s="360" t="n"/>
+      <c r="J53" s="355" t="n"/>
     </row>
     <row r="54" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A54" s="119">
@@ -19814,25 +19814,25 @@
       <c r="A55" s="316" t="n"/>
       <c r="B55" s="313" t="n"/>
       <c r="C55" s="313" t="n"/>
-      <c r="D55" s="353" t="n"/>
+      <c r="D55" s="354" t="n"/>
       <c r="E55" s="315" t="n"/>
       <c r="F55" s="315" t="n"/>
       <c r="G55" s="315" t="n"/>
       <c r="H55" s="315" t="n"/>
       <c r="I55" s="315" t="n"/>
-      <c r="J55" s="354" t="n"/>
+      <c r="J55" s="355" t="n"/>
     </row>
     <row r="56" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A56" s="316" t="n"/>
       <c r="B56" s="313" t="n"/>
       <c r="C56" s="313" t="n"/>
-      <c r="D56" s="353" t="n"/>
+      <c r="D56" s="354" t="n"/>
       <c r="E56" s="315" t="n"/>
       <c r="F56" s="315" t="n"/>
       <c r="G56" s="315" t="n"/>
       <c r="H56" s="315" t="n"/>
       <c r="I56" s="315" t="n"/>
-      <c r="J56" s="354" t="n"/>
+      <c r="J56" s="355" t="n"/>
     </row>
     <row r="57" ht="25.5" customFormat="1" customHeight="1" s="4">
       <c r="A57" s="119">
@@ -19853,7 +19853,7 @@
         <v/>
       </c>
       <c r="E57" s="183" t="n"/>
-      <c r="F57" s="360" t="n"/>
+      <c r="F57" s="361" t="n"/>
       <c r="G57" s="183" t="n"/>
       <c r="H57" s="183" t="n"/>
       <c r="I57" s="183" t="n"/>
@@ -19863,25 +19863,25 @@
       <c r="A58" s="316" t="n"/>
       <c r="B58" s="313" t="n"/>
       <c r="C58" s="313" t="n"/>
-      <c r="D58" s="353" t="n"/>
+      <c r="D58" s="354" t="n"/>
       <c r="E58" s="315" t="n"/>
-      <c r="F58" s="358" t="n"/>
+      <c r="F58" s="359" t="n"/>
       <c r="G58" s="315" t="n"/>
       <c r="H58" s="315" t="n"/>
       <c r="I58" s="315" t="n"/>
-      <c r="J58" s="354" t="n"/>
+      <c r="J58" s="355" t="n"/>
     </row>
     <row r="59" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A59" s="316" t="n"/>
       <c r="B59" s="313" t="n"/>
       <c r="C59" s="313" t="n"/>
-      <c r="D59" s="353" t="n"/>
+      <c r="D59" s="354" t="n"/>
       <c r="E59" s="315" t="n"/>
-      <c r="F59" s="359" t="n"/>
+      <c r="F59" s="360" t="n"/>
       <c r="G59" s="315" t="n"/>
       <c r="H59" s="315" t="n"/>
       <c r="I59" s="315" t="n"/>
-      <c r="J59" s="354" t="n"/>
+      <c r="J59" s="355" t="n"/>
     </row>
     <row r="60" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A60" s="281">
@@ -19913,24 +19913,24 @@
       <c r="B61" s="331" t="n"/>
       <c r="C61" s="331" t="n"/>
       <c r="D61" s="331" t="n"/>
-      <c r="E61" s="358" t="n"/>
-      <c r="F61" s="358" t="n"/>
-      <c r="G61" s="358" t="n"/>
-      <c r="H61" s="358" t="n"/>
-      <c r="I61" s="358" t="n"/>
-      <c r="J61" s="358" t="n"/>
+      <c r="E61" s="359" t="n"/>
+      <c r="F61" s="359" t="n"/>
+      <c r="G61" s="359" t="n"/>
+      <c r="H61" s="359" t="n"/>
+      <c r="I61" s="359" t="n"/>
+      <c r="J61" s="359" t="n"/>
     </row>
     <row r="62" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A62" s="332" t="n"/>
       <c r="B62" s="332" t="n"/>
       <c r="C62" s="332" t="n"/>
       <c r="D62" s="332" t="n"/>
-      <c r="E62" s="361" t="n"/>
-      <c r="F62" s="361" t="n"/>
-      <c r="G62" s="361" t="n"/>
-      <c r="H62" s="361" t="n"/>
-      <c r="I62" s="361" t="n"/>
-      <c r="J62" s="361" t="n"/>
+      <c r="E62" s="362" t="n"/>
+      <c r="F62" s="362" t="n"/>
+      <c r="G62" s="362" t="n"/>
+      <c r="H62" s="362" t="n"/>
+      <c r="I62" s="362" t="n"/>
+      <c r="J62" s="362" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="146">

--- a/Horario desenvolvido/Proposta_2_Calendario_Provas_2026_2SEM.xlsx
+++ b/Horario desenvolvido/Proposta_2_Calendario_Provas_2026_2SEM.xlsx
@@ -5367,24 +5367,19 @@
         <f>B9+4</f>
         <v/>
       </c>
-      <c r="E9" s="183" t="n"/>
-      <c r="F9" s="183" t="inlineStr">
-        <is>
-          <t>Fis - Cadu
-1º e 2º tempos</t>
-        </is>
-      </c>
+      <c r="E9" s="183" t="inlineStr">
+        <is>
+          <t>Ing - Isb
+4º e 5º tempos</t>
+        </is>
+      </c>
+      <c r="F9" s="183" t="n"/>
       <c r="G9" s="183" t="n"/>
-      <c r="H9" s="183" t="inlineStr">
-        <is>
-          <t>Mat - Bre/JJ
-4º e 5º tempos</t>
-        </is>
-      </c>
+      <c r="H9" s="183" t="n"/>
       <c r="I9" s="183" t="inlineStr">
         <is>
-          <t>Geo - Mar
-2º e 3º tempos</t>
+          <t>LP/LIT/RED - AMu/Deb
+1º ao 3º tempos</t>
         </is>
       </c>
       <c r="J9" s="183" t="n"/>
@@ -5470,13 +5465,18 @@
 4º e 5º tempos</t>
         </is>
       </c>
-      <c r="F12" s="11" t="n"/>
+      <c r="F12" s="11" t="inlineStr">
+        <is>
+          <t>Fis - Cadu
+2º e 3º tempos</t>
+        </is>
+      </c>
       <c r="G12" s="11" t="n"/>
       <c r="H12" s="11" t="n"/>
       <c r="I12" s="11" t="inlineStr">
         <is>
-          <t>Hist - Wag
-1º e 2º tempos</t>
+          <t>Qui - CAl/Fab
+4º e 5º tempos</t>
         </is>
       </c>
       <c r="J12" s="183" t="n"/>
@@ -5535,24 +5535,19 @@
         <f>B15+4</f>
         <v/>
       </c>
-      <c r="E15" s="11" t="inlineStr">
-        <is>
-          <t>Ing - Isb
-4º e 5º tempos</t>
-        </is>
-      </c>
+      <c r="E15" s="11" t="n"/>
       <c r="F15" s="11" t="inlineStr">
         <is>
-          <t>Bio - Ale
-2º e 3º tempos</t>
+          <t>Mat - Bre/JJ
+1º e 2º tempos</t>
         </is>
       </c>
       <c r="G15" s="11" t="n"/>
       <c r="H15" s="11" t="n"/>
       <c r="I15" s="11" t="inlineStr">
         <is>
-          <t>LP/LIT/RED - AMu/Deb
-1º ao 3º tempos</t>
+          <t>Hist - Wag
+1º e 2º tempos</t>
         </is>
       </c>
       <c r="J15" s="183" t="n"/>
@@ -5614,7 +5609,12 @@
           <t>unterrichtsfrei sem aula</t>
         </is>
       </c>
-      <c r="F18" s="11" t="n"/>
+      <c r="F18" s="11" t="inlineStr">
+        <is>
+          <t>Bio - Ale
+2º e 3º tempos</t>
+        </is>
+      </c>
       <c r="G18" s="11" t="n"/>
       <c r="H18" s="11" t="inlineStr">
         <is>
@@ -5624,8 +5624,8 @@
       </c>
       <c r="I18" s="350" t="inlineStr">
         <is>
-          <t>Qui - CAl/Fab
-4º e 5º tempos</t>
+          <t>Geo - Mar
+2º e 3º tempos</t>
         </is>
       </c>
       <c r="J18" s="262" t="inlineStr">
@@ -5694,7 +5694,12 @@
         <v/>
       </c>
       <c r="E21" s="11" t="n"/>
-      <c r="F21" s="62" t="n"/>
+      <c r="F21" s="62" t="inlineStr">
+        <is>
+          <t>Fis - Cadu
+1º e 2º tempos</t>
+        </is>
+      </c>
       <c r="G21" s="11" t="inlineStr">
         <is>
           <t>S4-12
@@ -5771,20 +5776,20 @@
         <v/>
       </c>
       <c r="E24" s="283" t="n"/>
-      <c r="F24" s="283" t="n"/>
-      <c r="G24" s="79" t="n"/>
-      <c r="H24" s="283" t="inlineStr">
-        <is>
-          <t>Mat - Bre/JJ
-4º e 5º tempos</t>
-        </is>
-      </c>
-      <c r="I24" s="78" t="inlineStr">
-        <is>
-          <t>Geo - Mar
+      <c r="F24" s="283" t="inlineStr">
+        <is>
+          <t>Bio - Ale
 2º e 3º tempos</t>
         </is>
       </c>
+      <c r="G24" s="353" t="inlineStr">
+        <is>
+          <t>Soc - Kle
+6º tempo</t>
+        </is>
+      </c>
+      <c r="H24" s="283" t="n"/>
+      <c r="I24" s="78" t="n"/>
       <c r="J24" s="265" t="n"/>
       <c r="L24" s="318" t="inlineStr">
         <is>
@@ -6106,18 +6111,13 @@
         <v/>
       </c>
       <c r="E36" s="283" t="n"/>
-      <c r="F36" s="283" t="inlineStr">
-        <is>
-          <t>Fis - Cadu
-1º e 2º tempos</t>
-        </is>
-      </c>
+      <c r="F36" s="283" t="n"/>
       <c r="G36" s="283" t="n"/>
       <c r="H36" s="283" t="n"/>
       <c r="I36" s="283" t="inlineStr">
         <is>
           <t>Hist - Wag
-1º e 2º tempos</t>
+4º e 5º tempos</t>
         </is>
       </c>
       <c r="J36" s="265" t="n"/>
@@ -6190,15 +6190,15 @@
 4º e 5º tempos</t>
         </is>
       </c>
-      <c r="F39" s="283" t="inlineStr">
-        <is>
-          <t>Bio - Ale
-2º e 3º tempos</t>
-        </is>
-      </c>
+      <c r="F39" s="283" t="n"/>
       <c r="G39" s="283" t="n"/>
       <c r="H39" s="283" t="n"/>
-      <c r="I39" s="283" t="n"/>
+      <c r="I39" s="283" t="inlineStr">
+        <is>
+          <t>Qui - CAl/Fab
+2º e 3º tempos</t>
+        </is>
+      </c>
       <c r="J39" s="265" t="n"/>
     </row>
     <row r="40" ht="18" customFormat="1" customHeight="1" s="4">
@@ -6252,7 +6252,12 @@
         </is>
       </c>
       <c r="H42" s="283" t="n"/>
-      <c r="I42" s="283" t="n"/>
+      <c r="I42" s="283" t="inlineStr">
+        <is>
+          <t>Geo - Mar
+2º e 3º tempos</t>
+        </is>
+      </c>
       <c r="J42" s="265" t="n"/>
       <c r="L42" s="259" t="inlineStr">
         <is>
@@ -6305,19 +6310,14 @@
         <f>B45+4</f>
         <v/>
       </c>
-      <c r="E45" s="283" t="inlineStr">
-        <is>
-          <t>Qui - CAl/Fab
+      <c r="E45" s="283" t="n"/>
+      <c r="F45" s="283" t="inlineStr">
+        <is>
+          <t>Mat - Bre/JJ
 1º e 2º tempos</t>
         </is>
       </c>
-      <c r="F45" s="283" t="n"/>
-      <c r="G45" s="283" t="inlineStr">
-        <is>
-          <t>Soc - Kle
-2º tempo</t>
-        </is>
-      </c>
+      <c r="G45" s="283" t="n"/>
       <c r="H45" s="283" t="n"/>
       <c r="I45" s="358" t="inlineStr">
         <is>
@@ -12260,8 +12260,8 @@
       <c r="G21" s="11" t="n"/>
       <c r="H21" s="11" t="inlineStr">
         <is>
-          <t>Geo - Mlo
-4º e 5º tempos</t>
+          <t>Ing - APa
+2º e 3º tempos</t>
         </is>
       </c>
       <c r="I21" s="11" t="n"/>
@@ -12327,17 +12327,12 @@
         <f>B24+4</f>
         <v/>
       </c>
-      <c r="E24" s="283" t="inlineStr">
-        <is>
-          <t>DaF - Eth-EFr-Swa
-1º e 2º tempos</t>
-        </is>
-      </c>
+      <c r="E24" s="283" t="n"/>
       <c r="F24" s="283" t="n"/>
       <c r="G24" s="353" t="inlineStr">
         <is>
-          <t>Soc - Kle
-5º tempo</t>
+          <t>Fil - LAn
+1º tempo</t>
         </is>
       </c>
       <c r="H24" s="283" t="n"/>
@@ -12407,12 +12402,7 @@
         <f>B27+4</f>
         <v/>
       </c>
-      <c r="E27" s="78" t="inlineStr">
-        <is>
-          <t>Mat - BrSa/FBri
-1º e 2º tempos</t>
-        </is>
-      </c>
+      <c r="E27" s="78" t="n"/>
       <c r="F27" s="283" t="n"/>
       <c r="G27" s="283" t="inlineStr">
         <is>
@@ -12487,16 +12477,21 @@
         <f>B30+4</f>
         <v/>
       </c>
-      <c r="E30" s="283" t="inlineStr">
-        <is>
-          <t>LP/LIT/RED - BPad/MFo/SMo
-1º ao 3º tempos</t>
-        </is>
-      </c>
+      <c r="E30" s="283" t="n"/>
       <c r="F30" s="283" t="n"/>
       <c r="G30" s="283" t="n"/>
-      <c r="H30" s="283" t="n"/>
-      <c r="I30" s="283" t="n"/>
+      <c r="H30" s="283" t="inlineStr">
+        <is>
+          <t>Mat - BrSa/FBri
+4º e 5º tempos</t>
+        </is>
+      </c>
+      <c r="I30" s="283" t="inlineStr">
+        <is>
+          <t>Soc - Kle
+5º tempo</t>
+        </is>
+      </c>
       <c r="J30" s="183" t="inlineStr">
         <is>
           <t>unterrichtsfrei sem aula</t>
@@ -12670,12 +12665,7 @@
       </c>
       <c r="F36" s="283" t="n"/>
       <c r="G36" s="283" t="n"/>
-      <c r="H36" s="283" t="inlineStr">
-        <is>
-          <t>Ing - APa
-2º e 3º tempos</t>
-        </is>
-      </c>
+      <c r="H36" s="283" t="n"/>
       <c r="I36" s="283" t="n"/>
       <c r="J36" s="265" t="n"/>
       <c r="L36" s="81" t="inlineStr">
@@ -12741,15 +12731,20 @@
         <f>B39+4</f>
         <v/>
       </c>
-      <c r="E39" s="283" t="n"/>
+      <c r="E39" s="283" t="inlineStr">
+        <is>
+          <t>LP/LIT/RED - BPad/MFo/SMo
+1º ao 3º tempos</t>
+        </is>
+      </c>
       <c r="F39" s="283" t="n"/>
-      <c r="G39" s="283" t="inlineStr">
-        <is>
-          <t>Fil - LAn
-1º tempo</t>
-        </is>
-      </c>
-      <c r="H39" s="283" t="n"/>
+      <c r="G39" s="283" t="n"/>
+      <c r="H39" s="283" t="inlineStr">
+        <is>
+          <t>Geo - Mlo
+4º e 5º tempos</t>
+        </is>
+      </c>
       <c r="I39" s="283" t="n"/>
       <c r="J39" s="265" t="n"/>
     </row>
@@ -12797,11 +12792,16 @@
       </c>
       <c r="E42" s="283" t="n"/>
       <c r="F42" s="283" t="n"/>
-      <c r="G42" s="283" t="n"/>
+      <c r="G42" s="283" t="inlineStr">
+        <is>
+          <t>DaF - Eth-EFr-Swa
+2º e 3º tempos</t>
+        </is>
+      </c>
       <c r="H42" s="283" t="inlineStr">
         <is>
-          <t>Fis - VSi
-1º e 2º tempos</t>
+          <t>Hist - ALu
+2º e 3º tempos</t>
         </is>
       </c>
       <c r="I42" s="283" t="n"/>
@@ -12862,8 +12862,8 @@
       <c r="G45" s="283" t="n"/>
       <c r="H45" s="283" t="inlineStr">
         <is>
-          <t>Hist - ALu
-2º e 3º tempos</t>
+          <t>Fis - VSi
+1º e 2º tempos</t>
         </is>
       </c>
       <c r="I45" s="358" t="inlineStr">
@@ -13939,12 +13939,7 @@
         </is>
       </c>
       <c r="G21" s="11" t="n"/>
-      <c r="H21" s="11" t="inlineStr">
-        <is>
-          <t>Geo - Mlo
-4º e 5º tempos</t>
-        </is>
-      </c>
+      <c r="H21" s="11" t="n"/>
       <c r="I21" s="11" t="n"/>
       <c r="J21" s="183" t="n"/>
       <c r="L21" s="80" t="inlineStr">
@@ -14008,17 +14003,12 @@
         <f>B24+4</f>
         <v/>
       </c>
-      <c r="E24" s="283" t="inlineStr">
-        <is>
-          <t>DaF - Eth-EFr-Swa
-1º e 2º tempos</t>
-        </is>
-      </c>
+      <c r="E24" s="283" t="n"/>
       <c r="F24" s="283" t="n"/>
       <c r="G24" s="353" t="inlineStr">
         <is>
-          <t>Soc - Kle
-5º tempo</t>
+          <t>Fil - LAn
+1º tempo</t>
         </is>
       </c>
       <c r="H24" s="283" t="n"/>
@@ -14088,12 +14078,7 @@
         <f>B27+4</f>
         <v/>
       </c>
-      <c r="E27" s="78" t="inlineStr">
-        <is>
-          <t>Mat - BrSa/FBri
-1º e 2º tempos</t>
-        </is>
-      </c>
+      <c r="E27" s="78" t="n"/>
       <c r="F27" s="283" t="n"/>
       <c r="G27" s="283" t="inlineStr">
         <is>
@@ -14168,21 +14153,21 @@
         <f>B30+4</f>
         <v/>
       </c>
-      <c r="E30" s="283" t="inlineStr">
-        <is>
-          <t>LP/LIT/RED - BPad/MFo/SMo
-1º ao 3º tempos</t>
-        </is>
-      </c>
+      <c r="E30" s="283" t="n"/>
       <c r="F30" s="283" t="n"/>
-      <c r="G30" s="283" t="inlineStr">
-        <is>
-          <t>Ing - Vir
+      <c r="G30" s="283" t="n"/>
+      <c r="H30" s="283" t="inlineStr">
+        <is>
+          <t>Mat - BrSa/FBri
 4º e 5º tempos</t>
         </is>
       </c>
-      <c r="H30" s="283" t="n"/>
-      <c r="I30" s="283" t="n"/>
+      <c r="I30" s="283" t="inlineStr">
+        <is>
+          <t>Soc - Kle
+5º tempo</t>
+        </is>
+      </c>
       <c r="J30" s="183" t="inlineStr">
         <is>
           <t>unterrichtsfrei sem aula</t>
@@ -14422,15 +14407,20 @@
         <f>B39+4</f>
         <v/>
       </c>
-      <c r="E39" s="283" t="n"/>
+      <c r="E39" s="283" t="inlineStr">
+        <is>
+          <t>LP/LIT/RED - BPad/MFo/SMo
+1º ao 3º tempos</t>
+        </is>
+      </c>
       <c r="F39" s="283" t="n"/>
-      <c r="G39" s="283" t="inlineStr">
-        <is>
-          <t>Fil - LAn
-1º tempo</t>
-        </is>
-      </c>
-      <c r="H39" s="283" t="n"/>
+      <c r="G39" s="283" t="n"/>
+      <c r="H39" s="283" t="inlineStr">
+        <is>
+          <t>Geo - Mlo
+4º e 5º tempos</t>
+        </is>
+      </c>
       <c r="I39" s="283" t="n"/>
       <c r="J39" s="265" t="n"/>
     </row>
@@ -14478,11 +14468,16 @@
       </c>
       <c r="E42" s="283" t="n"/>
       <c r="F42" s="283" t="n"/>
-      <c r="G42" s="283" t="n"/>
+      <c r="G42" s="283" t="inlineStr">
+        <is>
+          <t>DaF - Eth-EFr-Swa
+2º e 3º tempos</t>
+        </is>
+      </c>
       <c r="H42" s="283" t="inlineStr">
         <is>
-          <t>Fis - VSi
-1º e 2º tempos</t>
+          <t>Hist - ALu
+2º e 3º tempos</t>
         </is>
       </c>
       <c r="I42" s="283" t="n"/>
@@ -14540,11 +14535,16 @@
       </c>
       <c r="E45" s="283" t="n"/>
       <c r="F45" s="283" t="n"/>
-      <c r="G45" s="283" t="n"/>
+      <c r="G45" s="283" t="inlineStr">
+        <is>
+          <t>Ing - Vir
+4º e 5º tempos</t>
+        </is>
+      </c>
       <c r="H45" s="283" t="inlineStr">
         <is>
-          <t>Hist - ALu
-2º e 3º tempos</t>
+          <t>Fis - VSi
+1º e 2º tempos</t>
         </is>
       </c>
       <c r="I45" s="358" t="inlineStr">
@@ -15301,21 +15301,21 @@
       </c>
       <c r="E9" s="183" t="inlineStr">
         <is>
-          <t>LP/LIT/RED - ACo/AMu/Raf
-1º ao 3º tempos</t>
-        </is>
-      </c>
-      <c r="F9" s="183" t="n"/>
-      <c r="G9" s="183" t="inlineStr">
-        <is>
-          <t>Geo - Mar
+          <t>Bio - Ale
 1º e 2º tempos</t>
         </is>
       </c>
+      <c r="F9" s="183" t="inlineStr">
+        <is>
+          <t>DaF - CBu-SGa-Swa
+4º e 5º tempos</t>
+        </is>
+      </c>
+      <c r="G9" s="183" t="n"/>
       <c r="H9" s="183" t="inlineStr">
         <is>
-          <t>Bio - Ale
-2º e 3º tempos</t>
+          <t>Ing - Bea
+4º e 5º tempos</t>
         </is>
       </c>
       <c r="I9" s="183" t="n"/>
@@ -15398,8 +15398,8 @@
       </c>
       <c r="E12" s="11" t="inlineStr">
         <is>
-          <t>Qui - CAl
-1º e 2º tempos</t>
+          <t>LP/LIT/RED - ACo/AMu/Raf
+1º ao 3º tempos</t>
         </is>
       </c>
       <c r="F12" s="11" t="inlineStr">
@@ -15414,12 +15414,7 @@
 2º ao 7º tempos</t>
         </is>
       </c>
-      <c r="H12" s="11" t="inlineStr">
-        <is>
-          <t>Ing - Bea
-4º e 5º tempos</t>
-        </is>
-      </c>
+      <c r="H12" s="11" t="n"/>
       <c r="I12" s="11" t="n"/>
       <c r="J12" s="183" t="n"/>
       <c r="L12" s="15" t="n"/>
@@ -15479,17 +15474,22 @@
       </c>
       <c r="E15" s="11" t="inlineStr">
         <is>
+          <t>Mat - ClaMe/JJ
+2º e 3º tempos</t>
+        </is>
+      </c>
+      <c r="F15" s="11" t="inlineStr">
+        <is>
+          <t>Hist - Ver
+2º e 3º tempos</t>
+        </is>
+      </c>
+      <c r="G15" s="11" t="inlineStr">
+        <is>
           <t>GL - CBu-Swa-SGa
 4º e 5º tempos</t>
         </is>
       </c>
-      <c r="F15" s="11" t="inlineStr">
-        <is>
-          <t>Mat - ClaMe/JJ
-1º e 2º tempos</t>
-        </is>
-      </c>
-      <c r="G15" s="11" t="n"/>
       <c r="H15" s="11" t="n"/>
       <c r="I15" s="11" t="n"/>
       <c r="J15" s="183" t="n"/>
@@ -15553,13 +15553,13 @@
       </c>
       <c r="F18" s="11" t="inlineStr">
         <is>
-          <t>DaF - CBu-SGa-Swa
-4º e 5º tempos</t>
+          <t>Qui - CAl
+1º e 2º tempos</t>
         </is>
       </c>
       <c r="G18" s="11" t="inlineStr">
         <is>
-          <t>Hist - Ver
+          <t>Geo - Mar
 1º e 2º tempos</t>
         </is>
       </c>
@@ -15636,20 +15636,20 @@
         <v/>
       </c>
       <c r="E21" s="11" t="n"/>
-      <c r="F21" s="62" t="n"/>
-      <c r="G21" s="11" t="n"/>
-      <c r="H21" s="11" t="inlineStr">
-        <is>
-          <t>Fis - Cadu
+      <c r="F21" s="62" t="inlineStr">
+        <is>
+          <t>Mat - ClaMe/JJ
 1º e 2º tempos</t>
         </is>
       </c>
-      <c r="I21" s="11" t="inlineStr">
-        <is>
-          <t>Soc - Kle
-4º tempo</t>
-        </is>
-      </c>
+      <c r="G21" s="11" t="inlineStr">
+        <is>
+          <t>GL - CBu-Swa-SGa
+4º e 5º tempos</t>
+        </is>
+      </c>
+      <c r="H21" s="11" t="n"/>
+      <c r="I21" s="11" t="n"/>
       <c r="J21" s="183" t="n"/>
       <c r="L21" s="80" t="inlineStr">
         <is>
@@ -15720,7 +15720,12 @@
         </is>
       </c>
       <c r="G24" s="79" t="n"/>
-      <c r="H24" s="283" t="n"/>
+      <c r="H24" s="283" t="inlineStr">
+        <is>
+          <t>Ing - Bea
+4º e 5º tempos</t>
+        </is>
+      </c>
       <c r="I24" s="78" t="n"/>
       <c r="J24" s="265" t="n"/>
       <c r="L24" s="318" t="inlineStr">
@@ -15787,21 +15792,21 @@
         <f>B27+4</f>
         <v/>
       </c>
-      <c r="E27" s="78" t="n"/>
+      <c r="E27" s="78" t="inlineStr">
+        <is>
+          <t>Bio - Ale
+2º e 3º tempos</t>
+        </is>
+      </c>
       <c r="F27" s="283" t="n"/>
-      <c r="G27" s="283" t="inlineStr">
-        <is>
-          <t>GL - CBu-Swa-SGa
-4º e 5º tempos</t>
-        </is>
-      </c>
-      <c r="H27" s="283" t="inlineStr">
-        <is>
-          <t>Ing - Bea
-4º e 5º tempos</t>
-        </is>
-      </c>
-      <c r="I27" s="283" t="n"/>
+      <c r="G27" s="283" t="n"/>
+      <c r="H27" s="283" t="n"/>
+      <c r="I27" s="283" t="inlineStr">
+        <is>
+          <t>Soc - Kle
+4º tempo</t>
+        </is>
+      </c>
       <c r="J27" s="265" t="n"/>
       <c r="L27" s="45" t="n"/>
       <c r="M27" s="323" t="inlineStr">
@@ -15874,12 +15879,7 @@
         </is>
       </c>
       <c r="F30" s="283" t="n"/>
-      <c r="G30" s="283" t="inlineStr">
-        <is>
-          <t>Hist - Ver
-1º e 2º tempos</t>
-        </is>
-      </c>
+      <c r="G30" s="283" t="n"/>
       <c r="H30" s="283" t="n"/>
       <c r="I30" s="283" t="n"/>
       <c r="J30" s="183" t="inlineStr">
@@ -16047,12 +16047,7 @@
         <f>B36+4</f>
         <v/>
       </c>
-      <c r="E36" s="283" t="inlineStr">
-        <is>
-          <t>Mat - ClaMe/JJ
-2º e 3º tempos</t>
-        </is>
-      </c>
+      <c r="E36" s="283" t="n"/>
       <c r="F36" s="283" t="inlineStr">
         <is>
           <t>Qui - CAl
@@ -16060,7 +16055,12 @@
         </is>
       </c>
       <c r="G36" s="283" t="n"/>
-      <c r="H36" s="283" t="n"/>
+      <c r="H36" s="283" t="inlineStr">
+        <is>
+          <t>Fis - Cadu
+1º e 2º tempos</t>
+        </is>
+      </c>
       <c r="I36" s="283" t="n"/>
       <c r="J36" s="265" t="n"/>
       <c r="L36" s="81" t="inlineStr">
@@ -16186,13 +16186,13 @@
         <v/>
       </c>
       <c r="E42" s="283" t="n"/>
-      <c r="F42" s="283" t="n"/>
-      <c r="G42" s="283" t="inlineStr">
-        <is>
-          <t>Fil - LAn
-11º tempo</t>
-        </is>
-      </c>
+      <c r="F42" s="283" t="inlineStr">
+        <is>
+          <t>Hist - Ver
+2º e 3º tempos</t>
+        </is>
+      </c>
+      <c r="G42" s="283" t="n"/>
       <c r="H42" s="283" t="n"/>
       <c r="I42" s="283" t="n"/>
       <c r="J42" s="265" t="n"/>
@@ -16306,13 +16306,13 @@
       </c>
       <c r="E48" s="283" t="n"/>
       <c r="F48" s="361" t="n"/>
-      <c r="G48" s="283" t="n"/>
-      <c r="H48" s="283" t="inlineStr">
-        <is>
-          <t>Bio - Ale
-2º e 3º tempos</t>
-        </is>
-      </c>
+      <c r="G48" s="283" t="inlineStr">
+        <is>
+          <t>Fil - LAn
+9º tempo</t>
+        </is>
+      </c>
+      <c r="H48" s="283" t="n"/>
       <c r="I48" s="183" t="inlineStr">
         <is>
           <t>unterrichtsfrei sem aula</t>
@@ -16997,23 +16997,18 @@
       </c>
       <c r="E9" s="183" t="inlineStr">
         <is>
-          <t>LP/LIT/RED - ACo/AMu/Raf
-1º ao 3º tempos</t>
-        </is>
-      </c>
-      <c r="F9" s="183" t="n"/>
-      <c r="G9" s="183" t="inlineStr">
-        <is>
-          <t>Geo - Mar
+          <t>Bio - Ale
 1º e 2º tempos</t>
         </is>
       </c>
-      <c r="H9" s="183" t="inlineStr">
-        <is>
-          <t>Bio - Ale
-2º e 3º tempos</t>
-        </is>
-      </c>
+      <c r="F9" s="183" t="inlineStr">
+        <is>
+          <t>DaF - CBu-SGa-Swa
+4º e 5º tempos</t>
+        </is>
+      </c>
+      <c r="G9" s="183" t="n"/>
+      <c r="H9" s="183" t="n"/>
       <c r="I9" s="183" t="n"/>
       <c r="J9" s="183" t="n"/>
       <c r="L9" s="16" t="inlineStr">
@@ -17094,8 +17089,8 @@
       </c>
       <c r="E12" s="11" t="inlineStr">
         <is>
-          <t>Qui - CAl
-1º e 2º tempos</t>
+          <t>LP/LIT/RED - ACo/AMu/Raf
+1º ao 3º tempos</t>
         </is>
       </c>
       <c r="F12" s="11" t="inlineStr">
@@ -17175,17 +17170,22 @@
       </c>
       <c r="E15" s="11" t="inlineStr">
         <is>
+          <t>Mat - ClaMe/JJ
+2º e 3º tempos</t>
+        </is>
+      </c>
+      <c r="F15" s="11" t="inlineStr">
+        <is>
+          <t>Hist - Ver
+2º e 3º tempos</t>
+        </is>
+      </c>
+      <c r="G15" s="11" t="inlineStr">
+        <is>
           <t>GL - CBu-Swa-SGa
 4º e 5º tempos</t>
         </is>
       </c>
-      <c r="F15" s="11" t="inlineStr">
-        <is>
-          <t>Mat - ClaMe/JJ
-1º e 2º tempos</t>
-        </is>
-      </c>
-      <c r="G15" s="11" t="n"/>
       <c r="H15" s="11" t="n"/>
       <c r="I15" s="11" t="n"/>
       <c r="J15" s="183" t="n"/>
@@ -17249,13 +17249,13 @@
       </c>
       <c r="F18" s="11" t="inlineStr">
         <is>
-          <t>DaF - CBu-SGa-Swa
-4º e 5º tempos</t>
+          <t>Qui - CAl
+1º e 2º tempos</t>
         </is>
       </c>
       <c r="G18" s="11" t="inlineStr">
         <is>
-          <t>Hist - Ver
+          <t>Geo - Mar
 1º e 2º tempos</t>
         </is>
       </c>
@@ -17332,20 +17332,20 @@
         <v/>
       </c>
       <c r="E21" s="11" t="n"/>
-      <c r="F21" s="62" t="n"/>
-      <c r="G21" s="11" t="n"/>
-      <c r="H21" s="11" t="inlineStr">
-        <is>
-          <t>Fis - Cadu
+      <c r="F21" s="62" t="inlineStr">
+        <is>
+          <t>Mat - ClaMe/JJ
 1º e 2º tempos</t>
         </is>
       </c>
-      <c r="I21" s="11" t="inlineStr">
-        <is>
-          <t>Soc - Kle
-4º tempo</t>
-        </is>
-      </c>
+      <c r="G21" s="11" t="inlineStr">
+        <is>
+          <t>GL - CBu-Swa-SGa
+4º e 5º tempos</t>
+        </is>
+      </c>
+      <c r="H21" s="11" t="n"/>
+      <c r="I21" s="11" t="n"/>
       <c r="J21" s="183" t="n"/>
       <c r="L21" s="80" t="inlineStr">
         <is>
@@ -17485,19 +17485,19 @@
       </c>
       <c r="E27" s="78" t="inlineStr">
         <is>
-          <t>Ing - PaH
-4º e 5º tempos</t>
+          <t>Bio - Ale
+2º e 3º tempos</t>
         </is>
       </c>
       <c r="F27" s="283" t="n"/>
-      <c r="G27" s="283" t="inlineStr">
-        <is>
-          <t>GL - CBu-Swa-SGa
-4º e 5º tempos</t>
-        </is>
-      </c>
+      <c r="G27" s="283" t="n"/>
       <c r="H27" s="283" t="n"/>
-      <c r="I27" s="283" t="n"/>
+      <c r="I27" s="283" t="inlineStr">
+        <is>
+          <t>Soc - Kle
+4º tempo</t>
+        </is>
+      </c>
       <c r="J27" s="265" t="n"/>
       <c r="L27" s="45" t="n"/>
       <c r="M27" s="323" t="inlineStr">
@@ -17570,12 +17570,7 @@
         </is>
       </c>
       <c r="F30" s="283" t="n"/>
-      <c r="G30" s="283" t="inlineStr">
-        <is>
-          <t>Hist - Ver
-1º e 2º tempos</t>
-        </is>
-      </c>
+      <c r="G30" s="283" t="n"/>
       <c r="H30" s="283" t="n"/>
       <c r="I30" s="283" t="n"/>
       <c r="J30" s="183" t="inlineStr">
@@ -17743,12 +17738,7 @@
         <f>B36+4</f>
         <v/>
       </c>
-      <c r="E36" s="283" t="inlineStr">
-        <is>
-          <t>Mat - ClaMe/JJ
-2º e 3º tempos</t>
-        </is>
-      </c>
+      <c r="E36" s="283" t="n"/>
       <c r="F36" s="283" t="inlineStr">
         <is>
           <t>Qui - CAl
@@ -17756,7 +17746,12 @@
         </is>
       </c>
       <c r="G36" s="283" t="n"/>
-      <c r="H36" s="283" t="n"/>
+      <c r="H36" s="283" t="inlineStr">
+        <is>
+          <t>Fis - Cadu
+1º e 2º tempos</t>
+        </is>
+      </c>
       <c r="I36" s="283" t="n"/>
       <c r="J36" s="265" t="n"/>
       <c r="L36" s="81" t="inlineStr">
@@ -17882,13 +17877,13 @@
         <v/>
       </c>
       <c r="E42" s="283" t="n"/>
-      <c r="F42" s="283" t="n"/>
-      <c r="G42" s="283" t="inlineStr">
-        <is>
-          <t>Fil - LAn
-11º tempo</t>
-        </is>
-      </c>
+      <c r="F42" s="283" t="inlineStr">
+        <is>
+          <t>Hist - Ver
+2º e 3º tempos</t>
+        </is>
+      </c>
+      <c r="G42" s="283" t="n"/>
       <c r="H42" s="283" t="n"/>
       <c r="I42" s="283" t="n"/>
       <c r="J42" s="265" t="n"/>
@@ -17943,7 +17938,12 @@
         <f>B45+4</f>
         <v/>
       </c>
-      <c r="E45" s="283" t="n"/>
+      <c r="E45" s="283" t="inlineStr">
+        <is>
+          <t>Ing - PaH
+4º e 5º tempos</t>
+        </is>
+      </c>
       <c r="F45" s="283" t="n"/>
       <c r="G45" s="283" t="inlineStr">
         <is>
@@ -18002,13 +18002,13 @@
       </c>
       <c r="E48" s="283" t="n"/>
       <c r="F48" s="361" t="n"/>
-      <c r="G48" s="283" t="n"/>
-      <c r="H48" s="283" t="inlineStr">
-        <is>
-          <t>Bio - Ale
-2º e 3º tempos</t>
-        </is>
-      </c>
+      <c r="G48" s="283" t="inlineStr">
+        <is>
+          <t>Fil - LAn
+9º tempo</t>
+        </is>
+      </c>
+      <c r="H48" s="283" t="n"/>
       <c r="I48" s="183" t="inlineStr">
         <is>
           <t>unterrichtsfrei sem aula</t>
@@ -18691,24 +18691,19 @@
         <f>B9+4</f>
         <v/>
       </c>
-      <c r="E9" s="183" t="n"/>
-      <c r="F9" s="183" t="inlineStr">
-        <is>
-          <t>Fis - Cadu
+      <c r="E9" s="183" t="inlineStr">
+        <is>
+          <t>Ing - PaH
 1º e 2º tempos</t>
         </is>
       </c>
+      <c r="F9" s="183" t="n"/>
       <c r="G9" s="183" t="n"/>
-      <c r="H9" s="183" t="inlineStr">
-        <is>
-          <t>Mat - Bre/JJ
-4º e 5º tempos</t>
-        </is>
-      </c>
+      <c r="H9" s="183" t="n"/>
       <c r="I9" s="183" t="inlineStr">
         <is>
-          <t>Geo - Mar
-2º e 3º tempos</t>
+          <t>LP/LIT/RED - AMu/Deb
+1º ao 3º tempos</t>
         </is>
       </c>
       <c r="J9" s="183" t="n"/>
@@ -18794,13 +18789,18 @@
 4º e 5º tempos</t>
         </is>
       </c>
-      <c r="F12" s="11" t="n"/>
+      <c r="F12" s="11" t="inlineStr">
+        <is>
+          <t>Fis - Cadu
+2º e 3º tempos</t>
+        </is>
+      </c>
       <c r="G12" s="11" t="n"/>
       <c r="H12" s="11" t="n"/>
       <c r="I12" s="11" t="inlineStr">
         <is>
-          <t>Hist - Wag
-1º e 2º tempos</t>
+          <t>Qui - CAl/Fab
+4º e 5º tempos</t>
         </is>
       </c>
       <c r="J12" s="183" t="n"/>
@@ -18859,24 +18859,19 @@
         <f>B15+4</f>
         <v/>
       </c>
-      <c r="E15" s="11" t="inlineStr">
-        <is>
-          <t>Ing - PaH
+      <c r="E15" s="11" t="n"/>
+      <c r="F15" s="11" t="inlineStr">
+        <is>
+          <t>Mat - Bre/JJ
 1º e 2º tempos</t>
-        </is>
-      </c>
-      <c r="F15" s="11" t="inlineStr">
-        <is>
-          <t>Bio - Ale
-2º e 3º tempos</t>
         </is>
       </c>
       <c r="G15" s="11" t="n"/>
       <c r="H15" s="11" t="n"/>
       <c r="I15" s="11" t="inlineStr">
         <is>
-          <t>LP/LIT/RED - AMu/Deb
-1º ao 3º tempos</t>
+          <t>Hist - Wag
+1º e 2º tempos</t>
         </is>
       </c>
       <c r="J15" s="183" t="n"/>
@@ -18938,7 +18933,12 @@
           <t>unterrichtsfrei sem aula</t>
         </is>
       </c>
-      <c r="F18" s="11" t="n"/>
+      <c r="F18" s="11" t="inlineStr">
+        <is>
+          <t>Bio - Ale
+2º e 3º tempos</t>
+        </is>
+      </c>
       <c r="G18" s="11" t="n"/>
       <c r="H18" s="11" t="inlineStr">
         <is>
@@ -18948,8 +18948,8 @@
       </c>
       <c r="I18" s="350" t="inlineStr">
         <is>
-          <t>Qui - CAl/Fab
-4º e 5º tempos</t>
+          <t>Geo - Mar
+2º e 3º tempos</t>
         </is>
       </c>
       <c r="J18" s="262" t="inlineStr">
@@ -19018,7 +19018,12 @@
         <v/>
       </c>
       <c r="E21" s="11" t="n"/>
-      <c r="F21" s="62" t="n"/>
+      <c r="F21" s="62" t="inlineStr">
+        <is>
+          <t>Fis - Cadu
+1º e 2º tempos</t>
+        </is>
+      </c>
       <c r="G21" s="11" t="inlineStr">
         <is>
           <t>S4-12
@@ -19095,20 +19100,20 @@
         <v/>
       </c>
       <c r="E24" s="283" t="n"/>
-      <c r="F24" s="283" t="n"/>
-      <c r="G24" s="79" t="n"/>
-      <c r="H24" s="283" t="inlineStr">
-        <is>
-          <t>Mat - Bre/JJ
-4º e 5º tempos</t>
-        </is>
-      </c>
-      <c r="I24" s="78" t="inlineStr">
-        <is>
-          <t>Geo - Mar
+      <c r="F24" s="283" t="inlineStr">
+        <is>
+          <t>Bio - Ale
 2º e 3º tempos</t>
         </is>
       </c>
+      <c r="G24" s="353" t="inlineStr">
+        <is>
+          <t>Soc - Kle
+6º tempo</t>
+        </is>
+      </c>
+      <c r="H24" s="283" t="n"/>
+      <c r="I24" s="78" t="n"/>
       <c r="J24" s="265" t="n"/>
       <c r="L24" s="318" t="inlineStr">
         <is>
@@ -19174,12 +19179,7 @@
         <f>B27+4</f>
         <v/>
       </c>
-      <c r="E27" s="78" t="inlineStr">
-        <is>
-          <t>Ing - PaH
-1º e 2º tempos</t>
-        </is>
-      </c>
+      <c r="E27" s="78" t="n"/>
       <c r="F27" s="283" t="n"/>
       <c r="G27" s="283" t="n"/>
       <c r="H27" s="283" t="inlineStr">
@@ -19254,7 +19254,12 @@
         <f>B30+4</f>
         <v/>
       </c>
-      <c r="E30" s="283" t="n"/>
+      <c r="E30" s="283" t="inlineStr">
+        <is>
+          <t>Ing - PaH
+1º e 2º tempos</t>
+        </is>
+      </c>
       <c r="F30" s="283" t="n"/>
       <c r="G30" s="283" t="n"/>
       <c r="H30" s="283" t="n"/>
@@ -19430,18 +19435,13 @@
         <v/>
       </c>
       <c r="E36" s="283" t="n"/>
-      <c r="F36" s="283" t="inlineStr">
-        <is>
-          <t>Fis - Cadu
-1º e 2º tempos</t>
-        </is>
-      </c>
+      <c r="F36" s="283" t="n"/>
       <c r="G36" s="283" t="n"/>
       <c r="H36" s="283" t="n"/>
       <c r="I36" s="283" t="inlineStr">
         <is>
           <t>Hist - Wag
-1º e 2º tempos</t>
+4º e 5º tempos</t>
         </is>
       </c>
       <c r="J36" s="265" t="n"/>
@@ -19514,15 +19514,15 @@
 4º e 5º tempos</t>
         </is>
       </c>
-      <c r="F39" s="283" t="inlineStr">
-        <is>
-          <t>Bio - Ale
-2º e 3º tempos</t>
-        </is>
-      </c>
+      <c r="F39" s="283" t="n"/>
       <c r="G39" s="283" t="n"/>
       <c r="H39" s="283" t="n"/>
-      <c r="I39" s="283" t="n"/>
+      <c r="I39" s="283" t="inlineStr">
+        <is>
+          <t>Qui - CAl/Fab
+2º e 3º tempos</t>
+        </is>
+      </c>
       <c r="J39" s="265" t="n"/>
     </row>
     <row r="40" ht="18" customFormat="1" customHeight="1" s="4">
@@ -19576,7 +19576,12 @@
         </is>
       </c>
       <c r="H42" s="283" t="n"/>
-      <c r="I42" s="283" t="n"/>
+      <c r="I42" s="283" t="inlineStr">
+        <is>
+          <t>Geo - Mar
+2º e 3º tempos</t>
+        </is>
+      </c>
       <c r="J42" s="265" t="n"/>
       <c r="L42" s="259" t="inlineStr">
         <is>
@@ -19629,19 +19634,14 @@
         <f>B45+4</f>
         <v/>
       </c>
-      <c r="E45" s="283" t="inlineStr">
-        <is>
-          <t>Qui - CAl/Fab
+      <c r="E45" s="283" t="n"/>
+      <c r="F45" s="283" t="inlineStr">
+        <is>
+          <t>Mat - Bre/JJ
 1º e 2º tempos</t>
         </is>
       </c>
-      <c r="F45" s="283" t="n"/>
-      <c r="G45" s="283" t="inlineStr">
-        <is>
-          <t>Soc - Kle
-2º tempo</t>
-        </is>
-      </c>
+      <c r="G45" s="283" t="n"/>
       <c r="H45" s="283" t="n"/>
       <c r="I45" s="358" t="inlineStr">
         <is>

--- a/Horario desenvolvido/Proposta_2_Calendario_Provas_2026_2SEM.xlsx
+++ b/Horario desenvolvido/Proposta_2_Calendario_Provas_2026_2SEM.xlsx
@@ -5367,21 +5367,11 @@
         <f>B9+4</f>
         <v/>
       </c>
-      <c r="E9" s="183" t="inlineStr">
-        <is>
-          <t>Ing - Isb
-4º e 5º tempos</t>
-        </is>
-      </c>
+      <c r="E9" s="183" t="n"/>
       <c r="F9" s="183" t="n"/>
       <c r="G9" s="183" t="n"/>
       <c r="H9" s="183" t="n"/>
-      <c r="I9" s="183" t="inlineStr">
-        <is>
-          <t>LP/LIT/RED - AMu/Deb
-1º ao 3º tempos</t>
-        </is>
-      </c>
+      <c r="I9" s="183" t="n"/>
       <c r="J9" s="183" t="n"/>
       <c r="L9" s="16" t="inlineStr">
         <is>
@@ -5461,21 +5451,21 @@
       </c>
       <c r="E12" s="11" t="inlineStr">
         <is>
-          <t>DaF - CBu-EFr-Eth
+          <t>Ing - Isb
 4º e 5º tempos</t>
         </is>
       </c>
       <c r="F12" s="11" t="inlineStr">
         <is>
-          <t>Fis - Cadu
-2º e 3º tempos</t>
+          <t>Mat - Bre/JJ
+1º e 2º tempos</t>
         </is>
       </c>
       <c r="G12" s="11" t="n"/>
       <c r="H12" s="11" t="n"/>
       <c r="I12" s="11" t="inlineStr">
         <is>
-          <t>Qui - CAl/Fab
+          <t>Hist - Wag
 4º e 5º tempos</t>
         </is>
       </c>
@@ -5535,10 +5525,15 @@
         <f>B15+4</f>
         <v/>
       </c>
-      <c r="E15" s="11" t="n"/>
+      <c r="E15" s="11" t="inlineStr">
+        <is>
+          <t>DaF - CBu-EFr-Eth
+4º e 5º tempos</t>
+        </is>
+      </c>
       <c r="F15" s="11" t="inlineStr">
         <is>
-          <t>Mat - Bre/JJ
+          <t>Fis - Cadu
 1º e 2º tempos</t>
         </is>
       </c>
@@ -5546,8 +5541,8 @@
       <c r="H15" s="11" t="n"/>
       <c r="I15" s="11" t="inlineStr">
         <is>
-          <t>Hist - Wag
-1º e 2º tempos</t>
+          <t>Geo - Mar
+2º e 3º tempos</t>
         </is>
       </c>
       <c r="J15" s="183" t="n"/>
@@ -5609,12 +5604,7 @@
           <t>unterrichtsfrei sem aula</t>
         </is>
       </c>
-      <c r="F18" s="11" t="inlineStr">
-        <is>
-          <t>Bio - Ale
-2º e 3º tempos</t>
-        </is>
-      </c>
+      <c r="F18" s="11" t="n"/>
       <c r="G18" s="11" t="n"/>
       <c r="H18" s="11" t="inlineStr">
         <is>
@@ -5624,8 +5614,8 @@
       </c>
       <c r="I18" s="350" t="inlineStr">
         <is>
-          <t>Geo - Mar
-2º e 3º tempos</t>
+          <t>LP/LIT/RED - AMu/Deb
+1º ao 3º tempos</t>
         </is>
       </c>
       <c r="J18" s="262" t="inlineStr">
@@ -5696,8 +5686,8 @@
       <c r="E21" s="11" t="n"/>
       <c r="F21" s="62" t="inlineStr">
         <is>
-          <t>Fis - Cadu
-1º e 2º tempos</t>
+          <t>Bio - Ale
+2º e 3º tempos</t>
         </is>
       </c>
       <c r="G21" s="11" t="inlineStr">
@@ -5712,7 +5702,12 @@
 2º ao 7º tempos</t>
         </is>
       </c>
-      <c r="I21" s="11" t="n"/>
+      <c r="I21" s="11" t="inlineStr">
+        <is>
+          <t>Qui - CAl/Fab
+4º e 5º tempos</t>
+        </is>
+      </c>
       <c r="J21" s="183" t="n"/>
       <c r="L21" s="80" t="inlineStr">
         <is>
@@ -5778,14 +5773,14 @@
       <c r="E24" s="283" t="n"/>
       <c r="F24" s="283" t="inlineStr">
         <is>
-          <t>Bio - Ale
-2º e 3º tempos</t>
+          <t>Fis - Cadu
+1º e 2º tempos</t>
         </is>
       </c>
       <c r="G24" s="353" t="inlineStr">
         <is>
-          <t>Soc - Kle
-6º tempo</t>
+          <t>Fil - LAn
+4º tempo</t>
         </is>
       </c>
       <c r="H24" s="283" t="n"/>
@@ -5864,7 +5859,12 @@
 9º e 10º tempos</t>
         </is>
       </c>
-      <c r="I27" s="283" t="n"/>
+      <c r="I27" s="283" t="inlineStr">
+        <is>
+          <t>Qui - CAl/Fab
+2º e 3º tempos</t>
+        </is>
+      </c>
       <c r="J27" s="265" t="n"/>
       <c r="L27" s="45" t="n"/>
       <c r="M27" s="323" t="inlineStr">
@@ -5930,19 +5930,19 @@
         <f>B30+4</f>
         <v/>
       </c>
-      <c r="E30" s="283" t="inlineStr">
-        <is>
-          <t>Ing - Isb
-4º e 5º tempos</t>
-        </is>
-      </c>
-      <c r="F30" s="283" t="n"/>
+      <c r="E30" s="283" t="n"/>
+      <c r="F30" s="283" t="inlineStr">
+        <is>
+          <t>Mat - Bre/JJ
+1º e 2º tempos</t>
+        </is>
+      </c>
       <c r="G30" s="283" t="n"/>
       <c r="H30" s="283" t="n"/>
       <c r="I30" s="283" t="inlineStr">
         <is>
-          <t>LP/LIT/RED - AMu/Deb
-1º ao 3º tempos</t>
+          <t>Geo - Mar
+2º e 3º tempos</t>
         </is>
       </c>
       <c r="J30" s="183" t="inlineStr">
@@ -6116,8 +6116,8 @@
       <c r="H36" s="283" t="n"/>
       <c r="I36" s="283" t="inlineStr">
         <is>
-          <t>Hist - Wag
-4º e 5º tempos</t>
+          <t>LP/LIT/RED - AMu/Deb
+1º ao 3º tempos</t>
         </is>
       </c>
       <c r="J36" s="265" t="n"/>
@@ -6193,12 +6193,7 @@
       <c r="F39" s="283" t="n"/>
       <c r="G39" s="283" t="n"/>
       <c r="H39" s="283" t="n"/>
-      <c r="I39" s="283" t="inlineStr">
-        <is>
-          <t>Qui - CAl/Fab
-2º e 3º tempos</t>
-        </is>
-      </c>
+      <c r="I39" s="283" t="n"/>
       <c r="J39" s="265" t="n"/>
     </row>
     <row r="40" ht="18" customFormat="1" customHeight="1" s="4">
@@ -6244,18 +6239,18 @@
         <v/>
       </c>
       <c r="E42" s="283" t="n"/>
-      <c r="F42" s="283" t="n"/>
-      <c r="G42" s="283" t="inlineStr">
-        <is>
-          <t>Fil - LAn
-4º tempo</t>
-        </is>
-      </c>
+      <c r="F42" s="283" t="inlineStr">
+        <is>
+          <t>Bio - Ale
+2º e 3º tempos</t>
+        </is>
+      </c>
+      <c r="G42" s="283" t="n"/>
       <c r="H42" s="283" t="n"/>
       <c r="I42" s="283" t="inlineStr">
         <is>
-          <t>Geo - Mar
-2º e 3º tempos</t>
+          <t>Hist - Wag
+1º e 2º tempos</t>
         </is>
       </c>
       <c r="J42" s="265" t="n"/>
@@ -6310,14 +6305,19 @@
         <f>B45+4</f>
         <v/>
       </c>
-      <c r="E45" s="283" t="n"/>
-      <c r="F45" s="283" t="inlineStr">
-        <is>
-          <t>Mat - Bre/JJ
-1º e 2º tempos</t>
-        </is>
-      </c>
-      <c r="G45" s="283" t="n"/>
+      <c r="E45" s="283" t="inlineStr">
+        <is>
+          <t>Ing - Isb
+4º e 5º tempos</t>
+        </is>
+      </c>
+      <c r="F45" s="283" t="n"/>
+      <c r="G45" s="283" t="inlineStr">
+        <is>
+          <t>Soc - Kle
+6º tempo</t>
+        </is>
+      </c>
       <c r="H45" s="283" t="n"/>
       <c r="I45" s="358" t="inlineStr">
         <is>
@@ -8589,18 +8589,8 @@
       </c>
       <c r="E9" s="183" t="n"/>
       <c r="F9" s="183" t="n"/>
-      <c r="G9" s="183" t="inlineStr">
-        <is>
-          <t>Geo - Mar
-6º e 7º tempos</t>
-        </is>
-      </c>
-      <c r="H9" s="183" t="inlineStr">
-        <is>
-          <t>DaF - Caro-SGa-EFr
-1º e 2º tempos</t>
-        </is>
-      </c>
+      <c r="G9" s="183" t="n"/>
+      <c r="H9" s="183" t="n"/>
       <c r="I9" s="183" t="n"/>
       <c r="J9" s="183" t="n"/>
       <c r="L9" s="16" t="inlineStr">
@@ -8683,17 +8673,17 @@
       <c r="F12" s="11" t="n"/>
       <c r="G12" s="11" t="inlineStr">
         <is>
-          <t>Port - Jana
-4º e 5º tempos</t>
-        </is>
-      </c>
-      <c r="H12" s="11" t="n"/>
-      <c r="I12" s="11" t="inlineStr">
-        <is>
-          <t>GL - Caro-EFr-Eth
-4º e 5º tempos</t>
-        </is>
-      </c>
+          <t>Geo - Mar
+6º e 7º tempos</t>
+        </is>
+      </c>
+      <c r="H12" s="11" t="inlineStr">
+        <is>
+          <t>DaF - Caro-SGa-EFr
+1º e 2º tempos</t>
+        </is>
+      </c>
+      <c r="I12" s="11" t="n"/>
       <c r="J12" s="183" t="n"/>
       <c r="L12" s="15" t="n"/>
       <c r="M12" s="15" t="n"/>
@@ -8751,18 +8741,18 @@
         <v/>
       </c>
       <c r="E15" s="11" t="n"/>
-      <c r="F15" s="11" t="inlineStr">
-        <is>
-          <t>Hist - JuLa
+      <c r="F15" s="11" t="n"/>
+      <c r="G15" s="11" t="inlineStr">
+        <is>
+          <t>Port - Jana
 4º e 5º tempos</t>
         </is>
       </c>
-      <c r="G15" s="11" t="n"/>
       <c r="H15" s="11" t="n"/>
       <c r="I15" s="11" t="inlineStr">
         <is>
-          <t>Ing - APa-PaH-Velo
-2º e 3º tempos</t>
+          <t>GL - Caro-EFr-Eth
+4º e 5º tempos</t>
         </is>
       </c>
       <c r="J15" s="183" t="n"/>
@@ -8825,19 +8815,19 @@
         </is>
       </c>
       <c r="F18" s="11" t="n"/>
-      <c r="G18" s="11" t="inlineStr">
-        <is>
-          <t>Mat - BrSa
-4º e 5º tempos</t>
-        </is>
-      </c>
+      <c r="G18" s="11" t="n"/>
       <c r="H18" s="11" t="inlineStr">
         <is>
           <t>Redação - Raf
 4º e 5º tempos</t>
         </is>
       </c>
-      <c r="I18" s="350" t="n"/>
+      <c r="I18" s="350" t="inlineStr">
+        <is>
+          <t>Ing - APa-PaH-Velo
+2º e 3º tempos</t>
+        </is>
+      </c>
       <c r="J18" s="262" t="inlineStr">
         <is>
           <t>2CH 9,10,11,12</t>
@@ -8904,11 +8894,16 @@
         <v/>
       </c>
       <c r="E21" s="11" t="n"/>
-      <c r="F21" s="62" t="n"/>
+      <c r="F21" s="62" t="inlineStr">
+        <is>
+          <t>Hist - JuLa
+4º e 5º tempos</t>
+        </is>
+      </c>
       <c r="G21" s="11" t="inlineStr">
         <is>
-          <t>Geo - Mar
-6º e 7º tempos</t>
+          <t>Mat - BrSa
+4º e 5º tempos</t>
         </is>
       </c>
       <c r="H21" s="11" t="n"/>
@@ -8979,11 +8974,16 @@
       <c r="F24" s="283" t="n"/>
       <c r="G24" s="353" t="inlineStr">
         <is>
-          <t>Port - Jana
-4º e 5º tempos</t>
-        </is>
-      </c>
-      <c r="H24" s="283" t="n"/>
+          <t>Geo - Mar
+6º e 7º tempos</t>
+        </is>
+      </c>
+      <c r="H24" s="283" t="inlineStr">
+        <is>
+          <t>DaF - Caro-SGa-EFr
+1º e 2º tempos</t>
+        </is>
+      </c>
       <c r="I24" s="78" t="n"/>
       <c r="J24" s="265" t="n"/>
       <c r="L24" s="318" t="inlineStr">
@@ -9053,12 +9053,7 @@
       <c r="E27" s="78" t="n"/>
       <c r="F27" s="283" t="n"/>
       <c r="G27" s="283" t="n"/>
-      <c r="H27" s="283" t="inlineStr">
-        <is>
-          <t>DaF - Caro-SGa-EFr
-1º e 2º tempos</t>
-        </is>
-      </c>
+      <c r="H27" s="283" t="n"/>
       <c r="I27" s="283" t="inlineStr">
         <is>
           <t>AG9
@@ -9130,15 +9125,20 @@
         <f>B30+4</f>
         <v/>
       </c>
-      <c r="E30" s="283" t="inlineStr">
-        <is>
-          <t>Fis - VSi
-2º tempo</t>
-        </is>
-      </c>
+      <c r="E30" s="283" t="n"/>
       <c r="F30" s="283" t="n"/>
-      <c r="G30" s="283" t="n"/>
-      <c r="H30" s="283" t="n"/>
+      <c r="G30" s="283" t="inlineStr">
+        <is>
+          <t>Port - Jana
+4º e 5º tempos</t>
+        </is>
+      </c>
+      <c r="H30" s="283" t="inlineStr">
+        <is>
+          <t>Redação - Raf
+4º e 5º tempos</t>
+        </is>
+      </c>
       <c r="I30" s="283" t="n"/>
       <c r="J30" s="183" t="inlineStr">
         <is>
@@ -9305,21 +9305,21 @@
         <f>B36+4</f>
         <v/>
       </c>
-      <c r="E36" s="283" t="n"/>
-      <c r="F36" s="283" t="n"/>
-      <c r="G36" s="283" t="inlineStr">
-        <is>
-          <t>Mat - BrSa
-4º e 5º tempos</t>
-        </is>
-      </c>
+      <c r="E36" s="283" t="inlineStr">
+        <is>
+          <t>Fis - VSi
+2º tempo</t>
+        </is>
+      </c>
+      <c r="F36" s="283" t="inlineStr">
+        <is>
+          <t>Bio - Ale
+1º tempo</t>
+        </is>
+      </c>
+      <c r="G36" s="283" t="n"/>
       <c r="H36" s="283" t="n"/>
-      <c r="I36" s="283" t="inlineStr">
-        <is>
-          <t>GL - Caro-EFr-Eth
-4º e 5º tempos</t>
-        </is>
-      </c>
+      <c r="I36" s="283" t="n"/>
       <c r="J36" s="265" t="n"/>
       <c r="L36" s="81" t="inlineStr">
         <is>
@@ -9391,7 +9391,12 @@
 4º e 5º tempos</t>
         </is>
       </c>
-      <c r="G39" s="283" t="n"/>
+      <c r="G39" s="283" t="inlineStr">
+        <is>
+          <t>Mat - BrSa
+4º e 5º tempos</t>
+        </is>
+      </c>
       <c r="H39" s="283" t="n"/>
       <c r="I39" s="283" t="n"/>
       <c r="J39" s="265" t="n"/>
@@ -9500,21 +9505,16 @@
         <f>B45+4</f>
         <v/>
       </c>
-      <c r="E45" s="283" t="inlineStr">
-        <is>
-          <t>Bio - Ale
-1º tempo</t>
-        </is>
-      </c>
+      <c r="E45" s="283" t="n"/>
       <c r="F45" s="283" t="n"/>
       <c r="G45" s="283" t="n"/>
-      <c r="H45" s="283" t="inlineStr">
-        <is>
-          <t>Redação - Raf
+      <c r="H45" s="283" t="n"/>
+      <c r="I45" s="358" t="inlineStr">
+        <is>
+          <t>GL - Caro-EFr-Eth
 4º e 5º tempos</t>
         </is>
       </c>
-      <c r="I45" s="358" t="n"/>
       <c r="J45" s="269" t="n"/>
       <c r="L45" s="331" t="n"/>
     </row>
@@ -10255,18 +10255,8 @@
       </c>
       <c r="E9" s="183" t="n"/>
       <c r="F9" s="183" t="n"/>
-      <c r="G9" s="183" t="inlineStr">
-        <is>
-          <t>Geo - Mar
-6º e 7º tempos</t>
-        </is>
-      </c>
-      <c r="H9" s="183" t="inlineStr">
-        <is>
-          <t>DaF - Caro-SGa-EFr
-1º e 2º tempos</t>
-        </is>
-      </c>
+      <c r="G9" s="183" t="n"/>
+      <c r="H9" s="183" t="n"/>
       <c r="I9" s="183" t="n"/>
       <c r="J9" s="183" t="n"/>
       <c r="L9" s="16" t="inlineStr">
@@ -10349,17 +10339,17 @@
       <c r="F12" s="11" t="n"/>
       <c r="G12" s="11" t="inlineStr">
         <is>
-          <t>Port - Jana
-4º e 5º tempos</t>
-        </is>
-      </c>
-      <c r="H12" s="11" t="n"/>
-      <c r="I12" s="11" t="inlineStr">
-        <is>
-          <t>GL - Caro-EFr-Eth
-4º e 5º tempos</t>
-        </is>
-      </c>
+          <t>Geo - Mar
+6º e 7º tempos</t>
+        </is>
+      </c>
+      <c r="H12" s="11" t="inlineStr">
+        <is>
+          <t>DaF - Caro-SGa-EFr
+1º e 2º tempos</t>
+        </is>
+      </c>
+      <c r="I12" s="11" t="n"/>
       <c r="J12" s="183" t="n"/>
       <c r="L12" s="15" t="n"/>
       <c r="M12" s="15" t="n"/>
@@ -10417,18 +10407,18 @@
         <v/>
       </c>
       <c r="E15" s="11" t="n"/>
-      <c r="F15" s="11" t="inlineStr">
-        <is>
-          <t>Hist - JuLa
+      <c r="F15" s="11" t="n"/>
+      <c r="G15" s="11" t="inlineStr">
+        <is>
+          <t>Port - Jana
 4º e 5º tempos</t>
         </is>
       </c>
-      <c r="G15" s="11" t="n"/>
       <c r="H15" s="11" t="n"/>
       <c r="I15" s="11" t="inlineStr">
         <is>
-          <t>Ing - APa-PaH-Velo
-2º e 3º tempos</t>
+          <t>GL - Caro-EFr-Eth
+4º e 5º tempos</t>
         </is>
       </c>
       <c r="J15" s="183" t="n"/>
@@ -10491,19 +10481,19 @@
         </is>
       </c>
       <c r="F18" s="11" t="n"/>
-      <c r="G18" s="11" t="inlineStr">
-        <is>
-          <t>Mat - BrSa
-4º e 5º tempos</t>
-        </is>
-      </c>
+      <c r="G18" s="11" t="n"/>
       <c r="H18" s="11" t="inlineStr">
         <is>
           <t>Redação - Raf
 4º e 5º tempos</t>
         </is>
       </c>
-      <c r="I18" s="350" t="n"/>
+      <c r="I18" s="350" t="inlineStr">
+        <is>
+          <t>Ing - APa-PaH-Velo
+2º e 3º tempos</t>
+        </is>
+      </c>
       <c r="J18" s="262" t="inlineStr">
         <is>
           <t>2CH 9,10,11,12</t>
@@ -10570,11 +10560,16 @@
         <v/>
       </c>
       <c r="E21" s="11" t="n"/>
-      <c r="F21" s="62" t="n"/>
+      <c r="F21" s="62" t="inlineStr">
+        <is>
+          <t>Hist - JuLa
+4º e 5º tempos</t>
+        </is>
+      </c>
       <c r="G21" s="11" t="inlineStr">
         <is>
-          <t>Geo - Mar
-6º e 7º tempos</t>
+          <t>Mat - BrSa
+4º e 5º tempos</t>
         </is>
       </c>
       <c r="H21" s="11" t="n"/>
@@ -10645,11 +10640,16 @@
       <c r="F24" s="283" t="n"/>
       <c r="G24" s="353" t="inlineStr">
         <is>
-          <t>Port - Jana
-4º e 5º tempos</t>
-        </is>
-      </c>
-      <c r="H24" s="283" t="n"/>
+          <t>Geo - Mar
+6º e 7º tempos</t>
+        </is>
+      </c>
+      <c r="H24" s="283" t="inlineStr">
+        <is>
+          <t>DaF - Caro-SGa-EFr
+1º e 2º tempos</t>
+        </is>
+      </c>
       <c r="I24" s="78" t="n"/>
       <c r="J24" s="265" t="n"/>
       <c r="L24" s="318" t="inlineStr">
@@ -10719,12 +10719,7 @@
       <c r="E27" s="78" t="n"/>
       <c r="F27" s="283" t="n"/>
       <c r="G27" s="283" t="n"/>
-      <c r="H27" s="283" t="inlineStr">
-        <is>
-          <t>DaF - Caro-SGa-EFr
-1º e 2º tempos</t>
-        </is>
-      </c>
+      <c r="H27" s="283" t="n"/>
       <c r="I27" s="283" t="inlineStr">
         <is>
           <t>AG9
@@ -10796,15 +10791,20 @@
         <f>B30+4</f>
         <v/>
       </c>
-      <c r="E30" s="283" t="inlineStr">
-        <is>
-          <t>Fis - VSi
-2º tempo</t>
-        </is>
-      </c>
+      <c r="E30" s="283" t="n"/>
       <c r="F30" s="283" t="n"/>
-      <c r="G30" s="283" t="n"/>
-      <c r="H30" s="283" t="n"/>
+      <c r="G30" s="283" t="inlineStr">
+        <is>
+          <t>Port - Jana
+4º e 5º tempos</t>
+        </is>
+      </c>
+      <c r="H30" s="283" t="inlineStr">
+        <is>
+          <t>Redação - Raf
+4º e 5º tempos</t>
+        </is>
+      </c>
       <c r="I30" s="283" t="n"/>
       <c r="J30" s="183" t="inlineStr">
         <is>
@@ -10971,21 +10971,21 @@
         <f>B36+4</f>
         <v/>
       </c>
-      <c r="E36" s="283" t="n"/>
-      <c r="F36" s="283" t="n"/>
-      <c r="G36" s="283" t="inlineStr">
-        <is>
-          <t>Mat - BrSa
-4º e 5º tempos</t>
-        </is>
-      </c>
+      <c r="E36" s="283" t="inlineStr">
+        <is>
+          <t>Fis - VSi
+2º tempo</t>
+        </is>
+      </c>
+      <c r="F36" s="283" t="inlineStr">
+        <is>
+          <t>Bio - Ale
+1º tempo</t>
+        </is>
+      </c>
+      <c r="G36" s="283" t="n"/>
       <c r="H36" s="283" t="n"/>
-      <c r="I36" s="283" t="inlineStr">
-        <is>
-          <t>GL - Caro-EFr-Eth
-4º e 5º tempos</t>
-        </is>
-      </c>
+      <c r="I36" s="283" t="n"/>
       <c r="J36" s="265" t="n"/>
       <c r="L36" s="81" t="inlineStr">
         <is>
@@ -11057,7 +11057,12 @@
 4º e 5º tempos</t>
         </is>
       </c>
-      <c r="G39" s="283" t="n"/>
+      <c r="G39" s="283" t="inlineStr">
+        <is>
+          <t>Mat - BrSa
+4º e 5º tempos</t>
+        </is>
+      </c>
       <c r="H39" s="283" t="n"/>
       <c r="I39" s="283" t="n"/>
       <c r="J39" s="265" t="n"/>
@@ -11166,21 +11171,16 @@
         <f>B45+4</f>
         <v/>
       </c>
-      <c r="E45" s="283" t="inlineStr">
-        <is>
-          <t>Bio - Ale
-1º tempo</t>
-        </is>
-      </c>
+      <c r="E45" s="283" t="n"/>
       <c r="F45" s="283" t="n"/>
       <c r="G45" s="283" t="n"/>
-      <c r="H45" s="283" t="inlineStr">
-        <is>
-          <t>Redação - Raf
+      <c r="H45" s="283" t="n"/>
+      <c r="I45" s="358" t="inlineStr">
+        <is>
+          <t>GL - Caro-EFr-Eth
 4º e 5º tempos</t>
         </is>
       </c>
-      <c r="I45" s="358" t="n"/>
       <c r="J45" s="269" t="n"/>
       <c r="L45" s="331" t="n"/>
     </row>
@@ -11919,20 +11919,10 @@
         <f>B9+4</f>
         <v/>
       </c>
-      <c r="E9" s="183" t="inlineStr">
-        <is>
-          <t>Qui - CAl
-4º e 5º tempos</t>
-        </is>
-      </c>
+      <c r="E9" s="183" t="n"/>
       <c r="F9" s="183" t="n"/>
       <c r="G9" s="183" t="n"/>
-      <c r="H9" s="183" t="inlineStr">
-        <is>
-          <t>Mat - BrSa/FBri
-4º e 5º tempos</t>
-        </is>
-      </c>
+      <c r="H9" s="183" t="n"/>
       <c r="I9" s="183" t="n"/>
       <c r="J9" s="183" t="n"/>
       <c r="L9" s="16" t="inlineStr">
@@ -12013,21 +12003,16 @@
       </c>
       <c r="E12" s="11" t="inlineStr">
         <is>
-          <t>DaF - Eth-EFr-Swa
-1º e 2º tempos</t>
-        </is>
-      </c>
-      <c r="F12" s="11" t="inlineStr">
-        <is>
-          <t>Bio - Lza
-6º e 7º tempos</t>
-        </is>
-      </c>
+          <t>Qui - CAl
+4º e 5º tempos</t>
+        </is>
+      </c>
+      <c r="F12" s="11" t="n"/>
       <c r="G12" s="11" t="n"/>
       <c r="H12" s="11" t="inlineStr">
         <is>
-          <t>Fis - VSi
-1º e 2º tempos</t>
+          <t>Mat - BrSa/FBri
+4º e 5º tempos</t>
         </is>
       </c>
       <c r="I12" s="11" t="n"/>
@@ -12166,25 +12151,25 @@
           <t>unterrichtsfrei sem aula</t>
         </is>
       </c>
-      <c r="F18" s="11" t="n"/>
+      <c r="F18" s="11" t="inlineStr">
+        <is>
+          <t>Bio - Lza
+6º e 7º tempos</t>
+        </is>
+      </c>
       <c r="G18" s="11" t="inlineStr">
         <is>
-          <t>GL - EFr-Car-Swa
+          <t>DaF - Eth-EFr-Swa
 2º e 3º tempos</t>
         </is>
       </c>
       <c r="H18" s="11" t="inlineStr">
         <is>
-          <t>LP/LIT/RED - BPad/MFo/SMo
-1º ao 3º tempos</t>
-        </is>
-      </c>
-      <c r="I18" s="350" t="inlineStr">
-        <is>
-          <t>AG10
-2º ao 7º tempos</t>
-        </is>
-      </c>
+          <t>Fis - VSi
+1º e 2º tempos</t>
+        </is>
+      </c>
+      <c r="I18" s="350" t="n"/>
       <c r="J18" s="262" t="inlineStr">
         <is>
           <t>2CH 9,10,11,12</t>
@@ -12250,21 +12235,26 @@
         <f>B21+4</f>
         <v/>
       </c>
-      <c r="E21" s="11" t="n"/>
-      <c r="F21" s="62" t="inlineStr">
-        <is>
-          <t>Bio - Lza
-6º e 7º tempos</t>
-        </is>
-      </c>
-      <c r="G21" s="11" t="n"/>
-      <c r="H21" s="11" t="inlineStr">
-        <is>
-          <t>Ing - APa
+      <c r="E21" s="11" t="inlineStr">
+        <is>
+          <t>LP/LIT/RED - BPad/MFo/SMo
+1º ao 3º tempos</t>
+        </is>
+      </c>
+      <c r="F21" s="62" t="n"/>
+      <c r="G21" s="11" t="inlineStr">
+        <is>
+          <t>GL - EFr-Car-Swa
 2º e 3º tempos</t>
         </is>
       </c>
-      <c r="I21" s="11" t="n"/>
+      <c r="H21" s="11" t="n"/>
+      <c r="I21" s="11" t="inlineStr">
+        <is>
+          <t>AG10
+2º ao 7º tempos</t>
+        </is>
+      </c>
       <c r="J21" s="183" t="n"/>
       <c r="L21" s="80" t="inlineStr">
         <is>
@@ -12327,14 +12317,19 @@
         <f>B24+4</f>
         <v/>
       </c>
-      <c r="E24" s="283" t="n"/>
-      <c r="F24" s="283" t="n"/>
-      <c r="G24" s="353" t="inlineStr">
-        <is>
-          <t>Fil - LAn
-1º tempo</t>
-        </is>
-      </c>
+      <c r="E24" s="283" t="inlineStr">
+        <is>
+          <t>LP/LIT/RED - BPad/MFo/SMo
+1º ao 3º tempos</t>
+        </is>
+      </c>
+      <c r="F24" s="283" t="inlineStr">
+        <is>
+          <t>Bio - Lza
+6º e 7º tempos</t>
+        </is>
+      </c>
+      <c r="G24" s="79" t="n"/>
       <c r="H24" s="283" t="n"/>
       <c r="I24" s="78" t="n"/>
       <c r="J24" s="265" t="n"/>
@@ -12406,8 +12401,8 @@
       <c r="F27" s="283" t="n"/>
       <c r="G27" s="283" t="inlineStr">
         <is>
-          <t>GL - EFr-Car-Swa
-2º e 3º tempos</t>
+          <t>Fil - LAn
+1º tempo</t>
         </is>
       </c>
       <c r="H27" s="283" t="n"/>
@@ -12477,21 +12472,21 @@
         <f>B30+4</f>
         <v/>
       </c>
-      <c r="E30" s="283" t="n"/>
+      <c r="E30" s="283" t="inlineStr">
+        <is>
+          <t>Qui - CAl
+4º e 5º tempos</t>
+        </is>
+      </c>
       <c r="F30" s="283" t="n"/>
       <c r="G30" s="283" t="n"/>
       <c r="H30" s="283" t="inlineStr">
         <is>
-          <t>Mat - BrSa/FBri
-4º e 5º tempos</t>
-        </is>
-      </c>
-      <c r="I30" s="283" t="inlineStr">
-        <is>
-          <t>Soc - Kle
-5º tempo</t>
-        </is>
-      </c>
+          <t>Ing - APa
+2º e 3º tempos</t>
+        </is>
+      </c>
+      <c r="I30" s="283" t="n"/>
       <c r="J30" s="183" t="inlineStr">
         <is>
           <t>unterrichtsfrei sem aula</t>
@@ -12657,16 +12652,21 @@
         <f>B36+4</f>
         <v/>
       </c>
-      <c r="E36" s="283" t="inlineStr">
-        <is>
-          <t>Qui - CAl
-4º e 5º tempos</t>
-        </is>
-      </c>
+      <c r="E36" s="283" t="n"/>
       <c r="F36" s="283" t="n"/>
       <c r="G36" s="283" t="n"/>
-      <c r="H36" s="283" t="n"/>
-      <c r="I36" s="283" t="n"/>
+      <c r="H36" s="283" t="inlineStr">
+        <is>
+          <t>Geo - Mlo
+4º e 5º tempos</t>
+        </is>
+      </c>
+      <c r="I36" s="283" t="inlineStr">
+        <is>
+          <t>Soc - Kle
+5º tempo</t>
+        </is>
+      </c>
       <c r="J36" s="265" t="n"/>
       <c r="L36" s="81" t="inlineStr">
         <is>
@@ -12731,17 +12731,17 @@
         <f>B39+4</f>
         <v/>
       </c>
-      <c r="E39" s="283" t="inlineStr">
-        <is>
-          <t>LP/LIT/RED - BPad/MFo/SMo
-1º ao 3º tempos</t>
-        </is>
-      </c>
+      <c r="E39" s="283" t="n"/>
       <c r="F39" s="283" t="n"/>
-      <c r="G39" s="283" t="n"/>
+      <c r="G39" s="283" t="inlineStr">
+        <is>
+          <t>GL - EFr-Car-Swa
+2º e 3º tempos</t>
+        </is>
+      </c>
       <c r="H39" s="283" t="inlineStr">
         <is>
-          <t>Geo - Mlo
+          <t>Mat - BrSa/FBri
 4º e 5º tempos</t>
         </is>
       </c>
@@ -12792,16 +12792,11 @@
       </c>
       <c r="E42" s="283" t="n"/>
       <c r="F42" s="283" t="n"/>
-      <c r="G42" s="283" t="inlineStr">
-        <is>
-          <t>DaF - Eth-EFr-Swa
-2º e 3º tempos</t>
-        </is>
-      </c>
+      <c r="G42" s="283" t="n"/>
       <c r="H42" s="283" t="inlineStr">
         <is>
-          <t>Hist - ALu
-2º e 3º tempos</t>
+          <t>Fis - VSi
+1º e 2º tempos</t>
         </is>
       </c>
       <c r="I42" s="283" t="n"/>
@@ -12857,13 +12852,18 @@
         <f>B45+4</f>
         <v/>
       </c>
-      <c r="E45" s="283" t="n"/>
+      <c r="E45" s="283" t="inlineStr">
+        <is>
+          <t>DaF - Eth-EFr-Swa
+1º e 2º tempos</t>
+        </is>
+      </c>
       <c r="F45" s="283" t="n"/>
       <c r="G45" s="283" t="n"/>
       <c r="H45" s="283" t="inlineStr">
         <is>
-          <t>Fis - VSi
-1º e 2º tempos</t>
+          <t>Hist - ALu
+2º e 3º tempos</t>
         </is>
       </c>
       <c r="I45" s="358" t="inlineStr">
@@ -13600,20 +13600,10 @@
         <f>B9+4</f>
         <v/>
       </c>
-      <c r="E9" s="183" t="inlineStr">
-        <is>
-          <t>Qui - CAl
-4º e 5º tempos</t>
-        </is>
-      </c>
+      <c r="E9" s="183" t="n"/>
       <c r="F9" s="183" t="n"/>
       <c r="G9" s="183" t="n"/>
-      <c r="H9" s="183" t="inlineStr">
-        <is>
-          <t>Mat - BrSa/FBri
-4º e 5º tempos</t>
-        </is>
-      </c>
+      <c r="H9" s="183" t="n"/>
       <c r="I9" s="183" t="n"/>
       <c r="J9" s="183" t="n"/>
       <c r="L9" s="16" t="inlineStr">
@@ -13694,21 +13684,16 @@
       </c>
       <c r="E12" s="11" t="inlineStr">
         <is>
-          <t>DaF - Eth-EFr-Swa
-1º e 2º tempos</t>
-        </is>
-      </c>
-      <c r="F12" s="11" t="inlineStr">
-        <is>
-          <t>Bio - Lza
-6º e 7º tempos</t>
-        </is>
-      </c>
+          <t>Qui - CAl
+4º e 5º tempos</t>
+        </is>
+      </c>
+      <c r="F12" s="11" t="n"/>
       <c r="G12" s="11" t="n"/>
       <c r="H12" s="11" t="inlineStr">
         <is>
-          <t>Fis - VSi
-1º e 2º tempos</t>
+          <t>Mat - BrSa/FBri
+4º e 5º tempos</t>
         </is>
       </c>
       <c r="I12" s="11" t="n"/>
@@ -13847,25 +13832,25 @@
           <t>unterrichtsfrei sem aula</t>
         </is>
       </c>
-      <c r="F18" s="11" t="n"/>
+      <c r="F18" s="11" t="inlineStr">
+        <is>
+          <t>Bio - Lza
+6º e 7º tempos</t>
+        </is>
+      </c>
       <c r="G18" s="11" t="inlineStr">
         <is>
-          <t>GL - EFr-Car-Swa
+          <t>DaF - Eth-EFr-Swa
 2º e 3º tempos</t>
         </is>
       </c>
       <c r="H18" s="11" t="inlineStr">
         <is>
-          <t>LP/LIT/RED - BPad/MFo/SMo
-1º ao 3º tempos</t>
-        </is>
-      </c>
-      <c r="I18" s="350" t="inlineStr">
-        <is>
-          <t>AG10
-2º ao 7º tempos</t>
-        </is>
-      </c>
+          <t>Fis - VSi
+1º e 2º tempos</t>
+        </is>
+      </c>
+      <c r="I18" s="350" t="n"/>
       <c r="J18" s="262" t="inlineStr">
         <is>
           <t>2CH 9,10,11,12</t>
@@ -13931,16 +13916,26 @@
         <f>B21+4</f>
         <v/>
       </c>
-      <c r="E21" s="11" t="n"/>
-      <c r="F21" s="62" t="inlineStr">
-        <is>
-          <t>Bio - Lza
-6º e 7º tempos</t>
-        </is>
-      </c>
-      <c r="G21" s="11" t="n"/>
+      <c r="E21" s="11" t="inlineStr">
+        <is>
+          <t>LP/LIT/RED - BPad/MFo/SMo
+1º ao 3º tempos</t>
+        </is>
+      </c>
+      <c r="F21" s="62" t="n"/>
+      <c r="G21" s="11" t="inlineStr">
+        <is>
+          <t>GL - EFr-Car-Swa
+2º e 3º tempos</t>
+        </is>
+      </c>
       <c r="H21" s="11" t="n"/>
-      <c r="I21" s="11" t="n"/>
+      <c r="I21" s="11" t="inlineStr">
+        <is>
+          <t>AG10
+2º ao 7º tempos</t>
+        </is>
+      </c>
       <c r="J21" s="183" t="n"/>
       <c r="L21" s="80" t="inlineStr">
         <is>
@@ -14003,14 +13998,19 @@
         <f>B24+4</f>
         <v/>
       </c>
-      <c r="E24" s="283" t="n"/>
-      <c r="F24" s="283" t="n"/>
-      <c r="G24" s="353" t="inlineStr">
-        <is>
-          <t>Fil - LAn
-1º tempo</t>
-        </is>
-      </c>
+      <c r="E24" s="283" t="inlineStr">
+        <is>
+          <t>LP/LIT/RED - BPad/MFo/SMo
+1º ao 3º tempos</t>
+        </is>
+      </c>
+      <c r="F24" s="283" t="inlineStr">
+        <is>
+          <t>Bio - Lza
+6º e 7º tempos</t>
+        </is>
+      </c>
+      <c r="G24" s="79" t="n"/>
       <c r="H24" s="283" t="n"/>
       <c r="I24" s="78" t="n"/>
       <c r="J24" s="265" t="n"/>
@@ -14082,8 +14082,8 @@
       <c r="F27" s="283" t="n"/>
       <c r="G27" s="283" t="inlineStr">
         <is>
-          <t>GL - EFr-Car-Swa
-2º e 3º tempos</t>
+          <t>Fil - LAn
+1º tempo</t>
         </is>
       </c>
       <c r="H27" s="283" t="n"/>
@@ -14153,21 +14153,21 @@
         <f>B30+4</f>
         <v/>
       </c>
-      <c r="E30" s="283" t="n"/>
+      <c r="E30" s="283" t="inlineStr">
+        <is>
+          <t>Qui - CAl
+4º e 5º tempos</t>
+        </is>
+      </c>
       <c r="F30" s="283" t="n"/>
-      <c r="G30" s="283" t="n"/>
-      <c r="H30" s="283" t="inlineStr">
-        <is>
-          <t>Mat - BrSa/FBri
+      <c r="G30" s="283" t="inlineStr">
+        <is>
+          <t>Ing - Vir
 4º e 5º tempos</t>
         </is>
       </c>
-      <c r="I30" s="283" t="inlineStr">
-        <is>
-          <t>Soc - Kle
-5º tempo</t>
-        </is>
-      </c>
+      <c r="H30" s="283" t="n"/>
+      <c r="I30" s="283" t="n"/>
       <c r="J30" s="183" t="inlineStr">
         <is>
           <t>unterrichtsfrei sem aula</t>
@@ -14333,16 +14333,21 @@
         <f>B36+4</f>
         <v/>
       </c>
-      <c r="E36" s="283" t="inlineStr">
-        <is>
-          <t>Qui - CAl
-4º e 5º tempos</t>
-        </is>
-      </c>
+      <c r="E36" s="283" t="n"/>
       <c r="F36" s="283" t="n"/>
       <c r="G36" s="283" t="n"/>
-      <c r="H36" s="283" t="n"/>
-      <c r="I36" s="283" t="n"/>
+      <c r="H36" s="283" t="inlineStr">
+        <is>
+          <t>Geo - Mlo
+4º e 5º tempos</t>
+        </is>
+      </c>
+      <c r="I36" s="283" t="inlineStr">
+        <is>
+          <t>Soc - Kle
+5º tempo</t>
+        </is>
+      </c>
       <c r="J36" s="265" t="n"/>
       <c r="L36" s="81" t="inlineStr">
         <is>
@@ -14407,17 +14412,17 @@
         <f>B39+4</f>
         <v/>
       </c>
-      <c r="E39" s="283" t="inlineStr">
-        <is>
-          <t>LP/LIT/RED - BPad/MFo/SMo
-1º ao 3º tempos</t>
-        </is>
-      </c>
+      <c r="E39" s="283" t="n"/>
       <c r="F39" s="283" t="n"/>
-      <c r="G39" s="283" t="n"/>
+      <c r="G39" s="283" t="inlineStr">
+        <is>
+          <t>GL - EFr-Car-Swa
+2º e 3º tempos</t>
+        </is>
+      </c>
       <c r="H39" s="283" t="inlineStr">
         <is>
-          <t>Geo - Mlo
+          <t>Mat - BrSa/FBri
 4º e 5º tempos</t>
         </is>
       </c>
@@ -14468,16 +14473,11 @@
       </c>
       <c r="E42" s="283" t="n"/>
       <c r="F42" s="283" t="n"/>
-      <c r="G42" s="283" t="inlineStr">
-        <is>
-          <t>DaF - Eth-EFr-Swa
-2º e 3º tempos</t>
-        </is>
-      </c>
+      <c r="G42" s="283" t="n"/>
       <c r="H42" s="283" t="inlineStr">
         <is>
-          <t>Hist - ALu
-2º e 3º tempos</t>
+          <t>Fis - VSi
+1º e 2º tempos</t>
         </is>
       </c>
       <c r="I42" s="283" t="n"/>
@@ -14533,18 +14533,18 @@
         <f>B45+4</f>
         <v/>
       </c>
-      <c r="E45" s="283" t="n"/>
+      <c r="E45" s="283" t="inlineStr">
+        <is>
+          <t>DaF - Eth-EFr-Swa
+1º e 2º tempos</t>
+        </is>
+      </c>
       <c r="F45" s="283" t="n"/>
-      <c r="G45" s="283" t="inlineStr">
-        <is>
-          <t>Ing - Vir
-4º e 5º tempos</t>
-        </is>
-      </c>
+      <c r="G45" s="283" t="n"/>
       <c r="H45" s="283" t="inlineStr">
         <is>
-          <t>Fis - VSi
-1º e 2º tempos</t>
+          <t>Hist - ALu
+2º e 3º tempos</t>
         </is>
       </c>
       <c r="I45" s="358" t="inlineStr">
@@ -15299,25 +15299,10 @@
         <f>B9+4</f>
         <v/>
       </c>
-      <c r="E9" s="183" t="inlineStr">
-        <is>
-          <t>Bio - Ale
-1º e 2º tempos</t>
-        </is>
-      </c>
-      <c r="F9" s="183" t="inlineStr">
-        <is>
-          <t>DaF - CBu-SGa-Swa
-4º e 5º tempos</t>
-        </is>
-      </c>
+      <c r="E9" s="183" t="n"/>
+      <c r="F9" s="183" t="n"/>
       <c r="G9" s="183" t="n"/>
-      <c r="H9" s="183" t="inlineStr">
-        <is>
-          <t>Ing - Bea
-4º e 5º tempos</t>
-        </is>
-      </c>
+      <c r="H9" s="183" t="n"/>
       <c r="I9" s="183" t="n"/>
       <c r="J9" s="183" t="n"/>
       <c r="L9" s="16" t="inlineStr">
@@ -15474,20 +15459,20 @@
       </c>
       <c r="E15" s="11" t="inlineStr">
         <is>
-          <t>Mat - ClaMe/JJ
-2º e 3º tempos</t>
+          <t>Bio - Ale
+1º e 2º tempos</t>
         </is>
       </c>
       <c r="F15" s="11" t="inlineStr">
         <is>
+          <t>DaF - CBu-SGa-Swa
+4º e 5º tempos</t>
+        </is>
+      </c>
+      <c r="G15" s="11" t="inlineStr">
+        <is>
           <t>Hist - Ver
-2º e 3º tempos</t>
-        </is>
-      </c>
-      <c r="G15" s="11" t="inlineStr">
-        <is>
-          <t>GL - CBu-Swa-SGa
-4º e 5º tempos</t>
+1º e 2º tempos</t>
         </is>
       </c>
       <c r="H15" s="11" t="n"/>
@@ -15554,19 +15539,19 @@
       <c r="F18" s="11" t="inlineStr">
         <is>
           <t>Qui - CAl
-1º e 2º tempos</t>
+2º e 3º tempos</t>
         </is>
       </c>
       <c r="G18" s="11" t="inlineStr">
         <is>
-          <t>Geo - Mar
-1º e 2º tempos</t>
+          <t>GL - CBu-Swa-SGa
+4º e 5º tempos</t>
         </is>
       </c>
       <c r="H18" s="11" t="inlineStr">
         <is>
-          <t>Fis - Cadu
-1º e 2º tempos</t>
+          <t>Ing - Bea
+4º e 5º tempos</t>
         </is>
       </c>
       <c r="I18" s="350" t="n"/>
@@ -15635,20 +15620,25 @@
         <f>B21+4</f>
         <v/>
       </c>
-      <c r="E21" s="11" t="n"/>
+      <c r="E21" s="11" t="inlineStr">
+        <is>
+          <t>Geo - Mar
+2º e 3º tempos</t>
+        </is>
+      </c>
       <c r="F21" s="62" t="inlineStr">
         <is>
           <t>Mat - ClaMe/JJ
 1º e 2º tempos</t>
         </is>
       </c>
-      <c r="G21" s="11" t="inlineStr">
-        <is>
-          <t>GL - CBu-Swa-SGa
-4º e 5º tempos</t>
-        </is>
-      </c>
-      <c r="H21" s="11" t="n"/>
+      <c r="G21" s="11" t="n"/>
+      <c r="H21" s="11" t="inlineStr">
+        <is>
+          <t>Fis - Cadu
+1º e 2º tempos</t>
+        </is>
+      </c>
       <c r="I21" s="11" t="n"/>
       <c r="J21" s="183" t="n"/>
       <c r="L21" s="80" t="inlineStr">
@@ -15712,20 +15702,15 @@
         <f>B24+4</f>
         <v/>
       </c>
-      <c r="E24" s="283" t="n"/>
-      <c r="F24" s="283" t="inlineStr">
-        <is>
-          <t>DaF - CBu-SGa-Swa
-4º e 5º tempos</t>
-        </is>
-      </c>
+      <c r="E24" s="283" t="inlineStr">
+        <is>
+          <t>LP/LIT/RED - ACo/AMu/Raf
+1º ao 3º tempos</t>
+        </is>
+      </c>
+      <c r="F24" s="283" t="n"/>
       <c r="G24" s="79" t="n"/>
-      <c r="H24" s="283" t="inlineStr">
-        <is>
-          <t>Ing - Bea
-4º e 5º tempos</t>
-        </is>
-      </c>
+      <c r="H24" s="283" t="n"/>
       <c r="I24" s="78" t="n"/>
       <c r="J24" s="265" t="n"/>
       <c r="L24" s="318" t="inlineStr">
@@ -15794,19 +15779,19 @@
       </c>
       <c r="E27" s="78" t="inlineStr">
         <is>
-          <t>Bio - Ale
+          <t>Geo - Mar
 2º e 3º tempos</t>
         </is>
       </c>
       <c r="F27" s="283" t="n"/>
-      <c r="G27" s="283" t="n"/>
+      <c r="G27" s="283" t="inlineStr">
+        <is>
+          <t>Hist - Ver
+1º e 2º tempos</t>
+        </is>
+      </c>
       <c r="H27" s="283" t="n"/>
-      <c r="I27" s="283" t="inlineStr">
-        <is>
-          <t>Soc - Kle
-4º tempo</t>
-        </is>
-      </c>
+      <c r="I27" s="283" t="n"/>
       <c r="J27" s="265" t="n"/>
       <c r="L27" s="45" t="n"/>
       <c r="M27" s="323" t="inlineStr">
@@ -15874,11 +15859,16 @@
       </c>
       <c r="E30" s="283" t="inlineStr">
         <is>
-          <t>LP/LIT/RED - ACo/AMu/Raf
-1º ao 3º tempos</t>
-        </is>
-      </c>
-      <c r="F30" s="283" t="n"/>
+          <t>Bio - Ale
+2º e 3º tempos</t>
+        </is>
+      </c>
+      <c r="F30" s="283" t="inlineStr">
+        <is>
+          <t>Mat - ClaMe/JJ
+1º e 2º tempos</t>
+        </is>
+      </c>
       <c r="G30" s="283" t="n"/>
       <c r="H30" s="283" t="n"/>
       <c r="I30" s="283" t="n"/>
@@ -16048,17 +16038,17 @@
         <v/>
       </c>
       <c r="E36" s="283" t="n"/>
-      <c r="F36" s="283" t="inlineStr">
-        <is>
-          <t>Qui - CAl
-1º e 2º tempos</t>
-        </is>
-      </c>
-      <c r="G36" s="283" t="n"/>
+      <c r="F36" s="283" t="n"/>
+      <c r="G36" s="283" t="inlineStr">
+        <is>
+          <t>Fil - LAn
+9º tempo</t>
+        </is>
+      </c>
       <c r="H36" s="283" t="inlineStr">
         <is>
-          <t>Fis - Cadu
-1º e 2º tempos</t>
+          <t>Ing - Bea
+4º e 5º tempos</t>
         </is>
       </c>
       <c r="I36" s="283" t="n"/>
@@ -16188,8 +16178,8 @@
       <c r="E42" s="283" t="n"/>
       <c r="F42" s="283" t="inlineStr">
         <is>
-          <t>Hist - Ver
-2º e 3º tempos</t>
+          <t>DaF - CBu-SGa-Swa
+4º e 5º tempos</t>
         </is>
       </c>
       <c r="G42" s="283" t="n"/>
@@ -16248,15 +16238,20 @@
         <v/>
       </c>
       <c r="E45" s="283" t="n"/>
-      <c r="F45" s="283" t="n"/>
-      <c r="G45" s="283" t="inlineStr">
-        <is>
-          <t>Geo - Mar
+      <c r="F45" s="283" t="inlineStr">
+        <is>
+          <t>Qui - CAl
 1º e 2º tempos</t>
         </is>
       </c>
+      <c r="G45" s="283" t="n"/>
       <c r="H45" s="283" t="n"/>
-      <c r="I45" s="358" t="n"/>
+      <c r="I45" s="358" t="inlineStr">
+        <is>
+          <t>Soc - Kle
+4º tempo</t>
+        </is>
+      </c>
       <c r="J45" s="269" t="n"/>
       <c r="L45" s="331" t="n"/>
     </row>
@@ -16308,11 +16303,16 @@
       <c r="F48" s="361" t="n"/>
       <c r="G48" s="283" t="inlineStr">
         <is>
-          <t>Fil - LAn
-9º tempo</t>
-        </is>
-      </c>
-      <c r="H48" s="283" t="n"/>
+          <t>GL - CBu-Swa-SGa
+4º e 5º tempos</t>
+        </is>
+      </c>
+      <c r="H48" s="283" t="inlineStr">
+        <is>
+          <t>Fis - Cadu
+1º e 2º tempos</t>
+        </is>
+      </c>
       <c r="I48" s="183" t="inlineStr">
         <is>
           <t>unterrichtsfrei sem aula</t>
@@ -16995,18 +16995,8 @@
         <f>B9+4</f>
         <v/>
       </c>
-      <c r="E9" s="183" t="inlineStr">
-        <is>
-          <t>Bio - Ale
-1º e 2º tempos</t>
-        </is>
-      </c>
-      <c r="F9" s="183" t="inlineStr">
-        <is>
-          <t>DaF - CBu-SGa-Swa
-4º e 5º tempos</t>
-        </is>
-      </c>
+      <c r="E9" s="183" t="n"/>
+      <c r="F9" s="183" t="n"/>
       <c r="G9" s="183" t="n"/>
       <c r="H9" s="183" t="n"/>
       <c r="I9" s="183" t="n"/>
@@ -17105,12 +17095,7 @@
 2º ao 7º tempos</t>
         </is>
       </c>
-      <c r="H12" s="11" t="inlineStr">
-        <is>
-          <t>Ing - PaH
-1º e 2º tempos</t>
-        </is>
-      </c>
+      <c r="H12" s="11" t="n"/>
       <c r="I12" s="11" t="n"/>
       <c r="J12" s="183" t="n"/>
       <c r="L12" s="15" t="n"/>
@@ -17170,20 +17155,20 @@
       </c>
       <c r="E15" s="11" t="inlineStr">
         <is>
-          <t>Mat - ClaMe/JJ
-2º e 3º tempos</t>
+          <t>Bio - Ale
+1º e 2º tempos</t>
         </is>
       </c>
       <c r="F15" s="11" t="inlineStr">
         <is>
+          <t>DaF - CBu-SGa-Swa
+4º e 5º tempos</t>
+        </is>
+      </c>
+      <c r="G15" s="11" t="inlineStr">
+        <is>
           <t>Hist - Ver
-2º e 3º tempos</t>
-        </is>
-      </c>
-      <c r="G15" s="11" t="inlineStr">
-        <is>
-          <t>GL - CBu-Swa-SGa
-4º e 5º tempos</t>
+1º e 2º tempos</t>
         </is>
       </c>
       <c r="H15" s="11" t="n"/>
@@ -17250,18 +17235,18 @@
       <c r="F18" s="11" t="inlineStr">
         <is>
           <t>Qui - CAl
-1º e 2º tempos</t>
+2º e 3º tempos</t>
         </is>
       </c>
       <c r="G18" s="11" t="inlineStr">
         <is>
-          <t>Geo - Mar
-1º e 2º tempos</t>
+          <t>GL - CBu-Swa-SGa
+4º e 5º tempos</t>
         </is>
       </c>
       <c r="H18" s="11" t="inlineStr">
         <is>
-          <t>Fis - Cadu
+          <t>Ing - PaH
 1º e 2º tempos</t>
         </is>
       </c>
@@ -17331,20 +17316,25 @@
         <f>B21+4</f>
         <v/>
       </c>
-      <c r="E21" s="11" t="n"/>
+      <c r="E21" s="11" t="inlineStr">
+        <is>
+          <t>Geo - Mar
+2º e 3º tempos</t>
+        </is>
+      </c>
       <c r="F21" s="62" t="inlineStr">
         <is>
           <t>Mat - ClaMe/JJ
 1º e 2º tempos</t>
         </is>
       </c>
-      <c r="G21" s="11" t="inlineStr">
-        <is>
-          <t>GL - CBu-Swa-SGa
-4º e 5º tempos</t>
-        </is>
-      </c>
-      <c r="H21" s="11" t="n"/>
+      <c r="G21" s="11" t="n"/>
+      <c r="H21" s="11" t="inlineStr">
+        <is>
+          <t>Fis - Cadu
+1º e 2º tempos</t>
+        </is>
+      </c>
       <c r="I21" s="11" t="n"/>
       <c r="J21" s="183" t="n"/>
       <c r="L21" s="80" t="inlineStr">
@@ -17408,13 +17398,13 @@
         <f>B24+4</f>
         <v/>
       </c>
-      <c r="E24" s="283" t="n"/>
-      <c r="F24" s="283" t="inlineStr">
-        <is>
-          <t>DaF - CBu-SGa-Swa
-4º e 5º tempos</t>
-        </is>
-      </c>
+      <c r="E24" s="283" t="inlineStr">
+        <is>
+          <t>LP/LIT/RED - ACo/AMu/Raf
+1º ao 3º tempos</t>
+        </is>
+      </c>
+      <c r="F24" s="283" t="n"/>
       <c r="G24" s="79" t="n"/>
       <c r="H24" s="283" t="n"/>
       <c r="I24" s="78" t="n"/>
@@ -17485,19 +17475,19 @@
       </c>
       <c r="E27" s="78" t="inlineStr">
         <is>
-          <t>Bio - Ale
+          <t>Geo - Mar
 2º e 3º tempos</t>
         </is>
       </c>
       <c r="F27" s="283" t="n"/>
-      <c r="G27" s="283" t="n"/>
+      <c r="G27" s="283" t="inlineStr">
+        <is>
+          <t>Hist - Ver
+1º e 2º tempos</t>
+        </is>
+      </c>
       <c r="H27" s="283" t="n"/>
-      <c r="I27" s="283" t="inlineStr">
-        <is>
-          <t>Soc - Kle
-4º tempo</t>
-        </is>
-      </c>
+      <c r="I27" s="283" t="n"/>
       <c r="J27" s="265" t="n"/>
       <c r="L27" s="45" t="n"/>
       <c r="M27" s="323" t="inlineStr">
@@ -17565,11 +17555,16 @@
       </c>
       <c r="E30" s="283" t="inlineStr">
         <is>
-          <t>LP/LIT/RED - ACo/AMu/Raf
-1º ao 3º tempos</t>
-        </is>
-      </c>
-      <c r="F30" s="283" t="n"/>
+          <t>Bio - Ale
+2º e 3º tempos</t>
+        </is>
+      </c>
+      <c r="F30" s="283" t="inlineStr">
+        <is>
+          <t>Mat - ClaMe/JJ
+1º e 2º tempos</t>
+        </is>
+      </c>
       <c r="G30" s="283" t="n"/>
       <c r="H30" s="283" t="n"/>
       <c r="I30" s="283" t="n"/>
@@ -17738,20 +17733,20 @@
         <f>B36+4</f>
         <v/>
       </c>
-      <c r="E36" s="283" t="n"/>
-      <c r="F36" s="283" t="inlineStr">
-        <is>
-          <t>Qui - CAl
-1º e 2º tempos</t>
-        </is>
-      </c>
-      <c r="G36" s="283" t="n"/>
-      <c r="H36" s="283" t="inlineStr">
-        <is>
-          <t>Fis - Cadu
-1º e 2º tempos</t>
-        </is>
-      </c>
+      <c r="E36" s="283" t="inlineStr">
+        <is>
+          <t>Ing - PaH
+4º e 5º tempos</t>
+        </is>
+      </c>
+      <c r="F36" s="283" t="n"/>
+      <c r="G36" s="283" t="inlineStr">
+        <is>
+          <t>Fil - LAn
+9º tempo</t>
+        </is>
+      </c>
+      <c r="H36" s="283" t="n"/>
       <c r="I36" s="283" t="n"/>
       <c r="J36" s="265" t="n"/>
       <c r="L36" s="81" t="inlineStr">
@@ -17879,8 +17874,8 @@
       <c r="E42" s="283" t="n"/>
       <c r="F42" s="283" t="inlineStr">
         <is>
-          <t>Hist - Ver
-2º e 3º tempos</t>
+          <t>DaF - CBu-SGa-Swa
+4º e 5º tempos</t>
         </is>
       </c>
       <c r="G42" s="283" t="n"/>
@@ -17938,21 +17933,21 @@
         <f>B45+4</f>
         <v/>
       </c>
-      <c r="E45" s="283" t="inlineStr">
-        <is>
-          <t>Ing - PaH
-4º e 5º tempos</t>
-        </is>
-      </c>
-      <c r="F45" s="283" t="n"/>
-      <c r="G45" s="283" t="inlineStr">
-        <is>
-          <t>Geo - Mar
+      <c r="E45" s="283" t="n"/>
+      <c r="F45" s="283" t="inlineStr">
+        <is>
+          <t>Qui - CAl
 1º e 2º tempos</t>
         </is>
       </c>
+      <c r="G45" s="283" t="n"/>
       <c r="H45" s="283" t="n"/>
-      <c r="I45" s="358" t="n"/>
+      <c r="I45" s="358" t="inlineStr">
+        <is>
+          <t>Soc - Kle
+4º tempo</t>
+        </is>
+      </c>
       <c r="J45" s="269" t="n"/>
       <c r="L45" s="331" t="n"/>
     </row>
@@ -18004,11 +17999,16 @@
       <c r="F48" s="361" t="n"/>
       <c r="G48" s="283" t="inlineStr">
         <is>
-          <t>Fil - LAn
-9º tempo</t>
-        </is>
-      </c>
-      <c r="H48" s="283" t="n"/>
+          <t>GL - CBu-Swa-SGa
+4º e 5º tempos</t>
+        </is>
+      </c>
+      <c r="H48" s="283" t="inlineStr">
+        <is>
+          <t>Fis - Cadu
+1º e 2º tempos</t>
+        </is>
+      </c>
       <c r="I48" s="183" t="inlineStr">
         <is>
           <t>unterrichtsfrei sem aula</t>
@@ -18691,21 +18691,11 @@
         <f>B9+4</f>
         <v/>
       </c>
-      <c r="E9" s="183" t="inlineStr">
-        <is>
-          <t>Ing - PaH
-1º e 2º tempos</t>
-        </is>
-      </c>
+      <c r="E9" s="183" t="n"/>
       <c r="F9" s="183" t="n"/>
       <c r="G9" s="183" t="n"/>
       <c r="H9" s="183" t="n"/>
-      <c r="I9" s="183" t="inlineStr">
-        <is>
-          <t>LP/LIT/RED - AMu/Deb
-1º ao 3º tempos</t>
-        </is>
-      </c>
+      <c r="I9" s="183" t="n"/>
       <c r="J9" s="183" t="n"/>
       <c r="L9" s="16" t="inlineStr">
         <is>
@@ -18785,21 +18775,21 @@
       </c>
       <c r="E12" s="11" t="inlineStr">
         <is>
-          <t>DaF - CBu-EFr-Eth
-4º e 5º tempos</t>
+          <t>Ing - PaH
+1º e 2º tempos</t>
         </is>
       </c>
       <c r="F12" s="11" t="inlineStr">
         <is>
-          <t>Fis - Cadu
-2º e 3º tempos</t>
+          <t>Mat - Bre/JJ
+1º e 2º tempos</t>
         </is>
       </c>
       <c r="G12" s="11" t="n"/>
       <c r="H12" s="11" t="n"/>
       <c r="I12" s="11" t="inlineStr">
         <is>
-          <t>Qui - CAl/Fab
+          <t>Hist - Wag
 4º e 5º tempos</t>
         </is>
       </c>
@@ -18859,10 +18849,15 @@
         <f>B15+4</f>
         <v/>
       </c>
-      <c r="E15" s="11" t="n"/>
+      <c r="E15" s="11" t="inlineStr">
+        <is>
+          <t>DaF - CBu-EFr-Eth
+4º e 5º tempos</t>
+        </is>
+      </c>
       <c r="F15" s="11" t="inlineStr">
         <is>
-          <t>Mat - Bre/JJ
+          <t>Fis - Cadu
 1º e 2º tempos</t>
         </is>
       </c>
@@ -18870,8 +18865,8 @@
       <c r="H15" s="11" t="n"/>
       <c r="I15" s="11" t="inlineStr">
         <is>
-          <t>Hist - Wag
-1º e 2º tempos</t>
+          <t>Geo - Mar
+2º e 3º tempos</t>
         </is>
       </c>
       <c r="J15" s="183" t="n"/>
@@ -18933,12 +18928,7 @@
           <t>unterrichtsfrei sem aula</t>
         </is>
       </c>
-      <c r="F18" s="11" t="inlineStr">
-        <is>
-          <t>Bio - Ale
-2º e 3º tempos</t>
-        </is>
-      </c>
+      <c r="F18" s="11" t="n"/>
       <c r="G18" s="11" t="n"/>
       <c r="H18" s="11" t="inlineStr">
         <is>
@@ -18948,8 +18938,8 @@
       </c>
       <c r="I18" s="350" t="inlineStr">
         <is>
-          <t>Geo - Mar
-2º e 3º tempos</t>
+          <t>LP/LIT/RED - AMu/Deb
+1º ao 3º tempos</t>
         </is>
       </c>
       <c r="J18" s="262" t="inlineStr">
@@ -19020,8 +19010,8 @@
       <c r="E21" s="11" t="n"/>
       <c r="F21" s="62" t="inlineStr">
         <is>
-          <t>Fis - Cadu
-1º e 2º tempos</t>
+          <t>Bio - Ale
+2º e 3º tempos</t>
         </is>
       </c>
       <c r="G21" s="11" t="inlineStr">
@@ -19036,7 +19026,12 @@
 2º ao 7º tempos</t>
         </is>
       </c>
-      <c r="I21" s="11" t="n"/>
+      <c r="I21" s="11" t="inlineStr">
+        <is>
+          <t>Qui - CAl/Fab
+4º e 5º tempos</t>
+        </is>
+      </c>
       <c r="J21" s="183" t="n"/>
       <c r="L21" s="80" t="inlineStr">
         <is>
@@ -19102,14 +19097,14 @@
       <c r="E24" s="283" t="n"/>
       <c r="F24" s="283" t="inlineStr">
         <is>
-          <t>Bio - Ale
-2º e 3º tempos</t>
+          <t>Fis - Cadu
+1º e 2º tempos</t>
         </is>
       </c>
       <c r="G24" s="353" t="inlineStr">
         <is>
-          <t>Soc - Kle
-6º tempo</t>
+          <t>Fil - LAn
+4º tempo</t>
         </is>
       </c>
       <c r="H24" s="283" t="n"/>
@@ -19188,7 +19183,12 @@
 9º e 10º tempos</t>
         </is>
       </c>
-      <c r="I27" s="283" t="n"/>
+      <c r="I27" s="283" t="inlineStr">
+        <is>
+          <t>Qui - CAl/Fab
+2º e 3º tempos</t>
+        </is>
+      </c>
       <c r="J27" s="265" t="n"/>
       <c r="L27" s="45" t="n"/>
       <c r="M27" s="323" t="inlineStr">
@@ -19254,19 +19254,19 @@
         <f>B30+4</f>
         <v/>
       </c>
-      <c r="E30" s="283" t="inlineStr">
-        <is>
-          <t>Ing - PaH
+      <c r="E30" s="283" t="n"/>
+      <c r="F30" s="283" t="inlineStr">
+        <is>
+          <t>Mat - Bre/JJ
 1º e 2º tempos</t>
         </is>
       </c>
-      <c r="F30" s="283" t="n"/>
       <c r="G30" s="283" t="n"/>
       <c r="H30" s="283" t="n"/>
       <c r="I30" s="283" t="inlineStr">
         <is>
-          <t>LP/LIT/RED - AMu/Deb
-1º ao 3º tempos</t>
+          <t>Geo - Mar
+2º e 3º tempos</t>
         </is>
       </c>
       <c r="J30" s="183" t="inlineStr">
@@ -19434,14 +19434,19 @@
         <f>B36+4</f>
         <v/>
       </c>
-      <c r="E36" s="283" t="n"/>
+      <c r="E36" s="283" t="inlineStr">
+        <is>
+          <t>Ing - PaH
+1º e 2º tempos</t>
+        </is>
+      </c>
       <c r="F36" s="283" t="n"/>
       <c r="G36" s="283" t="n"/>
       <c r="H36" s="283" t="n"/>
       <c r="I36" s="283" t="inlineStr">
         <is>
-          <t>Hist - Wag
-4º e 5º tempos</t>
+          <t>LP/LIT/RED - AMu/Deb
+1º ao 3º tempos</t>
         </is>
       </c>
       <c r="J36" s="265" t="n"/>
@@ -19517,12 +19522,7 @@
       <c r="F39" s="283" t="n"/>
       <c r="G39" s="283" t="n"/>
       <c r="H39" s="283" t="n"/>
-      <c r="I39" s="283" t="inlineStr">
-        <is>
-          <t>Qui - CAl/Fab
-2º e 3º tempos</t>
-        </is>
-      </c>
+      <c r="I39" s="283" t="n"/>
       <c r="J39" s="265" t="n"/>
     </row>
     <row r="40" ht="18" customFormat="1" customHeight="1" s="4">
@@ -19568,18 +19568,18 @@
         <v/>
       </c>
       <c r="E42" s="283" t="n"/>
-      <c r="F42" s="283" t="n"/>
-      <c r="G42" s="283" t="inlineStr">
-        <is>
-          <t>Fil - LAn
-4º tempo</t>
-        </is>
-      </c>
+      <c r="F42" s="283" t="inlineStr">
+        <is>
+          <t>Bio - Ale
+2º e 3º tempos</t>
+        </is>
+      </c>
+      <c r="G42" s="283" t="n"/>
       <c r="H42" s="283" t="n"/>
       <c r="I42" s="283" t="inlineStr">
         <is>
-          <t>Geo - Mar
-2º e 3º tempos</t>
+          <t>Hist - Wag
+1º e 2º tempos</t>
         </is>
       </c>
       <c r="J42" s="265" t="n"/>
@@ -19635,13 +19635,13 @@
         <v/>
       </c>
       <c r="E45" s="283" t="n"/>
-      <c r="F45" s="283" t="inlineStr">
-        <is>
-          <t>Mat - Bre/JJ
-1º e 2º tempos</t>
-        </is>
-      </c>
-      <c r="G45" s="283" t="n"/>
+      <c r="F45" s="283" t="n"/>
+      <c r="G45" s="283" t="inlineStr">
+        <is>
+          <t>Soc - Kle
+6º tempo</t>
+        </is>
+      </c>
       <c r="H45" s="283" t="n"/>
       <c r="I45" s="358" t="inlineStr">
         <is>

--- a/Horario desenvolvido/Proposta_2_Calendario_Provas_2026_2SEM.xlsx
+++ b/Horario desenvolvido/Proposta_2_Calendario_Provas_2026_2SEM.xlsx
@@ -12003,16 +12003,16 @@
       </c>
       <c r="E12" s="11" t="inlineStr">
         <is>
-          <t>Qui - CAl
-4º e 5º tempos</t>
+          <t>Mat - BrSa/FBri
+2º e 3º tempos</t>
         </is>
       </c>
       <c r="F12" s="11" t="n"/>
       <c r="G12" s="11" t="n"/>
       <c r="H12" s="11" t="inlineStr">
         <is>
-          <t>Mat - BrSa/FBri
-4º e 5º tempos</t>
+          <t>Hist - ALu
+2º e 3º tempos</t>
         </is>
       </c>
       <c r="I12" s="11" t="n"/>
@@ -12074,24 +12074,24 @@
       </c>
       <c r="E15" s="11" t="inlineStr">
         <is>
+          <t>Fis - VSi
+4º e 5º tempos</t>
+        </is>
+      </c>
+      <c r="F15" s="11" t="n"/>
+      <c r="G15" s="11" t="inlineStr">
+        <is>
+          <t>GL - EFr-Car-Swa
+2º e 3º tempos</t>
+        </is>
+      </c>
+      <c r="H15" s="11" t="inlineStr">
+        <is>
           <t>Ing - APa
-4º e 5º tempos</t>
-        </is>
-      </c>
-      <c r="F15" s="11" t="n"/>
-      <c r="G15" s="11" t="n"/>
-      <c r="H15" s="11" t="inlineStr">
-        <is>
-          <t>Hist - ALu
-2º e 3º tempos</t>
-        </is>
-      </c>
-      <c r="I15" s="11" t="inlineStr">
-        <is>
-          <t>Geo - Mlo
-2º e 3º tempos</t>
-        </is>
-      </c>
+1º e 2º tempos</t>
+        </is>
+      </c>
+      <c r="I15" s="11" t="n"/>
       <c r="J15" s="183" t="n"/>
       <c r="L15" s="17" t="n"/>
       <c r="M15" s="15" t="n"/>
@@ -12157,19 +12157,19 @@
 6º e 7º tempos</t>
         </is>
       </c>
-      <c r="G18" s="11" t="inlineStr">
+      <c r="G18" s="11" t="n"/>
+      <c r="H18" s="11" t="inlineStr">
         <is>
           <t>DaF - Eth-EFr-Swa
-2º e 3º tempos</t>
-        </is>
-      </c>
-      <c r="H18" s="11" t="inlineStr">
-        <is>
-          <t>Fis - VSi
+4º e 5º tempos</t>
+        </is>
+      </c>
+      <c r="I18" s="350" t="inlineStr">
+        <is>
+          <t>Geo - Mlo
 1º e 2º tempos</t>
         </is>
       </c>
-      <c r="I18" s="350" t="n"/>
       <c r="J18" s="262" t="inlineStr">
         <is>
           <t>2CH 9,10,11,12</t>
@@ -12237,24 +12237,19 @@
       </c>
       <c r="E21" s="11" t="inlineStr">
         <is>
+          <t>Qui - CAl
+4º e 5º tempos</t>
+        </is>
+      </c>
+      <c r="F21" s="62" t="n"/>
+      <c r="G21" s="11" t="n"/>
+      <c r="H21" s="11" t="inlineStr">
+        <is>
           <t>LP/LIT/RED - BPad/MFo/SMo
 1º ao 3º tempos</t>
         </is>
       </c>
-      <c r="F21" s="62" t="n"/>
-      <c r="G21" s="11" t="inlineStr">
-        <is>
-          <t>GL - EFr-Car-Swa
-2º e 3º tempos</t>
-        </is>
-      </c>
-      <c r="H21" s="11" t="n"/>
-      <c r="I21" s="11" t="inlineStr">
-        <is>
-          <t>AG10
-2º ao 7º tempos</t>
-        </is>
-      </c>
+      <c r="I21" s="11" t="n"/>
       <c r="J21" s="183" t="n"/>
       <c r="L21" s="80" t="inlineStr">
         <is>
@@ -12319,19 +12314,19 @@
       </c>
       <c r="E24" s="283" t="inlineStr">
         <is>
-          <t>LP/LIT/RED - BPad/MFo/SMo
-1º ao 3º tempos</t>
-        </is>
-      </c>
-      <c r="F24" s="283" t="inlineStr">
-        <is>
-          <t>Bio - Lza
-6º e 7º tempos</t>
-        </is>
-      </c>
+          <t>DaF - Eth-EFr-Swa
+2º e 3º tempos</t>
+        </is>
+      </c>
+      <c r="F24" s="283" t="n"/>
       <c r="G24" s="79" t="n"/>
       <c r="H24" s="283" t="n"/>
-      <c r="I24" s="78" t="n"/>
+      <c r="I24" s="78" t="inlineStr">
+        <is>
+          <t>AG10
+2º ao 7º tempos</t>
+        </is>
+      </c>
       <c r="J24" s="265" t="n"/>
       <c r="L24" s="318" t="inlineStr">
         <is>
@@ -12405,7 +12400,12 @@
 1º tempo</t>
         </is>
       </c>
-      <c r="H27" s="283" t="n"/>
+      <c r="H27" s="283" t="inlineStr">
+        <is>
+          <t>Geo - Mlo
+4º e 5º tempos</t>
+        </is>
+      </c>
       <c r="I27" s="283" t="n"/>
       <c r="J27" s="265" t="n"/>
       <c r="L27" s="45" t="n"/>
@@ -12474,7 +12474,7 @@
       </c>
       <c r="E30" s="283" t="inlineStr">
         <is>
-          <t>Qui - CAl
+          <t>Fis - VSi
 4º e 5º tempos</t>
         </is>
       </c>
@@ -12482,7 +12482,7 @@
       <c r="G30" s="283" t="n"/>
       <c r="H30" s="283" t="inlineStr">
         <is>
-          <t>Ing - APa
+          <t>Hist - ALu
 2º e 3º tempos</t>
         </is>
       </c>
@@ -12652,15 +12652,15 @@
         <f>B36+4</f>
         <v/>
       </c>
-      <c r="E36" s="283" t="n"/>
+      <c r="E36" s="283" t="inlineStr">
+        <is>
+          <t>LP/LIT/RED - BPad/MFo/SMo
+1º ao 3º tempos</t>
+        </is>
+      </c>
       <c r="F36" s="283" t="n"/>
       <c r="G36" s="283" t="n"/>
-      <c r="H36" s="283" t="inlineStr">
-        <is>
-          <t>Geo - Mlo
-4º e 5º tempos</t>
-        </is>
-      </c>
+      <c r="H36" s="283" t="n"/>
       <c r="I36" s="283" t="inlineStr">
         <is>
           <t>Soc - Kle
@@ -12731,18 +12731,18 @@
         <f>B39+4</f>
         <v/>
       </c>
-      <c r="E39" s="283" t="n"/>
+      <c r="E39" s="283" t="inlineStr">
+        <is>
+          <t>Qui - CAl
+4º e 5º tempos</t>
+        </is>
+      </c>
       <c r="F39" s="283" t="n"/>
-      <c r="G39" s="283" t="inlineStr">
-        <is>
-          <t>GL - EFr-Car-Swa
+      <c r="G39" s="283" t="n"/>
+      <c r="H39" s="283" t="inlineStr">
+        <is>
+          <t>Ing - APa
 2º e 3º tempos</t>
-        </is>
-      </c>
-      <c r="H39" s="283" t="inlineStr">
-        <is>
-          <t>Mat - BrSa/FBri
-4º e 5º tempos</t>
         </is>
       </c>
       <c r="I39" s="283" t="n"/>
@@ -12792,13 +12792,13 @@
       </c>
       <c r="E42" s="283" t="n"/>
       <c r="F42" s="283" t="n"/>
-      <c r="G42" s="283" t="n"/>
-      <c r="H42" s="283" t="inlineStr">
-        <is>
-          <t>Fis - VSi
-1º e 2º tempos</t>
-        </is>
-      </c>
+      <c r="G42" s="283" t="inlineStr">
+        <is>
+          <t>GL - EFr-Car-Swa
+2º e 3º tempos</t>
+        </is>
+      </c>
+      <c r="H42" s="283" t="n"/>
       <c r="I42" s="283" t="n"/>
       <c r="J42" s="265" t="n"/>
       <c r="L42" s="259" t="inlineStr">
@@ -12854,18 +12854,18 @@
       </c>
       <c r="E45" s="283" t="inlineStr">
         <is>
-          <t>DaF - Eth-EFr-Swa
+          <t>Mat - BrSa/FBri
 1º e 2º tempos</t>
         </is>
       </c>
-      <c r="F45" s="283" t="n"/>
+      <c r="F45" s="283" t="inlineStr">
+        <is>
+          <t>Bio - Lza
+6º e 7º tempos</t>
+        </is>
+      </c>
       <c r="G45" s="283" t="n"/>
-      <c r="H45" s="283" t="inlineStr">
-        <is>
-          <t>Hist - ALu
-2º e 3º tempos</t>
-        </is>
-      </c>
+      <c r="H45" s="283" t="n"/>
       <c r="I45" s="358" t="inlineStr">
         <is>
           <t>2CH
@@ -13684,16 +13684,16 @@
       </c>
       <c r="E12" s="11" t="inlineStr">
         <is>
-          <t>Qui - CAl
-4º e 5º tempos</t>
+          <t>Mat - BrSa/FBri
+2º e 3º tempos</t>
         </is>
       </c>
       <c r="F12" s="11" t="n"/>
       <c r="G12" s="11" t="n"/>
       <c r="H12" s="11" t="inlineStr">
         <is>
-          <t>Mat - BrSa/FBri
-4º e 5º tempos</t>
+          <t>Hist - ALu
+2º e 3º tempos</t>
         </is>
       </c>
       <c r="I12" s="11" t="n"/>
@@ -13753,26 +13753,26 @@
         <f>B15+4</f>
         <v/>
       </c>
-      <c r="E15" s="11" t="n"/>
+      <c r="E15" s="11" t="inlineStr">
+        <is>
+          <t>Fis - VSi
+4º e 5º tempos</t>
+        </is>
+      </c>
       <c r="F15" s="11" t="inlineStr">
         <is>
           <t>Ing - Vir
 4º e 5º tempos</t>
         </is>
       </c>
-      <c r="G15" s="11" t="n"/>
-      <c r="H15" s="11" t="inlineStr">
-        <is>
-          <t>Hist - ALu
+      <c r="G15" s="11" t="inlineStr">
+        <is>
+          <t>GL - EFr-Car-Swa
 2º e 3º tempos</t>
         </is>
       </c>
-      <c r="I15" s="11" t="inlineStr">
-        <is>
-          <t>Geo - Mlo
-2º e 3º tempos</t>
-        </is>
-      </c>
+      <c r="H15" s="11" t="n"/>
+      <c r="I15" s="11" t="n"/>
       <c r="J15" s="183" t="n"/>
       <c r="L15" s="17" t="n"/>
       <c r="M15" s="15" t="n"/>
@@ -13838,19 +13838,19 @@
 6º e 7º tempos</t>
         </is>
       </c>
-      <c r="G18" s="11" t="inlineStr">
+      <c r="G18" s="11" t="n"/>
+      <c r="H18" s="11" t="inlineStr">
         <is>
           <t>DaF - Eth-EFr-Swa
-2º e 3º tempos</t>
-        </is>
-      </c>
-      <c r="H18" s="11" t="inlineStr">
-        <is>
-          <t>Fis - VSi
+4º e 5º tempos</t>
+        </is>
+      </c>
+      <c r="I18" s="350" t="inlineStr">
+        <is>
+          <t>Geo - Mlo
 1º e 2º tempos</t>
         </is>
       </c>
-      <c r="I18" s="350" t="n"/>
       <c r="J18" s="262" t="inlineStr">
         <is>
           <t>2CH 9,10,11,12</t>
@@ -13918,24 +13918,19 @@
       </c>
       <c r="E21" s="11" t="inlineStr">
         <is>
+          <t>Qui - CAl
+4º e 5º tempos</t>
+        </is>
+      </c>
+      <c r="F21" s="62" t="n"/>
+      <c r="G21" s="11" t="n"/>
+      <c r="H21" s="11" t="inlineStr">
+        <is>
           <t>LP/LIT/RED - BPad/MFo/SMo
 1º ao 3º tempos</t>
         </is>
       </c>
-      <c r="F21" s="62" t="n"/>
-      <c r="G21" s="11" t="inlineStr">
-        <is>
-          <t>GL - EFr-Car-Swa
-2º e 3º tempos</t>
-        </is>
-      </c>
-      <c r="H21" s="11" t="n"/>
-      <c r="I21" s="11" t="inlineStr">
-        <is>
-          <t>AG10
-2º ao 7º tempos</t>
-        </is>
-      </c>
+      <c r="I21" s="11" t="n"/>
       <c r="J21" s="183" t="n"/>
       <c r="L21" s="80" t="inlineStr">
         <is>
@@ -14000,19 +13995,19 @@
       </c>
       <c r="E24" s="283" t="inlineStr">
         <is>
-          <t>LP/LIT/RED - BPad/MFo/SMo
-1º ao 3º tempos</t>
-        </is>
-      </c>
-      <c r="F24" s="283" t="inlineStr">
-        <is>
-          <t>Bio - Lza
-6º e 7º tempos</t>
-        </is>
-      </c>
+          <t>DaF - Eth-EFr-Swa
+2º e 3º tempos</t>
+        </is>
+      </c>
+      <c r="F24" s="283" t="n"/>
       <c r="G24" s="79" t="n"/>
       <c r="H24" s="283" t="n"/>
-      <c r="I24" s="78" t="n"/>
+      <c r="I24" s="78" t="inlineStr">
+        <is>
+          <t>AG10
+2º ao 7º tempos</t>
+        </is>
+      </c>
       <c r="J24" s="265" t="n"/>
       <c r="L24" s="318" t="inlineStr">
         <is>
@@ -14086,7 +14081,12 @@
 1º tempo</t>
         </is>
       </c>
-      <c r="H27" s="283" t="n"/>
+      <c r="H27" s="283" t="inlineStr">
+        <is>
+          <t>Geo - Mlo
+4º e 5º tempos</t>
+        </is>
+      </c>
       <c r="I27" s="283" t="n"/>
       <c r="J27" s="265" t="n"/>
       <c r="L27" s="45" t="n"/>
@@ -14155,18 +14155,18 @@
       </c>
       <c r="E30" s="283" t="inlineStr">
         <is>
-          <t>Qui - CAl
+          <t>Fis - VSi
 4º e 5º tempos</t>
         </is>
       </c>
       <c r="F30" s="283" t="n"/>
-      <c r="G30" s="283" t="inlineStr">
-        <is>
-          <t>Ing - Vir
-4º e 5º tempos</t>
-        </is>
-      </c>
-      <c r="H30" s="283" t="n"/>
+      <c r="G30" s="283" t="n"/>
+      <c r="H30" s="283" t="inlineStr">
+        <is>
+          <t>Hist - ALu
+2º e 3º tempos</t>
+        </is>
+      </c>
       <c r="I30" s="283" t="n"/>
       <c r="J30" s="183" t="inlineStr">
         <is>
@@ -14333,15 +14333,15 @@
         <f>B36+4</f>
         <v/>
       </c>
-      <c r="E36" s="283" t="n"/>
+      <c r="E36" s="283" t="inlineStr">
+        <is>
+          <t>LP/LIT/RED - BPad/MFo/SMo
+1º ao 3º tempos</t>
+        </is>
+      </c>
       <c r="F36" s="283" t="n"/>
       <c r="G36" s="283" t="n"/>
-      <c r="H36" s="283" t="inlineStr">
-        <is>
-          <t>Geo - Mlo
-4º e 5º tempos</t>
-        </is>
-      </c>
+      <c r="H36" s="283" t="n"/>
       <c r="I36" s="283" t="inlineStr">
         <is>
           <t>Soc - Kle
@@ -14412,20 +14412,20 @@
         <f>B39+4</f>
         <v/>
       </c>
-      <c r="E39" s="283" t="n"/>
+      <c r="E39" s="283" t="inlineStr">
+        <is>
+          <t>Qui - CAl
+4º e 5º tempos</t>
+        </is>
+      </c>
       <c r="F39" s="283" t="n"/>
       <c r="G39" s="283" t="inlineStr">
         <is>
-          <t>GL - EFr-Car-Swa
-2º e 3º tempos</t>
-        </is>
-      </c>
-      <c r="H39" s="283" t="inlineStr">
-        <is>
-          <t>Mat - BrSa/FBri
+          <t>Ing - Vir
 4º e 5º tempos</t>
         </is>
       </c>
+      <c r="H39" s="283" t="n"/>
       <c r="I39" s="283" t="n"/>
       <c r="J39" s="265" t="n"/>
     </row>
@@ -14473,13 +14473,13 @@
       </c>
       <c r="E42" s="283" t="n"/>
       <c r="F42" s="283" t="n"/>
-      <c r="G42" s="283" t="n"/>
-      <c r="H42" s="283" t="inlineStr">
-        <is>
-          <t>Fis - VSi
-1º e 2º tempos</t>
-        </is>
-      </c>
+      <c r="G42" s="283" t="inlineStr">
+        <is>
+          <t>GL - EFr-Car-Swa
+2º e 3º tempos</t>
+        </is>
+      </c>
+      <c r="H42" s="283" t="n"/>
       <c r="I42" s="283" t="n"/>
       <c r="J42" s="265" t="n"/>
       <c r="L42" s="259" t="inlineStr">
@@ -14535,18 +14535,18 @@
       </c>
       <c r="E45" s="283" t="inlineStr">
         <is>
-          <t>DaF - Eth-EFr-Swa
+          <t>Mat - BrSa/FBri
 1º e 2º tempos</t>
         </is>
       </c>
-      <c r="F45" s="283" t="n"/>
+      <c r="F45" s="283" t="inlineStr">
+        <is>
+          <t>Bio - Lza
+6º e 7º tempos</t>
+        </is>
+      </c>
       <c r="G45" s="283" t="n"/>
-      <c r="H45" s="283" t="inlineStr">
-        <is>
-          <t>Hist - ALu
-2º e 3º tempos</t>
-        </is>
-      </c>
+      <c r="H45" s="283" t="n"/>
       <c r="I45" s="358" t="inlineStr">
         <is>
           <t>2CH
